--- a/data/PLN.MI.xlsx
+++ b/data/PLN.MI.xlsx
@@ -33676,6 +33676,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1449">
+      <c r="A1449" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1449" t="n">
+        <v>8250</v>
+      </c>
+      <c r="C1449" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="D1449" t="n">
+        <v>3.83999991416931</v>
+      </c>
+      <c r="E1449" t="n">
+        <v>3.94000005722046</v>
+      </c>
+      <c r="F1449" t="n">
+        <v>3.92000007629395</v>
+      </c>
+      <c r="G1449" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PLN.MI.xlsx
+++ b/data/PLN.MI.xlsx
@@ -33699,6 +33699,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1450">
+      <c r="A1450" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1450" t="n">
+        <v>750</v>
+      </c>
+      <c r="C1450" t="n">
+        <v>3.83999991416931</v>
+      </c>
+      <c r="D1450" t="n">
+        <v>3.83999991416931</v>
+      </c>
+      <c r="E1450" t="n">
+        <v>3.83999991416931</v>
+      </c>
+      <c r="F1450" t="n">
+        <v>3.83999991416931</v>
+      </c>
+      <c r="G1450" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PLN.MI.xlsx
+++ b/data/PLN.MI.xlsx
@@ -33722,6 +33722,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1451">
+      <c r="A1451" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1451" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1451" t="n">
+        <v>3.83999991416931</v>
+      </c>
+      <c r="D1451" t="n">
+        <v>3.83999991416931</v>
+      </c>
+      <c r="E1451" t="n">
+        <v>3.83999991416931</v>
+      </c>
+      <c r="F1451" t="n">
+        <v>3.83999991416931</v>
+      </c>
+      <c r="G1451" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1452" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C1452" t="n">
+        <v>3.83999991416931</v>
+      </c>
+      <c r="D1452" t="n">
+        <v>3.83999991416931</v>
+      </c>
+      <c r="E1452" t="n">
+        <v>3.83999991416931</v>
+      </c>
+      <c r="F1452" t="n">
+        <v>3.83999991416931</v>
+      </c>
+      <c r="G1452" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PLN.MI.xlsx
+++ b/data/PLN.MI.xlsx
@@ -33586,13 +33586,13 @@
     </row>
     <row r="1445">
       <c r="A1445" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1445" t="n">
-        <v>250</v>
+        <v>1750</v>
       </c>
       <c r="C1445" t="n">
-        <v>3.8199999332428</v>
+        <v>3.83999991416931</v>
       </c>
       <c r="D1445" t="n">
         <v>3.8199999332428</v>
@@ -33601,7 +33601,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="F1445" t="n">
-        <v>3.8199999332428</v>
+        <v>3.83999991416931</v>
       </c>
       <c r="G1445" t="s">
         <v>7</v>
@@ -33609,10 +33609,10 @@
     </row>
     <row r="1446">
       <c r="A1446" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1446" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="C1446" t="n">
         <v>3.8199999332428</v>
@@ -33632,22 +33632,22 @@
     </row>
     <row r="1447">
       <c r="A1447" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1447" t="n">
-        <v>1250</v>
+        <v>0</v>
       </c>
       <c r="C1447" t="n">
-        <v>3.90000009536743</v>
+        <v>3.8199999332428</v>
       </c>
       <c r="D1447" t="n">
-        <v>3.85999989509583</v>
+        <v>3.8199999332428</v>
       </c>
       <c r="E1447" t="n">
-        <v>3.85999989509583</v>
+        <v>3.8199999332428</v>
       </c>
       <c r="F1447" t="n">
-        <v>3.90000009536743</v>
+        <v>3.8199999332428</v>
       </c>
       <c r="G1447" t="s">
         <v>7</v>
@@ -33655,22 +33655,22 @@
     </row>
     <row r="1448">
       <c r="A1448" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1448" t="n">
-        <v>250</v>
+        <v>1250</v>
       </c>
       <c r="C1448" t="n">
-        <v>3.8199999332428</v>
+        <v>3.90000009536743</v>
       </c>
       <c r="D1448" t="n">
-        <v>3.8199999332428</v>
+        <v>3.85999989509583</v>
       </c>
       <c r="E1448" t="n">
-        <v>3.8199999332428</v>
+        <v>3.85999989509583</v>
       </c>
       <c r="F1448" t="n">
-        <v>3.8199999332428</v>
+        <v>3.90000009536743</v>
       </c>
       <c r="G1448" t="s">
         <v>7</v>
@@ -33678,22 +33678,22 @@
     </row>
     <row r="1449">
       <c r="A1449" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1449" t="n">
-        <v>8250</v>
+        <v>250</v>
       </c>
       <c r="C1449" t="n">
-        <v>3.96000003814697</v>
+        <v>3.8199999332428</v>
       </c>
       <c r="D1449" t="n">
-        <v>3.83999991416931</v>
+        <v>3.8199999332428</v>
       </c>
       <c r="E1449" t="n">
-        <v>3.94000005722046</v>
+        <v>3.8199999332428</v>
       </c>
       <c r="F1449" t="n">
-        <v>3.92000007629395</v>
+        <v>3.8199999332428</v>
       </c>
       <c r="G1449" t="s">
         <v>7</v>
@@ -33701,22 +33701,22 @@
     </row>
     <row r="1450">
       <c r="A1450" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1450" t="n">
-        <v>750</v>
+        <v>8250</v>
       </c>
       <c r="C1450" t="n">
-        <v>3.83999991416931</v>
+        <v>3.96000003814697</v>
       </c>
       <c r="D1450" t="n">
         <v>3.83999991416931</v>
       </c>
       <c r="E1450" t="n">
-        <v>3.83999991416931</v>
+        <v>3.94000005722046</v>
       </c>
       <c r="F1450" t="n">
-        <v>3.83999991416931</v>
+        <v>3.92000007629395</v>
       </c>
       <c r="G1450" t="s">
         <v>7</v>
@@ -33724,10 +33724,10 @@
     </row>
     <row r="1451">
       <c r="A1451" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1451" t="n">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="C1451" t="n">
         <v>3.83999991416931</v>
@@ -33747,10 +33747,10 @@
     </row>
     <row r="1452">
       <c r="A1452" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1452" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="C1452" t="n">
         <v>3.83999991416931</v>

--- a/data/PLN.MI.xlsx
+++ b/data/PLN.MI.xlsx
@@ -421,7 +421,7 @@
         <v>4.41200017929077</v>
       </c>
       <c r="G2" t="n">
-        <v>4.05409288406372</v>
+        <v>4.05409336090088</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G7" t="n">
-        <v>4.19927549362183</v>
+        <v>4.19927597045898</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G11" t="n">
-        <v>4.03387689590454</v>
+        <v>4.03387784957886</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G14" t="n">
-        <v>3.95117878913879</v>
+        <v>3.95117855072021</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G15" t="n">
-        <v>3.89604544639587</v>
+        <v>3.89604568481445</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G16" t="n">
-        <v>3.84091305732727</v>
+        <v>3.84091281890869</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G17" t="n">
-        <v>3.81334662437439</v>
+        <v>3.81334638595581</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G18" t="n">
-        <v>3.72145891189575</v>
+        <v>3.72145915031433</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G19" t="n">
-        <v>3.95117878913879</v>
+        <v>3.95117855072021</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>3.98793387413025</v>
+        <v>3.98793363571167</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.13495397567749</v>
+        <v>4.13495445251465</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G29" t="n">
-        <v>4.20846462249756</v>
+        <v>4.20846509933472</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G39" t="n">
-        <v>4.09819889068604</v>
+        <v>4.09819936752319</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>4.09819889068604</v>
+        <v>4.09819936752319</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>4.08901071548462</v>
+        <v>4.08901023864746</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>4.08901071548462</v>
+        <v>4.08901023864746</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G45" t="n">
-        <v>4.03387689590454</v>
+        <v>4.03387784957886</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G46" t="n">
-        <v>3.95117878913879</v>
+        <v>3.95117855072021</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G47" t="n">
-        <v>3.99712204933167</v>
+        <v>3.99712228775024</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G48" t="n">
-        <v>3.95117878913879</v>
+        <v>3.95117855072021</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G49" t="n">
-        <v>3.95117878913879</v>
+        <v>3.95117855072021</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G51" t="n">
-        <v>3.89604544639587</v>
+        <v>3.89604568481445</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>3.92361235618591</v>
+        <v>3.92361211776733</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G53" t="n">
-        <v>3.89604544639587</v>
+        <v>3.89604568481445</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G54" t="n">
-        <v>3.85929012298584</v>
+        <v>3.859290599823</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G55" t="n">
-        <v>3.85929012298584</v>
+        <v>3.859290599823</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>3.95117878913879</v>
+        <v>3.95117855072021</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>3.95117878913879</v>
+        <v>3.95117855072021</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G60" t="n">
-        <v>4.03387689590454</v>
+        <v>4.03387784957886</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G61" t="n">
-        <v>3.99712204933167</v>
+        <v>3.99712228775024</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G62" t="n">
-        <v>3.93280076980591</v>
+        <v>3.93280172348022</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G68" t="n">
-        <v>4.263596534729</v>
+        <v>4.26359748840332</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>4.61277151107788</v>
+        <v>4.61277103424072</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>5</v>
       </c>
       <c r="G76" t="n">
-        <v>4.59439325332642</v>
+        <v>4.59439373016357</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G78" t="n">
-        <v>4.70465850830078</v>
+        <v>4.7046594619751</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G82" t="n">
-        <v>4.77816915512085</v>
+        <v>4.77816867828369</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G83" t="n">
-        <v>4.92518997192383</v>
+        <v>4.92519044876099</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>5.18247509002686</v>
+        <v>5.18247604370117</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G85" t="n">
-        <v>4.96194505691528</v>
+        <v>4.96194553375244</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G86" t="n">
-        <v>5.18247509002686</v>
+        <v>5.18247604370117</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G87" t="n">
-        <v>5.311119556427</v>
+        <v>5.31111907958984</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G92" t="n">
-        <v>6.26675319671631</v>
+        <v>6.26675271987915</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>7</v>
       </c>
       <c r="G93" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G98" t="n">
-        <v>6.22999811172485</v>
+        <v>6.2299976348877</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>6.5</v>
       </c>
       <c r="G100" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>5.99108934402466</v>
+        <v>5.9910888671875</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G102" t="n">
-        <v>6.10135412216187</v>
+        <v>6.10135459899902</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G103" t="n">
-        <v>6.10135412216187</v>
+        <v>6.10135459899902</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G104" t="n">
-        <v>6.02784442901611</v>
+        <v>6.02784395217896</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>6.5</v>
       </c>
       <c r="G105" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G111" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G112" t="n">
-        <v>5.82569122314453</v>
+        <v>5.82569169998169</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>6</v>
       </c>
       <c r="G117" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>6</v>
       </c>
       <c r="G118" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>6</v>
       </c>
       <c r="G119" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>6</v>
       </c>
       <c r="G120" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>6</v>
       </c>
       <c r="G121" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G122" t="n">
-        <v>5.25598573684692</v>
+        <v>5.25598621368408</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G123" t="n">
-        <v>5.23760890960693</v>
+        <v>5.23760843276978</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G127" t="n">
-        <v>5.25598573684692</v>
+        <v>5.25598621368408</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>6</v>
       </c>
       <c r="G132" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>6</v>
       </c>
       <c r="G133" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G141" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>6.5</v>
       </c>
       <c r="G149" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>6.5</v>
       </c>
       <c r="G150" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>6.06459903717041</v>
+        <v>6.06459951400757</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G152" t="n">
-        <v>6.02784442901611</v>
+        <v>6.02784395217896</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G153" t="n">
-        <v>6.06459903717041</v>
+        <v>6.06459951400757</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>7</v>
       </c>
       <c r="G159" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>7</v>
       </c>
       <c r="G165" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>7</v>
       </c>
       <c r="G167" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>7</v>
       </c>
       <c r="G168" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>7</v>
       </c>
       <c r="G169" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>7</v>
       </c>
       <c r="G170" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>7</v>
       </c>
       <c r="G172" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G173" t="n">
-        <v>6.46890640258789</v>
+        <v>6.46890592575073</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G174" t="n">
-        <v>6.39539575576782</v>
+        <v>6.39539623260498</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>7</v>
       </c>
       <c r="G175" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G176" t="n">
-        <v>6.61592626571655</v>
+        <v>6.61592674255371</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G177" t="n">
-        <v>7.27751922607422</v>
+        <v>7.27751970291138</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G178" t="n">
-        <v>7.20400905609131</v>
+        <v>7.20400953292847</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G184" t="n">
-        <v>6.94672250747681</v>
+        <v>6.94672298431396</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G204" t="n">
-        <v>7.79209089279175</v>
+        <v>7.79209136962891</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>9</v>
       </c>
       <c r="G207" t="n">
-        <v>8.26990795135498</v>
+        <v>8.2699089050293</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G210" t="n">
-        <v>8.01262283325195</v>
+        <v>8.01262187957764</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G213" t="n">
-        <v>8.28828620910645</v>
+        <v>8.28828716278076</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G215" t="n">
-        <v>8.41692924499512</v>
+        <v>8.41693019866943</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G217" t="n">
-        <v>8.6190824508667</v>
+        <v>8.61908340454102</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G218" t="n">
-        <v>8.69259262084961</v>
+        <v>8.69259357452393</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G219" t="n">
-        <v>8.6190824508667</v>
+        <v>8.61908340454102</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>8.69259262084961</v>
+        <v>8.69259357452393</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>8.69259262084961</v>
+        <v>8.69259357452393</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G222" t="n">
-        <v>8.60070419311523</v>
+        <v>8.60070514678955</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G223" t="n">
-        <v>8.78448104858398</v>
+        <v>8.78448009490967</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G226" t="n">
-        <v>8.76610374450684</v>
+        <v>8.76610279083252</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>9.5</v>
       </c>
       <c r="G227" t="n">
-        <v>8.72934722900391</v>
+        <v>8.72934818267822</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G231" t="n">
-        <v>8.60070419311523</v>
+        <v>8.60070514678955</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G232" t="n">
-        <v>8.6190824508667</v>
+        <v>8.61908340454102</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G236" t="n">
-        <v>8.14126491546631</v>
+        <v>8.14126586914062</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>9</v>
       </c>
       <c r="G239" t="n">
-        <v>8.26990795135498</v>
+        <v>8.2699089050293</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G242" t="n">
-        <v>8.28828620910645</v>
+        <v>8.28828716278076</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>9.5</v>
       </c>
       <c r="G256" t="n">
-        <v>8.72934722900391</v>
+        <v>8.72934818267822</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G257" t="n">
-        <v>8.87636852264404</v>
+        <v>8.87636756896973</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G258" t="n">
-        <v>9.09689998626709</v>
+        <v>9.09689807891846</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G259" t="n">
-        <v>9.09689998626709</v>
+        <v>9.09689807891846</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G260" t="n">
-        <v>9.09689998626709</v>
+        <v>9.09689807891846</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>10</v>
       </c>
       <c r="G263" t="n">
-        <v>9.18878650665283</v>
+        <v>9.18878746032715</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G264" t="n">
-        <v>8.69259262084961</v>
+        <v>8.69259357452393</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>8.69259262084961</v>
+        <v>8.69259357452393</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>9.5</v>
       </c>
       <c r="G266" t="n">
-        <v>8.72934722900391</v>
+        <v>8.72934818267822</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G267" t="n">
-        <v>8.69259262084961</v>
+        <v>8.69259357452393</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G270" t="n">
-        <v>8.67421436309814</v>
+        <v>8.67421531677246</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G271" t="n">
-        <v>8.39855098724365</v>
+        <v>8.39855194091797</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>7.5348048210144</v>
+        <v>7.53480529785156</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G279" t="n">
-        <v>7.64507102966309</v>
+        <v>7.64507055282593</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G280" t="n">
-        <v>7.42453956604004</v>
+        <v>7.4245400428772</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G287" t="n">
-        <v>7.27751922607422</v>
+        <v>7.27751970291138</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G295" t="n">
-        <v>6.61592626571655</v>
+        <v>6.61592674255371</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G296" t="n">
-        <v>6.65268135070801</v>
+        <v>6.65268182754517</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>6.79970264434814</v>
+        <v>6.79970216751099</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G306" t="n">
-        <v>7.07536602020264</v>
+        <v>7.07536554336548</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G310" t="n">
-        <v>7.07536602020264</v>
+        <v>7.07536554336548</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G312" t="n">
-        <v>7.5348048210144</v>
+        <v>7.53480529785156</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G313" t="n">
-        <v>7.38778448104858</v>
+        <v>7.38778495788574</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G314" t="n">
-        <v>7.4429178237915</v>
+        <v>7.44291830062866</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G315" t="n">
-        <v>7.4429178237915</v>
+        <v>7.44291830062866</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G316" t="n">
-        <v>7.4429178237915</v>
+        <v>7.44291830062866</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>7.4429178237915</v>
+        <v>7.44291830062866</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G318" t="n">
-        <v>7.4429178237915</v>
+        <v>7.44291830062866</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G319" t="n">
-        <v>7.46129465103149</v>
+        <v>7.46129512786865</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G320" t="n">
-        <v>7.46129465103149</v>
+        <v>7.46129512786865</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G327" t="n">
-        <v>7.00185585021973</v>
+        <v>7.00185537338257</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G329" t="n">
-        <v>6.79970264434814</v>
+        <v>6.79970216751099</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G330" t="n">
-        <v>7.02023315429688</v>
+        <v>7.02023267745972</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G331" t="n">
-        <v>7.02023315429688</v>
+        <v>7.02023267745972</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G332" t="n">
-        <v>7.02023315429688</v>
+        <v>7.02023267745972</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G333" t="n">
-        <v>7.02023315429688</v>
+        <v>7.02023267745972</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G334" t="n">
-        <v>6.94672250747681</v>
+        <v>6.94672298431396</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>6.94672250747681</v>
+        <v>6.94672298431396</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>6.94672250747681</v>
+        <v>6.94672298431396</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>6.79970264434814</v>
+        <v>6.79970216751099</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>6.79970264434814</v>
+        <v>6.79970216751099</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G339" t="n">
-        <v>6.37701797485352</v>
+        <v>6.37701845169067</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>6.5</v>
       </c>
       <c r="G340" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G341" t="n">
-        <v>6.15648746490479</v>
+        <v>6.15648698806763</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G342" t="n">
-        <v>6.15648746490479</v>
+        <v>6.15648698806763</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G343" t="n">
-        <v>6.02784442901611</v>
+        <v>6.02784395217896</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G344" t="n">
-        <v>6.26675319671631</v>
+        <v>6.26675271987915</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G345" t="n">
-        <v>6.26675319671631</v>
+        <v>6.26675271987915</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G349" t="n">
-        <v>6.21161985397339</v>
+        <v>6.21162033081055</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>5.99108934402466</v>
+        <v>5.9910888671875</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G352" t="n">
-        <v>5.99108934402466</v>
+        <v>5.9910888671875</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G353" t="n">
-        <v>5.91757869720459</v>
+        <v>5.91757917404175</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G354" t="n">
-        <v>5.91757869720459</v>
+        <v>5.91757917404175</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G364" t="n">
-        <v>6.65268135070801</v>
+        <v>6.65268182754517</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G366" t="n">
-        <v>6.15648746490479</v>
+        <v>6.15648698806763</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G371" t="n">
-        <v>6.21161985397339</v>
+        <v>6.21162033081055</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G372" t="n">
-        <v>6.21161985397339</v>
+        <v>6.21162033081055</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G373" t="n">
-        <v>6.21161985397339</v>
+        <v>6.21162033081055</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G374" t="n">
-        <v>6.21161985397339</v>
+        <v>6.21162033081055</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>6.15648746490479</v>
+        <v>6.15648698806763</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>6.5</v>
       </c>
       <c r="G378" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>6.06459903717041</v>
+        <v>6.06459951400757</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>6.06459903717041</v>
+        <v>6.06459951400757</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>6.06459903717041</v>
+        <v>6.06459951400757</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G382" t="n">
-        <v>6.06459903717041</v>
+        <v>6.06459951400757</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>6.5</v>
       </c>
       <c r="G383" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>6.5</v>
       </c>
       <c r="G384" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>6.5</v>
       </c>
       <c r="G385" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.5</v>
       </c>
       <c r="G386" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G387" t="n">
-        <v>5.82569122314453</v>
+        <v>5.82569169998169</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G388" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G398" t="n">
-        <v>5.91757869720459</v>
+        <v>5.91757917404175</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G399" t="n">
-        <v>5.91757869720459</v>
+        <v>5.91757917404175</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G400" t="n">
-        <v>6.10135412216187</v>
+        <v>6.10135459899902</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G401" t="n">
-        <v>6.15648746490479</v>
+        <v>6.15648698806763</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G402" t="n">
-        <v>6.15648746490479</v>
+        <v>6.15648698806763</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G403" t="n">
-        <v>6.15648746490479</v>
+        <v>6.15648698806763</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>7</v>
       </c>
       <c r="G415" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>7</v>
       </c>
       <c r="G416" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7</v>
       </c>
       <c r="G417" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>7</v>
       </c>
       <c r="G418" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>7</v>
       </c>
       <c r="G419" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>7</v>
       </c>
       <c r="G420" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>7</v>
       </c>
       <c r="G421" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G422" t="n">
-        <v>6.30350828170776</v>
+        <v>6.30350780487061</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G423" t="n">
-        <v>6.30350828170776</v>
+        <v>6.30350780487061</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G424" t="n">
-        <v>6.30350828170776</v>
+        <v>6.30350780487061</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G425" t="n">
-        <v>6.30350828170776</v>
+        <v>6.30350780487061</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G426" t="n">
-        <v>6.30350828170776</v>
+        <v>6.30350780487061</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G427" t="n">
-        <v>6.30350828170776</v>
+        <v>6.30350780487061</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G428" t="n">
-        <v>6.30350828170776</v>
+        <v>6.30350780487061</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G429" t="n">
-        <v>6.30350828170776</v>
+        <v>6.30350780487061</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G430" t="n">
-        <v>6.30350828170776</v>
+        <v>6.30350780487061</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G431" t="n">
-        <v>6.21161985397339</v>
+        <v>6.21162033081055</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7</v>
       </c>
       <c r="G438" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>6.15648746490479</v>
+        <v>6.15648698806763</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G445" t="n">
-        <v>6.22999811172485</v>
+        <v>6.2299976348877</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G446" t="n">
-        <v>6.22999811172485</v>
+        <v>6.2299976348877</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G447" t="n">
-        <v>6.22999811172485</v>
+        <v>6.2299976348877</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G448" t="n">
-        <v>6.02784442901611</v>
+        <v>6.02784395217896</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>6.5</v>
       </c>
       <c r="G450" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G451" t="n">
-        <v>6.00946712493896</v>
+        <v>6.00946664810181</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G453" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893661499023</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G454" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893661499023</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G455" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893661499023</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G456" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893661499023</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G457" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893661499023</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G458" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893661499023</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G459" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893661499023</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G460" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893661499023</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G461" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893661499023</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G462" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893661499023</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G463" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893661499023</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G464" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893661499023</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G465" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893661499023</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G466" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893661499023</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G467" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893661499023</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G468" t="n">
-        <v>5.60516023635864</v>
+        <v>5.60515975952148</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G469" t="n">
-        <v>5.60516023635864</v>
+        <v>5.60515975952148</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G474" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>6</v>
       </c>
       <c r="G475" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>6</v>
       </c>
       <c r="G476" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>6</v>
       </c>
       <c r="G477" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>6</v>
       </c>
       <c r="G478" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G480" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G482" t="n">
-        <v>5.60516023635864</v>
+        <v>5.60515975952148</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>5.60516023635864</v>
+        <v>5.60515975952148</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G484" t="n">
-        <v>5.60516023635864</v>
+        <v>5.60515975952148</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G485" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893661499023</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G486" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893661499023</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G487" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893661499023</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G488" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893661499023</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>6</v>
       </c>
       <c r="G489" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>6</v>
       </c>
       <c r="G490" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>6</v>
       </c>
       <c r="G491" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>6</v>
       </c>
       <c r="G492" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>6</v>
       </c>
       <c r="G493" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>6</v>
       </c>
       <c r="G494" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G495" t="n">
-        <v>5.73380279541016</v>
+        <v>5.73380327224731</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G496" t="n">
-        <v>5.73380279541016</v>
+        <v>5.73380327224731</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G497" t="n">
-        <v>5.73380279541016</v>
+        <v>5.73380327224731</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G501" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G502" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G503" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G510" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893661499023</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G511" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893661499023</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G512" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893661499023</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G513" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893661499023</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G515" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G516" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G517" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G518" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G519" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G520" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G521" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G522" t="n">
-        <v>5.60516023635864</v>
+        <v>5.60515975952148</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>5.60516023635864</v>
+        <v>5.60515975952148</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G524" t="n">
-        <v>5.60516023635864</v>
+        <v>5.60515975952148</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>6</v>
       </c>
       <c r="G525" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>6</v>
       </c>
       <c r="G526" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>6</v>
       </c>
       <c r="G527" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>6</v>
       </c>
       <c r="G528" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>6</v>
       </c>
       <c r="G529" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>6</v>
       </c>
       <c r="G530" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G532" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G533" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G534" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G536" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G538" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G539" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G540" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G541" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G543" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G544" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G545" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G547" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G548" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G549" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G550" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G551" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G552" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G553" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G554" t="n">
-        <v>5.60516023635864</v>
+        <v>5.60515975952148</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G555" t="n">
-        <v>5.60516023635864</v>
+        <v>5.60515975952148</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G556" t="n">
-        <v>5.60516023635864</v>
+        <v>5.60515975952148</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G557" t="n">
-        <v>5.60516023635864</v>
+        <v>5.60515975952148</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G558" t="n">
-        <v>5.60516023635864</v>
+        <v>5.60515975952148</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G559" t="n">
-        <v>5.60516023635864</v>
+        <v>5.60515975952148</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G560" t="n">
-        <v>5.60516023635864</v>
+        <v>5.60515975952148</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G561" t="n">
-        <v>5.60516023635864</v>
+        <v>5.60515975952148</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G562" t="n">
-        <v>5.60516023635864</v>
+        <v>5.60515975952148</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G563" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G564" t="n">
-        <v>5.27436399459839</v>
+        <v>5.27436351776123</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G569" t="n">
-        <v>5.29274129867554</v>
+        <v>5.2927417755127</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G570" t="n">
-        <v>5.29274129867554</v>
+        <v>5.2927417755127</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G571" t="n">
-        <v>5.29274129867554</v>
+        <v>5.2927417755127</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G572" t="n">
-        <v>5.29274129867554</v>
+        <v>5.2927417755127</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G573" t="n">
-        <v>5.29274129867554</v>
+        <v>5.2927417755127</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G574" t="n">
-        <v>5.27436399459839</v>
+        <v>5.27436351776123</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G575" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G576" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>6</v>
       </c>
       <c r="G577" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>6</v>
       </c>
       <c r="G578" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>6</v>
       </c>
       <c r="G579" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G580" t="n">
-        <v>5.60516023635864</v>
+        <v>5.60515975952148</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G581" t="n">
-        <v>5.60516023635864</v>
+        <v>5.60515975952148</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>6</v>
       </c>
       <c r="G582" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G583" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G584" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G585" t="n">
-        <v>5.60516023635864</v>
+        <v>5.60515975952148</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G586" t="n">
-        <v>5.4673285484314</v>
+        <v>5.46732807159424</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G587" t="n">
-        <v>5.4673285484314</v>
+        <v>5.46732807159424</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>5.75</v>
       </c>
       <c r="G588" t="n">
-        <v>5.28355264663696</v>
+        <v>5.2835521697998</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>5.75</v>
       </c>
       <c r="G589" t="n">
-        <v>5.28355264663696</v>
+        <v>5.2835521697998</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>5.75</v>
       </c>
       <c r="G590" t="n">
-        <v>5.28355264663696</v>
+        <v>5.2835521697998</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G591" t="n">
-        <v>5.4673285484314</v>
+        <v>5.46732807159424</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G592" t="n">
-        <v>5.4673285484314</v>
+        <v>5.46732807159424</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G593" t="n">
-        <v>5.4673285484314</v>
+        <v>5.46732807159424</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G594" t="n">
-        <v>5.4673285484314</v>
+        <v>5.46732807159424</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G595" t="n">
-        <v>5.4673285484314</v>
+        <v>5.46732807159424</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G596" t="n">
-        <v>5.4673285484314</v>
+        <v>5.46732807159424</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>5.75</v>
       </c>
       <c r="G597" t="n">
-        <v>5.28355264663696</v>
+        <v>5.2835521697998</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>5.75</v>
       </c>
       <c r="G598" t="n">
-        <v>5.28355264663696</v>
+        <v>5.2835521697998</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>5.75</v>
       </c>
       <c r="G599" t="n">
-        <v>5.28355264663696</v>
+        <v>5.2835521697998</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G602" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G605" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G607" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G623" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G626" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G627" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G628" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G631" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G632" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G633" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G634" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G635" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G638" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G644" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G645" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G656" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G658" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G673" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658491134644</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G675" t="n">
-        <v>5.06960582733154</v>
+        <v>5.06960535049438</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G679" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658491134644</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G680" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658491134644</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658491134644</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G682" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658491134644</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G690" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G704" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403524398804</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G705" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403524398804</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G706" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403524398804</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G707" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403524398804</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G708" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403524398804</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G711" t="n">
-        <v>4.69752502441406</v>
+        <v>4.6975245475769</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G712" t="n">
-        <v>4.69752502441406</v>
+        <v>4.6975245475769</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G713" t="n">
-        <v>4.69752502441406</v>
+        <v>4.6975245475769</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G714" t="n">
-        <v>4.55799436569214</v>
+        <v>4.55799388885498</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G716" t="n">
-        <v>4.46497440338135</v>
+        <v>4.46497392654419</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G717" t="n">
-        <v>4.63241100311279</v>
+        <v>4.63241052627563</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G718" t="n">
-        <v>4.63241100311279</v>
+        <v>4.63241052627563</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G719" t="n">
-        <v>4.63241100311279</v>
+        <v>4.63241052627563</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G720" t="n">
-        <v>4.63241100311279</v>
+        <v>4.63241052627563</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G721" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G727" t="n">
-        <v>4.24172496795654</v>
+        <v>4.2417254447937</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G734" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G735" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G736" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G737" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G738" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G739" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G740" t="n">
-        <v>4.44636964797974</v>
+        <v>4.44637012481689</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G748" t="n">
-        <v>4.40916109085083</v>
+        <v>4.40916156768799</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G749" t="n">
-        <v>4.40916109085083</v>
+        <v>4.40916156768799</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G750" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G751" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G752" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G753" t="n">
-        <v>4.4277663230896</v>
+        <v>4.42776584625244</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G754" t="n">
-        <v>4.35334920883179</v>
+        <v>4.35334968566895</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G755" t="n">
-        <v>4.4277663230896</v>
+        <v>4.42776584625244</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G756" t="n">
-        <v>4.4277663230896</v>
+        <v>4.42776584625244</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G758" t="n">
-        <v>4.69752502441406</v>
+        <v>4.6975245475769</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G764" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403524398804</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G765" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403524398804</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G776" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658491134644</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G777" t="n">
-        <v>5.06960582733154</v>
+        <v>5.06960535049438</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G778" t="n">
-        <v>5.06960582733154</v>
+        <v>5.06960535049438</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G780" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658491134644</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G781" t="n">
-        <v>5.06960582733154</v>
+        <v>5.06960535049438</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G783" t="n">
-        <v>5.67423820495605</v>
+        <v>5.67423725128174</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G784" t="n">
-        <v>5.76725816726685</v>
+        <v>5.76725769042969</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G786" t="n">
-        <v>5.95329856872559</v>
+        <v>5.95329809188843</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G787" t="n">
-        <v>5.95329856872559</v>
+        <v>5.95329809188843</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G790" t="n">
-        <v>5.76725816726685</v>
+        <v>5.76725769042969</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>6.25</v>
       </c>
       <c r="G792" t="n">
-        <v>5.81376838684082</v>
+        <v>5.81376791000366</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G793" t="n">
-        <v>5.67423820495605</v>
+        <v>5.67423725128174</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G810" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G814" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G815" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G820" t="n">
-        <v>5.06960582733154</v>
+        <v>5.06960535049438</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G821" t="n">
-        <v>5.06960582733154</v>
+        <v>5.06960535049438</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G822" t="n">
-        <v>5.06960582733154</v>
+        <v>5.06960535049438</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G823" t="n">
-        <v>5.06960582733154</v>
+        <v>5.06960535049438</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G824" t="n">
-        <v>5.06960582733154</v>
+        <v>5.06960535049438</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G825" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658491134644</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G826" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658491134644</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G828" t="n">
-        <v>5.06960582733154</v>
+        <v>5.06960535049438</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G829" t="n">
-        <v>5.06960582733154</v>
+        <v>5.06960535049438</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G835" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403524398804</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G836" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403524398804</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G843" t="n">
-        <v>4.63241100311279</v>
+        <v>4.63241052627563</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G852" t="n">
-        <v>4.69752502441406</v>
+        <v>4.6975245475769</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G853" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G856" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G857" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G858" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G859" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G860" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G864" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G865" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G866" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G867" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>5</v>
       </c>
       <c r="G869" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>5</v>
       </c>
       <c r="G870" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>5</v>
       </c>
       <c r="G871" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G872" t="n">
-        <v>4.79242467880249</v>
+        <v>4.79242420196533</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G873" t="n">
-        <v>4.79242467880249</v>
+        <v>4.79242420196533</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>5</v>
       </c>
       <c r="G874" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G877" t="n">
-        <v>4.70701503753662</v>
+        <v>4.70701456069946</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>4.70701503753662</v>
+        <v>4.70701456069946</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G884" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G885" t="n">
-        <v>4.79242467880249</v>
+        <v>4.79242420196533</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>5</v>
       </c>
       <c r="G889" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G890" t="n">
-        <v>4.79242467880249</v>
+        <v>4.79242420196533</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>5</v>
       </c>
       <c r="G891" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>5</v>
       </c>
       <c r="G892" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>5</v>
       </c>
       <c r="G893" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>5</v>
       </c>
       <c r="G894" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G895" t="n">
-        <v>4.79242467880249</v>
+        <v>4.79242420196533</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>5</v>
       </c>
       <c r="G896" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>5</v>
       </c>
       <c r="G897" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>5</v>
       </c>
       <c r="G898" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>5</v>
       </c>
       <c r="G899" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>5</v>
       </c>
       <c r="G900" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>5</v>
       </c>
       <c r="G904" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>5</v>
       </c>
       <c r="G905" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>5</v>
       </c>
       <c r="G906" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>5</v>
       </c>
       <c r="G907" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>5</v>
       </c>
       <c r="G908" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>5</v>
       </c>
       <c r="G909" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>5</v>
       </c>
       <c r="G910" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>5</v>
       </c>
       <c r="G911" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>5</v>
       </c>
       <c r="G912" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>5</v>
       </c>
       <c r="G913" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>5</v>
       </c>
       <c r="G914" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>5</v>
       </c>
       <c r="G915" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>5</v>
       </c>
       <c r="G916" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>5</v>
       </c>
       <c r="G917" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>5</v>
       </c>
       <c r="G918" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>5</v>
       </c>
       <c r="G919" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>5</v>
       </c>
       <c r="G920" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>5</v>
       </c>
       <c r="G921" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>5</v>
       </c>
       <c r="G924" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G925" t="n">
-        <v>4.61211490631104</v>
+        <v>4.61211538314819</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G926" t="n">
-        <v>4.61211490631104</v>
+        <v>4.61211538314819</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G927" t="n">
-        <v>4.61211490631104</v>
+        <v>4.61211538314819</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G928" t="n">
-        <v>4.61211490631104</v>
+        <v>4.61211538314819</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G929" t="n">
-        <v>4.61211490631104</v>
+        <v>4.61211538314819</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G930" t="n">
-        <v>4.61211490631104</v>
+        <v>4.61211538314819</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G931" t="n">
-        <v>4.61211490631104</v>
+        <v>4.61211538314819</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G933" t="n">
-        <v>4.79242467880249</v>
+        <v>4.79242420196533</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G934" t="n">
-        <v>4.79242467880249</v>
+        <v>4.79242420196533</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G935" t="n">
-        <v>4.79242467880249</v>
+        <v>4.79242420196533</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>5</v>
       </c>
       <c r="G940" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G941" t="n">
-        <v>4.63109493255615</v>
+        <v>4.63109540939331</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G942" t="n">
-        <v>4.65007543563843</v>
+        <v>4.65007495880127</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G943" t="n">
-        <v>4.65007543563843</v>
+        <v>4.65007495880127</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G944" t="n">
-        <v>4.65007543563843</v>
+        <v>4.65007495880127</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G945" t="n">
-        <v>4.65007543563843</v>
+        <v>4.65007495880127</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G946" t="n">
-        <v>4.65007543563843</v>
+        <v>4.65007495880127</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G947" t="n">
-        <v>4.65007543563843</v>
+        <v>4.65007495880127</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G948" t="n">
-        <v>4.65007543563843</v>
+        <v>4.65007495880127</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G949" t="n">
-        <v>4.65007543563843</v>
+        <v>4.65007495880127</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G950" t="n">
-        <v>4.63109493255615</v>
+        <v>4.63109540939331</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G951" t="n">
-        <v>4.63109493255615</v>
+        <v>4.63109540939331</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G952" t="n">
-        <v>4.63109493255615</v>
+        <v>4.63109540939331</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G953" t="n">
-        <v>4.63109493255615</v>
+        <v>4.63109540939331</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G959" t="n">
-        <v>4.49823522567749</v>
+        <v>4.49823570251465</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G961" t="n">
-        <v>4.49823522567749</v>
+        <v>4.49823570251465</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G962" t="n">
-        <v>4.36537647247314</v>
+        <v>4.36537599563599</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G963" t="n">
-        <v>4.36537647247314</v>
+        <v>4.36537599563599</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G964" t="n">
-        <v>4.32741641998291</v>
+        <v>4.32741689682007</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G971" t="n">
-        <v>4.36537647247314</v>
+        <v>4.36537599563599</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G975" t="n">
-        <v>4.13761806488037</v>
+        <v>4.13761758804321</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G984" t="n">
-        <v>4.36537647247314</v>
+        <v>4.36537599563599</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G985" t="n">
-        <v>4.36537647247314</v>
+        <v>4.36537599563599</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G986" t="n">
-        <v>4.36537647247314</v>
+        <v>4.36537599563599</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G987" t="n">
-        <v>4.34639644622803</v>
+        <v>4.34639692306519</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G989" t="n">
-        <v>4.32741641998291</v>
+        <v>4.32741689682007</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G990" t="n">
-        <v>4.36537647247314</v>
+        <v>4.36537599563599</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G992" t="n">
-        <v>4.36537647247314</v>
+        <v>4.36537599563599</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.55517530441284</v>
+        <v>4.55517578125</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.57415533065796</v>
+        <v>4.57415580749512</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.63109493255615</v>
+        <v>4.63109540939331</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.32741641998291</v>
+        <v>4.32741689682007</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.32741641998291</v>
+        <v>4.32741689682007</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.32741641998291</v>
+        <v>4.32741689682007</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.32741641998291</v>
+        <v>4.32741689682007</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.32741641998291</v>
+        <v>4.32741689682007</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.13761806488037</v>
+        <v>4.13761758804321</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1030" t="n">
-        <v>4.11863803863525</v>
+        <v>4.1186375617981</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.85291910171509</v>
+        <v>3.85291934013367</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.08067846298218</v>
+        <v>4.08067798614502</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.08067846298218</v>
+        <v>4.08067798614502</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.08067846298218</v>
+        <v>4.08067798614502</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.08067846298218</v>
+        <v>4.08067798614502</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1053" t="n">
-        <v>4.08067846298218</v>
+        <v>4.08067798614502</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.94781875610352</v>
+        <v>3.94781851768494</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.94781875610352</v>
+        <v>3.94781851768494</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.89087915420532</v>
+        <v>3.89087891578674</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.6061806678772</v>
+        <v>3.60618042945862</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.58720064163208</v>
+        <v>3.5872004032135</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.6061806678772</v>
+        <v>3.60618042945862</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.81495928764343</v>
+        <v>3.81495952606201</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1096" t="n">
-        <v>4.11863803863525</v>
+        <v>4.1186375617981</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -38202,6 +38202,32 @@
         <v>3.90000009536743</v>
       </c>
       <c r="H1455" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1456" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1456" t="n">
+        <v>3.94000005722046</v>
+      </c>
+      <c r="D1456" t="n">
+        <v>3.92000007629395</v>
+      </c>
+      <c r="E1456" t="n">
+        <v>3.94000005722046</v>
+      </c>
+      <c r="F1456" t="n">
+        <v>3.92000007629395</v>
+      </c>
+      <c r="G1456" t="n">
+        <v>3.92000007629395</v>
+      </c>
+      <c r="H1456" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLN.MI.xlsx
+++ b/data/PLN.MI.xlsx
@@ -421,7 +421,7 @@
         <v>4.41200017929077</v>
       </c>
       <c r="G2" t="n">
-        <v>4.05409336090088</v>
+        <v>4.05409288406372</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G3" t="n">
-        <v>4.11657667160034</v>
+        <v>4.1165771484375</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G5" t="n">
-        <v>4.22684192657471</v>
+        <v>4.22684240341187</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G7" t="n">
-        <v>4.19927597045898</v>
+        <v>4.19927549362183</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G8" t="n">
-        <v>4.15333223342896</v>
+        <v>4.1533317565918</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G10" t="n">
-        <v>4.04306650161743</v>
+        <v>4.04306602478027</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G12" t="n">
-        <v>3.96955585479736</v>
+        <v>3.9695565700531</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>4.25</v>
       </c>
       <c r="G13" t="n">
-        <v>3.90523433685303</v>
+        <v>3.90523481369019</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G14" t="n">
-        <v>3.95117855072021</v>
+        <v>3.95117878913879</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G15" t="n">
-        <v>3.89604568481445</v>
+        <v>3.89604544639587</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G16" t="n">
-        <v>3.84091281890869</v>
+        <v>3.84091305732727</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G17" t="n">
-        <v>3.81334638595581</v>
+        <v>3.81334686279297</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G18" t="n">
-        <v>3.72145915031433</v>
+        <v>3.72145891189575</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G19" t="n">
-        <v>3.95117855072021</v>
+        <v>3.95117878913879</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G20" t="n">
-        <v>3.87766814231873</v>
+        <v>3.87766790390015</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G21" t="n">
-        <v>3.87766814231873</v>
+        <v>3.87766790390015</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G22" t="n">
-        <v>3.87766814231873</v>
+        <v>3.87766790390015</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G23" t="n">
-        <v>3.85010170936584</v>
+        <v>3.85010194778442</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G24" t="n">
-        <v>3.8868567943573</v>
+        <v>3.88685703277588</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>3.98793363571167</v>
+        <v>3.98793435096741</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G29" t="n">
-        <v>4.20846509933472</v>
+        <v>4.20846462249756</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G31" t="n">
-        <v>4.15333223342896</v>
+        <v>4.1533317565918</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>4.15333223342896</v>
+        <v>4.1533317565918</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>4.11657667160034</v>
+        <v>4.1165771484375</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G39" t="n">
-        <v>4.09819936752319</v>
+        <v>4.09819889068604</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>4.09819936752319</v>
+        <v>4.09819889068604</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G46" t="n">
-        <v>3.95117855072021</v>
+        <v>3.95117878913879</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G48" t="n">
-        <v>3.95117855072021</v>
+        <v>3.95117878913879</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G49" t="n">
-        <v>3.95117855072021</v>
+        <v>3.95117878913879</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>4.04306650161743</v>
+        <v>4.04306602478027</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G51" t="n">
-        <v>3.89604568481445</v>
+        <v>3.89604544639587</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>3.92361211776733</v>
+        <v>3.92361235618591</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G53" t="n">
-        <v>3.89604568481445</v>
+        <v>3.89604544639587</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.25</v>
       </c>
       <c r="G56" t="n">
-        <v>3.90523433685303</v>
+        <v>3.90523481369019</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.25</v>
       </c>
       <c r="G57" t="n">
-        <v>3.90523433685303</v>
+        <v>3.90523481369019</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>3.95117855072021</v>
+        <v>3.95117878913879</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>3.95117855072021</v>
+        <v>3.95117878913879</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G62" t="n">
-        <v>3.93280172348022</v>
+        <v>3.93280100822449</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G66" t="n">
-        <v>4.16252040863037</v>
+        <v>4.16252088546753</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G68" t="n">
-        <v>4.26359748840332</v>
+        <v>4.26359701156616</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G71" t="n">
-        <v>4.48412847518921</v>
+        <v>4.48412799835205</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G73" t="n">
-        <v>4.72303628921509</v>
+        <v>4.72303676605225</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G74" t="n">
-        <v>4.8149242401123</v>
+        <v>4.81492471694946</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G77" t="n">
-        <v>4.52088308334351</v>
+        <v>4.52088356018066</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G78" t="n">
-        <v>4.7046594619751</v>
+        <v>4.70465898513794</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G79" t="n">
-        <v>4.8149242401123</v>
+        <v>4.81492471694946</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G82" t="n">
-        <v>4.77816867828369</v>
+        <v>4.77816915512085</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G83" t="n">
-        <v>4.92519044876099</v>
+        <v>4.92518997192383</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>5.18247604370117</v>
+        <v>5.18247556686401</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G86" t="n">
-        <v>5.18247604370117</v>
+        <v>5.18247556686401</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G88" t="n">
-        <v>5.58678245544434</v>
+        <v>5.58678293228149</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G89" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G91" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G92" t="n">
-        <v>6.26675271987915</v>
+        <v>6.26675319671631</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>7</v>
       </c>
       <c r="G93" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G94" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G95" t="n">
-        <v>6.32188558578491</v>
+        <v>6.32188606262207</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G98" t="n">
-        <v>6.2299976348877</v>
+        <v>6.22999811172485</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G99" t="n">
-        <v>6.08297681808472</v>
+        <v>6.08297729492188</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>6.5</v>
       </c>
       <c r="G100" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271108627319</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G102" t="n">
-        <v>6.10135459899902</v>
+        <v>6.10135412216187</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G103" t="n">
-        <v>6.10135459899902</v>
+        <v>6.10135412216187</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G104" t="n">
-        <v>6.02784395217896</v>
+        <v>6.02784442901611</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>6.5</v>
       </c>
       <c r="G105" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271108627319</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G106" t="n">
-        <v>5.9543342590332</v>
+        <v>5.95433378219604</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>6.04622173309326</v>
+        <v>6.04622220993042</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G109" t="n">
-        <v>5.86244630813599</v>
+        <v>5.86244583129883</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G110" t="n">
-        <v>5.86244630813599</v>
+        <v>5.86244583129883</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G111" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G112" t="n">
-        <v>5.82569169998169</v>
+        <v>5.82569122314453</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G122" t="n">
-        <v>5.25598621368408</v>
+        <v>5.25598573684692</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G123" t="n">
-        <v>5.23760843276978</v>
+        <v>5.23760795593262</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G124" t="n">
-        <v>5.32949638366699</v>
+        <v>5.32949686050415</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G126" t="n">
-        <v>5.58678245544434</v>
+        <v>5.58678293228149</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G127" t="n">
-        <v>5.25598621368408</v>
+        <v>5.25598573684692</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G129" t="n">
-        <v>5.43976211547852</v>
+        <v>5.43976259231567</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G130" t="n">
-        <v>5.49489450454712</v>
+        <v>5.49489498138428</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G131" t="n">
-        <v>5.43976211547852</v>
+        <v>5.43976259231567</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>5.55002737045288</v>
+        <v>5.55002784729004</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>5.55002737045288</v>
+        <v>5.55002784729004</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G138" t="n">
-        <v>5.55002737045288</v>
+        <v>5.55002784729004</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G139" t="n">
-        <v>5.55002737045288</v>
+        <v>5.55002784729004</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>5.45813989639282</v>
+        <v>5.45814037322998</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G141" t="n">
-        <v>5.45813989639282</v>
+        <v>5.45814037322998</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>5.45813989639282</v>
+        <v>5.45814037322998</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G145" t="n">
-        <v>5.86244630813599</v>
+        <v>5.86244583129883</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G146" t="n">
-        <v>5.86244630813599</v>
+        <v>5.86244583129883</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>6.5</v>
       </c>
       <c r="G149" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271108627319</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>6.5</v>
       </c>
       <c r="G150" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271108627319</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G152" t="n">
-        <v>6.02784395217896</v>
+        <v>6.02784442901611</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G154" t="n">
-        <v>6.24837493896484</v>
+        <v>6.248375415802</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G155" t="n">
-        <v>6.28513050079346</v>
+        <v>6.28513097763062</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>7</v>
       </c>
       <c r="G159" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>7</v>
       </c>
       <c r="G165" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>6.56079435348511</v>
+        <v>6.56079387664795</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>7</v>
       </c>
       <c r="G167" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>7</v>
       </c>
       <c r="G168" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>7</v>
       </c>
       <c r="G169" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>7</v>
       </c>
       <c r="G170" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>7</v>
       </c>
       <c r="G172" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G174" t="n">
-        <v>6.39539623260498</v>
+        <v>6.39539575576782</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>7</v>
       </c>
       <c r="G175" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G176" t="n">
-        <v>6.61592674255371</v>
+        <v>6.61592626571655</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G178" t="n">
-        <v>7.20400953292847</v>
+        <v>7.20400905609131</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>7.5</v>
       </c>
       <c r="G185" t="n">
-        <v>6.89159059524536</v>
+        <v>6.8915901184082</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>7.5</v>
       </c>
       <c r="G186" t="n">
-        <v>6.89159059524536</v>
+        <v>6.8915901184082</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G187" t="n">
-        <v>7.05698823928833</v>
+        <v>7.05698871612549</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G192" t="n">
-        <v>7.36940765380859</v>
+        <v>7.36940813064575</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G202" t="n">
-        <v>7.70020341873169</v>
+        <v>7.70020389556885</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G203" t="n">
-        <v>7.70020341873169</v>
+        <v>7.70020389556885</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G204" t="n">
-        <v>7.79209136962891</v>
+        <v>7.79209089279175</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>8.5</v>
       </c>
       <c r="G205" t="n">
-        <v>7.81046867370605</v>
+        <v>7.81046962738037</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G208" t="n">
-        <v>8.08613300323486</v>
+        <v>8.08613204956055</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G213" t="n">
-        <v>8.28828716278076</v>
+        <v>8.28828620910645</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G215" t="n">
-        <v>8.41693019866943</v>
+        <v>8.41692924499512</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G217" t="n">
-        <v>8.61908340454102</v>
+        <v>8.61908149719238</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G218" t="n">
-        <v>8.69259357452393</v>
+        <v>8.69259166717529</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G219" t="n">
-        <v>8.61908340454102</v>
+        <v>8.61908149719238</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>8.69259357452393</v>
+        <v>8.69259166717529</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>8.69259357452393</v>
+        <v>8.69259166717529</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G222" t="n">
-        <v>8.60070514678955</v>
+        <v>8.60070419311523</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>9.5</v>
       </c>
       <c r="G227" t="n">
-        <v>8.72934818267822</v>
+        <v>8.72934722900391</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G228" t="n">
-        <v>8.63746070861816</v>
+        <v>8.63745975494385</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G229" t="n">
-        <v>8.63746070861816</v>
+        <v>8.63745975494385</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G230" t="n">
-        <v>8.63746070861816</v>
+        <v>8.63745975494385</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G231" t="n">
-        <v>8.60070514678955</v>
+        <v>8.60070419311523</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G232" t="n">
-        <v>8.61908340454102</v>
+        <v>8.61908149719238</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G233" t="n">
-        <v>8.63746070861816</v>
+        <v>8.63745975494385</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G236" t="n">
-        <v>8.14126586914062</v>
+        <v>8.14126491546631</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>8.23315334320068</v>
+        <v>8.233154296875</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G242" t="n">
-        <v>8.28828716278076</v>
+        <v>8.28828620910645</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G248" t="n">
-        <v>8.63746070861816</v>
+        <v>8.63745975494385</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G249" t="n">
-        <v>8.45368385314941</v>
+        <v>8.45368480682373</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G250" t="n">
-        <v>8.49043941497803</v>
+        <v>8.49043846130371</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>9.5</v>
       </c>
       <c r="G256" t="n">
-        <v>8.72934818267822</v>
+        <v>8.72934722900391</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G258" t="n">
-        <v>9.09689807891846</v>
+        <v>9.09689903259277</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G259" t="n">
-        <v>9.09689807891846</v>
+        <v>9.09689903259277</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G260" t="n">
-        <v>9.09689807891846</v>
+        <v>9.09689903259277</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G261" t="n">
-        <v>8.98663330078125</v>
+        <v>8.98663425445557</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G262" t="n">
-        <v>8.98663330078125</v>
+        <v>8.98663425445557</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G264" t="n">
-        <v>8.69259357452393</v>
+        <v>8.69259166717529</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>8.69259357452393</v>
+        <v>8.69259166717529</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>9.5</v>
       </c>
       <c r="G266" t="n">
-        <v>8.72934818267822</v>
+        <v>8.72934722900391</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G267" t="n">
-        <v>8.69259357452393</v>
+        <v>8.69259166717529</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G268" t="n">
-        <v>8.50881767272949</v>
+        <v>8.50881671905518</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G270" t="n">
-        <v>8.67421531677246</v>
+        <v>8.67421436309814</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G271" t="n">
-        <v>8.39855194091797</v>
+        <v>8.39855098724365</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G272" t="n">
-        <v>7.47967338562012</v>
+        <v>7.47967290878296</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G273" t="n">
-        <v>7.29589700698853</v>
+        <v>7.29589748382568</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>7.53480529785156</v>
+        <v>7.53480577468872</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G277" t="n">
-        <v>7.40616273880005</v>
+        <v>7.40616321563721</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G278" t="n">
-        <v>7.66344833374023</v>
+        <v>7.66344928741455</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G279" t="n">
-        <v>7.64507055282593</v>
+        <v>7.64507102966309</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G295" t="n">
-        <v>6.61592674255371</v>
+        <v>6.61592626571655</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>6.79970216751099</v>
+        <v>6.79970264434814</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>6.98347759246826</v>
+        <v>6.98347806930542</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>6.98347759246826</v>
+        <v>6.98347806930542</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>6.98347759246826</v>
+        <v>6.98347806930542</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G301" t="n">
-        <v>6.98347759246826</v>
+        <v>6.98347806930542</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>7.5</v>
       </c>
       <c r="G302" t="n">
-        <v>6.89159059524536</v>
+        <v>6.8915901184082</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>7.5</v>
       </c>
       <c r="G303" t="n">
-        <v>6.89159059524536</v>
+        <v>6.8915901184082</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>7.5</v>
       </c>
       <c r="G304" t="n">
-        <v>6.89159059524536</v>
+        <v>6.8915901184082</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>7.5</v>
       </c>
       <c r="G305" t="n">
-        <v>6.89159059524536</v>
+        <v>6.8915901184082</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G306" t="n">
-        <v>7.07536554336548</v>
+        <v>7.07536602020264</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G309" t="n">
-        <v>7.05698823928833</v>
+        <v>7.05698871612549</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G310" t="n">
-        <v>7.07536554336548</v>
+        <v>7.07536602020264</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G311" t="n">
-        <v>7.55318355560303</v>
+        <v>7.55318403244019</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G312" t="n">
-        <v>7.53480529785156</v>
+        <v>7.53480577468872</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G314" t="n">
-        <v>7.44291830062866</v>
+        <v>7.4429178237915</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G315" t="n">
-        <v>7.44291830062866</v>
+        <v>7.4429178237915</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G316" t="n">
-        <v>7.44291830062866</v>
+        <v>7.4429178237915</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>7.44291830062866</v>
+        <v>7.4429178237915</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G318" t="n">
-        <v>7.44291830062866</v>
+        <v>7.4429178237915</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G327" t="n">
-        <v>7.00185537338257</v>
+        <v>7.00185585021973</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G328" t="n">
-        <v>6.98347759246826</v>
+        <v>6.98347806930542</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G329" t="n">
-        <v>6.79970216751099</v>
+        <v>6.79970264434814</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G330" t="n">
-        <v>7.02023267745972</v>
+        <v>7.02023363113403</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G331" t="n">
-        <v>7.02023267745972</v>
+        <v>7.02023363113403</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G332" t="n">
-        <v>7.02023267745972</v>
+        <v>7.02023363113403</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G333" t="n">
-        <v>7.02023267745972</v>
+        <v>7.02023363113403</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>6.79970216751099</v>
+        <v>6.79970264434814</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>6.79970216751099</v>
+        <v>6.79970264434814</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>6.5</v>
       </c>
       <c r="G340" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271108627319</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G341" t="n">
-        <v>6.15648698806763</v>
+        <v>6.15648746490479</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G342" t="n">
-        <v>6.15648698806763</v>
+        <v>6.15648746490479</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G343" t="n">
-        <v>6.02784395217896</v>
+        <v>6.02784442901611</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G344" t="n">
-        <v>6.26675271987915</v>
+        <v>6.26675319671631</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G345" t="n">
-        <v>6.26675271987915</v>
+        <v>6.26675319671631</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G346" t="n">
-        <v>6.04622173309326</v>
+        <v>6.04622220993042</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G347" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G348" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G350" t="n">
-        <v>6.04622173309326</v>
+        <v>6.04622220993042</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G353" t="n">
-        <v>5.91757917404175</v>
+        <v>5.91757869720459</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G354" t="n">
-        <v>5.91757917404175</v>
+        <v>5.91757869720459</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G355" t="n">
-        <v>6.24837493896484</v>
+        <v>6.248375415802</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>6.24837493896484</v>
+        <v>6.248375415802</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G357" t="n">
-        <v>6.24837493896484</v>
+        <v>6.248375415802</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G358" t="n">
-        <v>6.24837493896484</v>
+        <v>6.248375415802</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G360" t="n">
-        <v>6.68943691253662</v>
+        <v>6.68943738937378</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G362" t="n">
-        <v>6.68943691253662</v>
+        <v>6.68943738937378</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G363" t="n">
-        <v>6.68943691253662</v>
+        <v>6.68943738937378</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G365" t="n">
-        <v>6.59754943847656</v>
+        <v>6.59754848480225</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G366" t="n">
-        <v>6.15648698806763</v>
+        <v>6.15648746490479</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>6.15648698806763</v>
+        <v>6.15648746490479</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G376" t="n">
-        <v>6.04622173309326</v>
+        <v>6.04622220993042</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>6.04622173309326</v>
+        <v>6.04622220993042</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>6.5</v>
       </c>
       <c r="G378" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271108627319</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>6.5</v>
       </c>
       <c r="G383" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271108627319</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>6.5</v>
       </c>
       <c r="G384" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271108627319</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>6.5</v>
       </c>
       <c r="G385" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271108627319</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.5</v>
       </c>
       <c r="G386" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271108627319</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G387" t="n">
-        <v>5.82569169998169</v>
+        <v>5.82569122314453</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G388" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G395" t="n">
-        <v>5.80731391906738</v>
+        <v>5.80731344223022</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G396" t="n">
-        <v>5.80731391906738</v>
+        <v>5.80731344223022</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G397" t="n">
-        <v>5.80731391906738</v>
+        <v>5.80731344223022</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G398" t="n">
-        <v>5.91757917404175</v>
+        <v>5.91757869720459</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G399" t="n">
-        <v>5.91757917404175</v>
+        <v>5.91757869720459</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G400" t="n">
-        <v>6.10135459899902</v>
+        <v>6.10135412216187</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G401" t="n">
-        <v>6.15648698806763</v>
+        <v>6.15648746490479</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G402" t="n">
-        <v>6.15648698806763</v>
+        <v>6.15648746490479</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G403" t="n">
-        <v>6.15648698806763</v>
+        <v>6.15648746490479</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G404" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G405" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G406" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G407" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G408" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G409" t="n">
-        <v>6.28513050079346</v>
+        <v>6.28513097763062</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G410" t="n">
-        <v>6.28513050079346</v>
+        <v>6.28513097763062</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G411" t="n">
-        <v>6.28513050079346</v>
+        <v>6.28513097763062</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G412" t="n">
-        <v>6.28513050079346</v>
+        <v>6.28513097763062</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>7</v>
       </c>
       <c r="G415" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>7</v>
       </c>
       <c r="G416" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7</v>
       </c>
       <c r="G417" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>7</v>
       </c>
       <c r="G418" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>7</v>
       </c>
       <c r="G419" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>7</v>
       </c>
       <c r="G420" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>7</v>
       </c>
       <c r="G421" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G422" t="n">
-        <v>6.30350780487061</v>
+        <v>6.30350828170776</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G423" t="n">
-        <v>6.30350780487061</v>
+        <v>6.30350828170776</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G424" t="n">
-        <v>6.30350780487061</v>
+        <v>6.30350828170776</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G425" t="n">
-        <v>6.30350780487061</v>
+        <v>6.30350828170776</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G426" t="n">
-        <v>6.30350780487061</v>
+        <v>6.30350828170776</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G427" t="n">
-        <v>6.30350780487061</v>
+        <v>6.30350828170776</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G428" t="n">
-        <v>6.30350780487061</v>
+        <v>6.30350828170776</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G429" t="n">
-        <v>6.30350780487061</v>
+        <v>6.30350828170776</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G430" t="n">
-        <v>6.30350780487061</v>
+        <v>6.30350828170776</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G432" t="n">
-        <v>6.08297681808472</v>
+        <v>6.08297729492188</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>6.08297681808472</v>
+        <v>6.08297729492188</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G434" t="n">
-        <v>6.08297681808472</v>
+        <v>6.08297729492188</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G435" t="n">
-        <v>6.08297681808472</v>
+        <v>6.08297729492188</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G436" t="n">
-        <v>6.08297681808472</v>
+        <v>6.08297729492188</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G437" t="n">
-        <v>6.08297681808472</v>
+        <v>6.08297729492188</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7</v>
       </c>
       <c r="G438" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>6.15648698806763</v>
+        <v>6.15648746490479</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G441" t="n">
-        <v>6.32188558578491</v>
+        <v>6.32188606262207</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G442" t="n">
-        <v>6.32188558578491</v>
+        <v>6.32188606262207</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G443" t="n">
-        <v>6.32188558578491</v>
+        <v>6.32188606262207</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G444" t="n">
-        <v>6.32188558578491</v>
+        <v>6.32188606262207</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G445" t="n">
-        <v>6.2299976348877</v>
+        <v>6.22999811172485</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G446" t="n">
-        <v>6.2299976348877</v>
+        <v>6.22999811172485</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G447" t="n">
-        <v>6.2299976348877</v>
+        <v>6.22999811172485</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G448" t="n">
-        <v>6.02784395217896</v>
+        <v>6.02784442901611</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>6.5</v>
       </c>
       <c r="G450" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271108627319</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G453" t="n">
-        <v>5.78893661499023</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G454" t="n">
-        <v>5.78893661499023</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G455" t="n">
-        <v>5.78893661499023</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G456" t="n">
-        <v>5.78893661499023</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G457" t="n">
-        <v>5.78893661499023</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G458" t="n">
-        <v>5.78893661499023</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G459" t="n">
-        <v>5.78893661499023</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G460" t="n">
-        <v>5.78893661499023</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G461" t="n">
-        <v>5.78893661499023</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G462" t="n">
-        <v>5.78893661499023</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G463" t="n">
-        <v>5.78893661499023</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G464" t="n">
-        <v>5.78893661499023</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G465" t="n">
-        <v>5.78893661499023</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G466" t="n">
-        <v>5.78893661499023</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G467" t="n">
-        <v>5.78893661499023</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G468" t="n">
-        <v>5.60515975952148</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G469" t="n">
-        <v>5.60515975952148</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G470" t="n">
-        <v>5.58678245544434</v>
+        <v>5.58678293228149</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>5.58678245544434</v>
+        <v>5.58678293228149</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G472" t="n">
-        <v>5.58678245544434</v>
+        <v>5.58678293228149</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G473" t="n">
-        <v>5.58678245544434</v>
+        <v>5.58678293228149</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G480" t="n">
-        <v>5.45813989639282</v>
+        <v>5.45814037322998</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G482" t="n">
-        <v>5.60515975952148</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>5.60515975952148</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G484" t="n">
-        <v>5.60515975952148</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G485" t="n">
-        <v>5.78893661499023</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G486" t="n">
-        <v>5.78893661499023</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G487" t="n">
-        <v>5.78893661499023</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G488" t="n">
-        <v>5.78893661499023</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G495" t="n">
-        <v>5.73380327224731</v>
+        <v>5.73380279541016</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G496" t="n">
-        <v>5.73380327224731</v>
+        <v>5.73380279541016</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G497" t="n">
-        <v>5.73380327224731</v>
+        <v>5.73380279541016</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G498" t="n">
-        <v>5.58678245544434</v>
+        <v>5.58678293228149</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G499" t="n">
-        <v>5.58678245544434</v>
+        <v>5.58678293228149</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G500" t="n">
-        <v>5.58678245544434</v>
+        <v>5.58678293228149</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>5.36625194549561</v>
+        <v>5.36625146865845</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G506" t="n">
-        <v>5.32949638366699</v>
+        <v>5.32949686050415</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>5.32949638366699</v>
+        <v>5.32949686050415</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>5.55002737045288</v>
+        <v>5.55002784729004</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G510" t="n">
-        <v>5.78893661499023</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G511" t="n">
-        <v>5.78893661499023</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G512" t="n">
-        <v>5.78893661499023</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G513" t="n">
-        <v>5.78893661499023</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G514" t="n">
-        <v>5.55002737045288</v>
+        <v>5.55002784729004</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G521" t="n">
-        <v>5.45813989639282</v>
+        <v>5.45814037322998</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G522" t="n">
-        <v>5.60515975952148</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>5.60515975952148</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G524" t="n">
-        <v>5.60515975952148</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G548" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G549" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G550" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G551" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G552" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G553" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G554" t="n">
-        <v>5.60515975952148</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G555" t="n">
-        <v>5.60515975952148</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G556" t="n">
-        <v>5.60515975952148</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G557" t="n">
-        <v>5.60515975952148</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G558" t="n">
-        <v>5.60515975952148</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G559" t="n">
-        <v>5.60515975952148</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G560" t="n">
-        <v>5.60515975952148</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G561" t="n">
-        <v>5.60515975952148</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G562" t="n">
-        <v>5.60515975952148</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G563" t="n">
-        <v>5.45813989639282</v>
+        <v>5.45814037322998</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G564" t="n">
-        <v>5.27436351776123</v>
+        <v>5.27436304092407</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G568" t="n">
-        <v>5.43976211547852</v>
+        <v>5.43976259231567</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G569" t="n">
-        <v>5.2927417755127</v>
+        <v>5.29274129867554</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G570" t="n">
-        <v>5.2927417755127</v>
+        <v>5.29274129867554</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G571" t="n">
-        <v>5.2927417755127</v>
+        <v>5.29274129867554</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G572" t="n">
-        <v>5.2927417755127</v>
+        <v>5.29274129867554</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G573" t="n">
-        <v>5.2927417755127</v>
+        <v>5.29274129867554</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G574" t="n">
-        <v>5.27436351776123</v>
+        <v>5.27436304092407</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G575" t="n">
-        <v>5.45813989639282</v>
+        <v>5.45814037322998</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G576" t="n">
-        <v>5.45813989639282</v>
+        <v>5.45814037322998</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G580" t="n">
-        <v>5.60515975952148</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G581" t="n">
-        <v>5.60515975952148</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G585" t="n">
-        <v>5.60515975952148</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>5.75</v>
       </c>
       <c r="G588" t="n">
-        <v>5.2835521697998</v>
+        <v>5.28355264663696</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>5.75</v>
       </c>
       <c r="G589" t="n">
-        <v>5.2835521697998</v>
+        <v>5.28355264663696</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>5.75</v>
       </c>
       <c r="G590" t="n">
-        <v>5.2835521697998</v>
+        <v>5.28355264663696</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>5.75</v>
       </c>
       <c r="G597" t="n">
-        <v>5.2835521697998</v>
+        <v>5.28355264663696</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>5.75</v>
       </c>
       <c r="G598" t="n">
-        <v>5.2835521697998</v>
+        <v>5.28355264663696</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>5.75</v>
       </c>
       <c r="G599" t="n">
-        <v>5.2835521697998</v>
+        <v>5.28355264663696</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G608" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G609" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G616" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G617" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G618" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G619" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G620" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G621" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G629" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G630" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G639" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G640" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G641" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G642" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G643" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G649" t="n">
-        <v>4.5021824836731</v>
+        <v>4.50218200683594</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>5</v>
       </c>
       <c r="G650" t="n">
-        <v>4.65101432800293</v>
+        <v>4.65101480484009</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G673" t="n">
-        <v>4.97658491134644</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G675" t="n">
-        <v>5.06960535049438</v>
+        <v>5.06960582733154</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G679" t="n">
-        <v>4.97658491134644</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G680" t="n">
-        <v>4.97658491134644</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>4.97658491134644</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G682" t="n">
-        <v>4.97658491134644</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G689" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G704" t="n">
-        <v>4.74403524398804</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G705" t="n">
-        <v>4.74403524398804</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G706" t="n">
-        <v>4.74403524398804</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G707" t="n">
-        <v>4.74403524398804</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G708" t="n">
-        <v>4.74403524398804</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G711" t="n">
-        <v>4.6975245475769</v>
+        <v>4.69752502441406</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G712" t="n">
-        <v>4.6975245475769</v>
+        <v>4.69752502441406</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G713" t="n">
-        <v>4.6975245475769</v>
+        <v>4.69752502441406</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G714" t="n">
-        <v>4.55799388885498</v>
+        <v>4.55799436569214</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G717" t="n">
-        <v>4.63241052627563</v>
+        <v>4.63241100311279</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G718" t="n">
-        <v>4.63241052627563</v>
+        <v>4.63241100311279</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G719" t="n">
-        <v>4.63241052627563</v>
+        <v>4.63241100311279</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G720" t="n">
-        <v>4.63241052627563</v>
+        <v>4.63241100311279</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G723" t="n">
-        <v>4.01847648620605</v>
+        <v>4.01847696304321</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G724" t="n">
-        <v>4.01847648620605</v>
+        <v>4.01847696304321</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G725" t="n">
-        <v>4.01847648620605</v>
+        <v>4.01847696304321</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G727" t="n">
-        <v>4.2417254447937</v>
+        <v>4.24172496795654</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>4.27893304824829</v>
+        <v>4.27893352508545</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G730" t="n">
-        <v>4.27893304824829</v>
+        <v>4.27893352508545</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G731" t="n">
-        <v>4.29753732681274</v>
+        <v>4.29753684997559</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G732" t="n">
-        <v>4.20451736450195</v>
+        <v>4.20451688766479</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G733" t="n">
-        <v>4.20451736450195</v>
+        <v>4.20451688766479</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G740" t="n">
-        <v>4.44637012481689</v>
+        <v>4.44636964797974</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G754" t="n">
-        <v>4.35334968566895</v>
+        <v>4.35334920883179</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>5</v>
       </c>
       <c r="G757" t="n">
-        <v>4.65101432800293</v>
+        <v>4.65101480484009</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G758" t="n">
-        <v>4.6975245475769</v>
+        <v>4.69752502441406</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G764" t="n">
-        <v>4.74403524398804</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G765" t="n">
-        <v>4.74403524398804</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G776" t="n">
-        <v>4.97658491134644</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G777" t="n">
-        <v>5.06960535049438</v>
+        <v>5.06960582733154</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G778" t="n">
-        <v>5.06960535049438</v>
+        <v>5.06960582733154</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G780" t="n">
-        <v>4.97658491134644</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G781" t="n">
-        <v>5.06960535049438</v>
+        <v>5.06960582733154</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G782" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G783" t="n">
-        <v>5.67423725128174</v>
+        <v>5.6742377281189</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G784" t="n">
-        <v>5.76725769042969</v>
+        <v>5.76725816726685</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G785" t="n">
-        <v>5.99980878829956</v>
+        <v>5.9998083114624</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G786" t="n">
-        <v>5.95329809188843</v>
+        <v>5.95329856872559</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G787" t="n">
-        <v>5.95329809188843</v>
+        <v>5.95329856872559</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G790" t="n">
-        <v>5.76725769042969</v>
+        <v>5.76725816726685</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>6.25</v>
       </c>
       <c r="G792" t="n">
-        <v>5.81376791000366</v>
+        <v>5.81376838684082</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G793" t="n">
-        <v>5.67423725128174</v>
+        <v>5.6742377281189</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G798" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G803" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G805" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G806" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G807" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G808" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G809" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G820" t="n">
-        <v>5.06960535049438</v>
+        <v>5.06960582733154</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G821" t="n">
-        <v>5.06960535049438</v>
+        <v>5.06960582733154</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G822" t="n">
-        <v>5.06960535049438</v>
+        <v>5.06960582733154</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G823" t="n">
-        <v>5.06960535049438</v>
+        <v>5.06960582733154</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G824" t="n">
-        <v>5.06960535049438</v>
+        <v>5.06960582733154</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G825" t="n">
-        <v>4.97658491134644</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G826" t="n">
-        <v>4.97658491134644</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G828" t="n">
-        <v>5.06960535049438</v>
+        <v>5.06960582733154</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G829" t="n">
-        <v>5.06960535049438</v>
+        <v>5.06960582733154</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G835" t="n">
-        <v>4.74403524398804</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G836" t="n">
-        <v>4.74403524398804</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G843" t="n">
-        <v>4.63241052627563</v>
+        <v>4.63241100311279</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>5</v>
       </c>
       <c r="G844" t="n">
-        <v>4.65101432800293</v>
+        <v>4.65101480484009</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>5</v>
       </c>
       <c r="G845" t="n">
-        <v>4.65101432800293</v>
+        <v>4.65101480484009</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>5</v>
       </c>
       <c r="G846" t="n">
-        <v>4.65101432800293</v>
+        <v>4.65101480484009</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>5</v>
       </c>
       <c r="G847" t="n">
-        <v>4.65101432800293</v>
+        <v>4.65101480484009</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G852" t="n">
-        <v>4.6975245475769</v>
+        <v>4.69752502441406</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G853" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G856" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G857" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G858" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G859" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G860" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G864" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G865" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G866" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G867" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>5</v>
       </c>
       <c r="G869" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>5</v>
       </c>
       <c r="G870" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>5</v>
       </c>
       <c r="G871" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G872" t="n">
-        <v>4.79242420196533</v>
+        <v>4.79242467880249</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G873" t="n">
-        <v>4.79242420196533</v>
+        <v>4.79242467880249</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>5</v>
       </c>
       <c r="G874" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G877" t="n">
-        <v>4.70701456069946</v>
+        <v>4.70701503753662</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>4.70701456069946</v>
+        <v>4.70701503753662</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G884" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G885" t="n">
-        <v>4.79242420196533</v>
+        <v>4.79242467880249</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>5</v>
       </c>
       <c r="G889" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G890" t="n">
-        <v>4.79242420196533</v>
+        <v>4.79242467880249</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>5</v>
       </c>
       <c r="G891" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>5</v>
       </c>
       <c r="G892" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>5</v>
       </c>
       <c r="G893" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>5</v>
       </c>
       <c r="G894" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G895" t="n">
-        <v>4.79242420196533</v>
+        <v>4.79242467880249</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>5</v>
       </c>
       <c r="G896" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>5</v>
       </c>
       <c r="G897" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>5</v>
       </c>
       <c r="G898" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>5</v>
       </c>
       <c r="G899" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>5</v>
       </c>
       <c r="G900" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>5</v>
       </c>
       <c r="G904" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>5</v>
       </c>
       <c r="G905" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>5</v>
       </c>
       <c r="G906" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>5</v>
       </c>
       <c r="G907" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>5</v>
       </c>
       <c r="G908" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>5</v>
       </c>
       <c r="G909" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>5</v>
       </c>
       <c r="G910" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>5</v>
       </c>
       <c r="G911" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>5</v>
       </c>
       <c r="G912" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>5</v>
       </c>
       <c r="G913" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>5</v>
       </c>
       <c r="G914" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>5</v>
       </c>
       <c r="G915" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>5</v>
       </c>
       <c r="G916" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>5</v>
       </c>
       <c r="G917" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>5</v>
       </c>
       <c r="G918" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>5</v>
       </c>
       <c r="G919" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>5</v>
       </c>
       <c r="G920" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>5</v>
       </c>
       <c r="G921" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>5</v>
       </c>
       <c r="G924" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G925" t="n">
-        <v>4.61211538314819</v>
+        <v>4.61211490631104</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G926" t="n">
-        <v>4.61211538314819</v>
+        <v>4.61211490631104</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G927" t="n">
-        <v>4.61211538314819</v>
+        <v>4.61211490631104</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G928" t="n">
-        <v>4.61211538314819</v>
+        <v>4.61211490631104</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G929" t="n">
-        <v>4.61211538314819</v>
+        <v>4.61211490631104</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G930" t="n">
-        <v>4.61211538314819</v>
+        <v>4.61211490631104</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G931" t="n">
-        <v>4.61211538314819</v>
+        <v>4.61211490631104</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G933" t="n">
-        <v>4.79242420196533</v>
+        <v>4.79242467880249</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G934" t="n">
-        <v>4.79242420196533</v>
+        <v>4.79242467880249</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G935" t="n">
-        <v>4.79242420196533</v>
+        <v>4.79242467880249</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>5</v>
       </c>
       <c r="G940" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G941" t="n">
-        <v>4.63109540939331</v>
+        <v>4.63109493255615</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G942" t="n">
-        <v>4.65007495880127</v>
+        <v>4.65007543563843</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G943" t="n">
-        <v>4.65007495880127</v>
+        <v>4.65007543563843</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G944" t="n">
-        <v>4.65007495880127</v>
+        <v>4.65007543563843</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G945" t="n">
-        <v>4.65007495880127</v>
+        <v>4.65007543563843</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G946" t="n">
-        <v>4.65007495880127</v>
+        <v>4.65007543563843</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G947" t="n">
-        <v>4.65007495880127</v>
+        <v>4.65007543563843</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G948" t="n">
-        <v>4.65007495880127</v>
+        <v>4.65007543563843</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G949" t="n">
-        <v>4.65007495880127</v>
+        <v>4.65007543563843</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G950" t="n">
-        <v>4.63109540939331</v>
+        <v>4.63109493255615</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G951" t="n">
-        <v>4.63109540939331</v>
+        <v>4.63109493255615</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G952" t="n">
-        <v>4.63109540939331</v>
+        <v>4.63109493255615</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G953" t="n">
-        <v>4.63109540939331</v>
+        <v>4.63109493255615</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G959" t="n">
-        <v>4.49823570251465</v>
+        <v>4.49823522567749</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G961" t="n">
-        <v>4.49823570251465</v>
+        <v>4.49823522567749</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G962" t="n">
-        <v>4.36537599563599</v>
+        <v>4.36537647247314</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G963" t="n">
-        <v>4.36537599563599</v>
+        <v>4.36537647247314</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G964" t="n">
-        <v>4.32741689682007</v>
+        <v>4.32741641998291</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G971" t="n">
-        <v>4.36537599563599</v>
+        <v>4.36537647247314</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G975" t="n">
-        <v>4.13761758804321</v>
+        <v>4.13761806488037</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G984" t="n">
-        <v>4.36537599563599</v>
+        <v>4.36537647247314</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G985" t="n">
-        <v>4.36537599563599</v>
+        <v>4.36537647247314</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G986" t="n">
-        <v>4.36537599563599</v>
+        <v>4.36537647247314</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G987" t="n">
-        <v>4.34639692306519</v>
+        <v>4.34639644622803</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G989" t="n">
-        <v>4.32741689682007</v>
+        <v>4.32741641998291</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G990" t="n">
-        <v>4.36537599563599</v>
+        <v>4.36537647247314</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G992" t="n">
-        <v>4.36537599563599</v>
+        <v>4.36537647247314</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.55517578125</v>
+        <v>4.55517530441284</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.57415580749512</v>
+        <v>4.57415533065796</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.63109540939331</v>
+        <v>4.63109493255615</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.32741689682007</v>
+        <v>4.32741641998291</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.32741689682007</v>
+        <v>4.32741641998291</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.32741689682007</v>
+        <v>4.32741641998291</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.32741689682007</v>
+        <v>4.32741641998291</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.32741689682007</v>
+        <v>4.32741641998291</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.13761758804321</v>
+        <v>4.13761806488037</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1030" t="n">
-        <v>4.1186375617981</v>
+        <v>4.11863803863525</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.85291934013367</v>
+        <v>3.85291910171509</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.08067798614502</v>
+        <v>4.08067846298218</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.08067798614502</v>
+        <v>4.08067846298218</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.08067798614502</v>
+        <v>4.08067846298218</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.08067798614502</v>
+        <v>4.08067846298218</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1053" t="n">
-        <v>4.08067798614502</v>
+        <v>4.08067846298218</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.94781851768494</v>
+        <v>3.94781875610352</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.94781851768494</v>
+        <v>3.94781875610352</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.89087891578674</v>
+        <v>3.89087915420532</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.60618042945862</v>
+        <v>3.6061806678772</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.5872004032135</v>
+        <v>3.58720064163208</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.60618042945862</v>
+        <v>3.6061806678772</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.81495952606201</v>
+        <v>3.81495928764343</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1096" t="n">
-        <v>4.1186375617981</v>
+        <v>4.11863803863525</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -38228,6 +38228,32 @@
         <v>3.92000007629395</v>
       </c>
       <c r="H1456" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1457" t="n">
+        <v>5750</v>
+      </c>
+      <c r="C1457" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D1457" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="E1457" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F1457" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="G1457" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="H1457" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLN.MI.xlsx
+++ b/data/PLN.MI.xlsx
@@ -33883,6 +33883,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1458">
+      <c r="A1458" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1458" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1458" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="D1458" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="E1458" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="F1458" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="G1458" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PLN.MI.xlsx
+++ b/data/PLN.MI.xlsx
@@ -33906,6 +33906,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1459">
+      <c r="A1459" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1459" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1459" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="D1459" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="E1459" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="F1459" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="G1459" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B1460" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C1460" t="n">
+        <v>3.88000011444092</v>
+      </c>
+      <c r="D1460" t="n">
+        <v>3.88000011444092</v>
+      </c>
+      <c r="E1460" t="n">
+        <v>3.88000011444092</v>
+      </c>
+      <c r="F1460"/>
+      <c r="G1460" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PLN.MI.xlsx
+++ b/data/PLN.MI.xlsx
@@ -473,7 +473,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G4" t="n">
-        <v>4.10738801956177</v>
+        <v>4.10738754272461</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G9" t="n">
-        <v>4.12576484680176</v>
+        <v>4.12576532363892</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G11" t="n">
-        <v>4.0338773727417</v>
+        <v>4.03387784957886</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>4.25</v>
       </c>
       <c r="G13" t="n">
-        <v>3.90523481369019</v>
+        <v>3.90523457527161</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G15" t="n">
-        <v>3.89604568481445</v>
+        <v>3.89604592323303</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G16" t="n">
-        <v>3.84091305732727</v>
+        <v>3.84091281890869</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G20" t="n">
-        <v>3.8776683807373</v>
+        <v>3.87766814231873</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G21" t="n">
-        <v>3.8776683807373</v>
+        <v>3.87766814231873</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G22" t="n">
-        <v>3.8776683807373</v>
+        <v>3.87766814231873</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G32" t="n">
-        <v>4.10738801956177</v>
+        <v>4.10738754272461</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G34" t="n">
-        <v>4.10738801956177</v>
+        <v>4.10738754272461</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G39" t="n">
-        <v>4.09819889068604</v>
+        <v>4.09819936752319</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>4.09819889068604</v>
+        <v>4.09819936752319</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G45" t="n">
-        <v>4.0338773727417</v>
+        <v>4.03387784957886</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G51" t="n">
-        <v>3.89604568481445</v>
+        <v>3.89604592323303</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G53" t="n">
-        <v>3.89604568481445</v>
+        <v>3.89604592323303</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.25</v>
       </c>
       <c r="G56" t="n">
-        <v>3.90523481369019</v>
+        <v>3.90523457527161</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.25</v>
       </c>
       <c r="G57" t="n">
-        <v>3.90523481369019</v>
+        <v>3.90523457527161</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G60" t="n">
-        <v>4.0338773727417</v>
+        <v>4.03387784957886</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G65" t="n">
-        <v>4.10738801956177</v>
+        <v>4.10738754272461</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G68" t="n">
-        <v>4.263596534729</v>
+        <v>4.26359701156616</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G70" t="n">
-        <v>4.42899513244629</v>
+        <v>4.42899560928345</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G72" t="n">
-        <v>4.66790342330933</v>
+        <v>4.66790390014648</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>4.61277103424072</v>
+        <v>4.61277151107788</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G82" t="n">
-        <v>4.77816915512085</v>
+        <v>4.77816963195801</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G87" t="n">
-        <v>5.31111907958984</v>
+        <v>5.31111860275269</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G89" t="n">
-        <v>6.11973190307617</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>5.93595600128174</v>
+        <v>5.9359564781189</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G91" t="n">
-        <v>6.11973190307617</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G92" t="n">
-        <v>6.26675271987915</v>
+        <v>6.26675319671631</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>7</v>
       </c>
       <c r="G93" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G94" t="n">
-        <v>6.11973190307617</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G98" t="n">
-        <v>6.22999858856201</v>
+        <v>6.22999811172485</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G102" t="n">
-        <v>6.10135412216187</v>
+        <v>6.10135459899902</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G103" t="n">
-        <v>6.10135412216187</v>
+        <v>6.10135459899902</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G107" t="n">
-        <v>5.93595600128174</v>
+        <v>5.9359564781189</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>6.04622173309326</v>
+        <v>6.04622220993042</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>5.88082361221313</v>
+        <v>5.88082408905029</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G114" t="n">
-        <v>5.88082361221313</v>
+        <v>5.88082408905029</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G116" t="n">
-        <v>5.53164958953857</v>
+        <v>5.53165006637573</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G128" t="n">
-        <v>5.56840515136719</v>
+        <v>5.56840467453003</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G134" t="n">
-        <v>5.53164958953857</v>
+        <v>5.53165006637573</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>5.53164958953857</v>
+        <v>5.53165006637573</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G143" t="n">
-        <v>5.88082361221313</v>
+        <v>5.88082408905029</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>5.88082361221313</v>
+        <v>5.88082408905029</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G148" t="n">
-        <v>5.88082361221313</v>
+        <v>5.88082408905029</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>6.06459951400757</v>
+        <v>6.06459903717041</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G153" t="n">
-        <v>6.06459951400757</v>
+        <v>6.06459903717041</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G154" t="n">
-        <v>6.24837589263916</v>
+        <v>6.248375415802</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>7</v>
       </c>
       <c r="G159" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>7</v>
       </c>
       <c r="G165" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>7</v>
       </c>
       <c r="G167" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>7</v>
       </c>
       <c r="G168" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>7</v>
       </c>
       <c r="G169" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>7</v>
       </c>
       <c r="G170" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>7</v>
       </c>
       <c r="G172" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>7</v>
       </c>
       <c r="G175" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G178" t="n">
-        <v>7.20400905609131</v>
+        <v>7.20400953292847</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G182" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>8</v>
       </c>
       <c r="G189" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G192" t="n">
-        <v>7.36940765380859</v>
+        <v>7.36940813064575</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G195" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>7.31427431106567</v>
+        <v>7.31427478790283</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G201" t="n">
-        <v>7.31427431106567</v>
+        <v>7.31427478790283</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G204" t="n">
-        <v>7.79209136962891</v>
+        <v>7.79209184646606</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>8.5</v>
       </c>
       <c r="G205" t="n">
-        <v>7.81046962738037</v>
+        <v>7.81046915054321</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G210" t="n">
-        <v>8.01262283325195</v>
+        <v>8.01262378692627</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G214" t="n">
-        <v>8.25152969360352</v>
+        <v>8.25153064727783</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G216" t="n">
-        <v>8.54557228088379</v>
+        <v>8.54557132720947</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G224" t="n">
-        <v>8.8212366104126</v>
+        <v>8.82123565673828</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.8212366104126</v>
+        <v>8.82123565673828</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G234" t="n">
-        <v>8.54557228088379</v>
+        <v>8.54557132720947</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>8.54557228088379</v>
+        <v>8.54557132720947</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G236" t="n">
-        <v>8.14126491546631</v>
+        <v>8.14126586914062</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G238" t="n">
-        <v>8.25152969360352</v>
+        <v>8.25153064727783</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G240" t="n">
-        <v>8.25152969360352</v>
+        <v>8.25153064727783</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G241" t="n">
-        <v>8.25152969360352</v>
+        <v>8.25153064727783</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>8.54557228088379</v>
+        <v>8.54557132720947</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G251" t="n">
-        <v>8.54557228088379</v>
+        <v>8.54557132720947</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G252" t="n">
-        <v>8.54557228088379</v>
+        <v>8.54557132720947</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G257" t="n">
-        <v>8.87636852264404</v>
+        <v>8.87636756896973</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G272" t="n">
-        <v>7.47967290878296</v>
+        <v>7.47967338562012</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>7.53480529785156</v>
+        <v>7.53480577468872</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G279" t="n">
-        <v>7.64507150650024</v>
+        <v>7.64507102966309</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>8</v>
       </c>
       <c r="G281" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>8</v>
       </c>
       <c r="G282" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>8</v>
       </c>
       <c r="G283" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>8</v>
       </c>
       <c r="G289" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>8</v>
       </c>
       <c r="G290" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>8</v>
       </c>
       <c r="G291" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>8</v>
       </c>
       <c r="G292" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G307" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G311" t="n">
-        <v>7.55318403244019</v>
+        <v>7.55318355560303</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G312" t="n">
-        <v>7.53480529785156</v>
+        <v>7.53480577468872</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G313" t="n">
-        <v>7.38778495788574</v>
+        <v>7.38778448104858</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G321" t="n">
-        <v>7.22238683700562</v>
+        <v>7.22238636016846</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G322" t="n">
-        <v>7.22238683700562</v>
+        <v>7.22238636016846</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G323" t="n">
-        <v>7.22238683700562</v>
+        <v>7.22238636016846</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G324" t="n">
-        <v>7.22238683700562</v>
+        <v>7.22238636016846</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G327" t="n">
-        <v>7.00185632705688</v>
+        <v>7.00185585021973</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G330" t="n">
-        <v>7.02023315429688</v>
+        <v>7.02023363113403</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G331" t="n">
-        <v>7.02023315429688</v>
+        <v>7.02023363113403</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G332" t="n">
-        <v>7.02023315429688</v>
+        <v>7.02023363113403</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G333" t="n">
-        <v>7.02023315429688</v>
+        <v>7.02023363113403</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G344" t="n">
-        <v>6.26675271987915</v>
+        <v>6.26675319671631</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G345" t="n">
-        <v>6.26675271987915</v>
+        <v>6.26675319671631</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G346" t="n">
-        <v>6.04622173309326</v>
+        <v>6.04622220993042</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G347" t="n">
-        <v>6.11973190307617</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G348" t="n">
-        <v>6.11973190307617</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G349" t="n">
-        <v>6.21162033081055</v>
+        <v>6.21162080764771</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G350" t="n">
-        <v>6.04622173309326</v>
+        <v>6.04622220993042</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G355" t="n">
-        <v>6.24837589263916</v>
+        <v>6.248375415802</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>6.24837589263916</v>
+        <v>6.248375415802</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G357" t="n">
-        <v>6.24837589263916</v>
+        <v>6.248375415802</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G358" t="n">
-        <v>6.24837589263916</v>
+        <v>6.248375415802</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G365" t="n">
-        <v>6.5975489616394</v>
+        <v>6.59754943847656</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G371" t="n">
-        <v>6.21162033081055</v>
+        <v>6.21162080764771</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G372" t="n">
-        <v>6.21162033081055</v>
+        <v>6.21162080764771</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G373" t="n">
-        <v>6.21162033081055</v>
+        <v>6.21162080764771</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G374" t="n">
-        <v>6.21162033081055</v>
+        <v>6.21162080764771</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G376" t="n">
-        <v>6.04622173309326</v>
+        <v>6.04622220993042</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>6.04622173309326</v>
+        <v>6.04622220993042</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>6.06459951400757</v>
+        <v>6.06459903717041</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>6.06459951400757</v>
+        <v>6.06459903717041</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>6.06459951400757</v>
+        <v>6.06459903717041</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G382" t="n">
-        <v>6.06459951400757</v>
+        <v>6.06459903717041</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G389" t="n">
-        <v>5.93595600128174</v>
+        <v>5.9359564781189</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>5.93595600128174</v>
+        <v>5.9359564781189</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G391" t="n">
-        <v>5.93595600128174</v>
+        <v>5.9359564781189</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>5.93595600128174</v>
+        <v>5.9359564781189</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G393" t="n">
-        <v>5.93595600128174</v>
+        <v>5.9359564781189</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G394" t="n">
-        <v>5.93595600128174</v>
+        <v>5.9359564781189</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G400" t="n">
-        <v>6.10135412216187</v>
+        <v>6.10135459899902</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G404" t="n">
-        <v>6.11973190307617</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G405" t="n">
-        <v>6.11973190307617</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G406" t="n">
-        <v>6.11973190307617</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G407" t="n">
-        <v>6.11973190307617</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G408" t="n">
-        <v>6.11973190307617</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>7</v>
       </c>
       <c r="G415" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>7</v>
       </c>
       <c r="G416" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7</v>
       </c>
       <c r="G417" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>7</v>
       </c>
       <c r="G418" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>7</v>
       </c>
       <c r="G419" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>7</v>
       </c>
       <c r="G420" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>7</v>
       </c>
       <c r="G421" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G431" t="n">
-        <v>6.21162033081055</v>
+        <v>6.21162080764771</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7</v>
       </c>
       <c r="G438" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G445" t="n">
-        <v>6.22999858856201</v>
+        <v>6.22999811172485</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G446" t="n">
-        <v>6.22999858856201</v>
+        <v>6.22999811172485</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G447" t="n">
-        <v>6.22999858856201</v>
+        <v>6.22999811172485</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G452" t="n">
-        <v>5.88082361221313</v>
+        <v>5.88082408905029</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G474" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G481" t="n">
-        <v>5.56840515136719</v>
+        <v>5.56840467453003</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G495" t="n">
-        <v>5.73380327224731</v>
+        <v>5.73380279541016</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G496" t="n">
-        <v>5.73380327224731</v>
+        <v>5.73380279541016</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G497" t="n">
-        <v>5.73380327224731</v>
+        <v>5.73380279541016</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G501" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G502" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G503" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>5.36625194549561</v>
+        <v>5.36625242233276</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G531" t="n">
-        <v>5.53164958953857</v>
+        <v>5.53165006637573</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G583" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G584" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G586" t="n">
-        <v>5.46732807159424</v>
+        <v>5.4673285484314</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G587" t="n">
-        <v>5.46732807159424</v>
+        <v>5.4673285484314</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>5.75</v>
       </c>
       <c r="G588" t="n">
-        <v>5.28355264663696</v>
+        <v>5.2835521697998</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>5.75</v>
       </c>
       <c r="G589" t="n">
-        <v>5.28355264663696</v>
+        <v>5.2835521697998</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>5.75</v>
       </c>
       <c r="G590" t="n">
-        <v>5.28355264663696</v>
+        <v>5.2835521697998</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G591" t="n">
-        <v>5.46732807159424</v>
+        <v>5.4673285484314</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G592" t="n">
-        <v>5.46732807159424</v>
+        <v>5.4673285484314</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G593" t="n">
-        <v>5.46732807159424</v>
+        <v>5.4673285484314</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G594" t="n">
-        <v>5.46732807159424</v>
+        <v>5.4673285484314</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G595" t="n">
-        <v>5.46732807159424</v>
+        <v>5.4673285484314</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G596" t="n">
-        <v>5.46732807159424</v>
+        <v>5.4673285484314</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>5.75</v>
       </c>
       <c r="G597" t="n">
-        <v>5.28355264663696</v>
+        <v>5.2835521697998</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>5.75</v>
       </c>
       <c r="G598" t="n">
-        <v>5.28355264663696</v>
+        <v>5.2835521697998</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>5.75</v>
       </c>
       <c r="G599" t="n">
-        <v>5.28355264663696</v>
+        <v>5.2835521697998</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -38358,6 +38358,32 @@
         <v>3.79999995231628</v>
       </c>
       <c r="H1461" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1462" t="n">
+        <v>2750</v>
+      </c>
+      <c r="C1462" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D1462" t="n">
+        <v>3.8199999332428</v>
+      </c>
+      <c r="E1462" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F1462" t="n">
+        <v>3.8199999332428</v>
+      </c>
+      <c r="G1462" t="n">
+        <v>3.8199999332428</v>
+      </c>
+      <c r="H1462" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PLN.MI.xlsx
+++ b/data/PLN.MI.xlsx
@@ -34060,8 +34060,31 @@
       <c r="E1465" t="n">
         <v>3.83999991416931</v>
       </c>
-      <c r="F1465"/>
+      <c r="F1465" t="n">
+        <v>3.88000011444092</v>
+      </c>
       <c r="G1465" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1466" t="n">
+        <v>5250</v>
+      </c>
+      <c r="C1466" t="n">
+        <v>3.85999989509583</v>
+      </c>
+      <c r="D1466" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="E1466" t="n">
+        <v>3.83999991416931</v>
+      </c>
+      <c r="F1466"/>
+      <c r="G1466" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PLN.MI.xlsx
+++ b/data/PLN.MI.xlsx
@@ -34083,8 +34083,31 @@
       <c r="E1466" t="n">
         <v>3.83999991416931</v>
       </c>
-      <c r="F1466"/>
+      <c r="F1466" t="n">
+        <v>3.85999989509583</v>
+      </c>
       <c r="G1466" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1467" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1467" t="n">
+        <v>3.79999995231628</v>
+      </c>
+      <c r="D1467" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="E1467" t="n">
+        <v>3.79999995231628</v>
+      </c>
+      <c r="F1467"/>
+      <c r="G1467" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PLN.MI.xlsx
+++ b/data/PLN.MI.xlsx
@@ -34106,8 +34106,31 @@
       <c r="E1467" t="n">
         <v>3.79999995231628</v>
       </c>
-      <c r="F1467"/>
+      <c r="F1467" t="n">
+        <v>3.75999999046326</v>
+      </c>
       <c r="G1467" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1468" t="n">
+        <v>4250</v>
+      </c>
+      <c r="C1468" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="D1468" t="n">
+        <v>3.70000004768372</v>
+      </c>
+      <c r="E1468" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="F1468"/>
+      <c r="G1468" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PLN.MI.xlsx
+++ b/data/PLN.MI.xlsx
@@ -34129,7 +34129,9 @@
       <c r="E1468" t="n">
         <v>3.74000000953674</v>
       </c>
-      <c r="F1468"/>
+      <c r="F1468" t="n">
+        <v>3.72000002861023</v>
+      </c>
       <c r="G1468" t="s">
         <v>7</v>
       </c>

--- a/data/PLN.MI.xlsx
+++ b/data/PLN.MI.xlsx
@@ -34159,6 +34159,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1470">
+      <c r="A1470" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1470" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1470" t="n">
+        <v>3.72000002861023</v>
+      </c>
+      <c r="D1470" t="n">
+        <v>3.72000002861023</v>
+      </c>
+      <c r="E1470" t="n">
+        <v>3.72000002861023</v>
+      </c>
+      <c r="F1470" t="n">
+        <v>3.72000002861023</v>
+      </c>
+      <c r="G1470" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PLN.MI.xlsx
+++ b/data/PLN.MI.xlsx
@@ -514,7 +514,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G5" t="n">
-        <v>4.22684192657471</v>
+        <v>4.22684240341187</v>
       </c>
       <c r="H5" t="n">
         <v>12000</v>
@@ -572,7 +572,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G7" t="n">
-        <v>4.19927549362183</v>
+        <v>4.19927644729614</v>
       </c>
       <c r="H7" t="n">
         <v>11500</v>
@@ -601,7 +601,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G8" t="n">
-        <v>4.15333223342896</v>
+        <v>4.1533317565918</v>
       </c>
       <c r="H8" t="n">
         <v>6500</v>
@@ -688,7 +688,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G11" t="n">
-        <v>4.03387689590454</v>
+        <v>4.03387784957886</v>
       </c>
       <c r="H11" t="n">
         <v>12000</v>
@@ -717,7 +717,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G12" t="n">
-        <v>3.96955585479736</v>
+        <v>3.96955633163452</v>
       </c>
       <c r="H12" t="n">
         <v>26000</v>
@@ -746,7 +746,7 @@
         <v>4.25</v>
       </c>
       <c r="G13" t="n">
-        <v>3.90523433685303</v>
+        <v>3.90523457527161</v>
       </c>
       <c r="H13" t="n">
         <v>19500</v>
@@ -804,7 +804,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G15" t="n">
-        <v>3.89604544639587</v>
+        <v>3.89604592323303</v>
       </c>
       <c r="H15" t="n">
         <v>12500</v>
@@ -833,7 +833,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G16" t="n">
-        <v>3.84091305732727</v>
+        <v>3.84091281890869</v>
       </c>
       <c r="H16" t="n">
         <v>21500</v>
@@ -862,7 +862,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G17" t="n">
-        <v>3.81334662437439</v>
+        <v>3.81334686279297</v>
       </c>
       <c r="H17" t="n">
         <v>19000</v>
@@ -1036,7 +1036,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G23" t="n">
-        <v>3.85010170936584</v>
+        <v>3.850102186203</v>
       </c>
       <c r="H23" t="n">
         <v>32000</v>
@@ -1152,7 +1152,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>4.1717095375061</v>
+        <v>4.17170906066895</v>
       </c>
       <c r="H27" t="n">
         <v>10500</v>
@@ -1181,7 +1181,7 @@
         <v>4.5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.13495397567749</v>
+        <v>4.13495445251465</v>
       </c>
       <c r="H28" t="n">
         <v>28500</v>
@@ -1210,7 +1210,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G29" t="n">
-        <v>4.20846462249756</v>
+        <v>4.2084641456604</v>
       </c>
       <c r="H29" t="n">
         <v>24500</v>
@@ -1268,7 +1268,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G31" t="n">
-        <v>4.15333223342896</v>
+        <v>4.1533317565918</v>
       </c>
       <c r="H31" t="n">
         <v>9000</v>
@@ -1326,7 +1326,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>4.15333223342896</v>
+        <v>4.1533317565918</v>
       </c>
       <c r="H33" t="n">
         <v>2000</v>
@@ -1413,7 +1413,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G36" t="n">
-        <v>4.06144380569458</v>
+        <v>4.06144428253174</v>
       </c>
       <c r="H36" t="n">
         <v>18500</v>
@@ -1442,7 +1442,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G37" t="n">
-        <v>4.05225515365601</v>
+        <v>4.05225467681885</v>
       </c>
       <c r="H37" t="n">
         <v>2000</v>
@@ -1471,7 +1471,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G38" t="n">
-        <v>4.05225515365601</v>
+        <v>4.05225467681885</v>
       </c>
       <c r="H38" t="n">
         <v>11500</v>
@@ -1500,7 +1500,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G39" t="n">
-        <v>4.09819889068604</v>
+        <v>4.09819936752319</v>
       </c>
       <c r="H39" t="n">
         <v>3500</v>
@@ -1529,7 +1529,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>4.09819889068604</v>
+        <v>4.09819936752319</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G41" t="n">
-        <v>4.1717095375061</v>
+        <v>4.17170906066895</v>
       </c>
       <c r="H41" t="n">
         <v>5500</v>
@@ -1587,7 +1587,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>4.1717095375061</v>
+        <v>4.17170906066895</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>4.08901071548462</v>
+        <v>4.08901023864746</v>
       </c>
       <c r="H43" t="n">
         <v>2000</v>
@@ -1645,7 +1645,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>4.08901071548462</v>
+        <v>4.08901023864746</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G45" t="n">
-        <v>4.03387689590454</v>
+        <v>4.03387784957886</v>
       </c>
       <c r="H45" t="n">
         <v>12500</v>
@@ -1732,7 +1732,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G47" t="n">
-        <v>3.99712204933167</v>
+        <v>3.99712228775024</v>
       </c>
       <c r="H47" t="n">
         <v>3000</v>
@@ -1848,7 +1848,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G51" t="n">
-        <v>3.89604544639587</v>
+        <v>3.89604592323303</v>
       </c>
       <c r="H51" t="n">
         <v>31000</v>
@@ -1906,7 +1906,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G53" t="n">
-        <v>3.89604544639587</v>
+        <v>3.89604592323303</v>
       </c>
       <c r="H53" t="n">
         <v>11000</v>
@@ -1935,7 +1935,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G54" t="n">
-        <v>3.85929012298584</v>
+        <v>3.85929036140442</v>
       </c>
       <c r="H54" t="n">
         <v>5000</v>
@@ -1964,7 +1964,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G55" t="n">
-        <v>3.85929012298584</v>
+        <v>3.85929036140442</v>
       </c>
       <c r="H55" t="n">
         <v>6000</v>
@@ -1993,7 +1993,7 @@
         <v>4.25</v>
       </c>
       <c r="G56" t="n">
-        <v>3.90523433685303</v>
+        <v>3.90523457527161</v>
       </c>
       <c r="H56" t="n">
         <v>7500</v>
@@ -2022,7 +2022,7 @@
         <v>4.25</v>
       </c>
       <c r="G57" t="n">
-        <v>3.90523433685303</v>
+        <v>3.90523457527161</v>
       </c>
       <c r="H57" t="n">
         <v>3000</v>
@@ -2109,7 +2109,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G60" t="n">
-        <v>4.03387689590454</v>
+        <v>4.03387784957886</v>
       </c>
       <c r="H60" t="n">
         <v>1000</v>
@@ -2138,7 +2138,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G61" t="n">
-        <v>3.99712204933167</v>
+        <v>3.99712228775024</v>
       </c>
       <c r="H61" t="n">
         <v>7000</v>
@@ -2167,7 +2167,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G62" t="n">
-        <v>3.93280076980591</v>
+        <v>3.93280124664307</v>
       </c>
       <c r="H62" t="n">
         <v>40500</v>
@@ -2225,7 +2225,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G64" t="n">
-        <v>4.05225515365601</v>
+        <v>4.05225467681885</v>
       </c>
       <c r="H64" t="n">
         <v>26000</v>
@@ -2283,7 +2283,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G66" t="n">
-        <v>4.16252040863037</v>
+        <v>4.16252088546753</v>
       </c>
       <c r="H66" t="n">
         <v>21000</v>
@@ -2341,7 +2341,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G68" t="n">
-        <v>4.263596534729</v>
+        <v>4.26359701156616</v>
       </c>
       <c r="H68" t="n">
         <v>12500</v>
@@ -2370,7 +2370,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G69" t="n">
-        <v>4.23603105545044</v>
+        <v>4.23603057861328</v>
       </c>
       <c r="H69" t="n">
         <v>7000</v>
@@ -2428,7 +2428,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G71" t="n">
-        <v>4.48412847518921</v>
+        <v>4.48412799835205</v>
       </c>
       <c r="H71" t="n">
         <v>24000</v>
@@ -2486,7 +2486,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G73" t="n">
-        <v>4.72303628921509</v>
+        <v>4.72303676605225</v>
       </c>
       <c r="H73" t="n">
         <v>3000</v>
@@ -2515,7 +2515,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G74" t="n">
-        <v>4.8149242401123</v>
+        <v>4.81492471694946</v>
       </c>
       <c r="H74" t="n">
         <v>1500</v>
@@ -2573,7 +2573,7 @@
         <v>5</v>
       </c>
       <c r="G76" t="n">
-        <v>4.59439325332642</v>
+        <v>4.59439373016357</v>
       </c>
       <c r="H76" t="n">
         <v>6000</v>
@@ -2602,7 +2602,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G77" t="n">
-        <v>4.52088308334351</v>
+        <v>4.52088356018066</v>
       </c>
       <c r="H77" t="n">
         <v>500</v>
@@ -2631,7 +2631,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G78" t="n">
-        <v>4.70465850830078</v>
+        <v>4.70465898513794</v>
       </c>
       <c r="H78" t="n">
         <v>1500</v>
@@ -2660,7 +2660,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G79" t="n">
-        <v>4.8149242401123</v>
+        <v>4.81492471694946</v>
       </c>
       <c r="H79" t="n">
         <v>11500</v>
@@ -2747,7 +2747,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G82" t="n">
-        <v>4.77816915512085</v>
+        <v>4.77816963195801</v>
       </c>
       <c r="H82" t="n">
         <v>3500</v>
@@ -2805,7 +2805,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>5.18247509002686</v>
+        <v>5.18247556686401</v>
       </c>
       <c r="H84" t="n">
         <v>27000</v>
@@ -2863,7 +2863,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G86" t="n">
-        <v>5.18247509002686</v>
+        <v>5.18247556686401</v>
       </c>
       <c r="H86" t="n">
         <v>18000</v>
@@ -2892,7 +2892,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G87" t="n">
-        <v>5.311119556427</v>
+        <v>5.31111860275269</v>
       </c>
       <c r="H87" t="n">
         <v>23500</v>
@@ -2950,7 +2950,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G89" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H89" t="n">
         <v>78500</v>
@@ -3008,7 +3008,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G91" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H91" t="n">
         <v>34500</v>
@@ -3095,7 +3095,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G94" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H94" t="n">
         <v>29500</v>
@@ -3124,7 +3124,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G95" t="n">
-        <v>6.32188558578491</v>
+        <v>6.32188606262207</v>
       </c>
       <c r="H95" t="n">
         <v>57500</v>
@@ -3153,7 +3153,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>6.45052862167358</v>
+        <v>6.45052814483643</v>
       </c>
       <c r="H96" t="n">
         <v>59500</v>
@@ -3269,7 +3269,7 @@
         <v>6.5</v>
       </c>
       <c r="G100" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H100" t="n">
         <v>8000</v>
@@ -3298,7 +3298,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>5.99108934402466</v>
+        <v>5.9910888671875</v>
       </c>
       <c r="H101" t="n">
         <v>7000</v>
@@ -3327,7 +3327,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G102" t="n">
-        <v>6.10135412216187</v>
+        <v>6.10135459899902</v>
       </c>
       <c r="H102" t="n">
         <v>2000</v>
@@ -3356,7 +3356,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G103" t="n">
-        <v>6.10135412216187</v>
+        <v>6.10135459899902</v>
       </c>
       <c r="H103" t="n">
         <v>2000</v>
@@ -3385,7 +3385,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G104" t="n">
-        <v>6.02784442901611</v>
+        <v>6.02784395217896</v>
       </c>
       <c r="H104" t="n">
         <v>15000</v>
@@ -3414,7 +3414,7 @@
         <v>6.5</v>
       </c>
       <c r="G105" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H105" t="n">
         <v>22000</v>
@@ -3501,7 +3501,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>6.04622173309326</v>
+        <v>6.04622220993042</v>
       </c>
       <c r="H108" t="n">
         <v>12500</v>
@@ -3588,7 +3588,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G111" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H111" t="n">
         <v>3500</v>
@@ -3646,7 +3646,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>5.88082361221313</v>
+        <v>5.88082408905029</v>
       </c>
       <c r="H113" t="n">
         <v>500</v>
@@ -3675,7 +3675,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G114" t="n">
-        <v>5.88082361221313</v>
+        <v>5.88082408905029</v>
       </c>
       <c r="H114" t="n">
         <v>500</v>
@@ -3762,7 +3762,7 @@
         <v>6</v>
       </c>
       <c r="G117" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H117" t="n">
         <v>2500</v>
@@ -3791,7 +3791,7 @@
         <v>6</v>
       </c>
       <c r="G118" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H118" t="n">
         <v>12500</v>
@@ -3820,7 +3820,7 @@
         <v>6</v>
       </c>
       <c r="G119" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H119" t="n">
         <v>500</v>
@@ -3849,7 +3849,7 @@
         <v>6</v>
       </c>
       <c r="G120" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H120" t="n">
         <v>500</v>
@@ -3878,7 +3878,7 @@
         <v>6</v>
       </c>
       <c r="G121" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H121" t="n">
         <v>500</v>
@@ -3936,7 +3936,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G123" t="n">
-        <v>5.23760890960693</v>
+        <v>5.23760843276978</v>
       </c>
       <c r="H123" t="n">
         <v>13000</v>
@@ -3965,7 +3965,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G124" t="n">
-        <v>5.32949638366699</v>
+        <v>5.32949733734131</v>
       </c>
       <c r="H124" t="n">
         <v>500</v>
@@ -4081,7 +4081,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G128" t="n">
-        <v>5.56840515136719</v>
+        <v>5.56840467453003</v>
       </c>
       <c r="H128" t="n">
         <v>10500</v>
@@ -4139,7 +4139,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G130" t="n">
-        <v>5.49489450454712</v>
+        <v>5.49489498138428</v>
       </c>
       <c r="H130" t="n">
         <v>500</v>
@@ -4197,7 +4197,7 @@
         <v>6</v>
       </c>
       <c r="G132" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H132" t="n">
         <v>8500</v>
@@ -4226,7 +4226,7 @@
         <v>6</v>
       </c>
       <c r="G133" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H133" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>5.55002737045288</v>
+        <v>5.55002784729004</v>
       </c>
       <c r="H136" t="n">
         <v>7000</v>
@@ -4342,7 +4342,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>5.55002737045288</v>
+        <v>5.55002784729004</v>
       </c>
       <c r="H137" t="n">
         <v>1000</v>
@@ -4371,7 +4371,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G138" t="n">
-        <v>5.55002737045288</v>
+        <v>5.55002784729004</v>
       </c>
       <c r="H138" t="n">
         <v>3000</v>
@@ -4400,7 +4400,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G139" t="n">
-        <v>5.55002737045288</v>
+        <v>5.55002784729004</v>
       </c>
       <c r="H139" t="n">
         <v>10500</v>
@@ -4429,7 +4429,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H140" t="n">
         <v>2000</v>
@@ -4458,7 +4458,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G141" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G143" t="n">
-        <v>5.88082361221313</v>
+        <v>5.88082408905029</v>
       </c>
       <c r="H143" t="n">
         <v>5500</v>
@@ -4545,7 +4545,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G144" t="n">
-        <v>5.66029262542725</v>
+        <v>5.6602931022644</v>
       </c>
       <c r="H144" t="n">
         <v>2500</v>
@@ -4632,7 +4632,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>5.88082361221313</v>
+        <v>5.88082408905029</v>
       </c>
       <c r="H147" t="n">
         <v>5000</v>
@@ -4661,7 +4661,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G148" t="n">
-        <v>5.88082361221313</v>
+        <v>5.88082408905029</v>
       </c>
       <c r="H148" t="n">
         <v>500</v>
@@ -4690,7 +4690,7 @@
         <v>6.5</v>
       </c>
       <c r="G149" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H149" t="n">
         <v>2000</v>
@@ -4719,7 +4719,7 @@
         <v>6.5</v>
       </c>
       <c r="G150" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H150" t="n">
         <v>1500</v>
@@ -4777,7 +4777,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G152" t="n">
-        <v>6.02784442901611</v>
+        <v>6.02784395217896</v>
       </c>
       <c r="H152" t="n">
         <v>6000</v>
@@ -4835,7 +4835,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G154" t="n">
-        <v>6.24837493896484</v>
+        <v>6.248375415802</v>
       </c>
       <c r="H154" t="n">
         <v>55500</v>
@@ -5183,7 +5183,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>6.56079435348511</v>
+        <v>6.56079387664795</v>
       </c>
       <c r="H166" t="n">
         <v>2500</v>
@@ -5328,7 +5328,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G171" t="n">
-        <v>6.45052862167358</v>
+        <v>6.45052814483643</v>
       </c>
       <c r="H171" t="n">
         <v>1500</v>
@@ -5502,7 +5502,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G177" t="n">
-        <v>7.27751922607422</v>
+        <v>7.27751970291138</v>
       </c>
       <c r="H177" t="n">
         <v>28000</v>
@@ -5531,7 +5531,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G178" t="n">
-        <v>7.20400905609131</v>
+        <v>7.20400953292847</v>
       </c>
       <c r="H178" t="n">
         <v>25000</v>
@@ -5560,7 +5560,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H179" t="n">
         <v>1500</v>
@@ -5589,7 +5589,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5618,7 +5618,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H181" t="n">
         <v>1500</v>
@@ -5647,7 +5647,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G182" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H182" t="n">
         <v>2500</v>
@@ -5676,7 +5676,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G184" t="n">
-        <v>6.94672250747681</v>
+        <v>6.94672298431396</v>
       </c>
       <c r="H184" t="n">
         <v>6000</v>
@@ -5734,7 +5734,7 @@
         <v>7.5</v>
       </c>
       <c r="G185" t="n">
-        <v>6.89159059524536</v>
+        <v>6.8915901184082</v>
       </c>
       <c r="H185" t="n">
         <v>5000</v>
@@ -5763,7 +5763,7 @@
         <v>7.5</v>
       </c>
       <c r="G186" t="n">
-        <v>6.89159059524536</v>
+        <v>6.8915901184082</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G187" t="n">
-        <v>7.05698823928833</v>
+        <v>7.05698871612549</v>
       </c>
       <c r="H187" t="n">
         <v>5500</v>
@@ -5821,7 +5821,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G188" t="n">
-        <v>7.24076414108276</v>
+        <v>7.24076461791992</v>
       </c>
       <c r="H188" t="n">
         <v>1000</v>
@@ -5850,7 +5850,7 @@
         <v>8</v>
       </c>
       <c r="G189" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H189" t="n">
         <v>3500</v>
@@ -5908,7 +5908,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G191" t="n">
-        <v>7.14887666702271</v>
+        <v>7.14887714385986</v>
       </c>
       <c r="H191" t="n">
         <v>1000</v>
@@ -5937,7 +5937,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G192" t="n">
-        <v>7.36940765380859</v>
+        <v>7.36940813064575</v>
       </c>
       <c r="H192" t="n">
         <v>4000</v>
@@ -6024,7 +6024,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G195" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H195" t="n">
         <v>12000</v>
@@ -6227,7 +6227,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G202" t="n">
-        <v>7.70020341873169</v>
+        <v>7.70020437240601</v>
       </c>
       <c r="H202" t="n">
         <v>6500</v>
@@ -6256,7 +6256,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G203" t="n">
-        <v>7.70020341873169</v>
+        <v>7.70020437240601</v>
       </c>
       <c r="H203" t="n">
         <v>3000</v>
@@ -6285,7 +6285,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G204" t="n">
-        <v>7.79209089279175</v>
+        <v>7.79209184646606</v>
       </c>
       <c r="H204" t="n">
         <v>6500</v>
@@ -6314,7 +6314,7 @@
         <v>8.5</v>
       </c>
       <c r="G205" t="n">
-        <v>7.81046867370605</v>
+        <v>7.81046915054321</v>
       </c>
       <c r="H205" t="n">
         <v>6500</v>
@@ -6343,7 +6343,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G206" t="n">
-        <v>8.12288761138916</v>
+        <v>8.12288856506348</v>
       </c>
       <c r="H206" t="n">
         <v>16500</v>
@@ -6372,7 +6372,7 @@
         <v>9</v>
       </c>
       <c r="G207" t="n">
-        <v>8.26990795135498</v>
+        <v>8.2699089050293</v>
       </c>
       <c r="H207" t="n">
         <v>3000</v>
@@ -6459,7 +6459,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G210" t="n">
-        <v>8.01262283325195</v>
+        <v>8.01262378692627</v>
       </c>
       <c r="H210" t="n">
         <v>3500</v>
@@ -6488,7 +6488,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G211" t="n">
-        <v>8.15964317321777</v>
+        <v>8.15964221954346</v>
       </c>
       <c r="H211" t="n">
         <v>8000</v>
@@ -6517,7 +6517,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G212" t="n">
-        <v>8.12288761138916</v>
+        <v>8.12288856506348</v>
       </c>
       <c r="H212" t="n">
         <v>500</v>
@@ -6604,7 +6604,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G215" t="n">
-        <v>8.41692924499512</v>
+        <v>8.4169282913208</v>
       </c>
       <c r="H215" t="n">
         <v>1000</v>
@@ -6633,7 +6633,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G216" t="n">
-        <v>8.54557228088379</v>
+        <v>8.54557132720947</v>
       </c>
       <c r="H216" t="n">
         <v>2500</v>
@@ -6923,7 +6923,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G226" t="n">
-        <v>8.76610374450684</v>
+        <v>8.76610279083252</v>
       </c>
       <c r="H226" t="n">
         <v>500</v>
@@ -6952,7 +6952,7 @@
         <v>9.5</v>
       </c>
       <c r="G227" t="n">
-        <v>8.72934722900391</v>
+        <v>8.72934818267822</v>
       </c>
       <c r="H227" t="n">
         <v>4500</v>
@@ -6981,7 +6981,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G228" t="n">
-        <v>8.63746070861816</v>
+        <v>8.63745975494385</v>
       </c>
       <c r="H228" t="n">
         <v>20000</v>
@@ -7010,7 +7010,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G229" t="n">
-        <v>8.63746070861816</v>
+        <v>8.63745975494385</v>
       </c>
       <c r="H229" t="n">
         <v>12500</v>
@@ -7039,7 +7039,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G230" t="n">
-        <v>8.63746070861816</v>
+        <v>8.63745975494385</v>
       </c>
       <c r="H230" t="n">
         <v>7000</v>
@@ -7126,7 +7126,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G233" t="n">
-        <v>8.63746070861816</v>
+        <v>8.63745975494385</v>
       </c>
       <c r="H233" t="n">
         <v>11000</v>
@@ -7155,7 +7155,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G234" t="n">
-        <v>8.54557228088379</v>
+        <v>8.54557132720947</v>
       </c>
       <c r="H234" t="n">
         <v>4500</v>
@@ -7184,7 +7184,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>8.54557228088379</v>
+        <v>8.54557132720947</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G236" t="n">
-        <v>8.14126491546631</v>
+        <v>8.14126586914062</v>
       </c>
       <c r="H236" t="n">
         <v>6500</v>
@@ -7300,7 +7300,7 @@
         <v>9</v>
       </c>
       <c r="G239" t="n">
-        <v>8.26990795135498</v>
+        <v>8.2699089050293</v>
       </c>
       <c r="H239" t="n">
         <v>3000</v>
@@ -7532,7 +7532,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>8.54557228088379</v>
+        <v>8.54557132720947</v>
       </c>
       <c r="H247" t="n">
         <v>7500</v>
@@ -7561,7 +7561,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G248" t="n">
-        <v>8.63746070861816</v>
+        <v>8.63745975494385</v>
       </c>
       <c r="H248" t="n">
         <v>7500</v>
@@ -7590,7 +7590,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G249" t="n">
-        <v>8.45368385314941</v>
+        <v>8.45368480682373</v>
       </c>
       <c r="H249" t="n">
         <v>1000</v>
@@ -7619,7 +7619,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G250" t="n">
-        <v>8.49043941497803</v>
+        <v>8.49043846130371</v>
       </c>
       <c r="H250" t="n">
         <v>500</v>
@@ -7648,7 +7648,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G251" t="n">
-        <v>8.54557228088379</v>
+        <v>8.54557132720947</v>
       </c>
       <c r="H251" t="n">
         <v>6000</v>
@@ -7677,7 +7677,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G252" t="n">
-        <v>8.54557228088379</v>
+        <v>8.54557132720947</v>
       </c>
       <c r="H252" t="n">
         <v>500</v>
@@ -7793,7 +7793,7 @@
         <v>9.5</v>
       </c>
       <c r="G256" t="n">
-        <v>8.72934722900391</v>
+        <v>8.72934818267822</v>
       </c>
       <c r="H256" t="n">
         <v>500</v>
@@ -7822,7 +7822,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G257" t="n">
-        <v>8.87636852264404</v>
+        <v>8.87636756896973</v>
       </c>
       <c r="H257" t="n">
         <v>4000</v>
@@ -7851,7 +7851,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G258" t="n">
-        <v>9.09689998626709</v>
+        <v>9.09689903259277</v>
       </c>
       <c r="H258" t="n">
         <v>1500</v>
@@ -7880,7 +7880,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G259" t="n">
-        <v>9.09689998626709</v>
+        <v>9.09689903259277</v>
       </c>
       <c r="H259" t="n">
         <v>4500</v>
@@ -7909,7 +7909,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G260" t="n">
-        <v>9.09689998626709</v>
+        <v>9.09689903259277</v>
       </c>
       <c r="H260" t="n">
         <v>500</v>
@@ -7938,7 +7938,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G261" t="n">
-        <v>8.98663330078125</v>
+        <v>8.98663425445557</v>
       </c>
       <c r="H261" t="n">
         <v>1000</v>
@@ -7967,7 +7967,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G262" t="n">
-        <v>8.98663330078125</v>
+        <v>8.98663425445557</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>10</v>
       </c>
       <c r="G263" t="n">
-        <v>9.18878650665283</v>
+        <v>9.18878746032715</v>
       </c>
       <c r="H263" t="n">
         <v>500</v>
@@ -8083,7 +8083,7 @@
         <v>9.5</v>
       </c>
       <c r="G266" t="n">
-        <v>8.72934722900391</v>
+        <v>8.72934818267822</v>
       </c>
       <c r="H266" t="n">
         <v>3000</v>
@@ -8228,7 +8228,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G271" t="n">
-        <v>8.39855098724365</v>
+        <v>8.39855289459229</v>
       </c>
       <c r="H271" t="n">
         <v>5000</v>
@@ -8315,7 +8315,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>7.5348048210144</v>
+        <v>7.53480577468872</v>
       </c>
       <c r="H274" t="n">
         <v>3000</v>
@@ -8431,7 +8431,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G278" t="n">
-        <v>7.66344833374023</v>
+        <v>7.66344881057739</v>
       </c>
       <c r="H278" t="n">
         <v>3000</v>
@@ -8489,7 +8489,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G280" t="n">
-        <v>7.42453956604004</v>
+        <v>7.4245400428772</v>
       </c>
       <c r="H280" t="n">
         <v>3500</v>
@@ -8518,7 +8518,7 @@
         <v>8</v>
       </c>
       <c r="G281" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H281" t="n">
         <v>3000</v>
@@ -8547,7 +8547,7 @@
         <v>8</v>
       </c>
       <c r="G282" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>8</v>
       </c>
       <c r="G283" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H283" t="n">
         <v>7500</v>
@@ -8692,7 +8692,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G287" t="n">
-        <v>7.27751922607422</v>
+        <v>7.27751970291138</v>
       </c>
       <c r="H287" t="n">
         <v>3500</v>
@@ -8750,7 +8750,7 @@
         <v>8</v>
       </c>
       <c r="G289" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H289" t="n">
         <v>1500</v>
@@ -8779,7 +8779,7 @@
         <v>8</v>
       </c>
       <c r="G290" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H290" t="n">
         <v>9000</v>
@@ -8808,7 +8808,7 @@
         <v>8</v>
       </c>
       <c r="G291" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H291" t="n">
         <v>1500</v>
@@ -8837,7 +8837,7 @@
         <v>8</v>
       </c>
       <c r="G292" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H292" t="n">
         <v>3000</v>
@@ -8953,7 +8953,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G296" t="n">
-        <v>6.65268135070801</v>
+        <v>6.65268182754517</v>
       </c>
       <c r="H296" t="n">
         <v>10500</v>
@@ -8982,7 +8982,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>6.79970264434814</v>
+        <v>6.79970216751099</v>
       </c>
       <c r="H297" t="n">
         <v>3500</v>
@@ -9011,7 +9011,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>6.98347759246826</v>
+        <v>6.98347854614258</v>
       </c>
       <c r="H298" t="n">
         <v>7000</v>
@@ -9040,7 +9040,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>6.98347759246826</v>
+        <v>6.98347854614258</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>6.98347759246826</v>
+        <v>6.98347854614258</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G301" t="n">
-        <v>6.98347759246826</v>
+        <v>6.98347854614258</v>
       </c>
       <c r="H301" t="n">
         <v>18500</v>
@@ -9127,7 +9127,7 @@
         <v>7.5</v>
       </c>
       <c r="G302" t="n">
-        <v>6.89159059524536</v>
+        <v>6.8915901184082</v>
       </c>
       <c r="H302" t="n">
         <v>2000</v>
@@ -9156,7 +9156,7 @@
         <v>7.5</v>
       </c>
       <c r="G303" t="n">
-        <v>6.89159059524536</v>
+        <v>6.8915901184082</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9185,7 +9185,7 @@
         <v>7.5</v>
       </c>
       <c r="G304" t="n">
-        <v>6.89159059524536</v>
+        <v>6.8915901184082</v>
       </c>
       <c r="H304" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>7.5</v>
       </c>
       <c r="G305" t="n">
-        <v>6.89159059524536</v>
+        <v>6.8915901184082</v>
       </c>
       <c r="H305" t="n">
         <v>15500</v>
@@ -9272,7 +9272,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G307" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H307" t="n">
         <v>500</v>
@@ -9301,7 +9301,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G308" t="n">
-        <v>6.72619247436523</v>
+        <v>6.72619199752808</v>
       </c>
       <c r="H308" t="n">
         <v>5000</v>
@@ -9330,7 +9330,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G309" t="n">
-        <v>7.05698823928833</v>
+        <v>7.05698871612549</v>
       </c>
       <c r="H309" t="n">
         <v>1000</v>
@@ -9417,7 +9417,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G312" t="n">
-        <v>7.5348048210144</v>
+        <v>7.53480577468872</v>
       </c>
       <c r="H312" t="n">
         <v>2000</v>
@@ -9620,7 +9620,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G319" t="n">
-        <v>7.46129465103149</v>
+        <v>7.46129512786865</v>
       </c>
       <c r="H319" t="n">
         <v>500</v>
@@ -9649,7 +9649,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G320" t="n">
-        <v>7.46129465103149</v>
+        <v>7.46129512786865</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G321" t="n">
-        <v>7.22238683700562</v>
+        <v>7.22238636016846</v>
       </c>
       <c r="H321" t="n">
         <v>500</v>
@@ -9707,7 +9707,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G322" t="n">
-        <v>7.22238683700562</v>
+        <v>7.22238636016846</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G323" t="n">
-        <v>7.22238683700562</v>
+        <v>7.22238636016846</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G324" t="n">
-        <v>7.22238683700562</v>
+        <v>7.22238636016846</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G328" t="n">
-        <v>6.98347759246826</v>
+        <v>6.98347854614258</v>
       </c>
       <c r="H328" t="n">
         <v>1000</v>
@@ -9910,7 +9910,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G329" t="n">
-        <v>6.79970264434814</v>
+        <v>6.79970216751099</v>
       </c>
       <c r="H329" t="n">
         <v>1000</v>
@@ -9939,7 +9939,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G330" t="n">
-        <v>7.02023315429688</v>
+        <v>7.02023363113403</v>
       </c>
       <c r="H330" t="n">
         <v>500</v>
@@ -9968,7 +9968,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G331" t="n">
-        <v>7.02023315429688</v>
+        <v>7.02023363113403</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G332" t="n">
-        <v>7.02023315429688</v>
+        <v>7.02023363113403</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G333" t="n">
-        <v>7.02023315429688</v>
+        <v>7.02023363113403</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10055,7 +10055,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G334" t="n">
-        <v>6.94672250747681</v>
+        <v>6.94672298431396</v>
       </c>
       <c r="H334" t="n">
         <v>500</v>
@@ -10084,7 +10084,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>6.94672250747681</v>
+        <v>6.94672298431396</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>6.94672250747681</v>
+        <v>6.94672298431396</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>6.79970264434814</v>
+        <v>6.79970216751099</v>
       </c>
       <c r="H337" t="n">
         <v>500</v>
@@ -10171,7 +10171,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>6.79970264434814</v>
+        <v>6.79970216751099</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10200,7 +10200,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G339" t="n">
-        <v>6.37701797485352</v>
+        <v>6.37701845169067</v>
       </c>
       <c r="H339" t="n">
         <v>4500</v>
@@ -10229,7 +10229,7 @@
         <v>6.5</v>
       </c>
       <c r="G340" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H340" t="n">
         <v>32500</v>
@@ -10316,7 +10316,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G343" t="n">
-        <v>6.02784442901611</v>
+        <v>6.02784395217896</v>
       </c>
       <c r="H343" t="n">
         <v>9500</v>
@@ -10403,7 +10403,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G346" t="n">
-        <v>6.04622173309326</v>
+        <v>6.04622220993042</v>
       </c>
       <c r="H346" t="n">
         <v>1000</v>
@@ -10432,7 +10432,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G347" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H347" t="n">
         <v>1000</v>
@@ -10461,7 +10461,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G348" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -10490,7 +10490,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G349" t="n">
-        <v>6.21161985397339</v>
+        <v>6.21162080764771</v>
       </c>
       <c r="H349" t="n">
         <v>1500</v>
@@ -10519,7 +10519,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G350" t="n">
-        <v>6.04622173309326</v>
+        <v>6.04622220993042</v>
       </c>
       <c r="H350" t="n">
         <v>1000</v>
@@ -10548,7 +10548,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>5.99108934402466</v>
+        <v>5.9910888671875</v>
       </c>
       <c r="H351" t="n">
         <v>14500</v>
@@ -10577,7 +10577,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G352" t="n">
-        <v>5.99108934402466</v>
+        <v>5.9910888671875</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -10606,7 +10606,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G353" t="n">
-        <v>5.91757869720459</v>
+        <v>5.91757917404175</v>
       </c>
       <c r="H353" t="n">
         <v>3000</v>
@@ -10635,7 +10635,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G354" t="n">
-        <v>5.91757869720459</v>
+        <v>5.91757917404175</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G355" t="n">
-        <v>6.24837493896484</v>
+        <v>6.248375415802</v>
       </c>
       <c r="H355" t="n">
         <v>4000</v>
@@ -10693,7 +10693,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>6.24837493896484</v>
+        <v>6.248375415802</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -10722,7 +10722,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G357" t="n">
-        <v>6.24837493896484</v>
+        <v>6.248375415802</v>
       </c>
       <c r="H357" t="n">
         <v>500</v>
@@ -10751,7 +10751,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G358" t="n">
-        <v>6.24837493896484</v>
+        <v>6.248375415802</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -10809,7 +10809,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G360" t="n">
-        <v>6.68943691253662</v>
+        <v>6.68943738937378</v>
       </c>
       <c r="H360" t="n">
         <v>2000</v>
@@ -10867,7 +10867,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G362" t="n">
-        <v>6.68943691253662</v>
+        <v>6.68943738937378</v>
       </c>
       <c r="H362" t="n">
         <v>5500</v>
@@ -10896,7 +10896,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G363" t="n">
-        <v>6.68943691253662</v>
+        <v>6.68943738937378</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10925,7 +10925,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G364" t="n">
-        <v>6.65268135070801</v>
+        <v>6.65268182754517</v>
       </c>
       <c r="H364" t="n">
         <v>5000</v>
@@ -11128,7 +11128,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G371" t="n">
-        <v>6.21161985397339</v>
+        <v>6.21162080764771</v>
       </c>
       <c r="H371" t="n">
         <v>4000</v>
@@ -11157,7 +11157,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G372" t="n">
-        <v>6.21161985397339</v>
+        <v>6.21162080764771</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G373" t="n">
-        <v>6.21161985397339</v>
+        <v>6.21162080764771</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G374" t="n">
-        <v>6.21161985397339</v>
+        <v>6.21162080764771</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G376" t="n">
-        <v>6.04622173309326</v>
+        <v>6.04622220993042</v>
       </c>
       <c r="H376" t="n">
         <v>3000</v>
@@ -11302,7 +11302,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>6.04622173309326</v>
+        <v>6.04622220993042</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>6.5</v>
       </c>
       <c r="G378" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H378" t="n">
         <v>500</v>
@@ -11476,7 +11476,7 @@
         <v>6.5</v>
       </c>
       <c r="G383" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H383" t="n">
         <v>500</v>
@@ -11505,7 +11505,7 @@
         <v>6.5</v>
       </c>
       <c r="G384" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>6.5</v>
       </c>
       <c r="G385" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -11563,7 +11563,7 @@
         <v>6.5</v>
       </c>
       <c r="G386" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -11621,7 +11621,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G388" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H388" t="n">
         <v>1000</v>
@@ -11824,7 +11824,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G395" t="n">
-        <v>5.80731391906738</v>
+        <v>5.80731344223022</v>
       </c>
       <c r="H395" t="n">
         <v>1500</v>
@@ -11853,7 +11853,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G396" t="n">
-        <v>5.80731391906738</v>
+        <v>5.80731344223022</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G397" t="n">
-        <v>5.80731391906738</v>
+        <v>5.80731344223022</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -11911,7 +11911,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G398" t="n">
-        <v>5.91757869720459</v>
+        <v>5.91757917404175</v>
       </c>
       <c r="H398" t="n">
         <v>500</v>
@@ -11940,7 +11940,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G399" t="n">
-        <v>5.91757869720459</v>
+        <v>5.91757917404175</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -11969,7 +11969,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G400" t="n">
-        <v>6.10135412216187</v>
+        <v>6.10135459899902</v>
       </c>
       <c r="H400" t="n">
         <v>500</v>
@@ -12085,7 +12085,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G404" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H404" t="n">
         <v>1000</v>
@@ -12114,7 +12114,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G405" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -12143,7 +12143,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G406" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G407" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -12201,7 +12201,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G408" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G413" t="n">
-        <v>6.45052862167358</v>
+        <v>6.45052814483643</v>
       </c>
       <c r="H413" t="n">
         <v>5500</v>
@@ -12375,7 +12375,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G414" t="n">
-        <v>6.45052862167358</v>
+        <v>6.45052814483643</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G431" t="n">
-        <v>6.21161985397339</v>
+        <v>6.21162080764771</v>
       </c>
       <c r="H431" t="n">
         <v>1000</v>
@@ -13158,7 +13158,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G441" t="n">
-        <v>6.32188558578491</v>
+        <v>6.32188606262207</v>
       </c>
       <c r="H441" t="n">
         <v>500</v>
@@ -13187,7 +13187,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G442" t="n">
-        <v>6.32188558578491</v>
+        <v>6.32188606262207</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G443" t="n">
-        <v>6.32188558578491</v>
+        <v>6.32188606262207</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G444" t="n">
-        <v>6.32188558578491</v>
+        <v>6.32188606262207</v>
       </c>
       <c r="H444" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G448" t="n">
-        <v>6.02784442901611</v>
+        <v>6.02784395217896</v>
       </c>
       <c r="H448" t="n">
         <v>1000</v>
@@ -13419,7 +13419,7 @@
         <v>6.5</v>
       </c>
       <c r="G450" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H450" t="n">
         <v>500</v>
@@ -13448,7 +13448,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G451" t="n">
-        <v>6.00946712493896</v>
+        <v>6.00946664810181</v>
       </c>
       <c r="H451" t="n">
         <v>500</v>
@@ -13477,7 +13477,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G452" t="n">
-        <v>5.88082361221313</v>
+        <v>5.88082408905029</v>
       </c>
       <c r="H452" t="n">
         <v>1000</v>
@@ -14115,7 +14115,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G474" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H474" t="n">
         <v>500</v>
@@ -14144,7 +14144,7 @@
         <v>6</v>
       </c>
       <c r="G475" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H475" t="n">
         <v>500</v>
@@ -14173,7 +14173,7 @@
         <v>6</v>
       </c>
       <c r="G476" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H476" t="n">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>6</v>
       </c>
       <c r="G477" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H477" t="n">
         <v>0</v>
@@ -14231,7 +14231,7 @@
         <v>6</v>
       </c>
       <c r="G478" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H478" t="n">
         <v>0</v>
@@ -14289,7 +14289,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G480" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H480" t="n">
         <v>1500</v>
@@ -14318,7 +14318,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G481" t="n">
-        <v>5.56840515136719</v>
+        <v>5.56840467453003</v>
       </c>
       <c r="H481" t="n">
         <v>1500</v>
@@ -14550,7 +14550,7 @@
         <v>6</v>
       </c>
       <c r="G489" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H489" t="n">
         <v>1500</v>
@@ -14579,7 +14579,7 @@
         <v>6</v>
       </c>
       <c r="G490" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H490" t="n">
         <v>3500</v>
@@ -14608,7 +14608,7 @@
         <v>6</v>
       </c>
       <c r="G491" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H491" t="n">
         <v>0</v>
@@ -14637,7 +14637,7 @@
         <v>6</v>
       </c>
       <c r="G492" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H492" t="n">
         <v>0</v>
@@ -14666,7 +14666,7 @@
         <v>6</v>
       </c>
       <c r="G493" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H493" t="n">
         <v>500</v>
@@ -14695,7 +14695,7 @@
         <v>6</v>
       </c>
       <c r="G494" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H494" t="n">
         <v>0</v>
@@ -14898,7 +14898,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G501" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H501" t="n">
         <v>500</v>
@@ -14927,7 +14927,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G502" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H502" t="n">
         <v>0</v>
@@ -14956,7 +14956,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G503" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H503" t="n">
         <v>0</v>
@@ -14985,7 +14985,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15014,7 +15014,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>5.36625194549561</v>
+        <v>5.36625242233276</v>
       </c>
       <c r="H505" t="n">
         <v>1000</v>
@@ -15043,7 +15043,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G506" t="n">
-        <v>5.32949638366699</v>
+        <v>5.32949733734131</v>
       </c>
       <c r="H506" t="n">
         <v>1000</v>
@@ -15072,7 +15072,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>5.32949638366699</v>
+        <v>5.32949733734131</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -15101,7 +15101,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>5.55002737045288</v>
+        <v>5.55002784729004</v>
       </c>
       <c r="H508" t="n">
         <v>500</v>
@@ -15275,7 +15275,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G514" t="n">
-        <v>5.55002737045288</v>
+        <v>5.55002784729004</v>
       </c>
       <c r="H514" t="n">
         <v>1000</v>
@@ -15304,7 +15304,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G515" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H515" t="n">
         <v>1500</v>
@@ -15333,7 +15333,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G516" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H516" t="n">
         <v>0</v>
@@ -15362,7 +15362,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G517" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H517" t="n">
         <v>0</v>
@@ -15391,7 +15391,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G518" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15420,7 +15420,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G519" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H519" t="n">
         <v>0</v>
@@ -15449,7 +15449,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G520" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H520" t="n">
         <v>0</v>
@@ -15478,7 +15478,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G521" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H521" t="n">
         <v>1000</v>
@@ -15594,7 +15594,7 @@
         <v>6</v>
       </c>
       <c r="G525" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H525" t="n">
         <v>500</v>
@@ -15623,7 +15623,7 @@
         <v>6</v>
       </c>
       <c r="G526" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H526" t="n">
         <v>0</v>
@@ -15652,7 +15652,7 @@
         <v>6</v>
       </c>
       <c r="G527" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H527" t="n">
         <v>26000</v>
@@ -15681,7 +15681,7 @@
         <v>6</v>
       </c>
       <c r="G528" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H528" t="n">
         <v>0</v>
@@ -15710,7 +15710,7 @@
         <v>6</v>
       </c>
       <c r="G529" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H529" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>6</v>
       </c>
       <c r="G530" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H530" t="n">
         <v>0</v>
@@ -15797,7 +15797,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G532" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H532" t="n">
         <v>500</v>
@@ -15826,7 +15826,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G533" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H533" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G534" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H534" t="n">
         <v>0</v>
@@ -15942,7 +15942,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G537" t="n">
-        <v>5.66029262542725</v>
+        <v>5.6602931022644</v>
       </c>
       <c r="H537" t="n">
         <v>5000</v>
@@ -16261,7 +16261,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G548" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H548" t="n">
         <v>1500</v>
@@ -16290,7 +16290,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G549" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H549" t="n">
         <v>0</v>
@@ -16319,7 +16319,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G550" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -16348,7 +16348,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G551" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H551" t="n">
         <v>0</v>
@@ -16377,7 +16377,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G552" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H552" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G553" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G563" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H563" t="n">
         <v>500</v>
@@ -16725,7 +16725,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G564" t="n">
-        <v>5.27436399459839</v>
+        <v>5.27436351776123</v>
       </c>
       <c r="H564" t="n">
         <v>2500</v>
@@ -17015,7 +17015,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G574" t="n">
-        <v>5.27436399459839</v>
+        <v>5.27436351776123</v>
       </c>
       <c r="H574" t="n">
         <v>4500</v>
@@ -17044,7 +17044,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G575" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H575" t="n">
         <v>500</v>
@@ -17073,7 +17073,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G576" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H576" t="n">
         <v>0</v>
@@ -17102,7 +17102,7 @@
         <v>6</v>
       </c>
       <c r="G577" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H577" t="n">
         <v>13500</v>
@@ -17131,7 +17131,7 @@
         <v>6</v>
       </c>
       <c r="G578" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H578" t="n">
         <v>0</v>
@@ -17160,7 +17160,7 @@
         <v>6</v>
       </c>
       <c r="G579" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H579" t="n">
         <v>0</v>
@@ -17247,7 +17247,7 @@
         <v>6</v>
       </c>
       <c r="G582" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H582" t="n">
         <v>500</v>
@@ -17276,7 +17276,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G583" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H583" t="n">
         <v>1500</v>
@@ -17305,7 +17305,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G584" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H584" t="n">
         <v>0</v>
@@ -17421,7 +17421,7 @@
         <v>5.75</v>
       </c>
       <c r="G588" t="n">
-        <v>5.28355264663696</v>
+        <v>5.2835521697998</v>
       </c>
       <c r="H588" t="n">
         <v>2000</v>
@@ -17450,7 +17450,7 @@
         <v>5.75</v>
       </c>
       <c r="G589" t="n">
-        <v>5.28355264663696</v>
+        <v>5.2835521697998</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -17479,7 +17479,7 @@
         <v>5.75</v>
       </c>
       <c r="G590" t="n">
-        <v>5.28355264663696</v>
+        <v>5.2835521697998</v>
       </c>
       <c r="H590" t="n">
         <v>0</v>
@@ -17682,7 +17682,7 @@
         <v>5.75</v>
       </c>
       <c r="G597" t="n">
-        <v>5.28355264663696</v>
+        <v>5.2835521697998</v>
       </c>
       <c r="H597" t="n">
         <v>1000</v>
@@ -17711,7 +17711,7 @@
         <v>5.75</v>
       </c>
       <c r="G598" t="n">
-        <v>5.28355264663696</v>
+        <v>5.2835521697998</v>
       </c>
       <c r="H598" t="n">
         <v>0</v>
@@ -17740,7 +17740,7 @@
         <v>5.75</v>
       </c>
       <c r="G599" t="n">
-        <v>5.28355264663696</v>
+        <v>5.2835521697998</v>
       </c>
       <c r="H599" t="n">
         <v>0</v>
@@ -17827,7 +17827,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G602" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H602" t="n">
         <v>500</v>
@@ -17856,7 +17856,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G603" t="n">
-        <v>5.25564622879028</v>
+        <v>5.25564670562744</v>
       </c>
       <c r="H603" t="n">
         <v>500</v>
@@ -17885,7 +17885,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G604" t="n">
-        <v>5.25564622879028</v>
+        <v>5.25564670562744</v>
       </c>
       <c r="H604" t="n">
         <v>0</v>
@@ -17914,7 +17914,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G605" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H605" t="n">
         <v>3000</v>
@@ -17943,7 +17943,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H606" t="n">
         <v>0</v>
@@ -17972,7 +17972,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G607" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H607" t="n">
         <v>0</v>
@@ -18001,7 +18001,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G608" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H608" t="n">
         <v>2000</v>
@@ -18030,7 +18030,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G609" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H609" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G616" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H616" t="n">
         <v>500</v>
@@ -18262,7 +18262,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G617" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H617" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G618" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -18320,7 +18320,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G619" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -18349,7 +18349,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G620" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H620" t="n">
         <v>0</v>
@@ -18378,7 +18378,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G621" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H621" t="n">
         <v>1000</v>
@@ -18407,7 +18407,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G622" t="n">
-        <v>5.53470706939697</v>
+        <v>5.53470754623413</v>
       </c>
       <c r="H622" t="n">
         <v>3500</v>
@@ -18436,7 +18436,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G623" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H623" t="n">
         <v>500</v>
@@ -18523,7 +18523,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G626" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H626" t="n">
         <v>2500</v>
@@ -18552,7 +18552,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G627" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H627" t="n">
         <v>0</v>
@@ -18581,7 +18581,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G628" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H628" t="n">
         <v>5500</v>
@@ -18610,7 +18610,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G629" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H629" t="n">
         <v>2000</v>
@@ -18639,7 +18639,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G630" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H630" t="n">
         <v>500</v>
@@ -18668,7 +18668,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G631" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H631" t="n">
         <v>1000</v>
@@ -18697,7 +18697,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G632" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H632" t="n">
         <v>500</v>
@@ -18726,7 +18726,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G633" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H633" t="n">
         <v>0</v>
@@ -18755,7 +18755,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G634" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H634" t="n">
         <v>0</v>
@@ -18784,7 +18784,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G635" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H635" t="n">
         <v>0</v>
@@ -18871,7 +18871,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G638" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H638" t="n">
         <v>5500</v>
@@ -18900,7 +18900,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G639" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H639" t="n">
         <v>3250</v>
@@ -18929,7 +18929,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G640" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H640" t="n">
         <v>0</v>
@@ -18958,7 +18958,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G641" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H641" t="n">
         <v>0</v>
@@ -18987,7 +18987,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G642" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H642" t="n">
         <v>0</v>
@@ -19016,7 +19016,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G643" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H643" t="n">
         <v>0</v>
@@ -19045,7 +19045,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G644" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H644" t="n">
         <v>2000</v>
@@ -19074,7 +19074,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G645" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H645" t="n">
         <v>0</v>
@@ -19103,7 +19103,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H646" t="n">
         <v>0</v>
@@ -19132,7 +19132,7 @@
         <v>5.25</v>
       </c>
       <c r="G647" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H647" t="n">
         <v>10000</v>
@@ -19161,7 +19161,7 @@
         <v>5.25</v>
       </c>
       <c r="G648" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H648" t="n">
         <v>12500</v>
@@ -19190,7 +19190,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G649" t="n">
-        <v>4.5021824836731</v>
+        <v>4.50218200683594</v>
       </c>
       <c r="H649" t="n">
         <v>67000</v>
@@ -19219,7 +19219,7 @@
         <v>5</v>
       </c>
       <c r="G650" t="n">
-        <v>4.65101432800293</v>
+        <v>4.65101480484009</v>
       </c>
       <c r="H650" t="n">
         <v>8500</v>
@@ -19248,7 +19248,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G651" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H651" t="n">
         <v>9500</v>
@@ -19364,7 +19364,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H655" t="n">
         <v>1500</v>
@@ -19393,7 +19393,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G656" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H656" t="n">
         <v>0</v>
@@ -19451,7 +19451,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G658" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H658" t="n">
         <v>500</v>
@@ -19480,7 +19480,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G659" t="n">
-        <v>5.25564622879028</v>
+        <v>5.25564670562744</v>
       </c>
       <c r="H659" t="n">
         <v>2250</v>
@@ -19509,7 +19509,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G660" t="n">
-        <v>5.25564622879028</v>
+        <v>5.25564670562744</v>
       </c>
       <c r="H660" t="n">
         <v>1500</v>
@@ -19538,7 +19538,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G661" t="n">
-        <v>5.25564622879028</v>
+        <v>5.25564670562744</v>
       </c>
       <c r="H661" t="n">
         <v>0</v>
@@ -19567,7 +19567,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G662" t="n">
-        <v>5.25564622879028</v>
+        <v>5.25564670562744</v>
       </c>
       <c r="H662" t="n">
         <v>0</v>
@@ -19654,7 +19654,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G665" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H665" t="n">
         <v>500</v>
@@ -19712,7 +19712,7 @@
         <v>5.25</v>
       </c>
       <c r="G667" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H667" t="n">
         <v>7250</v>
@@ -19770,7 +19770,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G669" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H669" t="n">
         <v>500</v>
@@ -19799,7 +19799,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H670" t="n">
         <v>0</v>
@@ -19828,7 +19828,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H671" t="n">
         <v>0</v>
@@ -20002,7 +20002,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H677" t="n">
         <v>19750</v>
@@ -20031,7 +20031,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H678" t="n">
         <v>1750</v>
@@ -20350,7 +20350,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G689" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H689" t="n">
         <v>1250</v>
@@ -20379,7 +20379,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G690" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H690" t="n">
         <v>3000</v>
@@ -20437,7 +20437,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G692" t="n">
-        <v>5.25564622879028</v>
+        <v>5.25564670562744</v>
       </c>
       <c r="H692" t="n">
         <v>500</v>
@@ -20785,7 +20785,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G704" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H704" t="n">
         <v>41750</v>
@@ -20814,7 +20814,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G705" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H705" t="n">
         <v>7500</v>
@@ -20843,7 +20843,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G706" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H706" t="n">
         <v>2500</v>
@@ -20872,7 +20872,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G707" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H707" t="n">
         <v>7500</v>
@@ -20901,7 +20901,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G708" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H708" t="n">
         <v>2250</v>
@@ -20930,7 +20930,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G709" t="n">
-        <v>4.52078628540039</v>
+        <v>4.52078580856323</v>
       </c>
       <c r="H709" t="n">
         <v>36250</v>
@@ -21075,7 +21075,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G714" t="n">
-        <v>4.55799436569214</v>
+        <v>4.5579948425293</v>
       </c>
       <c r="H714" t="n">
         <v>4500</v>
@@ -21133,7 +21133,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G716" t="n">
-        <v>4.46497440338135</v>
+        <v>4.46497392654419</v>
       </c>
       <c r="H716" t="n">
         <v>22500</v>
@@ -21162,7 +21162,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G717" t="n">
-        <v>4.63241100311279</v>
+        <v>4.63241052627563</v>
       </c>
       <c r="H717" t="n">
         <v>1000</v>
@@ -21191,7 +21191,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G718" t="n">
-        <v>4.63241100311279</v>
+        <v>4.63241052627563</v>
       </c>
       <c r="H718" t="n">
         <v>0</v>
@@ -21220,7 +21220,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G719" t="n">
-        <v>4.63241100311279</v>
+        <v>4.63241052627563</v>
       </c>
       <c r="H719" t="n">
         <v>0</v>
@@ -21249,7 +21249,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G720" t="n">
-        <v>4.63241100311279</v>
+        <v>4.63241052627563</v>
       </c>
       <c r="H720" t="n">
         <v>0</v>
@@ -21278,7 +21278,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G721" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H721" t="n">
         <v>3000</v>
@@ -21423,7 +21423,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G726" t="n">
-        <v>4.0556845664978</v>
+        <v>4.05568504333496</v>
       </c>
       <c r="H726" t="n">
         <v>6000</v>
@@ -21510,7 +21510,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>4.27893304824829</v>
+        <v>4.27893352508545</v>
       </c>
       <c r="H729" t="n">
         <v>1250</v>
@@ -21539,7 +21539,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G730" t="n">
-        <v>4.27893304824829</v>
+        <v>4.27893352508545</v>
       </c>
       <c r="H730" t="n">
         <v>0</v>
@@ -21655,7 +21655,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G734" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H734" t="n">
         <v>250</v>
@@ -21684,7 +21684,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G735" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H735" t="n">
         <v>0</v>
@@ -21713,7 +21713,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G736" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H736" t="n">
         <v>0</v>
@@ -21742,7 +21742,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G737" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H737" t="n">
         <v>0</v>
@@ -21771,7 +21771,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G738" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H738" t="n">
         <v>0</v>
@@ -21800,7 +21800,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G739" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H739" t="n">
         <v>0</v>
@@ -21829,7 +21829,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G740" t="n">
-        <v>4.44636964797974</v>
+        <v>4.44637012481689</v>
       </c>
       <c r="H740" t="n">
         <v>750</v>
@@ -22119,7 +22119,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G750" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H750" t="n">
         <v>750</v>
@@ -22148,7 +22148,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G751" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H751" t="n">
         <v>0</v>
@@ -22177,7 +22177,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G752" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H752" t="n">
         <v>0</v>
@@ -22206,7 +22206,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G753" t="n">
-        <v>4.4277663230896</v>
+        <v>4.42776584625244</v>
       </c>
       <c r="H753" t="n">
         <v>2250</v>
@@ -22264,7 +22264,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G755" t="n">
-        <v>4.4277663230896</v>
+        <v>4.42776584625244</v>
       </c>
       <c r="H755" t="n">
         <v>3250</v>
@@ -22293,7 +22293,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G756" t="n">
-        <v>4.4277663230896</v>
+        <v>4.42776584625244</v>
       </c>
       <c r="H756" t="n">
         <v>0</v>
@@ -22322,7 +22322,7 @@
         <v>5</v>
       </c>
       <c r="G757" t="n">
-        <v>4.65101432800293</v>
+        <v>4.65101480484009</v>
       </c>
       <c r="H757" t="n">
         <v>2750</v>
@@ -22409,7 +22409,7 @@
         <v>5.25</v>
       </c>
       <c r="G760" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H760" t="n">
         <v>3000</v>
@@ -22438,7 +22438,7 @@
         <v>5.25</v>
       </c>
       <c r="G761" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H761" t="n">
         <v>2000</v>
@@ -22467,7 +22467,7 @@
         <v>5.25</v>
       </c>
       <c r="G762" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H762" t="n">
         <v>500</v>
@@ -22496,7 +22496,7 @@
         <v>5.25</v>
       </c>
       <c r="G763" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H763" t="n">
         <v>250</v>
@@ -22525,7 +22525,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G764" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H764" t="n">
         <v>4000</v>
@@ -22554,7 +22554,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G765" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H765" t="n">
         <v>0</v>
@@ -22583,7 +22583,7 @@
         <v>5.25</v>
       </c>
       <c r="G766" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H766" t="n">
         <v>2750</v>
@@ -22612,7 +22612,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G767" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H767" t="n">
         <v>6000</v>
@@ -22641,7 +22641,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H768" t="n">
         <v>500</v>
@@ -22670,7 +22670,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G769" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H769" t="n">
         <v>0</v>
@@ -22728,7 +22728,7 @@
         <v>5.25</v>
       </c>
       <c r="G771" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H771" t="n">
         <v>7500</v>
@@ -22757,7 +22757,7 @@
         <v>5.25</v>
       </c>
       <c r="G772" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H772" t="n">
         <v>0</v>
@@ -22786,7 +22786,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G773" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H773" t="n">
         <v>3750</v>
@@ -23047,7 +23047,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G782" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H782" t="n">
         <v>1750</v>
@@ -23076,7 +23076,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G783" t="n">
-        <v>5.67423820495605</v>
+        <v>5.6742377281189</v>
       </c>
       <c r="H783" t="n">
         <v>6750</v>
@@ -23105,7 +23105,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G784" t="n">
-        <v>5.76725816726685</v>
+        <v>5.76725769042969</v>
       </c>
       <c r="H784" t="n">
         <v>14500</v>
@@ -23134,7 +23134,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G785" t="n">
-        <v>5.99980878829956</v>
+        <v>5.9998083114624</v>
       </c>
       <c r="H785" t="n">
         <v>6250</v>
@@ -23221,7 +23221,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G788" t="n">
-        <v>5.86027860641479</v>
+        <v>5.86027812957764</v>
       </c>
       <c r="H788" t="n">
         <v>3250</v>
@@ -23250,7 +23250,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G789" t="n">
-        <v>5.86027860641479</v>
+        <v>5.86027812957764</v>
       </c>
       <c r="H789" t="n">
         <v>1500</v>
@@ -23279,7 +23279,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G790" t="n">
-        <v>5.76725816726685</v>
+        <v>5.76725769042969</v>
       </c>
       <c r="H790" t="n">
         <v>7750</v>
@@ -23308,7 +23308,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G791" t="n">
-        <v>5.86027860641479</v>
+        <v>5.86027812957764</v>
       </c>
       <c r="H791" t="n">
         <v>4750</v>
@@ -23366,7 +23366,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G793" t="n">
-        <v>5.67423820495605</v>
+        <v>5.6742377281189</v>
       </c>
       <c r="H793" t="n">
         <v>1250</v>
@@ -23511,7 +23511,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G798" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H798" t="n">
         <v>1000</v>
@@ -23627,7 +23627,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G802" t="n">
-        <v>5.53470706939697</v>
+        <v>5.53470754623413</v>
       </c>
       <c r="H802" t="n">
         <v>750</v>
@@ -23656,7 +23656,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G803" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H803" t="n">
         <v>750</v>
@@ -23714,7 +23714,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G805" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H805" t="n">
         <v>2750</v>
@@ -23743,7 +23743,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G806" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H806" t="n">
         <v>1750</v>
@@ -23772,7 +23772,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G807" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H807" t="n">
         <v>0</v>
@@ -23801,7 +23801,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G808" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H808" t="n">
         <v>0</v>
@@ -23830,7 +23830,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G809" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H809" t="n">
         <v>0</v>
@@ -23859,7 +23859,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G810" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H810" t="n">
         <v>1500</v>
@@ -23917,7 +23917,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G812" t="n">
-        <v>5.25564622879028</v>
+        <v>5.25564670562744</v>
       </c>
       <c r="H812" t="n">
         <v>750</v>
@@ -23946,7 +23946,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G813" t="n">
-        <v>5.25564622879028</v>
+        <v>5.25564670562744</v>
       </c>
       <c r="H813" t="n">
         <v>0</v>
@@ -23975,7 +23975,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G814" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H814" t="n">
         <v>3250</v>
@@ -24004,7 +24004,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G815" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H815" t="n">
         <v>0</v>
@@ -24120,7 +24120,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G819" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H819" t="n">
         <v>1000</v>
@@ -24352,7 +24352,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G827" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H827" t="n">
         <v>250</v>
@@ -24439,7 +24439,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G830" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H830" t="n">
         <v>9000</v>
@@ -24497,7 +24497,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G832" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H832" t="n">
         <v>750</v>
@@ -24526,7 +24526,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G833" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H833" t="n">
         <v>500</v>
@@ -24555,7 +24555,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G834" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -24584,7 +24584,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G835" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H835" t="n">
         <v>1000</v>
@@ -24613,7 +24613,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G836" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H836" t="n">
         <v>1000</v>
@@ -24642,7 +24642,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G837" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H837" t="n">
         <v>1500</v>
@@ -24816,7 +24816,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G843" t="n">
-        <v>4.63241100311279</v>
+        <v>4.63241052627563</v>
       </c>
       <c r="H843" t="n">
         <v>2750</v>
@@ -24845,7 +24845,7 @@
         <v>5</v>
       </c>
       <c r="G844" t="n">
-        <v>4.65101432800293</v>
+        <v>4.65101480484009</v>
       </c>
       <c r="H844" t="n">
         <v>250</v>
@@ -24874,7 +24874,7 @@
         <v>5</v>
       </c>
       <c r="G845" t="n">
-        <v>4.65101432800293</v>
+        <v>4.65101480484009</v>
       </c>
       <c r="H845" t="n">
         <v>0</v>
@@ -24903,7 +24903,7 @@
         <v>5</v>
       </c>
       <c r="G846" t="n">
-        <v>4.65101432800293</v>
+        <v>4.65101480484009</v>
       </c>
       <c r="H846" t="n">
         <v>500</v>
@@ -24932,7 +24932,7 @@
         <v>5</v>
       </c>
       <c r="G847" t="n">
-        <v>4.65101432800293</v>
+        <v>4.65101480484009</v>
       </c>
       <c r="H847" t="n">
         <v>0</v>
@@ -24990,7 +24990,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G849" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H849" t="n">
         <v>500</v>
@@ -25019,7 +25019,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G850" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H850" t="n">
         <v>1000</v>
@@ -25048,7 +25048,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G851" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H851" t="n">
         <v>1000</v>
@@ -43121,6 +43121,64 @@
         <v>500</v>
       </c>
       <c r="I1474" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1475" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1475" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="D1475" t="n">
+        <v>3.79999995231628</v>
+      </c>
+      <c r="E1475" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="F1475" t="n">
+        <v>3.79999995231628</v>
+      </c>
+      <c r="G1475" t="n">
+        <v>3.79999995231628</v>
+      </c>
+      <c r="H1475" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I1475" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1476" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1476" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="D1476" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="E1476" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="F1476" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="G1476" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="H1476" t="n">
+        <v>250</v>
+      </c>
+      <c r="I1476" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PLN.MI.xlsx
+++ b/data/PLN.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.41200017929077</v>
       </c>
       <c r="G2" t="n">
-        <v>4.05409288406372</v>
+        <v>4.05409336090088</v>
       </c>
       <c r="H2" t="n">
         <v>42000</v>
@@ -456,7 +456,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G3" t="n">
-        <v>4.11657667160034</v>
+        <v>4.1165771484375</v>
       </c>
       <c r="H3" t="n">
         <v>8500</v>
@@ -514,7 +514,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G5" t="n">
-        <v>4.22684240341187</v>
+        <v>4.22684192657471</v>
       </c>
       <c r="H5" t="n">
         <v>12000</v>
@@ -543,7 +543,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G6" t="n">
-        <v>4.21765327453613</v>
+        <v>4.21765375137329</v>
       </c>
       <c r="H6" t="n">
         <v>37000</v>
@@ -572,7 +572,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G7" t="n">
-        <v>4.19927644729614</v>
+        <v>4.19927549362183</v>
       </c>
       <c r="H7" t="n">
         <v>11500</v>
@@ -601,7 +601,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G8" t="n">
-        <v>4.1533317565918</v>
+        <v>4.15333223342896</v>
       </c>
       <c r="H8" t="n">
         <v>6500</v>
@@ -659,7 +659,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G10" t="n">
-        <v>4.04306650161743</v>
+        <v>4.04306602478027</v>
       </c>
       <c r="H10" t="n">
         <v>53000</v>
@@ -688,7 +688,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G11" t="n">
-        <v>4.03387784957886</v>
+        <v>4.0338773727417</v>
       </c>
       <c r="H11" t="n">
         <v>12000</v>
@@ -717,7 +717,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G12" t="n">
-        <v>3.96955633163452</v>
+        <v>3.96955609321594</v>
       </c>
       <c r="H12" t="n">
         <v>26000</v>
@@ -746,7 +746,7 @@
         <v>4.25</v>
       </c>
       <c r="G13" t="n">
-        <v>3.90523457527161</v>
+        <v>3.90523433685303</v>
       </c>
       <c r="H13" t="n">
         <v>19500</v>
@@ -804,7 +804,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G15" t="n">
-        <v>3.89604592323303</v>
+        <v>3.89604544639587</v>
       </c>
       <c r="H15" t="n">
         <v>12500</v>
@@ -833,7 +833,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G16" t="n">
-        <v>3.84091281890869</v>
+        <v>3.84091258049011</v>
       </c>
       <c r="H16" t="n">
         <v>21500</v>
@@ -949,7 +949,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G20" t="n">
-        <v>3.87766814231873</v>
+        <v>3.87766790390015</v>
       </c>
       <c r="H20" t="n">
         <v>12000</v>
@@ -978,7 +978,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G21" t="n">
-        <v>3.87766814231873</v>
+        <v>3.87766790390015</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G22" t="n">
-        <v>3.87766814231873</v>
+        <v>3.87766790390015</v>
       </c>
       <c r="H22" t="n">
         <v>60000</v>
@@ -1036,7 +1036,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G23" t="n">
-        <v>3.850102186203</v>
+        <v>3.85010194778442</v>
       </c>
       <c r="H23" t="n">
         <v>32000</v>
@@ -1065,7 +1065,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G24" t="n">
-        <v>3.8868567943573</v>
+        <v>3.88685703277588</v>
       </c>
       <c r="H24" t="n">
         <v>500</v>
@@ -1094,7 +1094,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>3.98793387413025</v>
+        <v>3.98793435096741</v>
       </c>
       <c r="H25" t="n">
         <v>7500</v>
@@ -1123,7 +1123,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G26" t="n">
-        <v>4.18089818954468</v>
+        <v>4.18089866638184</v>
       </c>
       <c r="H26" t="n">
         <v>15000</v>
@@ -1152,7 +1152,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>4.17170906066895</v>
+        <v>4.1717095375061</v>
       </c>
       <c r="H27" t="n">
         <v>10500</v>
@@ -1210,7 +1210,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G29" t="n">
-        <v>4.2084641456604</v>
+        <v>4.20846462249756</v>
       </c>
       <c r="H29" t="n">
         <v>24500</v>
@@ -1239,7 +1239,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G30" t="n">
-        <v>4.18089818954468</v>
+        <v>4.18089866638184</v>
       </c>
       <c r="H30" t="n">
         <v>3500</v>
@@ -1268,7 +1268,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G31" t="n">
-        <v>4.1533317565918</v>
+        <v>4.15333223342896</v>
       </c>
       <c r="H31" t="n">
         <v>9000</v>
@@ -1326,7 +1326,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>4.1533317565918</v>
+        <v>4.15333223342896</v>
       </c>
       <c r="H33" t="n">
         <v>2000</v>
@@ -1384,7 +1384,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>4.11657667160034</v>
+        <v>4.1165771484375</v>
       </c>
       <c r="H35" t="n">
         <v>27500</v>
@@ -1413,7 +1413,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G36" t="n">
-        <v>4.06144428253174</v>
+        <v>4.06144380569458</v>
       </c>
       <c r="H36" t="n">
         <v>18500</v>
@@ -1442,7 +1442,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G37" t="n">
-        <v>4.05225467681885</v>
+        <v>4.05225515365601</v>
       </c>
       <c r="H37" t="n">
         <v>2000</v>
@@ -1471,7 +1471,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G38" t="n">
-        <v>4.05225467681885</v>
+        <v>4.05225515365601</v>
       </c>
       <c r="H38" t="n">
         <v>11500</v>
@@ -1500,7 +1500,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G39" t="n">
-        <v>4.09819936752319</v>
+        <v>4.09819841384888</v>
       </c>
       <c r="H39" t="n">
         <v>3500</v>
@@ -1529,7 +1529,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>4.09819936752319</v>
+        <v>4.09819841384888</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G41" t="n">
-        <v>4.17170906066895</v>
+        <v>4.1717095375061</v>
       </c>
       <c r="H41" t="n">
         <v>5500</v>
@@ -1587,7 +1587,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>4.17170906066895</v>
+        <v>4.1717095375061</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>4.08901023864746</v>
+        <v>4.08901071548462</v>
       </c>
       <c r="H43" t="n">
         <v>2000</v>
@@ -1645,7 +1645,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>4.08901023864746</v>
+        <v>4.08901071548462</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G45" t="n">
-        <v>4.03387784957886</v>
+        <v>4.0338773727417</v>
       </c>
       <c r="H45" t="n">
         <v>12500</v>
@@ -1819,7 +1819,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>4.04306650161743</v>
+        <v>4.04306602478027</v>
       </c>
       <c r="H50" t="n">
         <v>3000</v>
@@ -1848,7 +1848,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G51" t="n">
-        <v>3.89604592323303</v>
+        <v>3.89604544639587</v>
       </c>
       <c r="H51" t="n">
         <v>31000</v>
@@ -1906,7 +1906,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G53" t="n">
-        <v>3.89604592323303</v>
+        <v>3.89604544639587</v>
       </c>
       <c r="H53" t="n">
         <v>11000</v>
@@ -1935,7 +1935,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G54" t="n">
-        <v>3.85929036140442</v>
+        <v>3.85929012298584</v>
       </c>
       <c r="H54" t="n">
         <v>5000</v>
@@ -1964,7 +1964,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G55" t="n">
-        <v>3.85929036140442</v>
+        <v>3.85929012298584</v>
       </c>
       <c r="H55" t="n">
         <v>6000</v>
@@ -1993,7 +1993,7 @@
         <v>4.25</v>
       </c>
       <c r="G56" t="n">
-        <v>3.90523457527161</v>
+        <v>3.90523433685303</v>
       </c>
       <c r="H56" t="n">
         <v>7500</v>
@@ -2022,7 +2022,7 @@
         <v>4.25</v>
       </c>
       <c r="G57" t="n">
-        <v>3.90523457527161</v>
+        <v>3.90523433685303</v>
       </c>
       <c r="H57" t="n">
         <v>3000</v>
@@ -2109,7 +2109,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G60" t="n">
-        <v>4.03387784957886</v>
+        <v>4.0338773727417</v>
       </c>
       <c r="H60" t="n">
         <v>1000</v>
@@ -2167,7 +2167,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G62" t="n">
-        <v>3.93280124664307</v>
+        <v>3.93280100822449</v>
       </c>
       <c r="H62" t="n">
         <v>40500</v>
@@ -2225,7 +2225,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G64" t="n">
-        <v>4.05225467681885</v>
+        <v>4.05225515365601</v>
       </c>
       <c r="H64" t="n">
         <v>26000</v>
@@ -2283,7 +2283,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G66" t="n">
-        <v>4.16252088546753</v>
+        <v>4.16252040863037</v>
       </c>
       <c r="H66" t="n">
         <v>21000</v>
@@ -2312,7 +2312,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G67" t="n">
-        <v>4.28197479248047</v>
+        <v>4.28197526931763</v>
       </c>
       <c r="H67" t="n">
         <v>12500</v>
@@ -2370,7 +2370,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G69" t="n">
-        <v>4.23603057861328</v>
+        <v>4.23603105545044</v>
       </c>
       <c r="H69" t="n">
         <v>7000</v>
@@ -2486,7 +2486,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G73" t="n">
-        <v>4.72303676605225</v>
+        <v>4.72303628921509</v>
       </c>
       <c r="H73" t="n">
         <v>3000</v>
@@ -2544,7 +2544,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>4.61277151107788</v>
+        <v>4.61277103424072</v>
       </c>
       <c r="H75" t="n">
         <v>9500</v>
@@ -2573,7 +2573,7 @@
         <v>5</v>
       </c>
       <c r="G76" t="n">
-        <v>4.59439373016357</v>
+        <v>4.59439325332642</v>
       </c>
       <c r="H76" t="n">
         <v>6000</v>
@@ -2602,7 +2602,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G77" t="n">
-        <v>4.52088356018066</v>
+        <v>4.52088308334351</v>
       </c>
       <c r="H77" t="n">
         <v>500</v>
@@ -2747,7 +2747,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G82" t="n">
-        <v>4.77816963195801</v>
+        <v>4.77816915512085</v>
       </c>
       <c r="H82" t="n">
         <v>3500</v>
@@ -2834,7 +2834,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G85" t="n">
-        <v>4.96194505691528</v>
+        <v>4.96194553375244</v>
       </c>
       <c r="H85" t="n">
         <v>27000</v>
@@ -2892,7 +2892,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G87" t="n">
-        <v>5.31111860275269</v>
+        <v>5.311119556427</v>
       </c>
       <c r="H87" t="n">
         <v>23500</v>
@@ -2950,7 +2950,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G89" t="n">
-        <v>6.11973142623901</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H89" t="n">
         <v>78500</v>
@@ -3008,7 +3008,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G91" t="n">
-        <v>6.11973142623901</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H91" t="n">
         <v>34500</v>
@@ -3095,7 +3095,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G94" t="n">
-        <v>6.11973142623901</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H94" t="n">
         <v>29500</v>
@@ -3124,7 +3124,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G95" t="n">
-        <v>6.32188606262207</v>
+        <v>6.32188558578491</v>
       </c>
       <c r="H95" t="n">
         <v>57500</v>
@@ -3182,7 +3182,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G97" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H97" t="n">
         <v>40000</v>
@@ -3240,7 +3240,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G99" t="n">
-        <v>6.08297681808472</v>
+        <v>6.08297729492188</v>
       </c>
       <c r="H99" t="n">
         <v>19500</v>
@@ -3298,7 +3298,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>5.9910888671875</v>
+        <v>5.99108934402466</v>
       </c>
       <c r="H101" t="n">
         <v>7000</v>
@@ -3385,7 +3385,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G104" t="n">
-        <v>6.02784395217896</v>
+        <v>6.02784442901611</v>
       </c>
       <c r="H104" t="n">
         <v>15000</v>
@@ -3443,7 +3443,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G106" t="n">
-        <v>5.9543342590332</v>
+        <v>5.95433378219604</v>
       </c>
       <c r="H106" t="n">
         <v>11500</v>
@@ -3588,7 +3588,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G111" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H111" t="n">
         <v>3500</v>
@@ -3646,7 +3646,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>5.88082408905029</v>
+        <v>5.88082361221313</v>
       </c>
       <c r="H113" t="n">
         <v>500</v>
@@ -3675,7 +3675,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G114" t="n">
-        <v>5.88082408905029</v>
+        <v>5.88082361221313</v>
       </c>
       <c r="H114" t="n">
         <v>500</v>
@@ -3965,7 +3965,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G124" t="n">
-        <v>5.32949733734131</v>
+        <v>5.32949638366699</v>
       </c>
       <c r="H124" t="n">
         <v>500</v>
@@ -3994,7 +3994,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G125" t="n">
-        <v>5.71542549133301</v>
+        <v>5.71542501449585</v>
       </c>
       <c r="H125" t="n">
         <v>14000</v>
@@ -4081,7 +4081,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G128" t="n">
-        <v>5.56840467453003</v>
+        <v>5.56840515136719</v>
       </c>
       <c r="H128" t="n">
         <v>10500</v>
@@ -4110,7 +4110,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G129" t="n">
-        <v>5.43976211547852</v>
+        <v>5.43976259231567</v>
       </c>
       <c r="H129" t="n">
         <v>500</v>
@@ -4168,7 +4168,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G131" t="n">
-        <v>5.43976211547852</v>
+        <v>5.43976259231567</v>
       </c>
       <c r="H131" t="n">
         <v>3500</v>
@@ -4313,7 +4313,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>5.55002784729004</v>
+        <v>5.55002737045288</v>
       </c>
       <c r="H136" t="n">
         <v>7000</v>
@@ -4342,7 +4342,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>5.55002784729004</v>
+        <v>5.55002737045288</v>
       </c>
       <c r="H137" t="n">
         <v>1000</v>
@@ -4371,7 +4371,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G138" t="n">
-        <v>5.55002784729004</v>
+        <v>5.55002737045288</v>
       </c>
       <c r="H138" t="n">
         <v>3000</v>
@@ -4400,7 +4400,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G139" t="n">
-        <v>5.55002784729004</v>
+        <v>5.55002737045288</v>
       </c>
       <c r="H139" t="n">
         <v>10500</v>
@@ -4516,7 +4516,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G143" t="n">
-        <v>5.88082408905029</v>
+        <v>5.88082361221313</v>
       </c>
       <c r="H143" t="n">
         <v>5500</v>
@@ -4545,7 +4545,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G144" t="n">
-        <v>5.6602931022644</v>
+        <v>5.66029262542725</v>
       </c>
       <c r="H144" t="n">
         <v>2500</v>
@@ -4632,7 +4632,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>5.88082408905029</v>
+        <v>5.88082361221313</v>
       </c>
       <c r="H147" t="n">
         <v>5000</v>
@@ -4661,7 +4661,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G148" t="n">
-        <v>5.88082408905029</v>
+        <v>5.88082361221313</v>
       </c>
       <c r="H148" t="n">
         <v>500</v>
@@ -4748,7 +4748,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>6.06459903717041</v>
+        <v>6.06459951400757</v>
       </c>
       <c r="H151" t="n">
         <v>5500</v>
@@ -4777,7 +4777,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G152" t="n">
-        <v>6.02784395217896</v>
+        <v>6.02784442901611</v>
       </c>
       <c r="H152" t="n">
         <v>6000</v>
@@ -4806,7 +4806,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G153" t="n">
-        <v>6.06459903717041</v>
+        <v>6.06459951400757</v>
       </c>
       <c r="H153" t="n">
         <v>1000</v>
@@ -4922,7 +4922,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H157" t="n">
         <v>1000</v>
@@ -4951,7 +4951,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G158" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H158" t="n">
         <v>4500</v>
@@ -5009,7 +5009,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G160" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H160" t="n">
         <v>2000</v>
@@ -5038,7 +5038,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G161" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H161" t="n">
         <v>1000</v>
@@ -5067,7 +5067,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G162" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G163" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H163" t="n">
         <v>4500</v>
@@ -5125,7 +5125,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G164" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H164" t="n">
         <v>17000</v>
@@ -5502,7 +5502,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G177" t="n">
-        <v>7.27751970291138</v>
+        <v>7.27751922607422</v>
       </c>
       <c r="H177" t="n">
         <v>28000</v>
@@ -5531,7 +5531,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G178" t="n">
-        <v>7.20400953292847</v>
+        <v>7.20400905609131</v>
       </c>
       <c r="H178" t="n">
         <v>25000</v>
@@ -5560,7 +5560,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H179" t="n">
         <v>1500</v>
@@ -5589,7 +5589,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5618,7 +5618,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H181" t="n">
         <v>1500</v>
@@ -5647,7 +5647,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G182" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H182" t="n">
         <v>2500</v>
@@ -5676,7 +5676,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G187" t="n">
-        <v>7.05698871612549</v>
+        <v>7.05698823928833</v>
       </c>
       <c r="H187" t="n">
         <v>5500</v>
@@ -5821,7 +5821,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G188" t="n">
-        <v>7.24076461791992</v>
+        <v>7.24076414108276</v>
       </c>
       <c r="H188" t="n">
         <v>1000</v>
@@ -5850,7 +5850,7 @@
         <v>8</v>
       </c>
       <c r="G189" t="n">
-        <v>7.35102939605713</v>
+        <v>7.35102987289429</v>
       </c>
       <c r="H189" t="n">
         <v>3500</v>
@@ -5908,7 +5908,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G191" t="n">
-        <v>7.14887714385986</v>
+        <v>7.14887619018555</v>
       </c>
       <c r="H191" t="n">
         <v>1000</v>
@@ -6024,7 +6024,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G195" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H195" t="n">
         <v>12000</v>
@@ -6227,7 +6227,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G202" t="n">
-        <v>7.70020437240601</v>
+        <v>7.70020389556885</v>
       </c>
       <c r="H202" t="n">
         <v>6500</v>
@@ -6256,7 +6256,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G203" t="n">
-        <v>7.70020437240601</v>
+        <v>7.70020389556885</v>
       </c>
       <c r="H203" t="n">
         <v>3000</v>
@@ -6285,7 +6285,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G204" t="n">
-        <v>7.79209184646606</v>
+        <v>7.79209089279175</v>
       </c>
       <c r="H204" t="n">
         <v>6500</v>
@@ -6314,7 +6314,7 @@
         <v>8.5</v>
       </c>
       <c r="G205" t="n">
-        <v>7.81046915054321</v>
+        <v>7.81046867370605</v>
       </c>
       <c r="H205" t="n">
         <v>6500</v>
@@ -6343,7 +6343,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G206" t="n">
-        <v>8.12288856506348</v>
+        <v>8.12288761138916</v>
       </c>
       <c r="H206" t="n">
         <v>16500</v>
@@ -6401,7 +6401,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G208" t="n">
-        <v>8.08613300323486</v>
+        <v>8.08613204956055</v>
       </c>
       <c r="H208" t="n">
         <v>3000</v>
@@ -6459,7 +6459,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G210" t="n">
-        <v>8.01262378692627</v>
+        <v>8.01262187957764</v>
       </c>
       <c r="H210" t="n">
         <v>3500</v>
@@ -6488,7 +6488,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G211" t="n">
-        <v>8.15964221954346</v>
+        <v>8.15964317321777</v>
       </c>
       <c r="H211" t="n">
         <v>8000</v>
@@ -6517,7 +6517,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G212" t="n">
-        <v>8.12288856506348</v>
+        <v>8.12288761138916</v>
       </c>
       <c r="H212" t="n">
         <v>500</v>
@@ -6604,7 +6604,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G215" t="n">
-        <v>8.4169282913208</v>
+        <v>8.41692924499512</v>
       </c>
       <c r="H215" t="n">
         <v>1000</v>
@@ -6633,7 +6633,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G216" t="n">
-        <v>8.54557132720947</v>
+        <v>8.54557228088379</v>
       </c>
       <c r="H216" t="n">
         <v>2500</v>
@@ -6836,7 +6836,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G223" t="n">
-        <v>8.78448104858398</v>
+        <v>8.78448009490967</v>
       </c>
       <c r="H223" t="n">
         <v>1000</v>
@@ -6865,7 +6865,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G224" t="n">
-        <v>8.82123565673828</v>
+        <v>8.8212366104126</v>
       </c>
       <c r="H224" t="n">
         <v>2000</v>
@@ -6894,7 +6894,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.82123565673828</v>
+        <v>8.8212366104126</v>
       </c>
       <c r="H225" t="n">
         <v>3500</v>
@@ -6952,7 +6952,7 @@
         <v>9.5</v>
       </c>
       <c r="G227" t="n">
-        <v>8.72934818267822</v>
+        <v>8.72934722900391</v>
       </c>
       <c r="H227" t="n">
         <v>4500</v>
@@ -6981,7 +6981,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G228" t="n">
-        <v>8.63745975494385</v>
+        <v>8.63746070861816</v>
       </c>
       <c r="H228" t="n">
         <v>20000</v>
@@ -7010,7 +7010,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G229" t="n">
-        <v>8.63745975494385</v>
+        <v>8.63746070861816</v>
       </c>
       <c r="H229" t="n">
         <v>12500</v>
@@ -7039,7 +7039,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G230" t="n">
-        <v>8.63745975494385</v>
+        <v>8.63746070861816</v>
       </c>
       <c r="H230" t="n">
         <v>7000</v>
@@ -7126,7 +7126,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G233" t="n">
-        <v>8.63745975494385</v>
+        <v>8.63746070861816</v>
       </c>
       <c r="H233" t="n">
         <v>11000</v>
@@ -7155,7 +7155,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G234" t="n">
-        <v>8.54557132720947</v>
+        <v>8.54557228088379</v>
       </c>
       <c r="H234" t="n">
         <v>4500</v>
@@ -7184,7 +7184,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>8.54557132720947</v>
+        <v>8.54557228088379</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G236" t="n">
-        <v>8.14126586914062</v>
+        <v>8.14126491546631</v>
       </c>
       <c r="H236" t="n">
         <v>6500</v>
@@ -7242,7 +7242,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>8.23315334320068</v>
+        <v>8.233154296875</v>
       </c>
       <c r="H237" t="n">
         <v>8500</v>
@@ -7416,7 +7416,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G243" t="n">
-        <v>8.56394958496094</v>
+        <v>8.56395053863525</v>
       </c>
       <c r="H243" t="n">
         <v>500</v>
@@ -7445,7 +7445,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G244" t="n">
-        <v>8.56394958496094</v>
+        <v>8.56395053863525</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G245" t="n">
-        <v>8.36179637908936</v>
+        <v>8.36179733276367</v>
       </c>
       <c r="H245" t="n">
         <v>500</v>
@@ -7503,7 +7503,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G246" t="n">
-        <v>8.36179637908936</v>
+        <v>8.36179733276367</v>
       </c>
       <c r="H246" t="n">
         <v>1500</v>
@@ -7532,7 +7532,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>8.54557132720947</v>
+        <v>8.54557228088379</v>
       </c>
       <c r="H247" t="n">
         <v>7500</v>
@@ -7561,7 +7561,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G248" t="n">
-        <v>8.63745975494385</v>
+        <v>8.63746070861816</v>
       </c>
       <c r="H248" t="n">
         <v>7500</v>
@@ -7590,7 +7590,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G249" t="n">
-        <v>8.45368480682373</v>
+        <v>8.45368385314941</v>
       </c>
       <c r="H249" t="n">
         <v>1000</v>
@@ -7619,7 +7619,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G250" t="n">
-        <v>8.49043846130371</v>
+        <v>8.49043941497803</v>
       </c>
       <c r="H250" t="n">
         <v>500</v>
@@ -7648,7 +7648,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G251" t="n">
-        <v>8.54557132720947</v>
+        <v>8.54557228088379</v>
       </c>
       <c r="H251" t="n">
         <v>6000</v>
@@ -7677,7 +7677,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G252" t="n">
-        <v>8.54557132720947</v>
+        <v>8.54557228088379</v>
       </c>
       <c r="H252" t="n">
         <v>500</v>
@@ -7706,7 +7706,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G253" t="n">
-        <v>8.71096992492676</v>
+        <v>8.71096897125244</v>
       </c>
       <c r="H253" t="n">
         <v>10500</v>
@@ -7735,7 +7735,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G254" t="n">
-        <v>8.71096992492676</v>
+        <v>8.71096897125244</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G255" t="n">
-        <v>8.71096992492676</v>
+        <v>8.71096897125244</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
         <v>9.5</v>
       </c>
       <c r="G256" t="n">
-        <v>8.72934818267822</v>
+        <v>8.72934722900391</v>
       </c>
       <c r="H256" t="n">
         <v>500</v>
@@ -7822,7 +7822,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G257" t="n">
-        <v>8.87636756896973</v>
+        <v>8.87636852264404</v>
       </c>
       <c r="H257" t="n">
         <v>4000</v>
@@ -7938,7 +7938,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G261" t="n">
-        <v>8.98663425445557</v>
+        <v>8.98663330078125</v>
       </c>
       <c r="H261" t="n">
         <v>1000</v>
@@ -7967,7 +7967,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G262" t="n">
-        <v>8.98663425445557</v>
+        <v>8.98663330078125</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>10</v>
       </c>
       <c r="G263" t="n">
-        <v>9.18878746032715</v>
+        <v>9.18878650665283</v>
       </c>
       <c r="H263" t="n">
         <v>500</v>
@@ -8083,7 +8083,7 @@
         <v>9.5</v>
       </c>
       <c r="G266" t="n">
-        <v>8.72934818267822</v>
+        <v>8.72934722900391</v>
       </c>
       <c r="H266" t="n">
         <v>3000</v>
@@ -8170,7 +8170,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G269" t="n">
-        <v>8.74772548675537</v>
+        <v>8.74772644042969</v>
       </c>
       <c r="H269" t="n">
         <v>4000</v>
@@ -8228,7 +8228,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G271" t="n">
-        <v>8.39855289459229</v>
+        <v>8.39855098724365</v>
       </c>
       <c r="H271" t="n">
         <v>5000</v>
@@ -8257,7 +8257,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G272" t="n">
-        <v>7.47967338562012</v>
+        <v>7.47967290878296</v>
       </c>
       <c r="H272" t="n">
         <v>11000</v>
@@ -8286,7 +8286,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G273" t="n">
-        <v>7.29589700698853</v>
+        <v>7.29589748382568</v>
       </c>
       <c r="H273" t="n">
         <v>6500</v>
@@ -8315,7 +8315,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>7.53480577468872</v>
+        <v>7.5348048210144</v>
       </c>
       <c r="H274" t="n">
         <v>3000</v>
@@ -8431,7 +8431,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G278" t="n">
-        <v>7.66344881057739</v>
+        <v>7.66344833374023</v>
       </c>
       <c r="H278" t="n">
         <v>3000</v>
@@ -8518,7 +8518,7 @@
         <v>8</v>
       </c>
       <c r="G281" t="n">
-        <v>7.35102939605713</v>
+        <v>7.35102987289429</v>
       </c>
       <c r="H281" t="n">
         <v>3000</v>
@@ -8547,7 +8547,7 @@
         <v>8</v>
       </c>
       <c r="G282" t="n">
-        <v>7.35102939605713</v>
+        <v>7.35102987289429</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>8</v>
       </c>
       <c r="G283" t="n">
-        <v>7.35102939605713</v>
+        <v>7.35102987289429</v>
       </c>
       <c r="H283" t="n">
         <v>7500</v>
@@ -8692,7 +8692,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G287" t="n">
-        <v>7.27751970291138</v>
+        <v>7.27751922607422</v>
       </c>
       <c r="H287" t="n">
         <v>3500</v>
@@ -8750,7 +8750,7 @@
         <v>8</v>
       </c>
       <c r="G289" t="n">
-        <v>7.35102939605713</v>
+        <v>7.35102987289429</v>
       </c>
       <c r="H289" t="n">
         <v>1500</v>
@@ -8779,7 +8779,7 @@
         <v>8</v>
       </c>
       <c r="G290" t="n">
-        <v>7.35102939605713</v>
+        <v>7.35102987289429</v>
       </c>
       <c r="H290" t="n">
         <v>9000</v>
@@ -8808,7 +8808,7 @@
         <v>8</v>
       </c>
       <c r="G291" t="n">
-        <v>7.35102939605713</v>
+        <v>7.35102987289429</v>
       </c>
       <c r="H291" t="n">
         <v>1500</v>
@@ -8837,7 +8837,7 @@
         <v>8</v>
       </c>
       <c r="G292" t="n">
-        <v>7.35102939605713</v>
+        <v>7.35102987289429</v>
       </c>
       <c r="H292" t="n">
         <v>3000</v>
@@ -8982,7 +8982,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>6.79970216751099</v>
+        <v>6.79970264434814</v>
       </c>
       <c r="H297" t="n">
         <v>3500</v>
@@ -9011,7 +9011,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>6.98347854614258</v>
+        <v>6.98347806930542</v>
       </c>
       <c r="H298" t="n">
         <v>7000</v>
@@ -9040,7 +9040,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>6.98347854614258</v>
+        <v>6.98347806930542</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>6.98347854614258</v>
+        <v>6.98347806930542</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G301" t="n">
-        <v>6.98347854614258</v>
+        <v>6.98347806930542</v>
       </c>
       <c r="H301" t="n">
         <v>18500</v>
@@ -9272,7 +9272,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G307" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H307" t="n">
         <v>500</v>
@@ -9301,7 +9301,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G308" t="n">
-        <v>6.72619199752808</v>
+        <v>6.72619295120239</v>
       </c>
       <c r="H308" t="n">
         <v>5000</v>
@@ -9330,7 +9330,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G309" t="n">
-        <v>7.05698871612549</v>
+        <v>7.05698823928833</v>
       </c>
       <c r="H309" t="n">
         <v>1000</v>
@@ -9417,7 +9417,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G312" t="n">
-        <v>7.53480577468872</v>
+        <v>7.5348048210144</v>
       </c>
       <c r="H312" t="n">
         <v>2000</v>
@@ -9446,7 +9446,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G313" t="n">
-        <v>7.38778448104858</v>
+        <v>7.38778495788574</v>
       </c>
       <c r="H313" t="n">
         <v>2000</v>
@@ -9620,7 +9620,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G319" t="n">
-        <v>7.46129512786865</v>
+        <v>7.46129560470581</v>
       </c>
       <c r="H319" t="n">
         <v>500</v>
@@ -9649,7 +9649,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G320" t="n">
-        <v>7.46129512786865</v>
+        <v>7.46129560470581</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G321" t="n">
-        <v>7.22238636016846</v>
+        <v>7.22238683700562</v>
       </c>
       <c r="H321" t="n">
         <v>500</v>
@@ -9707,7 +9707,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G322" t="n">
-        <v>7.22238636016846</v>
+        <v>7.22238683700562</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G323" t="n">
-        <v>7.22238636016846</v>
+        <v>7.22238683700562</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G324" t="n">
-        <v>7.22238636016846</v>
+        <v>7.22238683700562</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G328" t="n">
-        <v>6.98347854614258</v>
+        <v>6.98347806930542</v>
       </c>
       <c r="H328" t="n">
         <v>1000</v>
@@ -9910,7 +9910,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G329" t="n">
-        <v>6.79970216751099</v>
+        <v>6.79970264434814</v>
       </c>
       <c r="H329" t="n">
         <v>1000</v>
@@ -9939,7 +9939,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G330" t="n">
-        <v>7.02023363113403</v>
+        <v>7.02023315429688</v>
       </c>
       <c r="H330" t="n">
         <v>500</v>
@@ -9968,7 +9968,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G331" t="n">
-        <v>7.02023363113403</v>
+        <v>7.02023315429688</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G332" t="n">
-        <v>7.02023363113403</v>
+        <v>7.02023315429688</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G333" t="n">
-        <v>7.02023363113403</v>
+        <v>7.02023315429688</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>6.79970216751099</v>
+        <v>6.79970264434814</v>
       </c>
       <c r="H337" t="n">
         <v>500</v>
@@ -10171,7 +10171,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>6.79970216751099</v>
+        <v>6.79970264434814</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G341" t="n">
-        <v>6.15648746490479</v>
+        <v>6.15648698806763</v>
       </c>
       <c r="H341" t="n">
         <v>1000</v>
@@ -10287,7 +10287,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G342" t="n">
-        <v>6.15648746490479</v>
+        <v>6.15648698806763</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -10316,7 +10316,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G343" t="n">
-        <v>6.02784395217896</v>
+        <v>6.02784442901611</v>
       </c>
       <c r="H343" t="n">
         <v>9500</v>
@@ -10432,7 +10432,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G347" t="n">
-        <v>6.11973142623901</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H347" t="n">
         <v>1000</v>
@@ -10461,7 +10461,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G348" t="n">
-        <v>6.11973142623901</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -10490,7 +10490,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G349" t="n">
-        <v>6.21162080764771</v>
+        <v>6.21162033081055</v>
       </c>
       <c r="H349" t="n">
         <v>1500</v>
@@ -10548,7 +10548,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>5.9910888671875</v>
+        <v>5.99108934402466</v>
       </c>
       <c r="H351" t="n">
         <v>14500</v>
@@ -10577,7 +10577,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G352" t="n">
-        <v>5.9910888671875</v>
+        <v>5.99108934402466</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -10606,7 +10606,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G353" t="n">
-        <v>5.91757917404175</v>
+        <v>5.91757869720459</v>
       </c>
       <c r="H353" t="n">
         <v>3000</v>
@@ -10635,7 +10635,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G354" t="n">
-        <v>5.91757917404175</v>
+        <v>5.91757869720459</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -10780,7 +10780,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G359" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H359" t="n">
         <v>500</v>
@@ -10954,7 +10954,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G365" t="n">
-        <v>6.59754943847656</v>
+        <v>6.5975489616394</v>
       </c>
       <c r="H365" t="n">
         <v>500</v>
@@ -10983,7 +10983,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G366" t="n">
-        <v>6.15648746490479</v>
+        <v>6.15648698806763</v>
       </c>
       <c r="H366" t="n">
         <v>6500</v>
@@ -11012,7 +11012,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G367" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H367" t="n">
         <v>2000</v>
@@ -11041,7 +11041,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G368" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G369" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G370" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G371" t="n">
-        <v>6.21162080764771</v>
+        <v>6.21162033081055</v>
       </c>
       <c r="H371" t="n">
         <v>4000</v>
@@ -11157,7 +11157,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G372" t="n">
-        <v>6.21162080764771</v>
+        <v>6.21162033081055</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G373" t="n">
-        <v>6.21162080764771</v>
+        <v>6.21162033081055</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G374" t="n">
-        <v>6.21162080764771</v>
+        <v>6.21162033081055</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>6.15648746490479</v>
+        <v>6.15648698806763</v>
       </c>
       <c r="H375" t="n">
         <v>500</v>
@@ -11360,7 +11360,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>6.06459903717041</v>
+        <v>6.06459951400757</v>
       </c>
       <c r="H379" t="n">
         <v>1000</v>
@@ -11389,7 +11389,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>6.06459903717041</v>
+        <v>6.06459951400757</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>6.06459903717041</v>
+        <v>6.06459951400757</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G382" t="n">
-        <v>6.06459903717041</v>
+        <v>6.06459951400757</v>
       </c>
       <c r="H382" t="n">
         <v>500</v>
@@ -11621,7 +11621,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G388" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H388" t="n">
         <v>1000</v>
@@ -11911,7 +11911,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G398" t="n">
-        <v>5.91757917404175</v>
+        <v>5.91757869720459</v>
       </c>
       <c r="H398" t="n">
         <v>500</v>
@@ -11940,7 +11940,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G399" t="n">
-        <v>5.91757917404175</v>
+        <v>5.91757869720459</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G401" t="n">
-        <v>6.15648746490479</v>
+        <v>6.15648698806763</v>
       </c>
       <c r="H401" t="n">
         <v>2500</v>
@@ -12027,7 +12027,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G402" t="n">
-        <v>6.15648746490479</v>
+        <v>6.15648698806763</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G403" t="n">
-        <v>6.15648746490479</v>
+        <v>6.15648698806763</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -12085,7 +12085,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G404" t="n">
-        <v>6.11973142623901</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H404" t="n">
         <v>1000</v>
@@ -12114,7 +12114,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G405" t="n">
-        <v>6.11973142623901</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -12143,7 +12143,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G406" t="n">
-        <v>6.11973142623901</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G407" t="n">
-        <v>6.11973142623901</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -12201,7 +12201,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G408" t="n">
-        <v>6.11973142623901</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G431" t="n">
-        <v>6.21162080764771</v>
+        <v>6.21162033081055</v>
       </c>
       <c r="H431" t="n">
         <v>1000</v>
@@ -12897,7 +12897,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G432" t="n">
-        <v>6.08297681808472</v>
+        <v>6.08297729492188</v>
       </c>
       <c r="H432" t="n">
         <v>500</v>
@@ -12926,7 +12926,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>6.08297681808472</v>
+        <v>6.08297729492188</v>
       </c>
       <c r="H433" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G434" t="n">
-        <v>6.08297681808472</v>
+        <v>6.08297729492188</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G435" t="n">
-        <v>6.08297681808472</v>
+        <v>6.08297729492188</v>
       </c>
       <c r="H435" t="n">
         <v>0</v>
@@ -13013,7 +13013,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G436" t="n">
-        <v>6.08297681808472</v>
+        <v>6.08297729492188</v>
       </c>
       <c r="H436" t="n">
         <v>0</v>
@@ -13042,7 +13042,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G437" t="n">
-        <v>6.08297681808472</v>
+        <v>6.08297729492188</v>
       </c>
       <c r="H437" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G439" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H439" t="n">
         <v>3000</v>
@@ -13129,7 +13129,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>6.15648746490479</v>
+        <v>6.15648698806763</v>
       </c>
       <c r="H440" t="n">
         <v>1000</v>
@@ -13158,7 +13158,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G441" t="n">
-        <v>6.32188606262207</v>
+        <v>6.32188558578491</v>
       </c>
       <c r="H441" t="n">
         <v>500</v>
@@ -13187,7 +13187,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G442" t="n">
-        <v>6.32188606262207</v>
+        <v>6.32188558578491</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G443" t="n">
-        <v>6.32188606262207</v>
+        <v>6.32188558578491</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G444" t="n">
-        <v>6.32188606262207</v>
+        <v>6.32188558578491</v>
       </c>
       <c r="H444" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G448" t="n">
-        <v>6.02784395217896</v>
+        <v>6.02784442901611</v>
       </c>
       <c r="H448" t="n">
         <v>1000</v>
@@ -13448,7 +13448,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G451" t="n">
-        <v>6.00946664810181</v>
+        <v>6.00946712493896</v>
       </c>
       <c r="H451" t="n">
         <v>500</v>
@@ -13477,7 +13477,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G452" t="n">
-        <v>5.88082408905029</v>
+        <v>5.88082361221313</v>
       </c>
       <c r="H452" t="n">
         <v>1000</v>
@@ -13941,7 +13941,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G468" t="n">
-        <v>5.60516023635864</v>
+        <v>5.6051607131958</v>
       </c>
       <c r="H468" t="n">
         <v>2000</v>
@@ -13970,7 +13970,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G469" t="n">
-        <v>5.60516023635864</v>
+        <v>5.6051607131958</v>
       </c>
       <c r="H469" t="n">
         <v>0</v>
@@ -14115,7 +14115,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G474" t="n">
-        <v>5.42138481140137</v>
+        <v>5.42138433456421</v>
       </c>
       <c r="H474" t="n">
         <v>500</v>
@@ -14318,7 +14318,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G481" t="n">
-        <v>5.56840467453003</v>
+        <v>5.56840515136719</v>
       </c>
       <c r="H481" t="n">
         <v>1500</v>
@@ -14347,7 +14347,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G482" t="n">
-        <v>5.60516023635864</v>
+        <v>5.6051607131958</v>
       </c>
       <c r="H482" t="n">
         <v>1000</v>
@@ -14376,7 +14376,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>5.60516023635864</v>
+        <v>5.6051607131958</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14405,7 +14405,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G484" t="n">
-        <v>5.60516023635864</v>
+        <v>5.6051607131958</v>
       </c>
       <c r="H484" t="n">
         <v>0</v>
@@ -14724,7 +14724,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G495" t="n">
-        <v>5.73380279541016</v>
+        <v>5.73380327224731</v>
       </c>
       <c r="H495" t="n">
         <v>2000</v>
@@ -14753,7 +14753,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G496" t="n">
-        <v>5.73380279541016</v>
+        <v>5.73380327224731</v>
       </c>
       <c r="H496" t="n">
         <v>0</v>
@@ -14782,7 +14782,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G497" t="n">
-        <v>5.73380279541016</v>
+        <v>5.73380327224731</v>
       </c>
       <c r="H497" t="n">
         <v>0</v>
@@ -14898,7 +14898,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G501" t="n">
-        <v>5.42138481140137</v>
+        <v>5.42138433456421</v>
       </c>
       <c r="H501" t="n">
         <v>500</v>
@@ -14927,7 +14927,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G502" t="n">
-        <v>5.42138481140137</v>
+        <v>5.42138433456421</v>
       </c>
       <c r="H502" t="n">
         <v>0</v>
@@ -14956,7 +14956,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G503" t="n">
-        <v>5.42138481140137</v>
+        <v>5.42138433456421</v>
       </c>
       <c r="H503" t="n">
         <v>0</v>
@@ -14985,7 +14985,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>5.42138481140137</v>
+        <v>5.42138433456421</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15014,7 +15014,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>5.36625242233276</v>
+        <v>5.36625146865845</v>
       </c>
       <c r="H505" t="n">
         <v>1000</v>
@@ -15043,7 +15043,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G506" t="n">
-        <v>5.32949733734131</v>
+        <v>5.32949638366699</v>
       </c>
       <c r="H506" t="n">
         <v>1000</v>
@@ -15072,7 +15072,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>5.32949733734131</v>
+        <v>5.32949638366699</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -15101,7 +15101,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>5.55002784729004</v>
+        <v>5.55002737045288</v>
       </c>
       <c r="H508" t="n">
         <v>500</v>
@@ -15275,7 +15275,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G514" t="n">
-        <v>5.55002784729004</v>
+        <v>5.55002737045288</v>
       </c>
       <c r="H514" t="n">
         <v>1000</v>
@@ -15507,7 +15507,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G522" t="n">
-        <v>5.60516023635864</v>
+        <v>5.6051607131958</v>
       </c>
       <c r="H522" t="n">
         <v>500</v>
@@ -15536,7 +15536,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>5.60516023635864</v>
+        <v>5.6051607131958</v>
       </c>
       <c r="H523" t="n">
         <v>0</v>
@@ -15565,7 +15565,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G524" t="n">
-        <v>5.60516023635864</v>
+        <v>5.6051607131958</v>
       </c>
       <c r="H524" t="n">
         <v>0</v>
@@ -15884,7 +15884,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H535" t="n">
         <v>500</v>
@@ -15913,7 +15913,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G536" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H536" t="n">
         <v>0</v>
@@ -15942,7 +15942,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G537" t="n">
-        <v>5.6602931022644</v>
+        <v>5.66029262542725</v>
       </c>
       <c r="H537" t="n">
         <v>5000</v>
@@ -15971,7 +15971,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G538" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H538" t="n">
         <v>1000</v>
@@ -16000,7 +16000,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G539" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H539" t="n">
         <v>0</v>
@@ -16029,7 +16029,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G540" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H540" t="n">
         <v>0</v>
@@ -16058,7 +16058,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G541" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -16116,7 +16116,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G543" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H543" t="n">
         <v>0</v>
@@ -16145,7 +16145,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G544" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H544" t="n">
         <v>0</v>
@@ -16174,7 +16174,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G545" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H546" t="n">
         <v>0</v>
@@ -16232,7 +16232,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G547" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G548" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H548" t="n">
         <v>1500</v>
@@ -16290,7 +16290,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G549" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H549" t="n">
         <v>0</v>
@@ -16319,7 +16319,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G550" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -16348,7 +16348,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G551" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H551" t="n">
         <v>0</v>
@@ -16377,7 +16377,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G552" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H552" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G553" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -16435,7 +16435,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G554" t="n">
-        <v>5.60516023635864</v>
+        <v>5.6051607131958</v>
       </c>
       <c r="H554" t="n">
         <v>1000</v>
@@ -16464,7 +16464,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G555" t="n">
-        <v>5.60516023635864</v>
+        <v>5.6051607131958</v>
       </c>
       <c r="H555" t="n">
         <v>0</v>
@@ -16493,7 +16493,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G556" t="n">
-        <v>5.60516023635864</v>
+        <v>5.6051607131958</v>
       </c>
       <c r="H556" t="n">
         <v>0</v>
@@ -16522,7 +16522,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G557" t="n">
-        <v>5.60516023635864</v>
+        <v>5.6051607131958</v>
       </c>
       <c r="H557" t="n">
         <v>0</v>
@@ -16551,7 +16551,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G558" t="n">
-        <v>5.60516023635864</v>
+        <v>5.6051607131958</v>
       </c>
       <c r="H558" t="n">
         <v>0</v>
@@ -16580,7 +16580,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G559" t="n">
-        <v>5.60516023635864</v>
+        <v>5.6051607131958</v>
       </c>
       <c r="H559" t="n">
         <v>0</v>
@@ -16609,7 +16609,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G560" t="n">
-        <v>5.60516023635864</v>
+        <v>5.6051607131958</v>
       </c>
       <c r="H560" t="n">
         <v>0</v>
@@ -16638,7 +16638,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G561" t="n">
-        <v>5.60516023635864</v>
+        <v>5.6051607131958</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -16667,7 +16667,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G562" t="n">
-        <v>5.60516023635864</v>
+        <v>5.6051607131958</v>
       </c>
       <c r="H562" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G568" t="n">
-        <v>5.43976211547852</v>
+        <v>5.43976259231567</v>
       </c>
       <c r="H568" t="n">
         <v>500</v>
@@ -17189,7 +17189,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G580" t="n">
-        <v>5.60516023635864</v>
+        <v>5.6051607131958</v>
       </c>
       <c r="H580" t="n">
         <v>6500</v>
@@ -17218,7 +17218,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G581" t="n">
-        <v>5.60516023635864</v>
+        <v>5.6051607131958</v>
       </c>
       <c r="H581" t="n">
         <v>0</v>
@@ -17276,7 +17276,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G583" t="n">
-        <v>5.42138481140137</v>
+        <v>5.42138433456421</v>
       </c>
       <c r="H583" t="n">
         <v>1500</v>
@@ -17305,7 +17305,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G584" t="n">
-        <v>5.42138481140137</v>
+        <v>5.42138433456421</v>
       </c>
       <c r="H584" t="n">
         <v>0</v>
@@ -17334,7 +17334,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G585" t="n">
-        <v>5.60516023635864</v>
+        <v>5.6051607131958</v>
       </c>
       <c r="H585" t="n">
         <v>2000</v>
@@ -17363,7 +17363,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G586" t="n">
-        <v>5.4673285484314</v>
+        <v>5.46732807159424</v>
       </c>
       <c r="H586" t="n">
         <v>500</v>
@@ -17392,7 +17392,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G587" t="n">
-        <v>5.4673285484314</v>
+        <v>5.46732807159424</v>
       </c>
       <c r="H587" t="n">
         <v>0</v>
@@ -17421,7 +17421,7 @@
         <v>5.75</v>
       </c>
       <c r="G588" t="n">
-        <v>5.2835521697998</v>
+        <v>5.28355264663696</v>
       </c>
       <c r="H588" t="n">
         <v>2000</v>
@@ -17450,7 +17450,7 @@
         <v>5.75</v>
       </c>
       <c r="G589" t="n">
-        <v>5.2835521697998</v>
+        <v>5.28355264663696</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -17479,7 +17479,7 @@
         <v>5.75</v>
       </c>
       <c r="G590" t="n">
-        <v>5.2835521697998</v>
+        <v>5.28355264663696</v>
       </c>
       <c r="H590" t="n">
         <v>0</v>
@@ -17508,7 +17508,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G591" t="n">
-        <v>5.4673285484314</v>
+        <v>5.46732807159424</v>
       </c>
       <c r="H591" t="n">
         <v>500</v>
@@ -17537,7 +17537,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G592" t="n">
-        <v>5.4673285484314</v>
+        <v>5.46732807159424</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -17566,7 +17566,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G593" t="n">
-        <v>5.4673285484314</v>
+        <v>5.46732807159424</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G594" t="n">
-        <v>5.4673285484314</v>
+        <v>5.46732807159424</v>
       </c>
       <c r="H594" t="n">
         <v>1000</v>
@@ -17624,7 +17624,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G595" t="n">
-        <v>5.4673285484314</v>
+        <v>5.46732807159424</v>
       </c>
       <c r="H595" t="n">
         <v>0</v>
@@ -17653,7 +17653,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G596" t="n">
-        <v>5.4673285484314</v>
+        <v>5.46732807159424</v>
       </c>
       <c r="H596" t="n">
         <v>0</v>
@@ -17682,7 +17682,7 @@
         <v>5.75</v>
       </c>
       <c r="G597" t="n">
-        <v>5.2835521697998</v>
+        <v>5.28355264663696</v>
       </c>
       <c r="H597" t="n">
         <v>1000</v>
@@ -17711,7 +17711,7 @@
         <v>5.75</v>
       </c>
       <c r="G598" t="n">
-        <v>5.2835521697998</v>
+        <v>5.28355264663696</v>
       </c>
       <c r="H598" t="n">
         <v>0</v>
@@ -17740,7 +17740,7 @@
         <v>5.75</v>
       </c>
       <c r="G599" t="n">
-        <v>5.2835521697998</v>
+        <v>5.28355264663696</v>
       </c>
       <c r="H599" t="n">
         <v>0</v>
@@ -17827,7 +17827,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G602" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H602" t="n">
         <v>500</v>
@@ -17856,7 +17856,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G603" t="n">
-        <v>5.25564670562744</v>
+        <v>5.25564622879028</v>
       </c>
       <c r="H603" t="n">
         <v>500</v>
@@ -17885,7 +17885,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G604" t="n">
-        <v>5.25564670562744</v>
+        <v>5.25564622879028</v>
       </c>
       <c r="H604" t="n">
         <v>0</v>
@@ -17914,7 +17914,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G605" t="n">
-        <v>5.48819732666016</v>
+        <v>5.488196849823</v>
       </c>
       <c r="H605" t="n">
         <v>3000</v>
@@ -17943,7 +17943,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>5.48819732666016</v>
+        <v>5.488196849823</v>
       </c>
       <c r="H606" t="n">
         <v>0</v>
@@ -17972,7 +17972,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G607" t="n">
-        <v>5.48819732666016</v>
+        <v>5.488196849823</v>
       </c>
       <c r="H607" t="n">
         <v>0</v>
@@ -18001,7 +18001,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G608" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H608" t="n">
         <v>2000</v>
@@ -18030,7 +18030,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G609" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H609" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G616" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H616" t="n">
         <v>500</v>
@@ -18262,7 +18262,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G617" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H617" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G618" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -18320,7 +18320,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G619" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -18349,7 +18349,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G620" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H620" t="n">
         <v>0</v>
@@ -18378,7 +18378,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G621" t="n">
-        <v>5.39517736434937</v>
+        <v>5.39517688751221</v>
       </c>
       <c r="H621" t="n">
         <v>1000</v>
@@ -18407,7 +18407,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G622" t="n">
-        <v>5.53470754623413</v>
+        <v>5.53470706939697</v>
       </c>
       <c r="H622" t="n">
         <v>3500</v>
@@ -18436,7 +18436,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G623" t="n">
-        <v>5.48819732666016</v>
+        <v>5.488196849823</v>
       </c>
       <c r="H623" t="n">
         <v>500</v>
@@ -18523,7 +18523,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G626" t="n">
-        <v>5.48819732666016</v>
+        <v>5.488196849823</v>
       </c>
       <c r="H626" t="n">
         <v>2500</v>
@@ -18552,7 +18552,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G627" t="n">
-        <v>5.48819732666016</v>
+        <v>5.488196849823</v>
       </c>
       <c r="H627" t="n">
         <v>0</v>
@@ -18581,7 +18581,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G628" t="n">
-        <v>5.48819732666016</v>
+        <v>5.488196849823</v>
       </c>
       <c r="H628" t="n">
         <v>5500</v>
@@ -18610,7 +18610,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G629" t="n">
-        <v>5.39517736434937</v>
+        <v>5.39517688751221</v>
       </c>
       <c r="H629" t="n">
         <v>2000</v>
@@ -18639,7 +18639,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G630" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H630" t="n">
         <v>500</v>
@@ -18668,7 +18668,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G631" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H631" t="n">
         <v>1000</v>
@@ -18697,7 +18697,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G632" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H632" t="n">
         <v>500</v>
@@ -18726,7 +18726,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G633" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H633" t="n">
         <v>0</v>
@@ -18755,7 +18755,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G634" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H634" t="n">
         <v>0</v>
@@ -18784,7 +18784,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G635" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H635" t="n">
         <v>0</v>
@@ -18871,7 +18871,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G638" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H638" t="n">
         <v>5500</v>
@@ -18900,7 +18900,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G639" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H639" t="n">
         <v>3250</v>
@@ -18929,7 +18929,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G640" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H640" t="n">
         <v>0</v>
@@ -18958,7 +18958,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G641" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H641" t="n">
         <v>0</v>
@@ -18987,7 +18987,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G642" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H642" t="n">
         <v>0</v>
@@ -19016,7 +19016,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G643" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H643" t="n">
         <v>0</v>
@@ -19045,7 +19045,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G644" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H644" t="n">
         <v>2000</v>
@@ -19074,7 +19074,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G645" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H645" t="n">
         <v>0</v>
@@ -19103,7 +19103,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H646" t="n">
         <v>0</v>
@@ -19132,7 +19132,7 @@
         <v>5.25</v>
       </c>
       <c r="G647" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H647" t="n">
         <v>10000</v>
@@ -19161,7 +19161,7 @@
         <v>5.25</v>
       </c>
       <c r="G648" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H648" t="n">
         <v>12500</v>
@@ -19190,7 +19190,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G649" t="n">
-        <v>4.50218200683594</v>
+        <v>4.5021824836731</v>
       </c>
       <c r="H649" t="n">
         <v>67000</v>
@@ -19219,7 +19219,7 @@
         <v>5</v>
       </c>
       <c r="G650" t="n">
-        <v>4.65101480484009</v>
+        <v>4.65101432800293</v>
       </c>
       <c r="H650" t="n">
         <v>8500</v>
@@ -19248,7 +19248,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G651" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H651" t="n">
         <v>9500</v>
@@ -19364,7 +19364,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H655" t="n">
         <v>1500</v>
@@ -19393,7 +19393,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G656" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H656" t="n">
         <v>0</v>
@@ -19451,7 +19451,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G658" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H658" t="n">
         <v>500</v>
@@ -19480,7 +19480,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G659" t="n">
-        <v>5.25564670562744</v>
+        <v>5.25564622879028</v>
       </c>
       <c r="H659" t="n">
         <v>2250</v>
@@ -19509,7 +19509,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G660" t="n">
-        <v>5.25564670562744</v>
+        <v>5.25564622879028</v>
       </c>
       <c r="H660" t="n">
         <v>1500</v>
@@ -19538,7 +19538,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G661" t="n">
-        <v>5.25564670562744</v>
+        <v>5.25564622879028</v>
       </c>
       <c r="H661" t="n">
         <v>0</v>
@@ -19567,7 +19567,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G662" t="n">
-        <v>5.25564670562744</v>
+        <v>5.25564622879028</v>
       </c>
       <c r="H662" t="n">
         <v>0</v>
@@ -19654,7 +19654,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G665" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H665" t="n">
         <v>500</v>
@@ -19712,7 +19712,7 @@
         <v>5.25</v>
       </c>
       <c r="G667" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H667" t="n">
         <v>7250</v>
@@ -19770,7 +19770,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G669" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H669" t="n">
         <v>500</v>
@@ -19799,7 +19799,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H670" t="n">
         <v>0</v>
@@ -19828,7 +19828,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H671" t="n">
         <v>0</v>
@@ -20002,7 +20002,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H677" t="n">
         <v>19750</v>
@@ -20031,7 +20031,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H678" t="n">
         <v>1750</v>
@@ -20350,7 +20350,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G689" t="n">
-        <v>5.39517736434937</v>
+        <v>5.39517688751221</v>
       </c>
       <c r="H689" t="n">
         <v>1250</v>
@@ -20379,7 +20379,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G690" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H690" t="n">
         <v>3000</v>
@@ -20437,7 +20437,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G692" t="n">
-        <v>5.25564670562744</v>
+        <v>5.25564622879028</v>
       </c>
       <c r="H692" t="n">
         <v>500</v>
@@ -20785,7 +20785,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G704" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403429031372</v>
       </c>
       <c r="H704" t="n">
         <v>41750</v>
@@ -20814,7 +20814,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G705" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403429031372</v>
       </c>
       <c r="H705" t="n">
         <v>7500</v>
@@ -20843,7 +20843,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G706" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403429031372</v>
       </c>
       <c r="H706" t="n">
         <v>2500</v>
@@ -20872,7 +20872,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G707" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403429031372</v>
       </c>
       <c r="H707" t="n">
         <v>7500</v>
@@ -20901,7 +20901,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G708" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403429031372</v>
       </c>
       <c r="H708" t="n">
         <v>2250</v>
@@ -20930,7 +20930,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G709" t="n">
-        <v>4.52078580856323</v>
+        <v>4.52078628540039</v>
       </c>
       <c r="H709" t="n">
         <v>36250</v>
@@ -21075,7 +21075,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G714" t="n">
-        <v>4.5579948425293</v>
+        <v>4.55799436569214</v>
       </c>
       <c r="H714" t="n">
         <v>4500</v>
@@ -21133,7 +21133,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G716" t="n">
-        <v>4.46497392654419</v>
+        <v>4.46497440338135</v>
       </c>
       <c r="H716" t="n">
         <v>22500</v>
@@ -21162,7 +21162,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G717" t="n">
-        <v>4.63241052627563</v>
+        <v>4.63241100311279</v>
       </c>
       <c r="H717" t="n">
         <v>1000</v>
@@ -21191,7 +21191,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G718" t="n">
-        <v>4.63241052627563</v>
+        <v>4.63241100311279</v>
       </c>
       <c r="H718" t="n">
         <v>0</v>
@@ -21220,7 +21220,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G719" t="n">
-        <v>4.63241052627563</v>
+        <v>4.63241100311279</v>
       </c>
       <c r="H719" t="n">
         <v>0</v>
@@ -21249,7 +21249,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G720" t="n">
-        <v>4.63241052627563</v>
+        <v>4.63241100311279</v>
       </c>
       <c r="H720" t="n">
         <v>0</v>
@@ -21278,7 +21278,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G721" t="n">
-        <v>4.37195348739624</v>
+        <v>4.3719539642334</v>
       </c>
       <c r="H721" t="n">
         <v>3000</v>
@@ -21423,7 +21423,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G726" t="n">
-        <v>4.05568504333496</v>
+        <v>4.0556845664978</v>
       </c>
       <c r="H726" t="n">
         <v>6000</v>
@@ -21510,7 +21510,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>4.27893352508545</v>
+        <v>4.27893304824829</v>
       </c>
       <c r="H729" t="n">
         <v>1250</v>
@@ -21539,7 +21539,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G730" t="n">
-        <v>4.27893352508545</v>
+        <v>4.27893304824829</v>
       </c>
       <c r="H730" t="n">
         <v>0</v>
@@ -21655,7 +21655,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G734" t="n">
-        <v>4.37195348739624</v>
+        <v>4.3719539642334</v>
       </c>
       <c r="H734" t="n">
         <v>250</v>
@@ -21684,7 +21684,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G735" t="n">
-        <v>4.37195348739624</v>
+        <v>4.3719539642334</v>
       </c>
       <c r="H735" t="n">
         <v>0</v>
@@ -21713,7 +21713,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G736" t="n">
-        <v>4.37195348739624</v>
+        <v>4.3719539642334</v>
       </c>
       <c r="H736" t="n">
         <v>0</v>
@@ -21742,7 +21742,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G737" t="n">
-        <v>4.37195348739624</v>
+        <v>4.3719539642334</v>
       </c>
       <c r="H737" t="n">
         <v>0</v>
@@ -21771,7 +21771,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G738" t="n">
-        <v>4.37195348739624</v>
+        <v>4.3719539642334</v>
       </c>
       <c r="H738" t="n">
         <v>0</v>
@@ -21800,7 +21800,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G739" t="n">
-        <v>4.37195348739624</v>
+        <v>4.3719539642334</v>
       </c>
       <c r="H739" t="n">
         <v>0</v>
@@ -21829,7 +21829,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G740" t="n">
-        <v>4.44637012481689</v>
+        <v>4.44636964797974</v>
       </c>
       <c r="H740" t="n">
         <v>750</v>
@@ -22119,7 +22119,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G750" t="n">
-        <v>4.37195348739624</v>
+        <v>4.3719539642334</v>
       </c>
       <c r="H750" t="n">
         <v>750</v>
@@ -22148,7 +22148,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G751" t="n">
-        <v>4.37195348739624</v>
+        <v>4.3719539642334</v>
       </c>
       <c r="H751" t="n">
         <v>0</v>
@@ -22177,7 +22177,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G752" t="n">
-        <v>4.37195348739624</v>
+        <v>4.3719539642334</v>
       </c>
       <c r="H752" t="n">
         <v>0</v>
@@ -22206,7 +22206,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G753" t="n">
-        <v>4.42776584625244</v>
+        <v>4.4277663230896</v>
       </c>
       <c r="H753" t="n">
         <v>2250</v>
@@ -22264,7 +22264,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G755" t="n">
-        <v>4.42776584625244</v>
+        <v>4.4277663230896</v>
       </c>
       <c r="H755" t="n">
         <v>3250</v>
@@ -22293,7 +22293,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G756" t="n">
-        <v>4.42776584625244</v>
+        <v>4.4277663230896</v>
       </c>
       <c r="H756" t="n">
         <v>0</v>
@@ -22322,7 +22322,7 @@
         <v>5</v>
       </c>
       <c r="G757" t="n">
-        <v>4.65101480484009</v>
+        <v>4.65101432800293</v>
       </c>
       <c r="H757" t="n">
         <v>2750</v>
@@ -22409,7 +22409,7 @@
         <v>5.25</v>
       </c>
       <c r="G760" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H760" t="n">
         <v>3000</v>
@@ -22438,7 +22438,7 @@
         <v>5.25</v>
       </c>
       <c r="G761" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H761" t="n">
         <v>2000</v>
@@ -22467,7 +22467,7 @@
         <v>5.25</v>
       </c>
       <c r="G762" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H762" t="n">
         <v>500</v>
@@ -22496,7 +22496,7 @@
         <v>5.25</v>
       </c>
       <c r="G763" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H763" t="n">
         <v>250</v>
@@ -22525,7 +22525,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G764" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403429031372</v>
       </c>
       <c r="H764" t="n">
         <v>4000</v>
@@ -22554,7 +22554,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G765" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403429031372</v>
       </c>
       <c r="H765" t="n">
         <v>0</v>
@@ -22583,7 +22583,7 @@
         <v>5.25</v>
       </c>
       <c r="G766" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H766" t="n">
         <v>2750</v>
@@ -22612,7 +22612,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G767" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H767" t="n">
         <v>6000</v>
@@ -22641,7 +22641,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H768" t="n">
         <v>500</v>
@@ -22670,7 +22670,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G769" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H769" t="n">
         <v>0</v>
@@ -22728,7 +22728,7 @@
         <v>5.25</v>
       </c>
       <c r="G771" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H771" t="n">
         <v>7500</v>
@@ -22757,7 +22757,7 @@
         <v>5.25</v>
       </c>
       <c r="G772" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H772" t="n">
         <v>0</v>
@@ -22786,7 +22786,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G773" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H773" t="n">
         <v>3750</v>
@@ -23047,7 +23047,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G782" t="n">
-        <v>5.39517736434937</v>
+        <v>5.39517688751221</v>
       </c>
       <c r="H782" t="n">
         <v>1750</v>
@@ -23076,7 +23076,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G783" t="n">
-        <v>5.6742377281189</v>
+        <v>5.67423820495605</v>
       </c>
       <c r="H783" t="n">
         <v>6750</v>
@@ -23105,7 +23105,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G784" t="n">
-        <v>5.76725769042969</v>
+        <v>5.76725816726685</v>
       </c>
       <c r="H784" t="n">
         <v>14500</v>
@@ -23134,7 +23134,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G785" t="n">
-        <v>5.9998083114624</v>
+        <v>5.99980878829956</v>
       </c>
       <c r="H785" t="n">
         <v>6250</v>
@@ -23221,7 +23221,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G788" t="n">
-        <v>5.86027812957764</v>
+        <v>5.86027860641479</v>
       </c>
       <c r="H788" t="n">
         <v>3250</v>
@@ -23250,7 +23250,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G789" t="n">
-        <v>5.86027812957764</v>
+        <v>5.86027860641479</v>
       </c>
       <c r="H789" t="n">
         <v>1500</v>
@@ -23279,7 +23279,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G790" t="n">
-        <v>5.76725769042969</v>
+        <v>5.76725816726685</v>
       </c>
       <c r="H790" t="n">
         <v>7750</v>
@@ -23308,7 +23308,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G791" t="n">
-        <v>5.86027812957764</v>
+        <v>5.86027860641479</v>
       </c>
       <c r="H791" t="n">
         <v>4750</v>
@@ -23366,7 +23366,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G793" t="n">
-        <v>5.6742377281189</v>
+        <v>5.67423820495605</v>
       </c>
       <c r="H793" t="n">
         <v>1250</v>
@@ -23511,7 +23511,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G798" t="n">
-        <v>5.39517736434937</v>
+        <v>5.39517688751221</v>
       </c>
       <c r="H798" t="n">
         <v>1000</v>
@@ -23627,7 +23627,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G802" t="n">
-        <v>5.53470754623413</v>
+        <v>5.53470706939697</v>
       </c>
       <c r="H802" t="n">
         <v>750</v>
@@ -23656,7 +23656,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G803" t="n">
-        <v>5.39517736434937</v>
+        <v>5.39517688751221</v>
       </c>
       <c r="H803" t="n">
         <v>750</v>
@@ -23714,7 +23714,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G805" t="n">
-        <v>5.39517736434937</v>
+        <v>5.39517688751221</v>
       </c>
       <c r="H805" t="n">
         <v>2750</v>
@@ -23743,7 +23743,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G806" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H806" t="n">
         <v>1750</v>
@@ -23772,7 +23772,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G807" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H807" t="n">
         <v>0</v>
@@ -23801,7 +23801,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G808" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H808" t="n">
         <v>0</v>
@@ -23830,7 +23830,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G809" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H809" t="n">
         <v>0</v>
@@ -23859,7 +23859,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G810" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H810" t="n">
         <v>1500</v>
@@ -23917,7 +23917,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G812" t="n">
-        <v>5.25564670562744</v>
+        <v>5.25564622879028</v>
       </c>
       <c r="H812" t="n">
         <v>750</v>
@@ -23946,7 +23946,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G813" t="n">
-        <v>5.25564670562744</v>
+        <v>5.25564622879028</v>
       </c>
       <c r="H813" t="n">
         <v>0</v>
@@ -23975,7 +23975,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G814" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H814" t="n">
         <v>3250</v>
@@ -24004,7 +24004,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G815" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H815" t="n">
         <v>0</v>
@@ -24120,7 +24120,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G819" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H819" t="n">
         <v>1000</v>
@@ -24352,7 +24352,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G827" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H827" t="n">
         <v>250</v>
@@ -24439,7 +24439,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G830" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H830" t="n">
         <v>9000</v>
@@ -24497,7 +24497,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G832" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H832" t="n">
         <v>750</v>
@@ -24526,7 +24526,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G833" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H833" t="n">
         <v>500</v>
@@ -24555,7 +24555,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G834" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -24584,7 +24584,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G835" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403429031372</v>
       </c>
       <c r="H835" t="n">
         <v>1000</v>
@@ -24613,7 +24613,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G836" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403429031372</v>
       </c>
       <c r="H836" t="n">
         <v>1000</v>
@@ -24642,7 +24642,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G837" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H837" t="n">
         <v>1500</v>
@@ -24816,7 +24816,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G843" t="n">
-        <v>4.63241052627563</v>
+        <v>4.63241100311279</v>
       </c>
       <c r="H843" t="n">
         <v>2750</v>
@@ -24845,7 +24845,7 @@
         <v>5</v>
       </c>
       <c r="G844" t="n">
-        <v>4.65101480484009</v>
+        <v>4.65101432800293</v>
       </c>
       <c r="H844" t="n">
         <v>250</v>
@@ -24874,7 +24874,7 @@
         <v>5</v>
       </c>
       <c r="G845" t="n">
-        <v>4.65101480484009</v>
+        <v>4.65101432800293</v>
       </c>
       <c r="H845" t="n">
         <v>0</v>
@@ -24903,7 +24903,7 @@
         <v>5</v>
       </c>
       <c r="G846" t="n">
-        <v>4.65101480484009</v>
+        <v>4.65101432800293</v>
       </c>
       <c r="H846" t="n">
         <v>500</v>
@@ -24932,7 +24932,7 @@
         <v>5</v>
       </c>
       <c r="G847" t="n">
-        <v>4.65101480484009</v>
+        <v>4.65101432800293</v>
       </c>
       <c r="H847" t="n">
         <v>0</v>
@@ -24990,7 +24990,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G849" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H849" t="n">
         <v>500</v>
@@ -25019,7 +25019,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G850" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H850" t="n">
         <v>1000</v>
@@ -25048,7 +25048,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G851" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H851" t="n">
         <v>1000</v>
@@ -43179,6 +43179,35 @@
         <v>250</v>
       </c>
       <c r="I1476" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1477" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1477" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="D1477" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="E1477" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="F1477" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="G1477" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="H1477" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I1477" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PLN.MI.xlsx
+++ b/data/PLN.MI.xlsx
@@ -456,7 +456,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1165771484375</v>
+        <v>4.11657667160034</v>
       </c>
       <c r="H3" t="n">
         <v>8500</v>
@@ -572,7 +572,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G7" t="n">
-        <v>4.19927549362183</v>
+        <v>4.19927597045898</v>
       </c>
       <c r="H7" t="n">
         <v>11500</v>
@@ -601,7 +601,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G8" t="n">
-        <v>4.15333223342896</v>
+        <v>4.1533317565918</v>
       </c>
       <c r="H8" t="n">
         <v>6500</v>
@@ -659,7 +659,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G10" t="n">
-        <v>4.04306602478027</v>
+        <v>4.04306650161743</v>
       </c>
       <c r="H10" t="n">
         <v>53000</v>
@@ -717,7 +717,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G12" t="n">
-        <v>3.96955609321594</v>
+        <v>3.96955585479736</v>
       </c>
       <c r="H12" t="n">
         <v>26000</v>
@@ -746,7 +746,7 @@
         <v>4.25</v>
       </c>
       <c r="G13" t="n">
-        <v>3.90523433685303</v>
+        <v>3.90523457527161</v>
       </c>
       <c r="H13" t="n">
         <v>19500</v>
@@ -775,7 +775,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G14" t="n">
-        <v>3.95117878913879</v>
+        <v>3.95117902755737</v>
       </c>
       <c r="H14" t="n">
         <v>19000</v>
@@ -804,7 +804,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G15" t="n">
-        <v>3.89604544639587</v>
+        <v>3.89604520797729</v>
       </c>
       <c r="H15" t="n">
         <v>12500</v>
@@ -833,7 +833,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G16" t="n">
-        <v>3.84091258049011</v>
+        <v>3.84091281890869</v>
       </c>
       <c r="H16" t="n">
         <v>21500</v>
@@ -862,7 +862,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G17" t="n">
-        <v>3.81334686279297</v>
+        <v>3.81334662437439</v>
       </c>
       <c r="H17" t="n">
         <v>19000</v>
@@ -891,7 +891,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G18" t="n">
-        <v>3.72145891189575</v>
+        <v>3.72145915031433</v>
       </c>
       <c r="H18" t="n">
         <v>43500</v>
@@ -920,7 +920,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G19" t="n">
-        <v>3.95117878913879</v>
+        <v>3.95117902755737</v>
       </c>
       <c r="H19" t="n">
         <v>44000</v>
@@ -949,7 +949,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G20" t="n">
-        <v>3.87766790390015</v>
+        <v>3.87766814231873</v>
       </c>
       <c r="H20" t="n">
         <v>12000</v>
@@ -978,7 +978,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G21" t="n">
-        <v>3.87766790390015</v>
+        <v>3.87766814231873</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G22" t="n">
-        <v>3.87766790390015</v>
+        <v>3.87766814231873</v>
       </c>
       <c r="H22" t="n">
         <v>60000</v>
@@ -1036,7 +1036,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G23" t="n">
-        <v>3.85010194778442</v>
+        <v>3.85010170936584</v>
       </c>
       <c r="H23" t="n">
         <v>32000</v>
@@ -1065,7 +1065,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G24" t="n">
-        <v>3.88685703277588</v>
+        <v>3.8868567943573</v>
       </c>
       <c r="H24" t="n">
         <v>500</v>
@@ -1094,7 +1094,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>3.98793435096741</v>
+        <v>3.98793411254883</v>
       </c>
       <c r="H25" t="n">
         <v>7500</v>
@@ -1123,7 +1123,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G26" t="n">
-        <v>4.18089866638184</v>
+        <v>4.18089818954468</v>
       </c>
       <c r="H26" t="n">
         <v>15000</v>
@@ -1239,7 +1239,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G30" t="n">
-        <v>4.18089866638184</v>
+        <v>4.18089818954468</v>
       </c>
       <c r="H30" t="n">
         <v>3500</v>
@@ -1268,7 +1268,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G31" t="n">
-        <v>4.15333223342896</v>
+        <v>4.1533317565918</v>
       </c>
       <c r="H31" t="n">
         <v>9000</v>
@@ -1326,7 +1326,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>4.15333223342896</v>
+        <v>4.1533317565918</v>
       </c>
       <c r="H33" t="n">
         <v>2000</v>
@@ -1384,7 +1384,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>4.1165771484375</v>
+        <v>4.11657667160034</v>
       </c>
       <c r="H35" t="n">
         <v>27500</v>
@@ -1500,7 +1500,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G39" t="n">
-        <v>4.09819841384888</v>
+        <v>4.09819936752319</v>
       </c>
       <c r="H39" t="n">
         <v>3500</v>
@@ -1529,7 +1529,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>4.09819841384888</v>
+        <v>4.09819936752319</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>4.08901071548462</v>
+        <v>4.08901023864746</v>
       </c>
       <c r="H43" t="n">
         <v>2000</v>
@@ -1645,7 +1645,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>4.08901071548462</v>
+        <v>4.08901023864746</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G46" t="n">
-        <v>3.95117878913879</v>
+        <v>3.95117902755737</v>
       </c>
       <c r="H46" t="n">
         <v>4000</v>
@@ -1732,7 +1732,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G47" t="n">
-        <v>3.99712228775024</v>
+        <v>3.99712181091309</v>
       </c>
       <c r="H47" t="n">
         <v>3000</v>
@@ -1761,7 +1761,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G48" t="n">
-        <v>3.95117878913879</v>
+        <v>3.95117902755737</v>
       </c>
       <c r="H48" t="n">
         <v>2000</v>
@@ -1790,7 +1790,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G49" t="n">
-        <v>3.95117878913879</v>
+        <v>3.95117902755737</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>4.04306602478027</v>
+        <v>4.04306650161743</v>
       </c>
       <c r="H50" t="n">
         <v>3000</v>
@@ -1848,7 +1848,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G51" t="n">
-        <v>3.89604544639587</v>
+        <v>3.89604520797729</v>
       </c>
       <c r="H51" t="n">
         <v>31000</v>
@@ -1877,7 +1877,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>3.92361235618591</v>
+        <v>3.92361211776733</v>
       </c>
       <c r="H52" t="n">
         <v>9500</v>
@@ -1906,7 +1906,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G53" t="n">
-        <v>3.89604544639587</v>
+        <v>3.89604520797729</v>
       </c>
       <c r="H53" t="n">
         <v>11000</v>
@@ -1993,7 +1993,7 @@
         <v>4.25</v>
       </c>
       <c r="G56" t="n">
-        <v>3.90523433685303</v>
+        <v>3.90523457527161</v>
       </c>
       <c r="H56" t="n">
         <v>7500</v>
@@ -2022,7 +2022,7 @@
         <v>4.25</v>
       </c>
       <c r="G57" t="n">
-        <v>3.90523433685303</v>
+        <v>3.90523457527161</v>
       </c>
       <c r="H57" t="n">
         <v>3000</v>
@@ -2051,7 +2051,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>3.95117878913879</v>
+        <v>3.95117902755737</v>
       </c>
       <c r="H58" t="n">
         <v>3500</v>
@@ -2080,7 +2080,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>3.95117878913879</v>
+        <v>3.95117902755737</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G61" t="n">
-        <v>3.99712228775024</v>
+        <v>3.99712181091309</v>
       </c>
       <c r="H61" t="n">
         <v>7000</v>
@@ -2167,7 +2167,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G62" t="n">
-        <v>3.93280100822449</v>
+        <v>3.93280076980591</v>
       </c>
       <c r="H62" t="n">
         <v>40500</v>
@@ -2283,7 +2283,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G66" t="n">
-        <v>4.16252040863037</v>
+        <v>4.16252088546753</v>
       </c>
       <c r="H66" t="n">
         <v>21000</v>
@@ -2457,7 +2457,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G72" t="n">
-        <v>4.66790390014648</v>
+        <v>4.66790342330933</v>
       </c>
       <c r="H72" t="n">
         <v>16500</v>
@@ -2515,7 +2515,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G74" t="n">
-        <v>4.81492471694946</v>
+        <v>4.8149242401123</v>
       </c>
       <c r="H74" t="n">
         <v>1500</v>
@@ -2544,7 +2544,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>4.61277103424072</v>
+        <v>4.61277151107788</v>
       </c>
       <c r="H75" t="n">
         <v>9500</v>
@@ -2660,7 +2660,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G79" t="n">
-        <v>4.81492471694946</v>
+        <v>4.8149242401123</v>
       </c>
       <c r="H79" t="n">
         <v>11500</v>
@@ -2834,7 +2834,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G85" t="n">
-        <v>4.96194553375244</v>
+        <v>4.96194505691528</v>
       </c>
       <c r="H85" t="n">
         <v>27000</v>
@@ -2892,7 +2892,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G87" t="n">
-        <v>5.311119556427</v>
+        <v>5.31111907958984</v>
       </c>
       <c r="H87" t="n">
         <v>23500</v>
@@ -2950,7 +2950,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G89" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H89" t="n">
         <v>78500</v>
@@ -2979,7 +2979,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>5.9359564781189</v>
+        <v>5.93595695495605</v>
       </c>
       <c r="H90" t="n">
         <v>72500</v>
@@ -3008,7 +3008,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G91" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H91" t="n">
         <v>34500</v>
@@ -3066,7 +3066,7 @@
         <v>7</v>
       </c>
       <c r="G93" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H93" t="n">
         <v>93500</v>
@@ -3095,7 +3095,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G94" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H94" t="n">
         <v>29500</v>
@@ -3153,7 +3153,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>6.45052814483643</v>
+        <v>6.45052862167358</v>
       </c>
       <c r="H96" t="n">
         <v>59500</v>
@@ -3182,7 +3182,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G97" t="n">
-        <v>6.34026384353638</v>
+        <v>6.34026336669922</v>
       </c>
       <c r="H97" t="n">
         <v>40000</v>
@@ -3240,7 +3240,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G99" t="n">
-        <v>6.08297729492188</v>
+        <v>6.08297681808472</v>
       </c>
       <c r="H99" t="n">
         <v>19500</v>
@@ -3298,7 +3298,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>5.99108934402466</v>
+        <v>5.9910888671875</v>
       </c>
       <c r="H101" t="n">
         <v>7000</v>
@@ -3327,7 +3327,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G102" t="n">
-        <v>6.10135459899902</v>
+        <v>6.10135412216187</v>
       </c>
       <c r="H102" t="n">
         <v>2000</v>
@@ -3356,7 +3356,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G103" t="n">
-        <v>6.10135459899902</v>
+        <v>6.10135412216187</v>
       </c>
       <c r="H103" t="n">
         <v>2000</v>
@@ -3385,7 +3385,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G104" t="n">
-        <v>6.02784442901611</v>
+        <v>6.02784395217896</v>
       </c>
       <c r="H104" t="n">
         <v>15000</v>
@@ -3443,7 +3443,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G106" t="n">
-        <v>5.95433378219604</v>
+        <v>5.9543342590332</v>
       </c>
       <c r="H106" t="n">
         <v>11500</v>
@@ -3472,7 +3472,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G107" t="n">
-        <v>5.9359564781189</v>
+        <v>5.93595695495605</v>
       </c>
       <c r="H107" t="n">
         <v>15500</v>
@@ -3501,7 +3501,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>6.04622220993042</v>
+        <v>6.04622173309326</v>
       </c>
       <c r="H108" t="n">
         <v>12500</v>
@@ -3530,7 +3530,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G109" t="n">
-        <v>5.86244630813599</v>
+        <v>5.86244678497314</v>
       </c>
       <c r="H109" t="n">
         <v>14500</v>
@@ -3559,7 +3559,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G110" t="n">
-        <v>5.86244630813599</v>
+        <v>5.86244678497314</v>
       </c>
       <c r="H110" t="n">
         <v>5000</v>
@@ -3588,7 +3588,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G111" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H111" t="n">
         <v>3500</v>
@@ -3994,7 +3994,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G125" t="n">
-        <v>5.71542501449585</v>
+        <v>5.71542549133301</v>
       </c>
       <c r="H125" t="n">
         <v>14000</v>
@@ -4110,7 +4110,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G129" t="n">
-        <v>5.43976259231567</v>
+        <v>5.43976211547852</v>
       </c>
       <c r="H129" t="n">
         <v>500</v>
@@ -4168,7 +4168,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G131" t="n">
-        <v>5.43976259231567</v>
+        <v>5.43976211547852</v>
       </c>
       <c r="H131" t="n">
         <v>3500</v>
@@ -4313,7 +4313,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>5.55002737045288</v>
+        <v>5.55002689361572</v>
       </c>
       <c r="H136" t="n">
         <v>7000</v>
@@ -4342,7 +4342,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>5.55002737045288</v>
+        <v>5.55002689361572</v>
       </c>
       <c r="H137" t="n">
         <v>1000</v>
@@ -4371,7 +4371,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G138" t="n">
-        <v>5.55002737045288</v>
+        <v>5.55002689361572</v>
       </c>
       <c r="H138" t="n">
         <v>3000</v>
@@ -4400,7 +4400,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G139" t="n">
-        <v>5.55002737045288</v>
+        <v>5.55002689361572</v>
       </c>
       <c r="H139" t="n">
         <v>10500</v>
@@ -4429,7 +4429,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>5.45813989639282</v>
+        <v>5.45813941955566</v>
       </c>
       <c r="H140" t="n">
         <v>2000</v>
@@ -4458,7 +4458,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G141" t="n">
-        <v>5.45813989639282</v>
+        <v>5.45813941955566</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>5.45813989639282</v>
+        <v>5.45813941955566</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G145" t="n">
-        <v>5.86244630813599</v>
+        <v>5.86244678497314</v>
       </c>
       <c r="H145" t="n">
         <v>1500</v>
@@ -4603,7 +4603,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G146" t="n">
-        <v>5.86244630813599</v>
+        <v>5.86244678497314</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>6.06459951400757</v>
+        <v>6.06459903717041</v>
       </c>
       <c r="H151" t="n">
         <v>5500</v>
@@ -4777,7 +4777,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G152" t="n">
-        <v>6.02784442901611</v>
+        <v>6.02784395217896</v>
       </c>
       <c r="H152" t="n">
         <v>6000</v>
@@ -4806,7 +4806,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G153" t="n">
-        <v>6.06459951400757</v>
+        <v>6.06459903717041</v>
       </c>
       <c r="H153" t="n">
         <v>1000</v>
@@ -4835,7 +4835,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G154" t="n">
-        <v>6.248375415802</v>
+        <v>6.24837493896484</v>
       </c>
       <c r="H154" t="n">
         <v>55500</v>
@@ -4922,7 +4922,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>6.34026384353638</v>
+        <v>6.34026336669922</v>
       </c>
       <c r="H157" t="n">
         <v>1000</v>
@@ -4951,7 +4951,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G158" t="n">
-        <v>6.34026384353638</v>
+        <v>6.34026336669922</v>
       </c>
       <c r="H158" t="n">
         <v>4500</v>
@@ -4980,7 +4980,7 @@
         <v>7</v>
       </c>
       <c r="G159" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H159" t="n">
         <v>4000</v>
@@ -5009,7 +5009,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G160" t="n">
-        <v>6.34026384353638</v>
+        <v>6.34026336669922</v>
       </c>
       <c r="H160" t="n">
         <v>2000</v>
@@ -5038,7 +5038,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G161" t="n">
-        <v>6.34026384353638</v>
+        <v>6.34026336669922</v>
       </c>
       <c r="H161" t="n">
         <v>1000</v>
@@ -5067,7 +5067,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G162" t="n">
-        <v>6.34026384353638</v>
+        <v>6.34026336669922</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G163" t="n">
-        <v>6.34026384353638</v>
+        <v>6.34026336669922</v>
       </c>
       <c r="H163" t="n">
         <v>4500</v>
@@ -5125,7 +5125,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G164" t="n">
-        <v>6.34026384353638</v>
+        <v>6.34026336669922</v>
       </c>
       <c r="H164" t="n">
         <v>17000</v>
@@ -5154,7 +5154,7 @@
         <v>7</v>
       </c>
       <c r="G165" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H165" t="n">
         <v>2500</v>
@@ -5183,7 +5183,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>6.56079387664795</v>
+        <v>6.56079435348511</v>
       </c>
       <c r="H166" t="n">
         <v>2500</v>
@@ -5212,7 +5212,7 @@
         <v>7</v>
       </c>
       <c r="G167" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H167" t="n">
         <v>2000</v>
@@ -5241,7 +5241,7 @@
         <v>7</v>
       </c>
       <c r="G168" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>7</v>
       </c>
       <c r="G169" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H169" t="n">
         <v>1000</v>
@@ -5299,7 +5299,7 @@
         <v>7</v>
       </c>
       <c r="G170" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H170" t="n">
         <v>1000</v>
@@ -5328,7 +5328,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G171" t="n">
-        <v>6.45052814483643</v>
+        <v>6.45052862167358</v>
       </c>
       <c r="H171" t="n">
         <v>1500</v>
@@ -5357,7 +5357,7 @@
         <v>7</v>
       </c>
       <c r="G172" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H172" t="n">
         <v>1500</v>
@@ -5444,7 +5444,7 @@
         <v>7</v>
       </c>
       <c r="G175" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H175" t="n">
         <v>2000</v>
@@ -5560,7 +5560,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H179" t="n">
         <v>1500</v>
@@ -5589,7 +5589,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5618,7 +5618,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H181" t="n">
         <v>1500</v>
@@ -5647,7 +5647,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G182" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H182" t="n">
         <v>2500</v>
@@ -5676,7 +5676,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G184" t="n">
-        <v>6.94672298431396</v>
+        <v>6.94672250747681</v>
       </c>
       <c r="H184" t="n">
         <v>6000</v>
@@ -5879,7 +5879,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G190" t="n">
-        <v>7.25914192199707</v>
+        <v>7.25914239883423</v>
       </c>
       <c r="H190" t="n">
         <v>5000</v>
@@ -5908,7 +5908,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G191" t="n">
-        <v>7.14887619018555</v>
+        <v>7.14887666702271</v>
       </c>
       <c r="H191" t="n">
         <v>1000</v>
@@ -5937,7 +5937,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G192" t="n">
-        <v>7.36940813064575</v>
+        <v>7.36940765380859</v>
       </c>
       <c r="H192" t="n">
         <v>4000</v>
@@ -5966,7 +5966,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G193" t="n">
-        <v>7.25914192199707</v>
+        <v>7.25914239883423</v>
       </c>
       <c r="H193" t="n">
         <v>5500</v>
@@ -5995,7 +5995,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G194" t="n">
-        <v>7.25914192199707</v>
+        <v>7.25914239883423</v>
       </c>
       <c r="H194" t="n">
         <v>2000</v>
@@ -6024,7 +6024,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G195" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H195" t="n">
         <v>12000</v>
@@ -6053,7 +6053,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G196" t="n">
-        <v>7.25914192199707</v>
+        <v>7.25914239883423</v>
       </c>
       <c r="H196" t="n">
         <v>10000</v>
@@ -6082,7 +6082,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G197" t="n">
-        <v>7.25914192199707</v>
+        <v>7.25914239883423</v>
       </c>
       <c r="H197" t="n">
         <v>1000</v>
@@ -6111,7 +6111,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G198" t="n">
-        <v>7.25914192199707</v>
+        <v>7.25914239883423</v>
       </c>
       <c r="H198" t="n">
         <v>3000</v>
@@ -6140,7 +6140,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G199" t="n">
-        <v>7.25914192199707</v>
+        <v>7.25914239883423</v>
       </c>
       <c r="H199" t="n">
         <v>15500</v>
@@ -6169,7 +6169,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>7.31427478790283</v>
+        <v>7.31427431106567</v>
       </c>
       <c r="H200" t="n">
         <v>7500</v>
@@ -6198,7 +6198,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G201" t="n">
-        <v>7.31427478790283</v>
+        <v>7.31427431106567</v>
       </c>
       <c r="H201" t="n">
         <v>6000</v>
@@ -6227,7 +6227,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G202" t="n">
-        <v>7.70020389556885</v>
+        <v>7.70020341873169</v>
       </c>
       <c r="H202" t="n">
         <v>6500</v>
@@ -6256,7 +6256,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G203" t="n">
-        <v>7.70020389556885</v>
+        <v>7.70020341873169</v>
       </c>
       <c r="H203" t="n">
         <v>3000</v>
@@ -6285,7 +6285,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G204" t="n">
-        <v>7.79209089279175</v>
+        <v>7.79209041595459</v>
       </c>
       <c r="H204" t="n">
         <v>6500</v>
@@ -6314,7 +6314,7 @@
         <v>8.5</v>
       </c>
       <c r="G205" t="n">
-        <v>7.81046867370605</v>
+        <v>7.81046915054321</v>
       </c>
       <c r="H205" t="n">
         <v>6500</v>
@@ -6401,7 +6401,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G208" t="n">
-        <v>8.08613204956055</v>
+        <v>8.08613300323486</v>
       </c>
       <c r="H208" t="n">
         <v>3000</v>
@@ -6459,7 +6459,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G210" t="n">
-        <v>8.01262187957764</v>
+        <v>8.01262283325195</v>
       </c>
       <c r="H210" t="n">
         <v>3500</v>
@@ -6662,7 +6662,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G217" t="n">
-        <v>8.6190824508667</v>
+        <v>8.61908340454102</v>
       </c>
       <c r="H217" t="n">
         <v>4000</v>
@@ -6691,7 +6691,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G218" t="n">
-        <v>8.69259262084961</v>
+        <v>8.69259357452393</v>
       </c>
       <c r="H218" t="n">
         <v>3000</v>
@@ -6720,7 +6720,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G219" t="n">
-        <v>8.6190824508667</v>
+        <v>8.61908340454102</v>
       </c>
       <c r="H219" t="n">
         <v>1000</v>
@@ -6749,7 +6749,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>8.69259262084961</v>
+        <v>8.69259357452393</v>
       </c>
       <c r="H220" t="n">
         <v>3500</v>
@@ -6778,7 +6778,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>8.69259262084961</v>
+        <v>8.69259357452393</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G224" t="n">
-        <v>8.8212366104126</v>
+        <v>8.82123565673828</v>
       </c>
       <c r="H224" t="n">
         <v>2000</v>
@@ -6894,7 +6894,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.8212366104126</v>
+        <v>8.82123565673828</v>
       </c>
       <c r="H225" t="n">
         <v>3500</v>
@@ -6952,7 +6952,7 @@
         <v>9.5</v>
       </c>
       <c r="G227" t="n">
-        <v>8.72934722900391</v>
+        <v>8.72934818267822</v>
       </c>
       <c r="H227" t="n">
         <v>4500</v>
@@ -7097,7 +7097,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G232" t="n">
-        <v>8.6190824508667</v>
+        <v>8.61908340454102</v>
       </c>
       <c r="H232" t="n">
         <v>5000</v>
@@ -7242,7 +7242,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>8.233154296875</v>
+        <v>8.23315334320068</v>
       </c>
       <c r="H237" t="n">
         <v>8500</v>
@@ -7474,7 +7474,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G245" t="n">
-        <v>8.36179733276367</v>
+        <v>8.36179637908936</v>
       </c>
       <c r="H245" t="n">
         <v>500</v>
@@ -7503,7 +7503,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G246" t="n">
-        <v>8.36179733276367</v>
+        <v>8.36179637908936</v>
       </c>
       <c r="H246" t="n">
         <v>1500</v>
@@ -7706,7 +7706,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G253" t="n">
-        <v>8.71096897125244</v>
+        <v>8.71096992492676</v>
       </c>
       <c r="H253" t="n">
         <v>10500</v>
@@ -7735,7 +7735,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G254" t="n">
-        <v>8.71096897125244</v>
+        <v>8.71096992492676</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G255" t="n">
-        <v>8.71096897125244</v>
+        <v>8.71096992492676</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
         <v>9.5</v>
       </c>
       <c r="G256" t="n">
-        <v>8.72934722900391</v>
+        <v>8.72934818267822</v>
       </c>
       <c r="H256" t="n">
         <v>500</v>
@@ -8025,7 +8025,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G264" t="n">
-        <v>8.69259262084961</v>
+        <v>8.69259357452393</v>
       </c>
       <c r="H264" t="n">
         <v>7000</v>
@@ -8054,7 +8054,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>8.69259262084961</v>
+        <v>8.69259357452393</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>9.5</v>
       </c>
       <c r="G266" t="n">
-        <v>8.72934722900391</v>
+        <v>8.72934818267822</v>
       </c>
       <c r="H266" t="n">
         <v>3000</v>
@@ -8112,7 +8112,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G267" t="n">
-        <v>8.69259262084961</v>
+        <v>8.69259357452393</v>
       </c>
       <c r="H267" t="n">
         <v>5500</v>
@@ -8170,7 +8170,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G269" t="n">
-        <v>8.74772644042969</v>
+        <v>8.74772548675537</v>
       </c>
       <c r="H269" t="n">
         <v>4000</v>
@@ -8199,7 +8199,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G270" t="n">
-        <v>8.67421436309814</v>
+        <v>8.67421531677246</v>
       </c>
       <c r="H270" t="n">
         <v>1000</v>
@@ -8228,7 +8228,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G271" t="n">
-        <v>8.39855098724365</v>
+        <v>8.39855194091797</v>
       </c>
       <c r="H271" t="n">
         <v>5000</v>
@@ -8257,7 +8257,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G272" t="n">
-        <v>7.47967290878296</v>
+        <v>7.47967338562012</v>
       </c>
       <c r="H272" t="n">
         <v>11000</v>
@@ -8315,7 +8315,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>7.5348048210144</v>
+        <v>7.53480529785156</v>
       </c>
       <c r="H274" t="n">
         <v>3000</v>
@@ -8460,7 +8460,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G279" t="n">
-        <v>7.64507102966309</v>
+        <v>7.64507055282593</v>
       </c>
       <c r="H279" t="n">
         <v>1000</v>
@@ -8605,7 +8605,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G284" t="n">
-        <v>7.25914192199707</v>
+        <v>7.25914239883423</v>
       </c>
       <c r="H284" t="n">
         <v>15000</v>
@@ -8634,7 +8634,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G285" t="n">
-        <v>7.25914192199707</v>
+        <v>7.25914239883423</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G286" t="n">
-        <v>7.25914192199707</v>
+        <v>7.25914239883423</v>
       </c>
       <c r="H286" t="n">
         <v>500</v>
@@ -8721,7 +8721,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G288" t="n">
-        <v>7.25914192199707</v>
+        <v>7.25914239883423</v>
       </c>
       <c r="H288" t="n">
         <v>500</v>
@@ -8982,7 +8982,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>6.79970264434814</v>
+        <v>6.79970216751099</v>
       </c>
       <c r="H297" t="n">
         <v>3500</v>
@@ -9011,7 +9011,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>6.98347806930542</v>
+        <v>6.98347759246826</v>
       </c>
       <c r="H298" t="n">
         <v>7000</v>
@@ -9040,7 +9040,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>6.98347806930542</v>
+        <v>6.98347759246826</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>6.98347806930542</v>
+        <v>6.98347759246826</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G301" t="n">
-        <v>6.98347806930542</v>
+        <v>6.98347759246826</v>
       </c>
       <c r="H301" t="n">
         <v>18500</v>
@@ -9243,7 +9243,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G306" t="n">
-        <v>7.07536602020264</v>
+        <v>7.07536554336548</v>
       </c>
       <c r="H306" t="n">
         <v>1500</v>
@@ -9272,7 +9272,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G307" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H307" t="n">
         <v>500</v>
@@ -9301,7 +9301,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G308" t="n">
-        <v>6.72619295120239</v>
+        <v>6.72619247436523</v>
       </c>
       <c r="H308" t="n">
         <v>5000</v>
@@ -9359,7 +9359,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G310" t="n">
-        <v>7.07536602020264</v>
+        <v>7.07536554336548</v>
       </c>
       <c r="H310" t="n">
         <v>3000</v>
@@ -9417,7 +9417,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G312" t="n">
-        <v>7.5348048210144</v>
+        <v>7.53480529785156</v>
       </c>
       <c r="H312" t="n">
         <v>2000</v>
@@ -9475,7 +9475,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G314" t="n">
-        <v>7.4429178237915</v>
+        <v>7.44291830062866</v>
       </c>
       <c r="H314" t="n">
         <v>2000</v>
@@ -9504,7 +9504,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G315" t="n">
-        <v>7.4429178237915</v>
+        <v>7.44291830062866</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G316" t="n">
-        <v>7.4429178237915</v>
+        <v>7.44291830062866</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>7.4429178237915</v>
+        <v>7.44291830062866</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G318" t="n">
-        <v>7.4429178237915</v>
+        <v>7.44291830062866</v>
       </c>
       <c r="H318" t="n">
         <v>500</v>
@@ -9620,7 +9620,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G319" t="n">
-        <v>7.46129560470581</v>
+        <v>7.46129512786865</v>
       </c>
       <c r="H319" t="n">
         <v>500</v>
@@ -9649,7 +9649,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G320" t="n">
-        <v>7.46129560470581</v>
+        <v>7.46129512786865</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G328" t="n">
-        <v>6.98347806930542</v>
+        <v>6.98347759246826</v>
       </c>
       <c r="H328" t="n">
         <v>1000</v>
@@ -9910,7 +9910,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G329" t="n">
-        <v>6.79970264434814</v>
+        <v>6.79970216751099</v>
       </c>
       <c r="H329" t="n">
         <v>1000</v>
@@ -10055,7 +10055,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G334" t="n">
-        <v>6.94672298431396</v>
+        <v>6.94672250747681</v>
       </c>
       <c r="H334" t="n">
         <v>500</v>
@@ -10084,7 +10084,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>6.94672298431396</v>
+        <v>6.94672250747681</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>6.94672298431396</v>
+        <v>6.94672250747681</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>6.79970264434814</v>
+        <v>6.79970216751099</v>
       </c>
       <c r="H337" t="n">
         <v>500</v>
@@ -10171,7 +10171,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>6.79970264434814</v>
+        <v>6.79970216751099</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10316,7 +10316,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G343" t="n">
-        <v>6.02784442901611</v>
+        <v>6.02784395217896</v>
       </c>
       <c r="H343" t="n">
         <v>9500</v>
@@ -10403,7 +10403,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G346" t="n">
-        <v>6.04622220993042</v>
+        <v>6.04622173309326</v>
       </c>
       <c r="H346" t="n">
         <v>1000</v>
@@ -10432,7 +10432,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G347" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H347" t="n">
         <v>1000</v>
@@ -10461,7 +10461,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G348" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -10490,7 +10490,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G349" t="n">
-        <v>6.21162033081055</v>
+        <v>6.21161985397339</v>
       </c>
       <c r="H349" t="n">
         <v>1500</v>
@@ -10519,7 +10519,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G350" t="n">
-        <v>6.04622220993042</v>
+        <v>6.04622173309326</v>
       </c>
       <c r="H350" t="n">
         <v>1000</v>
@@ -10548,7 +10548,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>5.99108934402466</v>
+        <v>5.9910888671875</v>
       </c>
       <c r="H351" t="n">
         <v>14500</v>
@@ -10577,7 +10577,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G352" t="n">
-        <v>5.99108934402466</v>
+        <v>5.9910888671875</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G355" t="n">
-        <v>6.248375415802</v>
+        <v>6.24837493896484</v>
       </c>
       <c r="H355" t="n">
         <v>4000</v>
@@ -10693,7 +10693,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>6.248375415802</v>
+        <v>6.24837493896484</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -10722,7 +10722,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G357" t="n">
-        <v>6.248375415802</v>
+        <v>6.24837493896484</v>
       </c>
       <c r="H357" t="n">
         <v>500</v>
@@ -10751,7 +10751,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G358" t="n">
-        <v>6.248375415802</v>
+        <v>6.24837493896484</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -10780,7 +10780,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G359" t="n">
-        <v>6.34026384353638</v>
+        <v>6.34026336669922</v>
       </c>
       <c r="H359" t="n">
         <v>500</v>
@@ -10954,7 +10954,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G365" t="n">
-        <v>6.5975489616394</v>
+        <v>6.59754943847656</v>
       </c>
       <c r="H365" t="n">
         <v>500</v>
@@ -11012,7 +11012,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G367" t="n">
-        <v>6.34026384353638</v>
+        <v>6.34026336669922</v>
       </c>
       <c r="H367" t="n">
         <v>2000</v>
@@ -11041,7 +11041,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G368" t="n">
-        <v>6.34026384353638</v>
+        <v>6.34026336669922</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G369" t="n">
-        <v>6.34026384353638</v>
+        <v>6.34026336669922</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G370" t="n">
-        <v>6.34026384353638</v>
+        <v>6.34026336669922</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G371" t="n">
-        <v>6.21162033081055</v>
+        <v>6.21161985397339</v>
       </c>
       <c r="H371" t="n">
         <v>4000</v>
@@ -11157,7 +11157,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G372" t="n">
-        <v>6.21162033081055</v>
+        <v>6.21161985397339</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G373" t="n">
-        <v>6.21162033081055</v>
+        <v>6.21161985397339</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G374" t="n">
-        <v>6.21162033081055</v>
+        <v>6.21161985397339</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G376" t="n">
-        <v>6.04622220993042</v>
+        <v>6.04622173309326</v>
       </c>
       <c r="H376" t="n">
         <v>3000</v>
@@ -11302,7 +11302,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>6.04622220993042</v>
+        <v>6.04622173309326</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11360,7 +11360,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>6.06459951400757</v>
+        <v>6.06459903717041</v>
       </c>
       <c r="H379" t="n">
         <v>1000</v>
@@ -11389,7 +11389,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>6.06459951400757</v>
+        <v>6.06459903717041</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>6.06459951400757</v>
+        <v>6.06459903717041</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G382" t="n">
-        <v>6.06459951400757</v>
+        <v>6.06459903717041</v>
       </c>
       <c r="H382" t="n">
         <v>500</v>
@@ -11621,7 +11621,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G388" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H388" t="n">
         <v>1000</v>
@@ -11650,7 +11650,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G389" t="n">
-        <v>5.9359564781189</v>
+        <v>5.93595695495605</v>
       </c>
       <c r="H389" t="n">
         <v>500</v>
@@ -11679,7 +11679,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>5.9359564781189</v>
+        <v>5.93595695495605</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G391" t="n">
-        <v>5.9359564781189</v>
+        <v>5.93595695495605</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -11737,7 +11737,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>5.9359564781189</v>
+        <v>5.93595695495605</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -11766,7 +11766,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G393" t="n">
-        <v>5.9359564781189</v>
+        <v>5.93595695495605</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -11795,7 +11795,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G394" t="n">
-        <v>5.9359564781189</v>
+        <v>5.93595695495605</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -11824,7 +11824,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G395" t="n">
-        <v>5.80731344223022</v>
+        <v>5.80731391906738</v>
       </c>
       <c r="H395" t="n">
         <v>1500</v>
@@ -11853,7 +11853,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G396" t="n">
-        <v>5.80731344223022</v>
+        <v>5.80731391906738</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G397" t="n">
-        <v>5.80731344223022</v>
+        <v>5.80731391906738</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -11969,7 +11969,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G400" t="n">
-        <v>6.10135459899902</v>
+        <v>6.10135412216187</v>
       </c>
       <c r="H400" t="n">
         <v>500</v>
@@ -12085,7 +12085,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G404" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H404" t="n">
         <v>1000</v>
@@ -12114,7 +12114,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G405" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -12143,7 +12143,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G406" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G407" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -12201,7 +12201,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G408" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G413" t="n">
-        <v>6.45052814483643</v>
+        <v>6.45052862167358</v>
       </c>
       <c r="H413" t="n">
         <v>5500</v>
@@ -12375,7 +12375,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G414" t="n">
-        <v>6.45052814483643</v>
+        <v>6.45052862167358</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>7</v>
       </c>
       <c r="G415" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H415" t="n">
         <v>1500</v>
@@ -12433,7 +12433,7 @@
         <v>7</v>
       </c>
       <c r="G416" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H416" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>7</v>
       </c>
       <c r="G417" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12491,7 +12491,7 @@
         <v>7</v>
       </c>
       <c r="G418" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>7</v>
       </c>
       <c r="G419" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>7</v>
       </c>
       <c r="G420" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>7</v>
       </c>
       <c r="G421" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H421" t="n">
         <v>500</v>
@@ -12868,7 +12868,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G431" t="n">
-        <v>6.21162033081055</v>
+        <v>6.21161985397339</v>
       </c>
       <c r="H431" t="n">
         <v>1000</v>
@@ -12897,7 +12897,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G432" t="n">
-        <v>6.08297729492188</v>
+        <v>6.08297681808472</v>
       </c>
       <c r="H432" t="n">
         <v>500</v>
@@ -12926,7 +12926,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>6.08297729492188</v>
+        <v>6.08297681808472</v>
       </c>
       <c r="H433" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G434" t="n">
-        <v>6.08297729492188</v>
+        <v>6.08297681808472</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G435" t="n">
-        <v>6.08297729492188</v>
+        <v>6.08297681808472</v>
       </c>
       <c r="H435" t="n">
         <v>0</v>
@@ -13013,7 +13013,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G436" t="n">
-        <v>6.08297729492188</v>
+        <v>6.08297681808472</v>
       </c>
       <c r="H436" t="n">
         <v>0</v>
@@ -13042,7 +13042,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G437" t="n">
-        <v>6.08297729492188</v>
+        <v>6.08297681808472</v>
       </c>
       <c r="H437" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         <v>7</v>
       </c>
       <c r="G438" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H438" t="n">
         <v>3000</v>
@@ -13100,7 +13100,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G439" t="n">
-        <v>6.34026384353638</v>
+        <v>6.34026336669922</v>
       </c>
       <c r="H439" t="n">
         <v>3000</v>
@@ -13361,7 +13361,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G448" t="n">
-        <v>6.02784442901611</v>
+        <v>6.02784395217896</v>
       </c>
       <c r="H448" t="n">
         <v>1000</v>
@@ -13448,7 +13448,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G451" t="n">
-        <v>6.00946712493896</v>
+        <v>6.00946664810181</v>
       </c>
       <c r="H451" t="n">
         <v>500</v>
@@ -13941,7 +13941,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G468" t="n">
-        <v>5.6051607131958</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H468" t="n">
         <v>2000</v>
@@ -13970,7 +13970,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G469" t="n">
-        <v>5.6051607131958</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H469" t="n">
         <v>0</v>
@@ -14289,7 +14289,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G480" t="n">
-        <v>5.45813989639282</v>
+        <v>5.45813941955566</v>
       </c>
       <c r="H480" t="n">
         <v>1500</v>
@@ -14347,7 +14347,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G482" t="n">
-        <v>5.6051607131958</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H482" t="n">
         <v>1000</v>
@@ -14376,7 +14376,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G483" t="n">
-        <v>5.6051607131958</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14405,7 +14405,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G484" t="n">
-        <v>5.6051607131958</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H484" t="n">
         <v>0</v>
@@ -14724,7 +14724,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G495" t="n">
-        <v>5.73380327224731</v>
+        <v>5.73380279541016</v>
       </c>
       <c r="H495" t="n">
         <v>2000</v>
@@ -14753,7 +14753,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G496" t="n">
-        <v>5.73380327224731</v>
+        <v>5.73380279541016</v>
       </c>
       <c r="H496" t="n">
         <v>0</v>
@@ -14782,7 +14782,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G497" t="n">
-        <v>5.73380327224731</v>
+        <v>5.73380279541016</v>
       </c>
       <c r="H497" t="n">
         <v>0</v>
@@ -15101,7 +15101,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>5.55002737045288</v>
+        <v>5.55002689361572</v>
       </c>
       <c r="H508" t="n">
         <v>500</v>
@@ -15275,7 +15275,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G514" t="n">
-        <v>5.55002737045288</v>
+        <v>5.55002689361572</v>
       </c>
       <c r="H514" t="n">
         <v>1000</v>
@@ -15478,7 +15478,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G521" t="n">
-        <v>5.45813989639282</v>
+        <v>5.45813941955566</v>
       </c>
       <c r="H521" t="n">
         <v>1000</v>
@@ -15507,7 +15507,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G522" t="n">
-        <v>5.6051607131958</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H522" t="n">
         <v>500</v>
@@ -15536,7 +15536,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>5.6051607131958</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H523" t="n">
         <v>0</v>
@@ -15565,7 +15565,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G524" t="n">
-        <v>5.6051607131958</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H524" t="n">
         <v>0</v>
@@ -15884,7 +15884,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H535" t="n">
         <v>500</v>
@@ -15913,7 +15913,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G536" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H536" t="n">
         <v>0</v>
@@ -15971,7 +15971,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G538" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H538" t="n">
         <v>1000</v>
@@ -16000,7 +16000,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G539" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H539" t="n">
         <v>0</v>
@@ -16029,7 +16029,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G540" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H540" t="n">
         <v>0</v>
@@ -16058,7 +16058,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G541" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -16116,7 +16116,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G543" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H543" t="n">
         <v>0</v>
@@ -16145,7 +16145,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G544" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H544" t="n">
         <v>0</v>
@@ -16174,7 +16174,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G545" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H546" t="n">
         <v>0</v>
@@ -16232,7 +16232,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G547" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G548" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H548" t="n">
         <v>1500</v>
@@ -16290,7 +16290,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G549" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H549" t="n">
         <v>0</v>
@@ -16319,7 +16319,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G550" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -16348,7 +16348,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G551" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H551" t="n">
         <v>0</v>
@@ -16377,7 +16377,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G552" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H552" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G553" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -16435,7 +16435,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G554" t="n">
-        <v>5.6051607131958</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H554" t="n">
         <v>1000</v>
@@ -16464,7 +16464,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G555" t="n">
-        <v>5.6051607131958</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H555" t="n">
         <v>0</v>
@@ -16493,7 +16493,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G556" t="n">
-        <v>5.6051607131958</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H556" t="n">
         <v>0</v>
@@ -16522,7 +16522,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G557" t="n">
-        <v>5.6051607131958</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H557" t="n">
         <v>0</v>
@@ -16551,7 +16551,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G558" t="n">
-        <v>5.6051607131958</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H558" t="n">
         <v>0</v>
@@ -16580,7 +16580,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G559" t="n">
-        <v>5.6051607131958</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H559" t="n">
         <v>0</v>
@@ -16609,7 +16609,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G560" t="n">
-        <v>5.6051607131958</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H560" t="n">
         <v>0</v>
@@ -16638,7 +16638,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G561" t="n">
-        <v>5.6051607131958</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -16667,7 +16667,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G562" t="n">
-        <v>5.6051607131958</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H562" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G563" t="n">
-        <v>5.45813989639282</v>
+        <v>5.45813941955566</v>
       </c>
       <c r="H563" t="n">
         <v>500</v>
@@ -16841,7 +16841,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G568" t="n">
-        <v>5.43976259231567</v>
+        <v>5.43976211547852</v>
       </c>
       <c r="H568" t="n">
         <v>500</v>
@@ -17044,7 +17044,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G575" t="n">
-        <v>5.45813989639282</v>
+        <v>5.45813941955566</v>
       </c>
       <c r="H575" t="n">
         <v>500</v>
@@ -17073,7 +17073,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G576" t="n">
-        <v>5.45813989639282</v>
+        <v>5.45813941955566</v>
       </c>
       <c r="H576" t="n">
         <v>0</v>
@@ -17189,7 +17189,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G580" t="n">
-        <v>5.6051607131958</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H580" t="n">
         <v>6500</v>
@@ -17218,7 +17218,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G581" t="n">
-        <v>5.6051607131958</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H581" t="n">
         <v>0</v>
@@ -17334,7 +17334,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G585" t="n">
-        <v>5.6051607131958</v>
+        <v>5.60516023635864</v>
       </c>
       <c r="H585" t="n">
         <v>2000</v>
@@ -17363,7 +17363,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G586" t="n">
-        <v>5.46732807159424</v>
+        <v>5.4673285484314</v>
       </c>
       <c r="H586" t="n">
         <v>500</v>
@@ -17392,7 +17392,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G587" t="n">
-        <v>5.46732807159424</v>
+        <v>5.4673285484314</v>
       </c>
       <c r="H587" t="n">
         <v>0</v>
@@ -17508,7 +17508,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G591" t="n">
-        <v>5.46732807159424</v>
+        <v>5.4673285484314</v>
       </c>
       <c r="H591" t="n">
         <v>500</v>
@@ -17537,7 +17537,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G592" t="n">
-        <v>5.46732807159424</v>
+        <v>5.4673285484314</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -17566,7 +17566,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G593" t="n">
-        <v>5.46732807159424</v>
+        <v>5.4673285484314</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G594" t="n">
-        <v>5.46732807159424</v>
+        <v>5.4673285484314</v>
       </c>
       <c r="H594" t="n">
         <v>1000</v>
@@ -17624,7 +17624,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G595" t="n">
-        <v>5.46732807159424</v>
+        <v>5.4673285484314</v>
       </c>
       <c r="H595" t="n">
         <v>0</v>
@@ -17653,7 +17653,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G596" t="n">
-        <v>5.46732807159424</v>
+        <v>5.4673285484314</v>
       </c>
       <c r="H596" t="n">
         <v>0</v>
@@ -18407,7 +18407,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G622" t="n">
-        <v>5.53470706939697</v>
+        <v>5.53470754623413</v>
       </c>
       <c r="H622" t="n">
         <v>3500</v>
@@ -19132,7 +19132,7 @@
         <v>5.25</v>
       </c>
       <c r="G647" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H647" t="n">
         <v>10000</v>
@@ -19161,7 +19161,7 @@
         <v>5.25</v>
       </c>
       <c r="G648" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H648" t="n">
         <v>12500</v>
@@ -19248,7 +19248,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G651" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H651" t="n">
         <v>9500</v>
@@ -19654,7 +19654,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G665" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H665" t="n">
         <v>500</v>
@@ -19712,7 +19712,7 @@
         <v>5.25</v>
       </c>
       <c r="G667" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H667" t="n">
         <v>7250</v>
@@ -19770,7 +19770,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G669" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H669" t="n">
         <v>500</v>
@@ -19799,7 +19799,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H670" t="n">
         <v>0</v>
@@ -19828,7 +19828,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H671" t="n">
         <v>0</v>
@@ -19886,7 +19886,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G673" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H673" t="n">
         <v>13250</v>
@@ -20002,7 +20002,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H677" t="n">
         <v>19750</v>
@@ -20031,7 +20031,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H678" t="n">
         <v>1750</v>
@@ -20060,7 +20060,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G679" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H679" t="n">
         <v>4750</v>
@@ -20089,7 +20089,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G680" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H680" t="n">
         <v>500</v>
@@ -20118,7 +20118,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H681" t="n">
         <v>0</v>
@@ -20147,7 +20147,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G682" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H682" t="n">
         <v>0</v>
@@ -20785,7 +20785,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G704" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H704" t="n">
         <v>41750</v>
@@ -20814,7 +20814,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G705" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H705" t="n">
         <v>7500</v>
@@ -20843,7 +20843,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G706" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H706" t="n">
         <v>2500</v>
@@ -20872,7 +20872,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G707" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H707" t="n">
         <v>7500</v>
@@ -20901,7 +20901,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G708" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H708" t="n">
         <v>2250</v>
@@ -21075,7 +21075,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G714" t="n">
-        <v>4.55799436569214</v>
+        <v>4.55799388885498</v>
       </c>
       <c r="H714" t="n">
         <v>4500</v>
@@ -21133,7 +21133,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G716" t="n">
-        <v>4.46497440338135</v>
+        <v>4.46497392654419</v>
       </c>
       <c r="H716" t="n">
         <v>22500</v>
@@ -21162,7 +21162,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G717" t="n">
-        <v>4.63241100311279</v>
+        <v>4.63241052627563</v>
       </c>
       <c r="H717" t="n">
         <v>1000</v>
@@ -21191,7 +21191,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G718" t="n">
-        <v>4.63241100311279</v>
+        <v>4.63241052627563</v>
       </c>
       <c r="H718" t="n">
         <v>0</v>
@@ -21220,7 +21220,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G719" t="n">
-        <v>4.63241100311279</v>
+        <v>4.63241052627563</v>
       </c>
       <c r="H719" t="n">
         <v>0</v>
@@ -21249,7 +21249,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G720" t="n">
-        <v>4.63241100311279</v>
+        <v>4.63241052627563</v>
       </c>
       <c r="H720" t="n">
         <v>0</v>
@@ -21278,7 +21278,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G721" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H721" t="n">
         <v>3000</v>
@@ -21336,7 +21336,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G723" t="n">
-        <v>4.01847648620605</v>
+        <v>4.01847696304321</v>
       </c>
       <c r="H723" t="n">
         <v>20000</v>
@@ -21365,7 +21365,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G724" t="n">
-        <v>4.01847648620605</v>
+        <v>4.01847696304321</v>
       </c>
       <c r="H724" t="n">
         <v>6250</v>
@@ -21394,7 +21394,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G725" t="n">
-        <v>4.01847648620605</v>
+        <v>4.01847696304321</v>
       </c>
       <c r="H725" t="n">
         <v>32000</v>
@@ -21423,7 +21423,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G726" t="n">
-        <v>4.0556845664978</v>
+        <v>4.05568504333496</v>
       </c>
       <c r="H726" t="n">
         <v>6000</v>
@@ -21655,7 +21655,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G734" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H734" t="n">
         <v>250</v>
@@ -21684,7 +21684,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G735" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H735" t="n">
         <v>0</v>
@@ -21713,7 +21713,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G736" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H736" t="n">
         <v>0</v>
@@ -21742,7 +21742,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G737" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H737" t="n">
         <v>0</v>
@@ -21771,7 +21771,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G738" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H738" t="n">
         <v>0</v>
@@ -21800,7 +21800,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G739" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H739" t="n">
         <v>0</v>
@@ -21829,7 +21829,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G740" t="n">
-        <v>4.44636964797974</v>
+        <v>4.44637012481689</v>
       </c>
       <c r="H740" t="n">
         <v>750</v>
@@ -22061,7 +22061,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G748" t="n">
-        <v>4.40916109085083</v>
+        <v>4.40916156768799</v>
       </c>
       <c r="H748" t="n">
         <v>500</v>
@@ -22090,7 +22090,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G749" t="n">
-        <v>4.40916109085083</v>
+        <v>4.40916156768799</v>
       </c>
       <c r="H749" t="n">
         <v>0</v>
@@ -22119,7 +22119,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G750" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H750" t="n">
         <v>750</v>
@@ -22148,7 +22148,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G751" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H751" t="n">
         <v>0</v>
@@ -22177,7 +22177,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G752" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H752" t="n">
         <v>0</v>
@@ -22206,7 +22206,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G753" t="n">
-        <v>4.4277663230896</v>
+        <v>4.42776584625244</v>
       </c>
       <c r="H753" t="n">
         <v>2250</v>
@@ -22235,7 +22235,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G754" t="n">
-        <v>4.35334920883179</v>
+        <v>4.35334968566895</v>
       </c>
       <c r="H754" t="n">
         <v>5500</v>
@@ -22264,7 +22264,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G755" t="n">
-        <v>4.4277663230896</v>
+        <v>4.42776584625244</v>
       </c>
       <c r="H755" t="n">
         <v>3250</v>
@@ -22293,7 +22293,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G756" t="n">
-        <v>4.4277663230896</v>
+        <v>4.42776584625244</v>
       </c>
       <c r="H756" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>5.25</v>
       </c>
       <c r="G760" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H760" t="n">
         <v>3000</v>
@@ -22438,7 +22438,7 @@
         <v>5.25</v>
       </c>
       <c r="G761" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H761" t="n">
         <v>2000</v>
@@ -22467,7 +22467,7 @@
         <v>5.25</v>
       </c>
       <c r="G762" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H762" t="n">
         <v>500</v>
@@ -22496,7 +22496,7 @@
         <v>5.25</v>
       </c>
       <c r="G763" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H763" t="n">
         <v>250</v>
@@ -22525,7 +22525,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G764" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H764" t="n">
         <v>4000</v>
@@ -22554,7 +22554,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G765" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H765" t="n">
         <v>0</v>
@@ -22583,7 +22583,7 @@
         <v>5.25</v>
       </c>
       <c r="G766" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H766" t="n">
         <v>2750</v>
@@ -22612,7 +22612,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G767" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H767" t="n">
         <v>6000</v>
@@ -22641,7 +22641,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H768" t="n">
         <v>500</v>
@@ -22670,7 +22670,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G769" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H769" t="n">
         <v>0</v>
@@ -22728,7 +22728,7 @@
         <v>5.25</v>
       </c>
       <c r="G771" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H771" t="n">
         <v>7500</v>
@@ -22757,7 +22757,7 @@
         <v>5.25</v>
       </c>
       <c r="G772" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H772" t="n">
         <v>0</v>
@@ -22786,7 +22786,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G773" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H773" t="n">
         <v>3750</v>
@@ -22873,7 +22873,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G776" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H776" t="n">
         <v>2750</v>
@@ -22989,7 +22989,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G780" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H780" t="n">
         <v>40750</v>
@@ -23076,7 +23076,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G783" t="n">
-        <v>5.67423820495605</v>
+        <v>5.6742377281189</v>
       </c>
       <c r="H783" t="n">
         <v>6750</v>
@@ -23105,7 +23105,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G784" t="n">
-        <v>5.76725816726685</v>
+        <v>5.76725769042969</v>
       </c>
       <c r="H784" t="n">
         <v>14500</v>
@@ -23163,7 +23163,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G786" t="n">
-        <v>5.95329856872559</v>
+        <v>5.95329809188843</v>
       </c>
       <c r="H786" t="n">
         <v>750</v>
@@ -23192,7 +23192,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G787" t="n">
-        <v>5.95329856872559</v>
+        <v>5.95329809188843</v>
       </c>
       <c r="H787" t="n">
         <v>0</v>
@@ -23221,7 +23221,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G788" t="n">
-        <v>5.86027860641479</v>
+        <v>5.86027812957764</v>
       </c>
       <c r="H788" t="n">
         <v>3250</v>
@@ -23250,7 +23250,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G789" t="n">
-        <v>5.86027860641479</v>
+        <v>5.86027812957764</v>
       </c>
       <c r="H789" t="n">
         <v>1500</v>
@@ -23279,7 +23279,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G790" t="n">
-        <v>5.76725816726685</v>
+        <v>5.76725769042969</v>
       </c>
       <c r="H790" t="n">
         <v>7750</v>
@@ -23308,7 +23308,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G791" t="n">
-        <v>5.86027860641479</v>
+        <v>5.86027812957764</v>
       </c>
       <c r="H791" t="n">
         <v>4750</v>
@@ -23366,7 +23366,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G793" t="n">
-        <v>5.67423820495605</v>
+        <v>5.6742377281189</v>
       </c>
       <c r="H793" t="n">
         <v>1250</v>
@@ -23395,7 +23395,7 @@
         <v>6</v>
       </c>
       <c r="G794" t="n">
-        <v>5.58121728897095</v>
+        <v>5.58121776580811</v>
       </c>
       <c r="H794" t="n">
         <v>500</v>
@@ -23424,7 +23424,7 @@
         <v>6</v>
       </c>
       <c r="G795" t="n">
-        <v>5.58121728897095</v>
+        <v>5.58121776580811</v>
       </c>
       <c r="H795" t="n">
         <v>1250</v>
@@ -23540,7 +23540,7 @@
         <v>6</v>
       </c>
       <c r="G799" t="n">
-        <v>5.58121728897095</v>
+        <v>5.58121776580811</v>
       </c>
       <c r="H799" t="n">
         <v>1750</v>
@@ -23569,7 +23569,7 @@
         <v>6</v>
       </c>
       <c r="G800" t="n">
-        <v>5.58121728897095</v>
+        <v>5.58121776580811</v>
       </c>
       <c r="H800" t="n">
         <v>0</v>
@@ -23598,7 +23598,7 @@
         <v>6</v>
       </c>
       <c r="G801" t="n">
-        <v>5.58121728897095</v>
+        <v>5.58121776580811</v>
       </c>
       <c r="H801" t="n">
         <v>0</v>
@@ -23627,7 +23627,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G802" t="n">
-        <v>5.53470706939697</v>
+        <v>5.53470754623413</v>
       </c>
       <c r="H802" t="n">
         <v>750</v>
@@ -23685,7 +23685,7 @@
         <v>6</v>
       </c>
       <c r="G804" t="n">
-        <v>5.58121728897095</v>
+        <v>5.58121776580811</v>
       </c>
       <c r="H804" t="n">
         <v>1500</v>
@@ -24120,7 +24120,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G819" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H819" t="n">
         <v>1000</v>
@@ -24294,7 +24294,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G825" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H825" t="n">
         <v>500</v>
@@ -24323,7 +24323,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G826" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H826" t="n">
         <v>1000</v>
@@ -24352,7 +24352,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G827" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H827" t="n">
         <v>250</v>
@@ -24439,7 +24439,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G830" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H830" t="n">
         <v>9000</v>
@@ -24497,7 +24497,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G832" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H832" t="n">
         <v>750</v>
@@ -24526,7 +24526,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G833" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H833" t="n">
         <v>500</v>
@@ -24555,7 +24555,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G834" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -24584,7 +24584,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G835" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H835" t="n">
         <v>1000</v>
@@ -24613,7 +24613,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G836" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H836" t="n">
         <v>1000</v>
@@ -24642,7 +24642,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G837" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H837" t="n">
         <v>1500</v>
@@ -24816,7 +24816,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G843" t="n">
-        <v>4.63241100311279</v>
+        <v>4.63241052627563</v>
       </c>
       <c r="H843" t="n">
         <v>2750</v>
@@ -24990,7 +24990,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G849" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H849" t="n">
         <v>500</v>
@@ -25019,7 +25019,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G850" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H850" t="n">
         <v>1000</v>
@@ -25048,7 +25048,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G851" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H851" t="n">
         <v>1000</v>
@@ -25106,7 +25106,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G853" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H853" t="n">
         <v>2500</v>
@@ -25193,7 +25193,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G856" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H856" t="n">
         <v>250</v>
@@ -25222,7 +25222,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G857" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H857" t="n">
         <v>0</v>
@@ -25251,7 +25251,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G858" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H858" t="n">
         <v>250</v>
@@ -25280,7 +25280,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G859" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H859" t="n">
         <v>1000</v>
@@ -25309,7 +25309,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G860" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H860" t="n">
         <v>1000</v>
@@ -25396,7 +25396,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H863" t="n">
         <v>1000</v>
@@ -25425,7 +25425,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G864" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H864" t="n">
         <v>250</v>
@@ -25454,7 +25454,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G865" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H865" t="n">
         <v>250</v>
@@ -25483,7 +25483,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G866" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -25512,7 +25512,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G867" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -25570,7 +25570,7 @@
         <v>5</v>
       </c>
       <c r="G869" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H869" t="n">
         <v>1000</v>
@@ -25599,7 +25599,7 @@
         <v>5</v>
       </c>
       <c r="G870" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H870" t="n">
         <v>0</v>
@@ -25628,7 +25628,7 @@
         <v>5</v>
       </c>
       <c r="G871" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H871" t="n">
         <v>0</v>
@@ -25657,7 +25657,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G872" t="n">
-        <v>4.79242467880249</v>
+        <v>4.79242420196533</v>
       </c>
       <c r="H872" t="n">
         <v>1000</v>
@@ -25686,7 +25686,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G873" t="n">
-        <v>4.79242467880249</v>
+        <v>4.79242420196533</v>
       </c>
       <c r="H873" t="n">
         <v>0</v>
@@ -25715,7 +25715,7 @@
         <v>5</v>
       </c>
       <c r="G874" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H874" t="n">
         <v>1500</v>
@@ -25802,7 +25802,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G877" t="n">
-        <v>4.70701503753662</v>
+        <v>4.70701456069946</v>
       </c>
       <c r="H877" t="n">
         <v>250</v>
@@ -25831,7 +25831,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>4.70701503753662</v>
+        <v>4.70701456069946</v>
       </c>
       <c r="H878" t="n">
         <v>0</v>
@@ -26005,7 +26005,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G884" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H884" t="n">
         <v>3000</v>
@@ -26034,7 +26034,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G885" t="n">
-        <v>4.79242467880249</v>
+        <v>4.79242420196533</v>
       </c>
       <c r="H885" t="n">
         <v>1750</v>
@@ -26150,7 +26150,7 @@
         <v>5</v>
       </c>
       <c r="G889" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H889" t="n">
         <v>8000</v>
@@ -26179,7 +26179,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G890" t="n">
-        <v>4.79242467880249</v>
+        <v>4.79242420196533</v>
       </c>
       <c r="H890" t="n">
         <v>500</v>
@@ -26208,7 +26208,7 @@
         <v>5</v>
       </c>
       <c r="G891" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H891" t="n">
         <v>750</v>
@@ -26237,7 +26237,7 @@
         <v>5</v>
       </c>
       <c r="G892" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H892" t="n">
         <v>1750</v>
@@ -26266,7 +26266,7 @@
         <v>5</v>
       </c>
       <c r="G893" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H893" t="n">
         <v>750</v>
@@ -26295,7 +26295,7 @@
         <v>5</v>
       </c>
       <c r="G894" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -26324,7 +26324,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G895" t="n">
-        <v>4.79242467880249</v>
+        <v>4.79242420196533</v>
       </c>
       <c r="H895" t="n">
         <v>2000</v>
@@ -26353,7 +26353,7 @@
         <v>5</v>
       </c>
       <c r="G896" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H896" t="n">
         <v>750</v>
@@ -26382,7 +26382,7 @@
         <v>5</v>
       </c>
       <c r="G897" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H897" t="n">
         <v>500</v>
@@ -26411,7 +26411,7 @@
         <v>5</v>
       </c>
       <c r="G898" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H898" t="n">
         <v>0</v>
@@ -26440,7 +26440,7 @@
         <v>5</v>
       </c>
       <c r="G899" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H899" t="n">
         <v>0</v>
@@ -26469,7 +26469,7 @@
         <v>5</v>
       </c>
       <c r="G900" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H900" t="n">
         <v>500</v>
@@ -26585,7 +26585,7 @@
         <v>5</v>
       </c>
       <c r="G904" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H904" t="n">
         <v>1000</v>
@@ -26614,7 +26614,7 @@
         <v>5</v>
       </c>
       <c r="G905" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H905" t="n">
         <v>3250</v>
@@ -26643,7 +26643,7 @@
         <v>5</v>
       </c>
       <c r="G906" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H906" t="n">
         <v>0</v>
@@ -26672,7 +26672,7 @@
         <v>5</v>
       </c>
       <c r="G907" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H907" t="n">
         <v>1250</v>
@@ -26701,7 +26701,7 @@
         <v>5</v>
       </c>
       <c r="G908" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H908" t="n">
         <v>0</v>
@@ -26730,7 +26730,7 @@
         <v>5</v>
       </c>
       <c r="G909" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H909" t="n">
         <v>500</v>
@@ -26759,7 +26759,7 @@
         <v>5</v>
       </c>
       <c r="G910" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H910" t="n">
         <v>0</v>
@@ -26788,7 +26788,7 @@
         <v>5</v>
       </c>
       <c r="G911" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -26817,7 +26817,7 @@
         <v>5</v>
       </c>
       <c r="G912" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -26846,7 +26846,7 @@
         <v>5</v>
       </c>
       <c r="G913" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H913" t="n">
         <v>0</v>
@@ -26875,7 +26875,7 @@
         <v>5</v>
       </c>
       <c r="G914" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H914" t="n">
         <v>500</v>
@@ -26904,7 +26904,7 @@
         <v>5</v>
       </c>
       <c r="G915" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H915" t="n">
         <v>1500</v>
@@ -26933,7 +26933,7 @@
         <v>5</v>
       </c>
       <c r="G916" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H916" t="n">
         <v>1000</v>
@@ -26962,7 +26962,7 @@
         <v>5</v>
       </c>
       <c r="G917" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -26991,7 +26991,7 @@
         <v>5</v>
       </c>
       <c r="G918" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H918" t="n">
         <v>500</v>
@@ -27020,7 +27020,7 @@
         <v>5</v>
       </c>
       <c r="G919" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H919" t="n">
         <v>0</v>
@@ -27049,7 +27049,7 @@
         <v>5</v>
       </c>
       <c r="G920" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H920" t="n">
         <v>0</v>
@@ -27078,7 +27078,7 @@
         <v>5</v>
       </c>
       <c r="G921" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>
@@ -27165,7 +27165,7 @@
         <v>5</v>
       </c>
       <c r="G924" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H924" t="n">
         <v>4000</v>
@@ -27194,7 +27194,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G925" t="n">
-        <v>4.61211490631104</v>
+        <v>4.61211538314819</v>
       </c>
       <c r="H925" t="n">
         <v>5750</v>
@@ -27223,7 +27223,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G926" t="n">
-        <v>4.61211490631104</v>
+        <v>4.61211538314819</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -27252,7 +27252,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G927" t="n">
-        <v>4.61211490631104</v>
+        <v>4.61211538314819</v>
       </c>
       <c r="H927" t="n">
         <v>0</v>
@@ -27281,7 +27281,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G928" t="n">
-        <v>4.61211490631104</v>
+        <v>4.61211538314819</v>
       </c>
       <c r="H928" t="n">
         <v>0</v>
@@ -27310,7 +27310,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G929" t="n">
-        <v>4.61211490631104</v>
+        <v>4.61211538314819</v>
       </c>
       <c r="H929" t="n">
         <v>0</v>
@@ -27339,7 +27339,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G930" t="n">
-        <v>4.61211490631104</v>
+        <v>4.61211538314819</v>
       </c>
       <c r="H930" t="n">
         <v>0</v>
@@ -27368,7 +27368,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G931" t="n">
-        <v>4.61211490631104</v>
+        <v>4.61211538314819</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -27426,7 +27426,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G933" t="n">
-        <v>4.79242467880249</v>
+        <v>4.79242420196533</v>
       </c>
       <c r="H933" t="n">
         <v>750</v>
@@ -27455,7 +27455,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G934" t="n">
-        <v>4.79242467880249</v>
+        <v>4.79242420196533</v>
       </c>
       <c r="H934" t="n">
         <v>0</v>
@@ -27484,7 +27484,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G935" t="n">
-        <v>4.79242467880249</v>
+        <v>4.79242420196533</v>
       </c>
       <c r="H935" t="n">
         <v>250</v>
@@ -27629,7 +27629,7 @@
         <v>5</v>
       </c>
       <c r="G940" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H940" t="n">
         <v>500</v>
@@ -27658,7 +27658,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G941" t="n">
-        <v>4.63109493255615</v>
+        <v>4.63109540939331</v>
       </c>
       <c r="H941" t="n">
         <v>500</v>
@@ -27687,7 +27687,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G942" t="n">
-        <v>4.65007543563843</v>
+        <v>4.65007495880127</v>
       </c>
       <c r="H942" t="n">
         <v>1500</v>
@@ -27716,7 +27716,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G943" t="n">
-        <v>4.65007543563843</v>
+        <v>4.65007495880127</v>
       </c>
       <c r="H943" t="n">
         <v>0</v>
@@ -27745,7 +27745,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G944" t="n">
-        <v>4.65007543563843</v>
+        <v>4.65007495880127</v>
       </c>
       <c r="H944" t="n">
         <v>0</v>
@@ -27774,7 +27774,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G945" t="n">
-        <v>4.65007543563843</v>
+        <v>4.65007495880127</v>
       </c>
       <c r="H945" t="n">
         <v>0</v>
@@ -27803,7 +27803,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G946" t="n">
-        <v>4.65007543563843</v>
+        <v>4.65007495880127</v>
       </c>
       <c r="H946" t="n">
         <v>0</v>
@@ -27832,7 +27832,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G947" t="n">
-        <v>4.65007543563843</v>
+        <v>4.65007495880127</v>
       </c>
       <c r="H947" t="n">
         <v>0</v>
@@ -27861,7 +27861,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G948" t="n">
-        <v>4.65007543563843</v>
+        <v>4.65007495880127</v>
       </c>
       <c r="H948" t="n">
         <v>0</v>
@@ -27890,7 +27890,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G949" t="n">
-        <v>4.65007543563843</v>
+        <v>4.65007495880127</v>
       </c>
       <c r="H949" t="n">
         <v>0</v>
@@ -27919,7 +27919,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G950" t="n">
-        <v>4.63109493255615</v>
+        <v>4.63109540939331</v>
       </c>
       <c r="H950" t="n">
         <v>2250</v>
@@ -27948,7 +27948,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G951" t="n">
-        <v>4.63109493255615</v>
+        <v>4.63109540939331</v>
       </c>
       <c r="H951" t="n">
         <v>0</v>
@@ -27977,7 +27977,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G952" t="n">
-        <v>4.63109493255615</v>
+        <v>4.63109540939331</v>
       </c>
       <c r="H952" t="n">
         <v>250</v>
@@ -28006,7 +28006,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G953" t="n">
-        <v>4.63109493255615</v>
+        <v>4.63109540939331</v>
       </c>
       <c r="H953" t="n">
         <v>0</v>
@@ -28180,7 +28180,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G959" t="n">
-        <v>4.49823522567749</v>
+        <v>4.49823570251465</v>
       </c>
       <c r="H959" t="n">
         <v>1250</v>
@@ -28238,7 +28238,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G961" t="n">
-        <v>4.49823522567749</v>
+        <v>4.49823570251465</v>
       </c>
       <c r="H961" t="n">
         <v>1000</v>
@@ -28267,7 +28267,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G962" t="n">
-        <v>4.36537647247314</v>
+        <v>4.36537599563599</v>
       </c>
       <c r="H962" t="n">
         <v>1250</v>
@@ -28296,7 +28296,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G963" t="n">
-        <v>4.36537647247314</v>
+        <v>4.36537599563599</v>
       </c>
       <c r="H963" t="n">
         <v>2250</v>
@@ -28325,7 +28325,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G964" t="n">
-        <v>4.32741641998291</v>
+        <v>4.32741689682007</v>
       </c>
       <c r="H964" t="n">
         <v>1500</v>
@@ -28528,7 +28528,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G971" t="n">
-        <v>4.36537647247314</v>
+        <v>4.36537599563599</v>
       </c>
       <c r="H971" t="n">
         <v>7500</v>
@@ -28644,7 +28644,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G975" t="n">
-        <v>4.13761806488037</v>
+        <v>4.13761758804321</v>
       </c>
       <c r="H975" t="n">
         <v>2000</v>
@@ -28905,7 +28905,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G984" t="n">
-        <v>4.36537647247314</v>
+        <v>4.36537599563599</v>
       </c>
       <c r="H984" t="n">
         <v>1250</v>
@@ -28934,7 +28934,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G985" t="n">
-        <v>4.36537647247314</v>
+        <v>4.36537599563599</v>
       </c>
       <c r="H985" t="n">
         <v>1750</v>
@@ -28963,7 +28963,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G986" t="n">
-        <v>4.36537647247314</v>
+        <v>4.36537599563599</v>
       </c>
       <c r="H986" t="n">
         <v>5750</v>
@@ -28992,7 +28992,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G987" t="n">
-        <v>4.34639644622803</v>
+        <v>4.34639692306519</v>
       </c>
       <c r="H987" t="n">
         <v>750</v>
@@ -29050,7 +29050,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G989" t="n">
-        <v>4.32741641998291</v>
+        <v>4.32741689682007</v>
       </c>
       <c r="H989" t="n">
         <v>4250</v>
@@ -29079,7 +29079,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G990" t="n">
-        <v>4.36537647247314</v>
+        <v>4.36537599563599</v>
       </c>
       <c r="H990" t="n">
         <v>750</v>
@@ -29137,7 +29137,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G992" t="n">
-        <v>4.36537647247314</v>
+        <v>4.36537599563599</v>
       </c>
       <c r="H992" t="n">
         <v>4000</v>
@@ -29514,7 +29514,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.55517530441284</v>
+        <v>4.55517578125</v>
       </c>
       <c r="H1005" t="n">
         <v>500</v>
@@ -29572,7 +29572,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.57415533065796</v>
+        <v>4.57415580749512</v>
       </c>
       <c r="H1007" t="n">
         <v>18500</v>
@@ -29688,7 +29688,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.63109493255615</v>
+        <v>4.63109540939331</v>
       </c>
       <c r="H1011" t="n">
         <v>500</v>
@@ -30036,7 +30036,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.32741641998291</v>
+        <v>4.32741689682007</v>
       </c>
       <c r="H1023" t="n">
         <v>500</v>
@@ -30065,7 +30065,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.32741641998291</v>
+        <v>4.32741689682007</v>
       </c>
       <c r="H1024" t="n">
         <v>750</v>
@@ -30094,7 +30094,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.32741641998291</v>
+        <v>4.32741689682007</v>
       </c>
       <c r="H1025" t="n">
         <v>0</v>
@@ -30123,7 +30123,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.32741641998291</v>
+        <v>4.32741689682007</v>
       </c>
       <c r="H1026" t="n">
         <v>0</v>
@@ -30152,7 +30152,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.32741641998291</v>
+        <v>4.32741689682007</v>
       </c>
       <c r="H1027" t="n">
         <v>0</v>
@@ -30210,7 +30210,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.13761806488037</v>
+        <v>4.13761758804321</v>
       </c>
       <c r="H1029" t="n">
         <v>2000</v>
@@ -30239,7 +30239,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1030" t="n">
-        <v>4.11863803863525</v>
+        <v>4.1186375617981</v>
       </c>
       <c r="H1030" t="n">
         <v>1250</v>
@@ -30384,7 +30384,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.85291910171509</v>
+        <v>3.85291934013367</v>
       </c>
       <c r="H1035" t="n">
         <v>7500</v>
@@ -30587,7 +30587,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.08067846298218</v>
+        <v>4.08067798614502</v>
       </c>
       <c r="H1042" t="n">
         <v>750</v>
@@ -30790,7 +30790,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.08067846298218</v>
+        <v>4.08067798614502</v>
       </c>
       <c r="H1049" t="n">
         <v>250</v>
@@ -30819,7 +30819,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.08067846298218</v>
+        <v>4.08067798614502</v>
       </c>
       <c r="H1050" t="n">
         <v>0</v>
@@ -30848,7 +30848,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.08067846298218</v>
+        <v>4.08067798614502</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -30906,7 +30906,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1053" t="n">
-        <v>4.08067846298218</v>
+        <v>4.08067798614502</v>
       </c>
       <c r="H1053" t="n">
         <v>4500</v>
@@ -30993,7 +30993,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.94781875610352</v>
+        <v>3.94781851768494</v>
       </c>
       <c r="H1056" t="n">
         <v>1750</v>
@@ -31022,7 +31022,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.94781875610352</v>
+        <v>3.94781851768494</v>
       </c>
       <c r="H1057" t="n">
         <v>0</v>
@@ -31138,7 +31138,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.89087915420532</v>
+        <v>3.89087891578674</v>
       </c>
       <c r="H1061" t="n">
         <v>5750</v>
@@ -31225,7 +31225,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.6061806678772</v>
+        <v>3.60618042945862</v>
       </c>
       <c r="H1064" t="n">
         <v>3750</v>
@@ -31747,7 +31747,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.58720064163208</v>
+        <v>3.5872004032135</v>
       </c>
       <c r="H1082" t="n">
         <v>2750</v>
@@ -31921,7 +31921,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.6061806678772</v>
+        <v>3.60618042945862</v>
       </c>
       <c r="H1088" t="n">
         <v>500</v>
@@ -32037,7 +32037,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.81495928764343</v>
+        <v>3.81495952606201</v>
       </c>
       <c r="H1092" t="n">
         <v>19500</v>
@@ -32153,7 +32153,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1096" t="n">
-        <v>4.11863803863525</v>
+        <v>4.1186375617981</v>
       </c>
       <c r="H1096" t="n">
         <v>3750</v>
@@ -43208,6 +43208,35 @@
         <v>6500</v>
       </c>
       <c r="I1477" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1478" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1478" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="D1478" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="E1478" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F1478" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="G1478" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="H1478" t="n">
+        <v>11000</v>
+      </c>
+      <c r="I1478" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PLN.MI.xlsx
+++ b/data/PLN.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.41200017929077</v>
       </c>
       <c r="G2" t="n">
-        <v>4.05409336090088</v>
+        <v>4.05409288406372</v>
       </c>
       <c r="H2" t="n">
         <v>42000</v>
@@ -514,7 +514,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G5" t="n">
-        <v>4.22684192657471</v>
+        <v>4.22684240341187</v>
       </c>
       <c r="H5" t="n">
         <v>12000</v>
@@ -717,7 +717,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G12" t="n">
-        <v>3.96955585479736</v>
+        <v>3.96955633163452</v>
       </c>
       <c r="H12" t="n">
         <v>26000</v>
@@ -746,7 +746,7 @@
         <v>4.25</v>
       </c>
       <c r="G13" t="n">
-        <v>3.90523457527161</v>
+        <v>3.90523433685303</v>
       </c>
       <c r="H13" t="n">
         <v>19500</v>
@@ -775,7 +775,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G14" t="n">
-        <v>3.95117902755737</v>
+        <v>3.95117855072021</v>
       </c>
       <c r="H14" t="n">
         <v>19000</v>
@@ -804,7 +804,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G15" t="n">
-        <v>3.89604520797729</v>
+        <v>3.89604544639587</v>
       </c>
       <c r="H15" t="n">
         <v>12500</v>
@@ -862,7 +862,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G17" t="n">
-        <v>3.81334662437439</v>
+        <v>3.81334638595581</v>
       </c>
       <c r="H17" t="n">
         <v>19000</v>
@@ -891,7 +891,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G18" t="n">
-        <v>3.72145915031433</v>
+        <v>3.72145867347717</v>
       </c>
       <c r="H18" t="n">
         <v>43500</v>
@@ -920,7 +920,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G19" t="n">
-        <v>3.95117902755737</v>
+        <v>3.95117855072021</v>
       </c>
       <c r="H19" t="n">
         <v>44000</v>
@@ -949,7 +949,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G20" t="n">
-        <v>3.87766814231873</v>
+        <v>3.87766790390015</v>
       </c>
       <c r="H20" t="n">
         <v>12000</v>
@@ -978,7 +978,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G21" t="n">
-        <v>3.87766814231873</v>
+        <v>3.87766790390015</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G22" t="n">
-        <v>3.87766814231873</v>
+        <v>3.87766790390015</v>
       </c>
       <c r="H22" t="n">
         <v>60000</v>
@@ -1065,7 +1065,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G24" t="n">
-        <v>3.8868567943573</v>
+        <v>3.88685703277588</v>
       </c>
       <c r="H24" t="n">
         <v>500</v>
@@ -1094,7 +1094,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>3.98793411254883</v>
+        <v>3.98793363571167</v>
       </c>
       <c r="H25" t="n">
         <v>7500</v>
@@ -1123,7 +1123,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G26" t="n">
-        <v>4.18089818954468</v>
+        <v>4.18089866638184</v>
       </c>
       <c r="H26" t="n">
         <v>15000</v>
@@ -1239,7 +1239,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G30" t="n">
-        <v>4.18089818954468</v>
+        <v>4.18089866638184</v>
       </c>
       <c r="H30" t="n">
         <v>3500</v>
@@ -1413,7 +1413,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G36" t="n">
-        <v>4.06144380569458</v>
+        <v>4.06144428253174</v>
       </c>
       <c r="H36" t="n">
         <v>18500</v>
@@ -1442,7 +1442,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G37" t="n">
-        <v>4.05225515365601</v>
+        <v>4.05225467681885</v>
       </c>
       <c r="H37" t="n">
         <v>2000</v>
@@ -1471,7 +1471,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G38" t="n">
-        <v>4.05225515365601</v>
+        <v>4.05225467681885</v>
       </c>
       <c r="H38" t="n">
         <v>11500</v>
@@ -1703,7 +1703,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G46" t="n">
-        <v>3.95117902755737</v>
+        <v>3.95117855072021</v>
       </c>
       <c r="H46" t="n">
         <v>4000</v>
@@ -1732,7 +1732,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G47" t="n">
-        <v>3.99712181091309</v>
+        <v>3.99712228775024</v>
       </c>
       <c r="H47" t="n">
         <v>3000</v>
@@ -1761,7 +1761,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G48" t="n">
-        <v>3.95117902755737</v>
+        <v>3.95117855072021</v>
       </c>
       <c r="H48" t="n">
         <v>2000</v>
@@ -1790,7 +1790,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G49" t="n">
-        <v>3.95117902755737</v>
+        <v>3.95117855072021</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G51" t="n">
-        <v>3.89604520797729</v>
+        <v>3.89604544639587</v>
       </c>
       <c r="H51" t="n">
         <v>31000</v>
@@ -1906,7 +1906,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G53" t="n">
-        <v>3.89604520797729</v>
+        <v>3.89604544639587</v>
       </c>
       <c r="H53" t="n">
         <v>11000</v>
@@ -1935,7 +1935,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G54" t="n">
-        <v>3.85929012298584</v>
+        <v>3.859290599823</v>
       </c>
       <c r="H54" t="n">
         <v>5000</v>
@@ -1964,7 +1964,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G55" t="n">
-        <v>3.85929012298584</v>
+        <v>3.859290599823</v>
       </c>
       <c r="H55" t="n">
         <v>6000</v>
@@ -1993,7 +1993,7 @@
         <v>4.25</v>
       </c>
       <c r="G56" t="n">
-        <v>3.90523457527161</v>
+        <v>3.90523433685303</v>
       </c>
       <c r="H56" t="n">
         <v>7500</v>
@@ -2022,7 +2022,7 @@
         <v>4.25</v>
       </c>
       <c r="G57" t="n">
-        <v>3.90523457527161</v>
+        <v>3.90523433685303</v>
       </c>
       <c r="H57" t="n">
         <v>3000</v>
@@ -2051,7 +2051,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>3.95117902755737</v>
+        <v>3.95117855072021</v>
       </c>
       <c r="H58" t="n">
         <v>3500</v>
@@ -2080,7 +2080,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>3.95117902755737</v>
+        <v>3.95117855072021</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G61" t="n">
-        <v>3.99712181091309</v>
+        <v>3.99712228775024</v>
       </c>
       <c r="H61" t="n">
         <v>7000</v>
@@ -2225,7 +2225,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G64" t="n">
-        <v>4.05225515365601</v>
+        <v>4.05225467681885</v>
       </c>
       <c r="H64" t="n">
         <v>26000</v>
@@ -2312,7 +2312,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G67" t="n">
-        <v>4.28197526931763</v>
+        <v>4.28197479248047</v>
       </c>
       <c r="H67" t="n">
         <v>12500</v>
@@ -2399,7 +2399,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G70" t="n">
-        <v>4.42899560928345</v>
+        <v>4.42899513244629</v>
       </c>
       <c r="H70" t="n">
         <v>64500</v>
@@ -2544,7 +2544,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>4.61277151107788</v>
+        <v>4.61277103424072</v>
       </c>
       <c r="H75" t="n">
         <v>9500</v>
@@ -2573,7 +2573,7 @@
         <v>5</v>
       </c>
       <c r="G76" t="n">
-        <v>4.59439325332642</v>
+        <v>4.59439373016357</v>
       </c>
       <c r="H76" t="n">
         <v>6000</v>
@@ -2689,7 +2689,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G80" t="n">
-        <v>4.90681266784668</v>
+        <v>4.90681219100952</v>
       </c>
       <c r="H80" t="n">
         <v>35500</v>
@@ -2776,7 +2776,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G83" t="n">
-        <v>4.92518997192383</v>
+        <v>4.92519044876099</v>
       </c>
       <c r="H83" t="n">
         <v>3500</v>
@@ -2805,7 +2805,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>5.18247556686401</v>
+        <v>5.18247604370117</v>
       </c>
       <c r="H84" t="n">
         <v>27000</v>
@@ -2834,7 +2834,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G85" t="n">
-        <v>4.96194505691528</v>
+        <v>4.96194553375244</v>
       </c>
       <c r="H85" t="n">
         <v>27000</v>
@@ -2863,7 +2863,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G86" t="n">
-        <v>5.18247556686401</v>
+        <v>5.18247604370117</v>
       </c>
       <c r="H86" t="n">
         <v>18000</v>
@@ -2921,7 +2921,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G88" t="n">
-        <v>5.58678245544434</v>
+        <v>5.58678293228149</v>
       </c>
       <c r="H88" t="n">
         <v>20500</v>
@@ -3211,7 +3211,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G98" t="n">
-        <v>6.22999811172485</v>
+        <v>6.2299976348877</v>
       </c>
       <c r="H98" t="n">
         <v>26000</v>
@@ -3385,7 +3385,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G104" t="n">
-        <v>6.02784395217896</v>
+        <v>6.02784442901611</v>
       </c>
       <c r="H104" t="n">
         <v>15000</v>
@@ -3501,7 +3501,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>6.04622173309326</v>
+        <v>6.0462212562561</v>
       </c>
       <c r="H108" t="n">
         <v>12500</v>
@@ -3530,7 +3530,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G109" t="n">
-        <v>5.86244678497314</v>
+        <v>5.86244630813599</v>
       </c>
       <c r="H109" t="n">
         <v>14500</v>
@@ -3559,7 +3559,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G110" t="n">
-        <v>5.86244678497314</v>
+        <v>5.86244630813599</v>
       </c>
       <c r="H110" t="n">
         <v>5000</v>
@@ -3588,7 +3588,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G111" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H111" t="n">
         <v>3500</v>
@@ -3617,7 +3617,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G112" t="n">
-        <v>5.82569122314453</v>
+        <v>5.82569169998169</v>
       </c>
       <c r="H112" t="n">
         <v>3500</v>
@@ -3646,7 +3646,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>5.88082361221313</v>
+        <v>5.88082408905029</v>
       </c>
       <c r="H113" t="n">
         <v>500</v>
@@ -3675,7 +3675,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G114" t="n">
-        <v>5.88082361221313</v>
+        <v>5.88082408905029</v>
       </c>
       <c r="H114" t="n">
         <v>500</v>
@@ -3907,7 +3907,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G122" t="n">
-        <v>5.25598573684692</v>
+        <v>5.25598621368408</v>
       </c>
       <c r="H122" t="n">
         <v>10000</v>
@@ -3936,7 +3936,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G123" t="n">
-        <v>5.23760843276978</v>
+        <v>5.23760795593262</v>
       </c>
       <c r="H123" t="n">
         <v>13000</v>
@@ -3994,7 +3994,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G125" t="n">
-        <v>5.71542549133301</v>
+        <v>5.71542501449585</v>
       </c>
       <c r="H125" t="n">
         <v>14000</v>
@@ -4023,7 +4023,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G126" t="n">
-        <v>5.58678245544434</v>
+        <v>5.58678293228149</v>
       </c>
       <c r="H126" t="n">
         <v>1500</v>
@@ -4052,7 +4052,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G127" t="n">
-        <v>5.25598573684692</v>
+        <v>5.25598621368408</v>
       </c>
       <c r="H127" t="n">
         <v>22000</v>
@@ -4081,7 +4081,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G128" t="n">
-        <v>5.56840515136719</v>
+        <v>5.56840467453003</v>
       </c>
       <c r="H128" t="n">
         <v>10500</v>
@@ -4313,7 +4313,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>5.55002689361572</v>
+        <v>5.55002737045288</v>
       </c>
       <c r="H136" t="n">
         <v>7000</v>
@@ -4342,7 +4342,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>5.55002689361572</v>
+        <v>5.55002737045288</v>
       </c>
       <c r="H137" t="n">
         <v>1000</v>
@@ -4371,7 +4371,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G138" t="n">
-        <v>5.55002689361572</v>
+        <v>5.55002737045288</v>
       </c>
       <c r="H138" t="n">
         <v>3000</v>
@@ -4400,7 +4400,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G139" t="n">
-        <v>5.55002689361572</v>
+        <v>5.55002737045288</v>
       </c>
       <c r="H139" t="n">
         <v>10500</v>
@@ -4429,7 +4429,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H140" t="n">
         <v>2000</v>
@@ -4458,7 +4458,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G141" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G143" t="n">
-        <v>5.88082361221313</v>
+        <v>5.88082408905029</v>
       </c>
       <c r="H143" t="n">
         <v>5500</v>
@@ -4574,7 +4574,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G145" t="n">
-        <v>5.86244678497314</v>
+        <v>5.86244630813599</v>
       </c>
       <c r="H145" t="n">
         <v>1500</v>
@@ -4603,7 +4603,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G146" t="n">
-        <v>5.86244678497314</v>
+        <v>5.86244630813599</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>5.88082361221313</v>
+        <v>5.88082408905029</v>
       </c>
       <c r="H147" t="n">
         <v>5000</v>
@@ -4661,7 +4661,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G148" t="n">
-        <v>5.88082361221313</v>
+        <v>5.88082408905029</v>
       </c>
       <c r="H148" t="n">
         <v>500</v>
@@ -4748,7 +4748,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>6.06459903717041</v>
+        <v>6.06459951400757</v>
       </c>
       <c r="H151" t="n">
         <v>5500</v>
@@ -4777,7 +4777,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G152" t="n">
-        <v>6.02784395217896</v>
+        <v>6.02784442901611</v>
       </c>
       <c r="H152" t="n">
         <v>6000</v>
@@ -4806,7 +4806,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G153" t="n">
-        <v>6.06459903717041</v>
+        <v>6.06459951400757</v>
       </c>
       <c r="H153" t="n">
         <v>1000</v>
@@ -4835,7 +4835,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G154" t="n">
-        <v>6.24837493896484</v>
+        <v>6.248375415802</v>
       </c>
       <c r="H154" t="n">
         <v>55500</v>
@@ -4864,7 +4864,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G155" t="n">
-        <v>6.28513050079346</v>
+        <v>6.2851300239563</v>
       </c>
       <c r="H155" t="n">
         <v>3500</v>
@@ -4893,7 +4893,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G156" t="n">
-        <v>6.35864067077637</v>
+        <v>6.35864114761353</v>
       </c>
       <c r="H156" t="n">
         <v>13000</v>
@@ -5183,7 +5183,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>6.56079435348511</v>
+        <v>6.56079387664795</v>
       </c>
       <c r="H166" t="n">
         <v>2500</v>
@@ -5386,7 +5386,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G173" t="n">
-        <v>6.46890640258789</v>
+        <v>6.46890592575073</v>
       </c>
       <c r="H173" t="n">
         <v>2000</v>
@@ -5415,7 +5415,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G174" t="n">
-        <v>6.39539575576782</v>
+        <v>6.39539623260498</v>
       </c>
       <c r="H174" t="n">
         <v>4500</v>
@@ -5560,7 +5560,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H179" t="n">
         <v>1500</v>
@@ -5589,7 +5589,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5618,7 +5618,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H181" t="n">
         <v>1500</v>
@@ -5647,7 +5647,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G182" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H182" t="n">
         <v>2500</v>
@@ -5676,7 +5676,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G188" t="n">
-        <v>7.24076414108276</v>
+        <v>7.24076461791992</v>
       </c>
       <c r="H188" t="n">
         <v>1000</v>
@@ -5850,7 +5850,7 @@
         <v>8</v>
       </c>
       <c r="G189" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H189" t="n">
         <v>3500</v>
@@ -6024,7 +6024,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G195" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H195" t="n">
         <v>12000</v>
@@ -6169,7 +6169,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>7.31427431106567</v>
+        <v>7.31427478790283</v>
       </c>
       <c r="H200" t="n">
         <v>7500</v>
@@ -6198,7 +6198,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G201" t="n">
-        <v>7.31427431106567</v>
+        <v>7.31427478790283</v>
       </c>
       <c r="H201" t="n">
         <v>6000</v>
@@ -6285,7 +6285,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G204" t="n">
-        <v>7.79209041595459</v>
+        <v>7.79209089279175</v>
       </c>
       <c r="H204" t="n">
         <v>6500</v>
@@ -6314,7 +6314,7 @@
         <v>8.5</v>
       </c>
       <c r="G205" t="n">
-        <v>7.81046915054321</v>
+        <v>7.81046867370605</v>
       </c>
       <c r="H205" t="n">
         <v>6500</v>
@@ -6343,7 +6343,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G206" t="n">
-        <v>8.12288761138916</v>
+        <v>8.12288856506348</v>
       </c>
       <c r="H206" t="n">
         <v>16500</v>
@@ -6517,7 +6517,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G212" t="n">
-        <v>8.12288761138916</v>
+        <v>8.12288856506348</v>
       </c>
       <c r="H212" t="n">
         <v>500</v>
@@ -6662,7 +6662,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G217" t="n">
-        <v>8.61908340454102</v>
+        <v>8.6190824508667</v>
       </c>
       <c r="H217" t="n">
         <v>4000</v>
@@ -6720,7 +6720,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G219" t="n">
-        <v>8.61908340454102</v>
+        <v>8.6190824508667</v>
       </c>
       <c r="H219" t="n">
         <v>1000</v>
@@ -6807,7 +6807,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G222" t="n">
-        <v>8.60070419311523</v>
+        <v>8.60070514678955</v>
       </c>
       <c r="H222" t="n">
         <v>2500</v>
@@ -6836,7 +6836,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G223" t="n">
-        <v>8.78448009490967</v>
+        <v>8.78448104858398</v>
       </c>
       <c r="H223" t="n">
         <v>1000</v>
@@ -6981,7 +6981,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G228" t="n">
-        <v>8.63746070861816</v>
+        <v>8.63745975494385</v>
       </c>
       <c r="H228" t="n">
         <v>20000</v>
@@ -7010,7 +7010,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G229" t="n">
-        <v>8.63746070861816</v>
+        <v>8.63745975494385</v>
       </c>
       <c r="H229" t="n">
         <v>12500</v>
@@ -7039,7 +7039,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G230" t="n">
-        <v>8.63746070861816</v>
+        <v>8.63745975494385</v>
       </c>
       <c r="H230" t="n">
         <v>7000</v>
@@ -7068,7 +7068,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G231" t="n">
-        <v>8.60070419311523</v>
+        <v>8.60070514678955</v>
       </c>
       <c r="H231" t="n">
         <v>4000</v>
@@ -7097,7 +7097,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G232" t="n">
-        <v>8.61908340454102</v>
+        <v>8.6190824508667</v>
       </c>
       <c r="H232" t="n">
         <v>5000</v>
@@ -7126,7 +7126,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G233" t="n">
-        <v>8.63746070861816</v>
+        <v>8.63745975494385</v>
       </c>
       <c r="H233" t="n">
         <v>11000</v>
@@ -7213,7 +7213,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G236" t="n">
-        <v>8.14126491546631</v>
+        <v>8.14126586914062</v>
       </c>
       <c r="H236" t="n">
         <v>6500</v>
@@ -7416,7 +7416,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G243" t="n">
-        <v>8.56395053863525</v>
+        <v>8.56394958496094</v>
       </c>
       <c r="H243" t="n">
         <v>500</v>
@@ -7445,7 +7445,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G244" t="n">
-        <v>8.56395053863525</v>
+        <v>8.56394958496094</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G245" t="n">
-        <v>8.36179637908936</v>
+        <v>8.36179733276367</v>
       </c>
       <c r="H245" t="n">
         <v>500</v>
@@ -7503,7 +7503,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G246" t="n">
-        <v>8.36179637908936</v>
+        <v>8.36179733276367</v>
       </c>
       <c r="H246" t="n">
         <v>1500</v>
@@ -7561,7 +7561,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G248" t="n">
-        <v>8.63746070861816</v>
+        <v>8.63745975494385</v>
       </c>
       <c r="H248" t="n">
         <v>7500</v>
@@ -7590,7 +7590,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G249" t="n">
-        <v>8.45368385314941</v>
+        <v>8.45368480682373</v>
       </c>
       <c r="H249" t="n">
         <v>1000</v>
@@ -7822,7 +7822,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G257" t="n">
-        <v>8.87636852264404</v>
+        <v>8.87636756896973</v>
       </c>
       <c r="H257" t="n">
         <v>4000</v>
@@ -7851,7 +7851,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G258" t="n">
-        <v>9.09689903259277</v>
+        <v>9.09689807891846</v>
       </c>
       <c r="H258" t="n">
         <v>1500</v>
@@ -7880,7 +7880,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G259" t="n">
-        <v>9.09689903259277</v>
+        <v>9.09689807891846</v>
       </c>
       <c r="H259" t="n">
         <v>4500</v>
@@ -7909,7 +7909,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G260" t="n">
-        <v>9.09689903259277</v>
+        <v>9.09689807891846</v>
       </c>
       <c r="H260" t="n">
         <v>500</v>
@@ -7996,7 +7996,7 @@
         <v>10</v>
       </c>
       <c r="G263" t="n">
-        <v>9.18878650665283</v>
+        <v>9.18878746032715</v>
       </c>
       <c r="H263" t="n">
         <v>500</v>
@@ -8286,7 +8286,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G273" t="n">
-        <v>7.29589748382568</v>
+        <v>7.29589700698853</v>
       </c>
       <c r="H273" t="n">
         <v>6500</v>
@@ -8402,7 +8402,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G277" t="n">
-        <v>7.40616273880005</v>
+        <v>7.40616321563721</v>
       </c>
       <c r="H277" t="n">
         <v>14000</v>
@@ -8489,7 +8489,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G280" t="n">
-        <v>7.4245400428772</v>
+        <v>7.42454051971436</v>
       </c>
       <c r="H280" t="n">
         <v>3500</v>
@@ -8518,7 +8518,7 @@
         <v>8</v>
       </c>
       <c r="G281" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H281" t="n">
         <v>3000</v>
@@ -8547,7 +8547,7 @@
         <v>8</v>
       </c>
       <c r="G282" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>8</v>
       </c>
       <c r="G283" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H283" t="n">
         <v>7500</v>
@@ -8750,7 +8750,7 @@
         <v>8</v>
       </c>
       <c r="G289" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H289" t="n">
         <v>1500</v>
@@ -8779,7 +8779,7 @@
         <v>8</v>
       </c>
       <c r="G290" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H290" t="n">
         <v>9000</v>
@@ -8808,7 +8808,7 @@
         <v>8</v>
       </c>
       <c r="G291" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H291" t="n">
         <v>1500</v>
@@ -8837,7 +8837,7 @@
         <v>8</v>
       </c>
       <c r="G292" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H292" t="n">
         <v>3000</v>
@@ -9011,7 +9011,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>6.98347759246826</v>
+        <v>6.98347806930542</v>
       </c>
       <c r="H298" t="n">
         <v>7000</v>
@@ -9040,7 +9040,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>6.98347759246826</v>
+        <v>6.98347806930542</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>6.98347759246826</v>
+        <v>6.98347806930542</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G301" t="n">
-        <v>6.98347759246826</v>
+        <v>6.98347806930542</v>
       </c>
       <c r="H301" t="n">
         <v>18500</v>
@@ -9243,7 +9243,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G306" t="n">
-        <v>7.07536554336548</v>
+        <v>7.07536602020264</v>
       </c>
       <c r="H306" t="n">
         <v>1500</v>
@@ -9272,7 +9272,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G307" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H307" t="n">
         <v>500</v>
@@ -9359,7 +9359,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G310" t="n">
-        <v>7.07536554336548</v>
+        <v>7.07536602020264</v>
       </c>
       <c r="H310" t="n">
         <v>3000</v>
@@ -9475,7 +9475,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G314" t="n">
-        <v>7.44291830062866</v>
+        <v>7.44291734695435</v>
       </c>
       <c r="H314" t="n">
         <v>2000</v>
@@ -9504,7 +9504,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G315" t="n">
-        <v>7.44291830062866</v>
+        <v>7.44291734695435</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G316" t="n">
-        <v>7.44291830062866</v>
+        <v>7.44291734695435</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>7.44291830062866</v>
+        <v>7.44291734695435</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G318" t="n">
-        <v>7.44291830062866</v>
+        <v>7.44291734695435</v>
       </c>
       <c r="H318" t="n">
         <v>500</v>
@@ -9881,7 +9881,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G328" t="n">
-        <v>6.98347759246826</v>
+        <v>6.98347806930542</v>
       </c>
       <c r="H328" t="n">
         <v>1000</v>
@@ -9939,7 +9939,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G330" t="n">
-        <v>7.02023315429688</v>
+        <v>7.02023363113403</v>
       </c>
       <c r="H330" t="n">
         <v>500</v>
@@ -9968,7 +9968,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G331" t="n">
-        <v>7.02023315429688</v>
+        <v>7.02023363113403</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G332" t="n">
-        <v>7.02023315429688</v>
+        <v>7.02023363113403</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G333" t="n">
-        <v>7.02023315429688</v>
+        <v>7.02023363113403</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10200,7 +10200,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G339" t="n">
-        <v>6.37701845169067</v>
+        <v>6.37701797485352</v>
       </c>
       <c r="H339" t="n">
         <v>4500</v>
@@ -10258,7 +10258,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G341" t="n">
-        <v>6.15648698806763</v>
+        <v>6.15648746490479</v>
       </c>
       <c r="H341" t="n">
         <v>1000</v>
@@ -10287,7 +10287,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G342" t="n">
-        <v>6.15648698806763</v>
+        <v>6.15648746490479</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -10316,7 +10316,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G343" t="n">
-        <v>6.02784395217896</v>
+        <v>6.02784442901611</v>
       </c>
       <c r="H343" t="n">
         <v>9500</v>
@@ -10403,7 +10403,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G346" t="n">
-        <v>6.04622173309326</v>
+        <v>6.0462212562561</v>
       </c>
       <c r="H346" t="n">
         <v>1000</v>
@@ -10490,7 +10490,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G349" t="n">
-        <v>6.21161985397339</v>
+        <v>6.21162033081055</v>
       </c>
       <c r="H349" t="n">
         <v>1500</v>
@@ -10519,7 +10519,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G350" t="n">
-        <v>6.04622173309326</v>
+        <v>6.0462212562561</v>
       </c>
       <c r="H350" t="n">
         <v>1000</v>
@@ -10606,7 +10606,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G353" t="n">
-        <v>5.91757869720459</v>
+        <v>5.91757965087891</v>
       </c>
       <c r="H353" t="n">
         <v>3000</v>
@@ -10635,7 +10635,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G354" t="n">
-        <v>5.91757869720459</v>
+        <v>5.91757965087891</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G355" t="n">
-        <v>6.24837493896484</v>
+        <v>6.248375415802</v>
       </c>
       <c r="H355" t="n">
         <v>4000</v>
@@ -10693,7 +10693,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>6.24837493896484</v>
+        <v>6.248375415802</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -10722,7 +10722,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G357" t="n">
-        <v>6.24837493896484</v>
+        <v>6.248375415802</v>
       </c>
       <c r="H357" t="n">
         <v>500</v>
@@ -10751,7 +10751,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G358" t="n">
-        <v>6.24837493896484</v>
+        <v>6.248375415802</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -10809,7 +10809,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G360" t="n">
-        <v>6.68943738937378</v>
+        <v>6.68943786621094</v>
       </c>
       <c r="H360" t="n">
         <v>2000</v>
@@ -10867,7 +10867,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G362" t="n">
-        <v>6.68943738937378</v>
+        <v>6.68943786621094</v>
       </c>
       <c r="H362" t="n">
         <v>5500</v>
@@ -10896,7 +10896,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G363" t="n">
-        <v>6.68943738937378</v>
+        <v>6.68943786621094</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G366" t="n">
-        <v>6.15648698806763</v>
+        <v>6.15648746490479</v>
       </c>
       <c r="H366" t="n">
         <v>6500</v>
@@ -11128,7 +11128,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G371" t="n">
-        <v>6.21161985397339</v>
+        <v>6.21162033081055</v>
       </c>
       <c r="H371" t="n">
         <v>4000</v>
@@ -11157,7 +11157,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G372" t="n">
-        <v>6.21161985397339</v>
+        <v>6.21162033081055</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G373" t="n">
-        <v>6.21161985397339</v>
+        <v>6.21162033081055</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G374" t="n">
-        <v>6.21161985397339</v>
+        <v>6.21162033081055</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>6.15648698806763</v>
+        <v>6.15648746490479</v>
       </c>
       <c r="H375" t="n">
         <v>500</v>
@@ -11273,7 +11273,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G376" t="n">
-        <v>6.04622173309326</v>
+        <v>6.0462212562561</v>
       </c>
       <c r="H376" t="n">
         <v>3000</v>
@@ -11302,7 +11302,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>6.04622173309326</v>
+        <v>6.0462212562561</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11360,7 +11360,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>6.06459903717041</v>
+        <v>6.06459951400757</v>
       </c>
       <c r="H379" t="n">
         <v>1000</v>
@@ -11389,7 +11389,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>6.06459903717041</v>
+        <v>6.06459951400757</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>6.06459903717041</v>
+        <v>6.06459951400757</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G382" t="n">
-        <v>6.06459903717041</v>
+        <v>6.06459951400757</v>
       </c>
       <c r="H382" t="n">
         <v>500</v>
@@ -11592,7 +11592,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G387" t="n">
-        <v>5.82569122314453</v>
+        <v>5.82569169998169</v>
       </c>
       <c r="H387" t="n">
         <v>500</v>
@@ -11621,7 +11621,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G388" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H388" t="n">
         <v>1000</v>
@@ -11824,7 +11824,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G395" t="n">
-        <v>5.80731391906738</v>
+        <v>5.80731344223022</v>
       </c>
       <c r="H395" t="n">
         <v>1500</v>
@@ -11853,7 +11853,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G396" t="n">
-        <v>5.80731391906738</v>
+        <v>5.80731344223022</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G397" t="n">
-        <v>5.80731391906738</v>
+        <v>5.80731344223022</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -11911,7 +11911,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G398" t="n">
-        <v>5.91757869720459</v>
+        <v>5.91757965087891</v>
       </c>
       <c r="H398" t="n">
         <v>500</v>
@@ -11940,7 +11940,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G399" t="n">
-        <v>5.91757869720459</v>
+        <v>5.91757965087891</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G401" t="n">
-        <v>6.15648698806763</v>
+        <v>6.15648746490479</v>
       </c>
       <c r="H401" t="n">
         <v>2500</v>
@@ -12027,7 +12027,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G402" t="n">
-        <v>6.15648698806763</v>
+        <v>6.15648746490479</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G403" t="n">
-        <v>6.15648698806763</v>
+        <v>6.15648746490479</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G409" t="n">
-        <v>6.28513050079346</v>
+        <v>6.2851300239563</v>
       </c>
       <c r="H409" t="n">
         <v>1000</v>
@@ -12259,7 +12259,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G410" t="n">
-        <v>6.28513050079346</v>
+        <v>6.2851300239563</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -12288,7 +12288,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G411" t="n">
-        <v>6.28513050079346</v>
+        <v>6.2851300239563</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -12317,7 +12317,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G412" t="n">
-        <v>6.28513050079346</v>
+        <v>6.2851300239563</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G431" t="n">
-        <v>6.21161985397339</v>
+        <v>6.21162033081055</v>
       </c>
       <c r="H431" t="n">
         <v>1000</v>
@@ -13129,7 +13129,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>6.15648698806763</v>
+        <v>6.15648746490479</v>
       </c>
       <c r="H440" t="n">
         <v>1000</v>
@@ -13274,7 +13274,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G445" t="n">
-        <v>6.22999811172485</v>
+        <v>6.2299976348877</v>
       </c>
       <c r="H445" t="n">
         <v>500</v>
@@ -13303,7 +13303,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G446" t="n">
-        <v>6.22999811172485</v>
+        <v>6.2299976348877</v>
       </c>
       <c r="H446" t="n">
         <v>500</v>
@@ -13332,7 +13332,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G447" t="n">
-        <v>6.22999811172485</v>
+        <v>6.2299976348877</v>
       </c>
       <c r="H447" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G448" t="n">
-        <v>6.02784395217896</v>
+        <v>6.02784442901611</v>
       </c>
       <c r="H448" t="n">
         <v>1000</v>
@@ -13477,7 +13477,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G452" t="n">
-        <v>5.88082361221313</v>
+        <v>5.88082408905029</v>
       </c>
       <c r="H452" t="n">
         <v>1000</v>
@@ -13999,7 +13999,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G470" t="n">
-        <v>5.58678245544434</v>
+        <v>5.58678293228149</v>
       </c>
       <c r="H470" t="n">
         <v>500</v>
@@ -14028,7 +14028,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>5.58678245544434</v>
+        <v>5.58678293228149</v>
       </c>
       <c r="H471" t="n">
         <v>0</v>
@@ -14057,7 +14057,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G472" t="n">
-        <v>5.58678245544434</v>
+        <v>5.58678293228149</v>
       </c>
       <c r="H472" t="n">
         <v>0</v>
@@ -14086,7 +14086,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G473" t="n">
-        <v>5.58678245544434</v>
+        <v>5.58678293228149</v>
       </c>
       <c r="H473" t="n">
         <v>0</v>
@@ -14289,7 +14289,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G480" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H480" t="n">
         <v>1500</v>
@@ -14318,7 +14318,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G481" t="n">
-        <v>5.56840515136719</v>
+        <v>5.56840467453003</v>
       </c>
       <c r="H481" t="n">
         <v>1500</v>
@@ -14724,7 +14724,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G495" t="n">
-        <v>5.73380279541016</v>
+        <v>5.73380327224731</v>
       </c>
       <c r="H495" t="n">
         <v>2000</v>
@@ -14753,7 +14753,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G496" t="n">
-        <v>5.73380279541016</v>
+        <v>5.73380327224731</v>
       </c>
       <c r="H496" t="n">
         <v>0</v>
@@ -14782,7 +14782,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G497" t="n">
-        <v>5.73380279541016</v>
+        <v>5.73380327224731</v>
       </c>
       <c r="H497" t="n">
         <v>0</v>
@@ -14811,7 +14811,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G498" t="n">
-        <v>5.58678245544434</v>
+        <v>5.58678293228149</v>
       </c>
       <c r="H498" t="n">
         <v>500</v>
@@ -14840,7 +14840,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G499" t="n">
-        <v>5.58678245544434</v>
+        <v>5.58678293228149</v>
       </c>
       <c r="H499" t="n">
         <v>0</v>
@@ -14869,7 +14869,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G500" t="n">
-        <v>5.58678245544434</v>
+        <v>5.58678293228149</v>
       </c>
       <c r="H500" t="n">
         <v>1000</v>
@@ -15014,7 +15014,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>5.36625146865845</v>
+        <v>5.36625194549561</v>
       </c>
       <c r="H505" t="n">
         <v>1000</v>
@@ -15101,7 +15101,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>5.55002689361572</v>
+        <v>5.55002737045288</v>
       </c>
       <c r="H508" t="n">
         <v>500</v>
@@ -15275,7 +15275,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G514" t="n">
-        <v>5.55002689361572</v>
+        <v>5.55002737045288</v>
       </c>
       <c r="H514" t="n">
         <v>1000</v>
@@ -15478,7 +15478,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G521" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H521" t="n">
         <v>1000</v>
@@ -15884,7 +15884,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H535" t="n">
         <v>500</v>
@@ -15913,7 +15913,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G536" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H536" t="n">
         <v>0</v>
@@ -15971,7 +15971,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G538" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H538" t="n">
         <v>1000</v>
@@ -16000,7 +16000,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G539" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H539" t="n">
         <v>0</v>
@@ -16029,7 +16029,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G540" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H540" t="n">
         <v>0</v>
@@ -16058,7 +16058,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G541" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -16116,7 +16116,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G543" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H543" t="n">
         <v>0</v>
@@ -16145,7 +16145,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G544" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H544" t="n">
         <v>0</v>
@@ -16174,7 +16174,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G545" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H546" t="n">
         <v>0</v>
@@ -16232,7 +16232,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G547" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G548" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H548" t="n">
         <v>1500</v>
@@ -16290,7 +16290,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G549" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H549" t="n">
         <v>0</v>
@@ -16319,7 +16319,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G550" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -16348,7 +16348,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G551" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H551" t="n">
         <v>0</v>
@@ -16377,7 +16377,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G552" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H552" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G553" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G563" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H563" t="n">
         <v>500</v>
@@ -16870,7 +16870,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G569" t="n">
-        <v>5.29274129867554</v>
+        <v>5.2927417755127</v>
       </c>
       <c r="H569" t="n">
         <v>1000</v>
@@ -16899,7 +16899,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G570" t="n">
-        <v>5.29274129867554</v>
+        <v>5.2927417755127</v>
       </c>
       <c r="H570" t="n">
         <v>0</v>
@@ -16928,7 +16928,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G571" t="n">
-        <v>5.29274129867554</v>
+        <v>5.2927417755127</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G572" t="n">
-        <v>5.29274129867554</v>
+        <v>5.2927417755127</v>
       </c>
       <c r="H572" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G573" t="n">
-        <v>5.29274129867554</v>
+        <v>5.2927417755127</v>
       </c>
       <c r="H573" t="n">
         <v>0</v>
@@ -17044,7 +17044,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G575" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H575" t="n">
         <v>500</v>
@@ -17073,7 +17073,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G576" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H576" t="n">
         <v>0</v>
@@ -17827,7 +17827,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G602" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H602" t="n">
         <v>500</v>
@@ -17914,7 +17914,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G605" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H605" t="n">
         <v>3000</v>
@@ -17943,7 +17943,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H606" t="n">
         <v>0</v>
@@ -17972,7 +17972,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G607" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H607" t="n">
         <v>0</v>
@@ -18407,7 +18407,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G622" t="n">
-        <v>5.53470754623413</v>
+        <v>5.53470706939697</v>
       </c>
       <c r="H622" t="n">
         <v>3500</v>
@@ -18436,7 +18436,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G623" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H623" t="n">
         <v>500</v>
@@ -18523,7 +18523,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G626" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H626" t="n">
         <v>2500</v>
@@ -18552,7 +18552,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G627" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H627" t="n">
         <v>0</v>
@@ -18581,7 +18581,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G628" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H628" t="n">
         <v>5500</v>
@@ -18668,7 +18668,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G631" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H631" t="n">
         <v>1000</v>
@@ -18697,7 +18697,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G632" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H632" t="n">
         <v>500</v>
@@ -18726,7 +18726,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G633" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H633" t="n">
         <v>0</v>
@@ -18755,7 +18755,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G634" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H634" t="n">
         <v>0</v>
@@ -18784,7 +18784,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G635" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H635" t="n">
         <v>0</v>
@@ -18871,7 +18871,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G638" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H638" t="n">
         <v>5500</v>
@@ -19045,7 +19045,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G644" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H644" t="n">
         <v>2000</v>
@@ -19074,7 +19074,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G645" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H645" t="n">
         <v>0</v>
@@ -19103,7 +19103,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H646" t="n">
         <v>0</v>
@@ -19132,7 +19132,7 @@
         <v>5.25</v>
       </c>
       <c r="G647" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H647" t="n">
         <v>10000</v>
@@ -19161,7 +19161,7 @@
         <v>5.25</v>
       </c>
       <c r="G648" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H648" t="n">
         <v>12500</v>
@@ -19248,7 +19248,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G651" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H651" t="n">
         <v>9500</v>
@@ -19364,7 +19364,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H655" t="n">
         <v>1500</v>
@@ -19393,7 +19393,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G656" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H656" t="n">
         <v>0</v>
@@ -19451,7 +19451,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G658" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H658" t="n">
         <v>500</v>
@@ -19654,7 +19654,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G665" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H665" t="n">
         <v>500</v>
@@ -19712,7 +19712,7 @@
         <v>5.25</v>
       </c>
       <c r="G667" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H667" t="n">
         <v>7250</v>
@@ -19770,7 +19770,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G669" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H669" t="n">
         <v>500</v>
@@ -19799,7 +19799,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H670" t="n">
         <v>0</v>
@@ -19828,7 +19828,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H671" t="n">
         <v>0</v>
@@ -19886,7 +19886,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G673" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658491134644</v>
       </c>
       <c r="H673" t="n">
         <v>13250</v>
@@ -19944,7 +19944,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G675" t="n">
-        <v>5.06960582733154</v>
+        <v>5.06960535049438</v>
       </c>
       <c r="H675" t="n">
         <v>5250</v>
@@ -20002,7 +20002,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H677" t="n">
         <v>19750</v>
@@ -20031,7 +20031,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H678" t="n">
         <v>1750</v>
@@ -20060,7 +20060,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G679" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658491134644</v>
       </c>
       <c r="H679" t="n">
         <v>4750</v>
@@ -20089,7 +20089,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G680" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658491134644</v>
       </c>
       <c r="H680" t="n">
         <v>500</v>
@@ -20118,7 +20118,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658491134644</v>
       </c>
       <c r="H681" t="n">
         <v>0</v>
@@ -20147,7 +20147,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G682" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658491134644</v>
       </c>
       <c r="H682" t="n">
         <v>0</v>
@@ -20379,7 +20379,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G690" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H690" t="n">
         <v>3000</v>
@@ -20785,7 +20785,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G704" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403524398804</v>
       </c>
       <c r="H704" t="n">
         <v>41750</v>
@@ -20814,7 +20814,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G705" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403524398804</v>
       </c>
       <c r="H705" t="n">
         <v>7500</v>
@@ -20843,7 +20843,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G706" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403524398804</v>
       </c>
       <c r="H706" t="n">
         <v>2500</v>
@@ -20872,7 +20872,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G707" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403524398804</v>
       </c>
       <c r="H707" t="n">
         <v>7500</v>
@@ -20901,7 +20901,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G708" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403524398804</v>
       </c>
       <c r="H708" t="n">
         <v>2250</v>
@@ -20988,7 +20988,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G711" t="n">
-        <v>4.69752502441406</v>
+        <v>4.6975245475769</v>
       </c>
       <c r="H711" t="n">
         <v>2250</v>
@@ -21017,7 +21017,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G712" t="n">
-        <v>4.69752502441406</v>
+        <v>4.6975245475769</v>
       </c>
       <c r="H712" t="n">
         <v>0</v>
@@ -21046,7 +21046,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G713" t="n">
-        <v>4.69752502441406</v>
+        <v>4.6975245475769</v>
       </c>
       <c r="H713" t="n">
         <v>250</v>
@@ -21336,7 +21336,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G723" t="n">
-        <v>4.01847696304321</v>
+        <v>4.01847648620605</v>
       </c>
       <c r="H723" t="n">
         <v>20000</v>
@@ -21365,7 +21365,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G724" t="n">
-        <v>4.01847696304321</v>
+        <v>4.01847648620605</v>
       </c>
       <c r="H724" t="n">
         <v>6250</v>
@@ -21394,7 +21394,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G725" t="n">
-        <v>4.01847696304321</v>
+        <v>4.01847648620605</v>
       </c>
       <c r="H725" t="n">
         <v>32000</v>
@@ -21423,7 +21423,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G726" t="n">
-        <v>4.05568504333496</v>
+        <v>4.0556845664978</v>
       </c>
       <c r="H726" t="n">
         <v>6000</v>
@@ -21452,7 +21452,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G727" t="n">
-        <v>4.24172496795654</v>
+        <v>4.2417254447937</v>
       </c>
       <c r="H727" t="n">
         <v>1250</v>
@@ -22351,7 +22351,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G758" t="n">
-        <v>4.69752502441406</v>
+        <v>4.6975245475769</v>
       </c>
       <c r="H758" t="n">
         <v>250</v>
@@ -22409,7 +22409,7 @@
         <v>5.25</v>
       </c>
       <c r="G760" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H760" t="n">
         <v>3000</v>
@@ -22438,7 +22438,7 @@
         <v>5.25</v>
       </c>
       <c r="G761" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H761" t="n">
         <v>2000</v>
@@ -22467,7 +22467,7 @@
         <v>5.25</v>
       </c>
       <c r="G762" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H762" t="n">
         <v>500</v>
@@ -22496,7 +22496,7 @@
         <v>5.25</v>
       </c>
       <c r="G763" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H763" t="n">
         <v>250</v>
@@ -22525,7 +22525,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G764" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403524398804</v>
       </c>
       <c r="H764" t="n">
         <v>4000</v>
@@ -22554,7 +22554,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G765" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403524398804</v>
       </c>
       <c r="H765" t="n">
         <v>0</v>
@@ -22583,7 +22583,7 @@
         <v>5.25</v>
       </c>
       <c r="G766" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H766" t="n">
         <v>2750</v>
@@ -22612,7 +22612,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G767" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H767" t="n">
         <v>6000</v>
@@ -22641,7 +22641,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H768" t="n">
         <v>500</v>
@@ -22670,7 +22670,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G769" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H769" t="n">
         <v>0</v>
@@ -22728,7 +22728,7 @@
         <v>5.25</v>
       </c>
       <c r="G771" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H771" t="n">
         <v>7500</v>
@@ -22757,7 +22757,7 @@
         <v>5.25</v>
       </c>
       <c r="G772" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H772" t="n">
         <v>0</v>
@@ -22786,7 +22786,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G773" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H773" t="n">
         <v>3750</v>
@@ -22873,7 +22873,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G776" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658491134644</v>
       </c>
       <c r="H776" t="n">
         <v>2750</v>
@@ -22902,7 +22902,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G777" t="n">
-        <v>5.06960582733154</v>
+        <v>5.06960535049438</v>
       </c>
       <c r="H777" t="n">
         <v>2250</v>
@@ -22931,7 +22931,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G778" t="n">
-        <v>5.06960582733154</v>
+        <v>5.06960535049438</v>
       </c>
       <c r="H778" t="n">
         <v>0</v>
@@ -22989,7 +22989,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G780" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658491134644</v>
       </c>
       <c r="H780" t="n">
         <v>40750</v>
@@ -23018,7 +23018,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G781" t="n">
-        <v>5.06960582733154</v>
+        <v>5.06960535049438</v>
       </c>
       <c r="H781" t="n">
         <v>2750</v>
@@ -23076,7 +23076,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G783" t="n">
-        <v>5.6742377281189</v>
+        <v>5.67423725128174</v>
       </c>
       <c r="H783" t="n">
         <v>6750</v>
@@ -23221,7 +23221,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G788" t="n">
-        <v>5.86027812957764</v>
+        <v>5.86027860641479</v>
       </c>
       <c r="H788" t="n">
         <v>3250</v>
@@ -23250,7 +23250,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G789" t="n">
-        <v>5.86027812957764</v>
+        <v>5.86027860641479</v>
       </c>
       <c r="H789" t="n">
         <v>1500</v>
@@ -23308,7 +23308,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G791" t="n">
-        <v>5.86027812957764</v>
+        <v>5.86027860641479</v>
       </c>
       <c r="H791" t="n">
         <v>4750</v>
@@ -23337,7 +23337,7 @@
         <v>6.25</v>
       </c>
       <c r="G792" t="n">
-        <v>5.81376838684082</v>
+        <v>5.81376791000366</v>
       </c>
       <c r="H792" t="n">
         <v>2000</v>
@@ -23366,7 +23366,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G793" t="n">
-        <v>5.6742377281189</v>
+        <v>5.67423725128174</v>
       </c>
       <c r="H793" t="n">
         <v>1250</v>
@@ -23395,7 +23395,7 @@
         <v>6</v>
       </c>
       <c r="G794" t="n">
-        <v>5.58121776580811</v>
+        <v>5.58121728897095</v>
       </c>
       <c r="H794" t="n">
         <v>500</v>
@@ -23424,7 +23424,7 @@
         <v>6</v>
       </c>
       <c r="G795" t="n">
-        <v>5.58121776580811</v>
+        <v>5.58121728897095</v>
       </c>
       <c r="H795" t="n">
         <v>1250</v>
@@ -23540,7 +23540,7 @@
         <v>6</v>
       </c>
       <c r="G799" t="n">
-        <v>5.58121776580811</v>
+        <v>5.58121728897095</v>
       </c>
       <c r="H799" t="n">
         <v>1750</v>
@@ -23569,7 +23569,7 @@
         <v>6</v>
       </c>
       <c r="G800" t="n">
-        <v>5.58121776580811</v>
+        <v>5.58121728897095</v>
       </c>
       <c r="H800" t="n">
         <v>0</v>
@@ -23598,7 +23598,7 @@
         <v>6</v>
       </c>
       <c r="G801" t="n">
-        <v>5.58121776580811</v>
+        <v>5.58121728897095</v>
       </c>
       <c r="H801" t="n">
         <v>0</v>
@@ -23627,7 +23627,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G802" t="n">
-        <v>5.53470754623413</v>
+        <v>5.53470706939697</v>
       </c>
       <c r="H802" t="n">
         <v>750</v>
@@ -23685,7 +23685,7 @@
         <v>6</v>
       </c>
       <c r="G804" t="n">
-        <v>5.58121776580811</v>
+        <v>5.58121728897095</v>
       </c>
       <c r="H804" t="n">
         <v>1500</v>
@@ -23859,7 +23859,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G810" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H810" t="n">
         <v>1500</v>
@@ -23975,7 +23975,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G814" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H814" t="n">
         <v>3250</v>
@@ -24004,7 +24004,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G815" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H815" t="n">
         <v>0</v>
@@ -24120,7 +24120,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G819" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H819" t="n">
         <v>1000</v>
@@ -24149,7 +24149,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G820" t="n">
-        <v>5.06960582733154</v>
+        <v>5.06960535049438</v>
       </c>
       <c r="H820" t="n">
         <v>1500</v>
@@ -24178,7 +24178,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G821" t="n">
-        <v>5.06960582733154</v>
+        <v>5.06960535049438</v>
       </c>
       <c r="H821" t="n">
         <v>2000</v>
@@ -24207,7 +24207,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G822" t="n">
-        <v>5.06960582733154</v>
+        <v>5.06960535049438</v>
       </c>
       <c r="H822" t="n">
         <v>0</v>
@@ -24236,7 +24236,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G823" t="n">
-        <v>5.06960582733154</v>
+        <v>5.06960535049438</v>
       </c>
       <c r="H823" t="n">
         <v>0</v>
@@ -24265,7 +24265,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G824" t="n">
-        <v>5.06960582733154</v>
+        <v>5.06960535049438</v>
       </c>
       <c r="H824" t="n">
         <v>1250</v>
@@ -24294,7 +24294,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G825" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658491134644</v>
       </c>
       <c r="H825" t="n">
         <v>500</v>
@@ -24323,7 +24323,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G826" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658491134644</v>
       </c>
       <c r="H826" t="n">
         <v>1000</v>
@@ -24352,7 +24352,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G827" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H827" t="n">
         <v>250</v>
@@ -24381,7 +24381,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G828" t="n">
-        <v>5.06960582733154</v>
+        <v>5.06960535049438</v>
       </c>
       <c r="H828" t="n">
         <v>3000</v>
@@ -24410,7 +24410,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G829" t="n">
-        <v>5.06960582733154</v>
+        <v>5.06960535049438</v>
       </c>
       <c r="H829" t="n">
         <v>250</v>
@@ -24439,7 +24439,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G830" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H830" t="n">
         <v>9000</v>
@@ -24497,7 +24497,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G832" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H832" t="n">
         <v>750</v>
@@ -24526,7 +24526,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G833" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H833" t="n">
         <v>500</v>
@@ -24555,7 +24555,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G834" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -24584,7 +24584,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G835" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403524398804</v>
       </c>
       <c r="H835" t="n">
         <v>1000</v>
@@ -24613,7 +24613,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G836" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403524398804</v>
       </c>
       <c r="H836" t="n">
         <v>1000</v>
@@ -24642,7 +24642,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G837" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H837" t="n">
         <v>1500</v>
@@ -24990,7 +24990,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G849" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H849" t="n">
         <v>500</v>
@@ -25019,7 +25019,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G850" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H850" t="n">
         <v>1000</v>
@@ -25048,7 +25048,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G851" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H851" t="n">
         <v>1000</v>
@@ -25077,7 +25077,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G852" t="n">
-        <v>4.69752502441406</v>
+        <v>4.6975245475769</v>
       </c>
       <c r="H852" t="n">
         <v>1000</v>

--- a/data/PLN.MI.xlsx
+++ b/data/PLN.MI.xlsx
@@ -456,7 +456,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G3" t="n">
-        <v>4.11657667160034</v>
+        <v>4.1165771484375</v>
       </c>
       <c r="H3" t="n">
         <v>8500</v>
@@ -514,7 +514,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G5" t="n">
-        <v>4.22684240341187</v>
+        <v>4.22684192657471</v>
       </c>
       <c r="H5" t="n">
         <v>12000</v>
@@ -572,7 +572,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G7" t="n">
-        <v>4.19927597045898</v>
+        <v>4.19927549362183</v>
       </c>
       <c r="H7" t="n">
         <v>11500</v>
@@ -601,7 +601,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G8" t="n">
-        <v>4.1533317565918</v>
+        <v>4.15333223342896</v>
       </c>
       <c r="H8" t="n">
         <v>6500</v>
@@ -717,7 +717,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G12" t="n">
-        <v>3.96955633163452</v>
+        <v>3.9695565700531</v>
       </c>
       <c r="H12" t="n">
         <v>26000</v>
@@ -775,7 +775,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G14" t="n">
-        <v>3.95117855072021</v>
+        <v>3.95117878913879</v>
       </c>
       <c r="H14" t="n">
         <v>19000</v>
@@ -804,7 +804,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G15" t="n">
-        <v>3.89604544639587</v>
+        <v>3.89604520797729</v>
       </c>
       <c r="H15" t="n">
         <v>12500</v>
@@ -862,7 +862,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G17" t="n">
-        <v>3.81334638595581</v>
+        <v>3.81334686279297</v>
       </c>
       <c r="H17" t="n">
         <v>19000</v>
@@ -891,7 +891,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G18" t="n">
-        <v>3.72145867347717</v>
+        <v>3.72145915031433</v>
       </c>
       <c r="H18" t="n">
         <v>43500</v>
@@ -920,7 +920,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G19" t="n">
-        <v>3.95117855072021</v>
+        <v>3.95117878913879</v>
       </c>
       <c r="H19" t="n">
         <v>44000</v>
@@ -949,7 +949,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G20" t="n">
-        <v>3.87766790390015</v>
+        <v>3.87766814231873</v>
       </c>
       <c r="H20" t="n">
         <v>12000</v>
@@ -978,7 +978,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G21" t="n">
-        <v>3.87766790390015</v>
+        <v>3.87766814231873</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G22" t="n">
-        <v>3.87766790390015</v>
+        <v>3.87766814231873</v>
       </c>
       <c r="H22" t="n">
         <v>60000</v>
@@ -1036,7 +1036,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G23" t="n">
-        <v>3.85010170936584</v>
+        <v>3.85010194778442</v>
       </c>
       <c r="H23" t="n">
         <v>32000</v>
@@ -1065,7 +1065,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G24" t="n">
-        <v>3.88685703277588</v>
+        <v>3.88685727119446</v>
       </c>
       <c r="H24" t="n">
         <v>500</v>
@@ -1094,7 +1094,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>3.98793363571167</v>
+        <v>3.98793387413025</v>
       </c>
       <c r="H25" t="n">
         <v>7500</v>
@@ -1268,7 +1268,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G31" t="n">
-        <v>4.1533317565918</v>
+        <v>4.15333223342896</v>
       </c>
       <c r="H31" t="n">
         <v>9000</v>
@@ -1326,7 +1326,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>4.1533317565918</v>
+        <v>4.15333223342896</v>
       </c>
       <c r="H33" t="n">
         <v>2000</v>
@@ -1384,7 +1384,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>4.11657667160034</v>
+        <v>4.1165771484375</v>
       </c>
       <c r="H35" t="n">
         <v>27500</v>
@@ -1413,7 +1413,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G36" t="n">
-        <v>4.06144428253174</v>
+        <v>4.06144380569458</v>
       </c>
       <c r="H36" t="n">
         <v>18500</v>
@@ -1442,7 +1442,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G37" t="n">
-        <v>4.05225467681885</v>
+        <v>4.05225515365601</v>
       </c>
       <c r="H37" t="n">
         <v>2000</v>
@@ -1471,7 +1471,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G38" t="n">
-        <v>4.05225467681885</v>
+        <v>4.05225515365601</v>
       </c>
       <c r="H38" t="n">
         <v>11500</v>
@@ -1500,7 +1500,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G39" t="n">
-        <v>4.09819936752319</v>
+        <v>4.09819889068604</v>
       </c>
       <c r="H39" t="n">
         <v>3500</v>
@@ -1529,7 +1529,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>4.09819936752319</v>
+        <v>4.09819889068604</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>4.08901023864746</v>
+        <v>4.08901071548462</v>
       </c>
       <c r="H43" t="n">
         <v>2000</v>
@@ -1645,7 +1645,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>4.08901023864746</v>
+        <v>4.08901071548462</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G46" t="n">
-        <v>3.95117855072021</v>
+        <v>3.95117878913879</v>
       </c>
       <c r="H46" t="n">
         <v>4000</v>
@@ -1761,7 +1761,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G48" t="n">
-        <v>3.95117855072021</v>
+        <v>3.95117878913879</v>
       </c>
       <c r="H48" t="n">
         <v>2000</v>
@@ -1790,7 +1790,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G49" t="n">
-        <v>3.95117855072021</v>
+        <v>3.95117878913879</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G51" t="n">
-        <v>3.89604544639587</v>
+        <v>3.89604520797729</v>
       </c>
       <c r="H51" t="n">
         <v>31000</v>
@@ -1877,7 +1877,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>3.92361211776733</v>
+        <v>3.92361235618591</v>
       </c>
       <c r="H52" t="n">
         <v>9500</v>
@@ -1906,7 +1906,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G53" t="n">
-        <v>3.89604544639587</v>
+        <v>3.89604520797729</v>
       </c>
       <c r="H53" t="n">
         <v>11000</v>
@@ -1935,7 +1935,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G54" t="n">
-        <v>3.859290599823</v>
+        <v>3.85929012298584</v>
       </c>
       <c r="H54" t="n">
         <v>5000</v>
@@ -1964,7 +1964,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G55" t="n">
-        <v>3.859290599823</v>
+        <v>3.85929012298584</v>
       </c>
       <c r="H55" t="n">
         <v>6000</v>
@@ -2051,7 +2051,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>3.95117855072021</v>
+        <v>3.95117878913879</v>
       </c>
       <c r="H58" t="n">
         <v>3500</v>
@@ -2080,7 +2080,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>3.95117855072021</v>
+        <v>3.95117878913879</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G62" t="n">
-        <v>3.93280076980591</v>
+        <v>3.93280100822449</v>
       </c>
       <c r="H62" t="n">
         <v>40500</v>
@@ -2225,7 +2225,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G64" t="n">
-        <v>4.05225467681885</v>
+        <v>4.05225515365601</v>
       </c>
       <c r="H64" t="n">
         <v>26000</v>
@@ -2283,7 +2283,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G66" t="n">
-        <v>4.16252088546753</v>
+        <v>4.16252040863037</v>
       </c>
       <c r="H66" t="n">
         <v>21000</v>
@@ -2399,7 +2399,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G70" t="n">
-        <v>4.42899513244629</v>
+        <v>4.42899560928345</v>
       </c>
       <c r="H70" t="n">
         <v>64500</v>
@@ -2428,7 +2428,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G71" t="n">
-        <v>4.48412799835205</v>
+        <v>4.48412847518921</v>
       </c>
       <c r="H71" t="n">
         <v>24000</v>
@@ -2515,7 +2515,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G74" t="n">
-        <v>4.8149242401123</v>
+        <v>4.81492471694946</v>
       </c>
       <c r="H74" t="n">
         <v>1500</v>
@@ -2573,7 +2573,7 @@
         <v>5</v>
       </c>
       <c r="G76" t="n">
-        <v>4.59439373016357</v>
+        <v>4.59439325332642</v>
       </c>
       <c r="H76" t="n">
         <v>6000</v>
@@ -2631,7 +2631,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G78" t="n">
-        <v>4.70465898513794</v>
+        <v>4.70465850830078</v>
       </c>
       <c r="H78" t="n">
         <v>1500</v>
@@ -2660,7 +2660,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G79" t="n">
-        <v>4.8149242401123</v>
+        <v>4.81492471694946</v>
       </c>
       <c r="H79" t="n">
         <v>11500</v>
@@ -2689,7 +2689,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G80" t="n">
-        <v>4.90681219100952</v>
+        <v>4.90681266784668</v>
       </c>
       <c r="H80" t="n">
         <v>35500</v>
@@ -2747,7 +2747,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G82" t="n">
-        <v>4.77816915512085</v>
+        <v>4.77816963195801</v>
       </c>
       <c r="H82" t="n">
         <v>3500</v>
@@ -2805,7 +2805,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>5.18247604370117</v>
+        <v>5.18247556686401</v>
       </c>
       <c r="H84" t="n">
         <v>27000</v>
@@ -2834,7 +2834,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G85" t="n">
-        <v>4.96194553375244</v>
+        <v>4.96194505691528</v>
       </c>
       <c r="H85" t="n">
         <v>27000</v>
@@ -2863,7 +2863,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G86" t="n">
-        <v>5.18247604370117</v>
+        <v>5.18247556686401</v>
       </c>
       <c r="H86" t="n">
         <v>18000</v>
@@ -2921,7 +2921,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G88" t="n">
-        <v>5.58678293228149</v>
+        <v>5.58678245544434</v>
       </c>
       <c r="H88" t="n">
         <v>20500</v>
@@ -2979,7 +2979,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>5.93595695495605</v>
+        <v>5.9359564781189</v>
       </c>
       <c r="H90" t="n">
         <v>72500</v>
@@ -3066,7 +3066,7 @@
         <v>7</v>
       </c>
       <c r="G93" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H93" t="n">
         <v>93500</v>
@@ -3211,7 +3211,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G98" t="n">
-        <v>6.2299976348877</v>
+        <v>6.22999811172485</v>
       </c>
       <c r="H98" t="n">
         <v>26000</v>
@@ -3269,7 +3269,7 @@
         <v>6.5</v>
       </c>
       <c r="G100" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="H100" t="n">
         <v>8000</v>
@@ -3327,7 +3327,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G102" t="n">
-        <v>6.10135412216187</v>
+        <v>6.10135507583618</v>
       </c>
       <c r="H102" t="n">
         <v>2000</v>
@@ -3356,7 +3356,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G103" t="n">
-        <v>6.10135412216187</v>
+        <v>6.10135507583618</v>
       </c>
       <c r="H103" t="n">
         <v>2000</v>
@@ -3414,7 +3414,7 @@
         <v>6.5</v>
       </c>
       <c r="G105" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="H105" t="n">
         <v>22000</v>
@@ -3443,7 +3443,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G106" t="n">
-        <v>5.9543342590332</v>
+        <v>5.95433378219604</v>
       </c>
       <c r="H106" t="n">
         <v>11500</v>
@@ -3472,7 +3472,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G107" t="n">
-        <v>5.93595695495605</v>
+        <v>5.9359564781189</v>
       </c>
       <c r="H107" t="n">
         <v>15500</v>
@@ -3501,7 +3501,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>6.0462212562561</v>
+        <v>6.04622173309326</v>
       </c>
       <c r="H108" t="n">
         <v>12500</v>
@@ -3588,7 +3588,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G111" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H111" t="n">
         <v>3500</v>
@@ -3617,7 +3617,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G112" t="n">
-        <v>5.82569169998169</v>
+        <v>5.82569122314453</v>
       </c>
       <c r="H112" t="n">
         <v>3500</v>
@@ -3646,7 +3646,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>5.88082408905029</v>
+        <v>5.88082313537598</v>
       </c>
       <c r="H113" t="n">
         <v>500</v>
@@ -3675,7 +3675,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G114" t="n">
-        <v>5.88082408905029</v>
+        <v>5.88082313537598</v>
       </c>
       <c r="H114" t="n">
         <v>500</v>
@@ -3762,7 +3762,7 @@
         <v>6</v>
       </c>
       <c r="G117" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H117" t="n">
         <v>2500</v>
@@ -3791,7 +3791,7 @@
         <v>6</v>
       </c>
       <c r="G118" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H118" t="n">
         <v>12500</v>
@@ -3820,7 +3820,7 @@
         <v>6</v>
       </c>
       <c r="G119" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H119" t="n">
         <v>500</v>
@@ -3849,7 +3849,7 @@
         <v>6</v>
       </c>
       <c r="G120" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H120" t="n">
         <v>500</v>
@@ -3878,7 +3878,7 @@
         <v>6</v>
       </c>
       <c r="G121" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H121" t="n">
         <v>500</v>
@@ -3936,7 +3936,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G123" t="n">
-        <v>5.23760795593262</v>
+        <v>5.23760843276978</v>
       </c>
       <c r="H123" t="n">
         <v>13000</v>
@@ -4023,7 +4023,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G126" t="n">
-        <v>5.58678293228149</v>
+        <v>5.58678245544434</v>
       </c>
       <c r="H126" t="n">
         <v>1500</v>
@@ -4081,7 +4081,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G128" t="n">
-        <v>5.56840467453003</v>
+        <v>5.56840515136719</v>
       </c>
       <c r="H128" t="n">
         <v>10500</v>
@@ -4110,7 +4110,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G129" t="n">
-        <v>5.43976211547852</v>
+        <v>5.43976259231567</v>
       </c>
       <c r="H129" t="n">
         <v>500</v>
@@ -4168,7 +4168,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G131" t="n">
-        <v>5.43976211547852</v>
+        <v>5.43976259231567</v>
       </c>
       <c r="H131" t="n">
         <v>3500</v>
@@ -4197,7 +4197,7 @@
         <v>6</v>
       </c>
       <c r="G132" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H132" t="n">
         <v>8500</v>
@@ -4226,7 +4226,7 @@
         <v>6</v>
       </c>
       <c r="G133" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H133" t="n">
         <v>1500</v>
@@ -4429,7 +4429,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>5.45813989639282</v>
+        <v>5.45813941955566</v>
       </c>
       <c r="H140" t="n">
         <v>2000</v>
@@ -4458,7 +4458,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G141" t="n">
-        <v>5.45813989639282</v>
+        <v>5.45813941955566</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>5.45813989639282</v>
+        <v>5.45813941955566</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G143" t="n">
-        <v>5.88082408905029</v>
+        <v>5.88082313537598</v>
       </c>
       <c r="H143" t="n">
         <v>5500</v>
@@ -4632,7 +4632,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>5.88082408905029</v>
+        <v>5.88082313537598</v>
       </c>
       <c r="H147" t="n">
         <v>5000</v>
@@ -4661,7 +4661,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G148" t="n">
-        <v>5.88082408905029</v>
+        <v>5.88082313537598</v>
       </c>
       <c r="H148" t="n">
         <v>500</v>
@@ -4690,7 +4690,7 @@
         <v>6.5</v>
       </c>
       <c r="G149" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="H149" t="n">
         <v>2000</v>
@@ -4719,7 +4719,7 @@
         <v>6.5</v>
       </c>
       <c r="G150" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="H150" t="n">
         <v>1500</v>
@@ -4748,7 +4748,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>6.06459951400757</v>
+        <v>6.06459999084473</v>
       </c>
       <c r="H151" t="n">
         <v>5500</v>
@@ -4806,7 +4806,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G153" t="n">
-        <v>6.06459951400757</v>
+        <v>6.06459999084473</v>
       </c>
       <c r="H153" t="n">
         <v>1000</v>
@@ -4864,7 +4864,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G155" t="n">
-        <v>6.2851300239563</v>
+        <v>6.28513050079346</v>
       </c>
       <c r="H155" t="n">
         <v>3500</v>
@@ -4893,7 +4893,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G156" t="n">
-        <v>6.35864114761353</v>
+        <v>6.35864067077637</v>
       </c>
       <c r="H156" t="n">
         <v>13000</v>
@@ -4980,7 +4980,7 @@
         <v>7</v>
       </c>
       <c r="G159" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H159" t="n">
         <v>4000</v>
@@ -5154,7 +5154,7 @@
         <v>7</v>
       </c>
       <c r="G165" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H165" t="n">
         <v>2500</v>
@@ -5212,7 +5212,7 @@
         <v>7</v>
       </c>
       <c r="G167" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H167" t="n">
         <v>2000</v>
@@ -5241,7 +5241,7 @@
         <v>7</v>
       </c>
       <c r="G168" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>7</v>
       </c>
       <c r="G169" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H169" t="n">
         <v>1000</v>
@@ -5299,7 +5299,7 @@
         <v>7</v>
       </c>
       <c r="G170" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H170" t="n">
         <v>1000</v>
@@ -5357,7 +5357,7 @@
         <v>7</v>
       </c>
       <c r="G172" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H172" t="n">
         <v>1500</v>
@@ -5444,7 +5444,7 @@
         <v>7</v>
       </c>
       <c r="G175" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H175" t="n">
         <v>2000</v>
@@ -5502,7 +5502,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G177" t="n">
-        <v>7.27751922607422</v>
+        <v>7.27751970291138</v>
       </c>
       <c r="H177" t="n">
         <v>28000</v>
@@ -5560,7 +5560,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H179" t="n">
         <v>1500</v>
@@ -5589,7 +5589,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5618,7 +5618,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H181" t="n">
         <v>1500</v>
@@ -5647,7 +5647,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G182" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H182" t="n">
         <v>2500</v>
@@ -5676,7 +5676,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G184" t="n">
-        <v>6.94672250747681</v>
+        <v>6.94672298431396</v>
       </c>
       <c r="H184" t="n">
         <v>6000</v>
@@ -5734,7 +5734,7 @@
         <v>7.5</v>
       </c>
       <c r="G185" t="n">
-        <v>6.8915901184082</v>
+        <v>6.89159059524536</v>
       </c>
       <c r="H185" t="n">
         <v>5000</v>
@@ -5763,7 +5763,7 @@
         <v>7.5</v>
       </c>
       <c r="G186" t="n">
-        <v>6.8915901184082</v>
+        <v>6.89159059524536</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G188" t="n">
-        <v>7.24076461791992</v>
+        <v>7.24076414108276</v>
       </c>
       <c r="H188" t="n">
         <v>1000</v>
@@ -5850,7 +5850,7 @@
         <v>8</v>
       </c>
       <c r="G189" t="n">
-        <v>7.35102939605713</v>
+        <v>7.35103034973145</v>
       </c>
       <c r="H189" t="n">
         <v>3500</v>
@@ -5879,7 +5879,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G190" t="n">
-        <v>7.25914239883423</v>
+        <v>7.25914192199707</v>
       </c>
       <c r="H190" t="n">
         <v>5000</v>
@@ -5966,7 +5966,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G193" t="n">
-        <v>7.25914239883423</v>
+        <v>7.25914192199707</v>
       </c>
       <c r="H193" t="n">
         <v>5500</v>
@@ -5995,7 +5995,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G194" t="n">
-        <v>7.25914239883423</v>
+        <v>7.25914192199707</v>
       </c>
       <c r="H194" t="n">
         <v>2000</v>
@@ -6024,7 +6024,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G195" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H195" t="n">
         <v>12000</v>
@@ -6053,7 +6053,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G196" t="n">
-        <v>7.25914239883423</v>
+        <v>7.25914192199707</v>
       </c>
       <c r="H196" t="n">
         <v>10000</v>
@@ -6082,7 +6082,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G197" t="n">
-        <v>7.25914239883423</v>
+        <v>7.25914192199707</v>
       </c>
       <c r="H197" t="n">
         <v>1000</v>
@@ -6111,7 +6111,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G198" t="n">
-        <v>7.25914239883423</v>
+        <v>7.25914192199707</v>
       </c>
       <c r="H198" t="n">
         <v>3000</v>
@@ -6140,7 +6140,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G199" t="n">
-        <v>7.25914239883423</v>
+        <v>7.25914192199707</v>
       </c>
       <c r="H199" t="n">
         <v>15500</v>
@@ -6227,7 +6227,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G202" t="n">
-        <v>7.70020341873169</v>
+        <v>7.70020389556885</v>
       </c>
       <c r="H202" t="n">
         <v>6500</v>
@@ -6256,7 +6256,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G203" t="n">
-        <v>7.70020341873169</v>
+        <v>7.70020389556885</v>
       </c>
       <c r="H203" t="n">
         <v>3000</v>
@@ -6285,7 +6285,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G204" t="n">
-        <v>7.79209089279175</v>
+        <v>7.79209041595459</v>
       </c>
       <c r="H204" t="n">
         <v>6500</v>
@@ -6343,7 +6343,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G206" t="n">
-        <v>8.12288856506348</v>
+        <v>8.12288761138916</v>
       </c>
       <c r="H206" t="n">
         <v>16500</v>
@@ -6488,7 +6488,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G211" t="n">
-        <v>8.15964317321777</v>
+        <v>8.15964221954346</v>
       </c>
       <c r="H211" t="n">
         <v>8000</v>
@@ -6517,7 +6517,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G212" t="n">
-        <v>8.12288856506348</v>
+        <v>8.12288761138916</v>
       </c>
       <c r="H212" t="n">
         <v>500</v>
@@ -6691,7 +6691,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G218" t="n">
-        <v>8.69259357452393</v>
+        <v>8.69259262084961</v>
       </c>
       <c r="H218" t="n">
         <v>3000</v>
@@ -6749,7 +6749,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>8.69259357452393</v>
+        <v>8.69259262084961</v>
       </c>
       <c r="H220" t="n">
         <v>3500</v>
@@ -6778,7 +6778,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>8.69259357452393</v>
+        <v>8.69259262084961</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>9.5</v>
       </c>
       <c r="G227" t="n">
-        <v>8.72934818267822</v>
+        <v>8.72934722900391</v>
       </c>
       <c r="H227" t="n">
         <v>4500</v>
@@ -7213,7 +7213,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G236" t="n">
-        <v>8.14126586914062</v>
+        <v>8.14126491546631</v>
       </c>
       <c r="H236" t="n">
         <v>6500</v>
@@ -7242,7 +7242,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>8.23315334320068</v>
+        <v>8.233154296875</v>
       </c>
       <c r="H237" t="n">
         <v>8500</v>
@@ -7590,7 +7590,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G249" t="n">
-        <v>8.45368480682373</v>
+        <v>8.45368385314941</v>
       </c>
       <c r="H249" t="n">
         <v>1000</v>
@@ -7793,7 +7793,7 @@
         <v>9.5</v>
       </c>
       <c r="G256" t="n">
-        <v>8.72934818267822</v>
+        <v>8.72934722900391</v>
       </c>
       <c r="H256" t="n">
         <v>500</v>
@@ -7822,7 +7822,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G257" t="n">
-        <v>8.87636756896973</v>
+        <v>8.87636852264404</v>
       </c>
       <c r="H257" t="n">
         <v>4000</v>
@@ -7851,7 +7851,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G258" t="n">
-        <v>9.09689807891846</v>
+        <v>9.09689998626709</v>
       </c>
       <c r="H258" t="n">
         <v>1500</v>
@@ -7880,7 +7880,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G259" t="n">
-        <v>9.09689807891846</v>
+        <v>9.09689998626709</v>
       </c>
       <c r="H259" t="n">
         <v>4500</v>
@@ -7909,7 +7909,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G260" t="n">
-        <v>9.09689807891846</v>
+        <v>9.09689998626709</v>
       </c>
       <c r="H260" t="n">
         <v>500</v>
@@ -7996,7 +7996,7 @@
         <v>10</v>
       </c>
       <c r="G263" t="n">
-        <v>9.18878746032715</v>
+        <v>9.18878650665283</v>
       </c>
       <c r="H263" t="n">
         <v>500</v>
@@ -8025,7 +8025,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G264" t="n">
-        <v>8.69259357452393</v>
+        <v>8.69259262084961</v>
       </c>
       <c r="H264" t="n">
         <v>7000</v>
@@ -8054,7 +8054,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>8.69259357452393</v>
+        <v>8.69259262084961</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>9.5</v>
       </c>
       <c r="G266" t="n">
-        <v>8.72934818267822</v>
+        <v>8.72934722900391</v>
       </c>
       <c r="H266" t="n">
         <v>3000</v>
@@ -8112,7 +8112,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G267" t="n">
-        <v>8.69259357452393</v>
+        <v>8.69259262084961</v>
       </c>
       <c r="H267" t="n">
         <v>5500</v>
@@ -8228,7 +8228,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G271" t="n">
-        <v>8.39855194091797</v>
+        <v>8.39855098724365</v>
       </c>
       <c r="H271" t="n">
         <v>5000</v>
@@ -8286,7 +8286,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G273" t="n">
-        <v>7.29589700698853</v>
+        <v>7.29589748382568</v>
       </c>
       <c r="H273" t="n">
         <v>6500</v>
@@ -8402,7 +8402,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G277" t="n">
-        <v>7.40616321563721</v>
+        <v>7.40616273880005</v>
       </c>
       <c r="H277" t="n">
         <v>14000</v>
@@ -8460,7 +8460,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G279" t="n">
-        <v>7.64507055282593</v>
+        <v>7.64507102966309</v>
       </c>
       <c r="H279" t="n">
         <v>1000</v>
@@ -8489,7 +8489,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G280" t="n">
-        <v>7.42454051971436</v>
+        <v>7.4245400428772</v>
       </c>
       <c r="H280" t="n">
         <v>3500</v>
@@ -8518,7 +8518,7 @@
         <v>8</v>
       </c>
       <c r="G281" t="n">
-        <v>7.35102939605713</v>
+        <v>7.35103034973145</v>
       </c>
       <c r="H281" t="n">
         <v>3000</v>
@@ -8547,7 +8547,7 @@
         <v>8</v>
       </c>
       <c r="G282" t="n">
-        <v>7.35102939605713</v>
+        <v>7.35103034973145</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>8</v>
       </c>
       <c r="G283" t="n">
-        <v>7.35102939605713</v>
+        <v>7.35103034973145</v>
       </c>
       <c r="H283" t="n">
         <v>7500</v>
@@ -8605,7 +8605,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G284" t="n">
-        <v>7.25914239883423</v>
+        <v>7.25914192199707</v>
       </c>
       <c r="H284" t="n">
         <v>15000</v>
@@ -8634,7 +8634,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G285" t="n">
-        <v>7.25914239883423</v>
+        <v>7.25914192199707</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G286" t="n">
-        <v>7.25914239883423</v>
+        <v>7.25914192199707</v>
       </c>
       <c r="H286" t="n">
         <v>500</v>
@@ -8692,7 +8692,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G287" t="n">
-        <v>7.27751922607422</v>
+        <v>7.27751970291138</v>
       </c>
       <c r="H287" t="n">
         <v>3500</v>
@@ -8721,7 +8721,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G288" t="n">
-        <v>7.25914239883423</v>
+        <v>7.25914192199707</v>
       </c>
       <c r="H288" t="n">
         <v>500</v>
@@ -8750,7 +8750,7 @@
         <v>8</v>
       </c>
       <c r="G289" t="n">
-        <v>7.35102939605713</v>
+        <v>7.35103034973145</v>
       </c>
       <c r="H289" t="n">
         <v>1500</v>
@@ -8779,7 +8779,7 @@
         <v>8</v>
       </c>
       <c r="G290" t="n">
-        <v>7.35102939605713</v>
+        <v>7.35103034973145</v>
       </c>
       <c r="H290" t="n">
         <v>9000</v>
@@ -8808,7 +8808,7 @@
         <v>8</v>
       </c>
       <c r="G291" t="n">
-        <v>7.35102939605713</v>
+        <v>7.35103034973145</v>
       </c>
       <c r="H291" t="n">
         <v>1500</v>
@@ -8837,7 +8837,7 @@
         <v>8</v>
       </c>
       <c r="G292" t="n">
-        <v>7.35102939605713</v>
+        <v>7.35103034973145</v>
       </c>
       <c r="H292" t="n">
         <v>3000</v>
@@ -8982,7 +8982,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>6.79970216751099</v>
+        <v>6.79970264434814</v>
       </c>
       <c r="H297" t="n">
         <v>3500</v>
@@ -9127,7 +9127,7 @@
         <v>7.5</v>
       </c>
       <c r="G302" t="n">
-        <v>6.8915901184082</v>
+        <v>6.89159059524536</v>
       </c>
       <c r="H302" t="n">
         <v>2000</v>
@@ -9156,7 +9156,7 @@
         <v>7.5</v>
       </c>
       <c r="G303" t="n">
-        <v>6.8915901184082</v>
+        <v>6.89159059524536</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9185,7 +9185,7 @@
         <v>7.5</v>
       </c>
       <c r="G304" t="n">
-        <v>6.8915901184082</v>
+        <v>6.89159059524536</v>
       </c>
       <c r="H304" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>7.5</v>
       </c>
       <c r="G305" t="n">
-        <v>6.8915901184082</v>
+        <v>6.89159059524536</v>
       </c>
       <c r="H305" t="n">
         <v>15500</v>
@@ -9243,7 +9243,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G306" t="n">
-        <v>7.07536602020264</v>
+        <v>7.07536554336548</v>
       </c>
       <c r="H306" t="n">
         <v>1500</v>
@@ -9272,7 +9272,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G307" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H307" t="n">
         <v>500</v>
@@ -9301,7 +9301,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G308" t="n">
-        <v>6.72619247436523</v>
+        <v>6.72619295120239</v>
       </c>
       <c r="H308" t="n">
         <v>5000</v>
@@ -9359,7 +9359,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G310" t="n">
-        <v>7.07536602020264</v>
+        <v>7.07536554336548</v>
       </c>
       <c r="H310" t="n">
         <v>3000</v>
@@ -9388,7 +9388,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G311" t="n">
-        <v>7.55318355560303</v>
+        <v>7.55318307876587</v>
       </c>
       <c r="H311" t="n">
         <v>2000</v>
@@ -9475,7 +9475,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G314" t="n">
-        <v>7.44291734695435</v>
+        <v>7.44291830062866</v>
       </c>
       <c r="H314" t="n">
         <v>2000</v>
@@ -9504,7 +9504,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G315" t="n">
-        <v>7.44291734695435</v>
+        <v>7.44291830062866</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G316" t="n">
-        <v>7.44291734695435</v>
+        <v>7.44291830062866</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>7.44291734695435</v>
+        <v>7.44291830062866</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G318" t="n">
-        <v>7.44291734695435</v>
+        <v>7.44291830062866</v>
       </c>
       <c r="H318" t="n">
         <v>500</v>
@@ -9678,7 +9678,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G321" t="n">
-        <v>7.22238683700562</v>
+        <v>7.22238636016846</v>
       </c>
       <c r="H321" t="n">
         <v>500</v>
@@ -9707,7 +9707,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G322" t="n">
-        <v>7.22238683700562</v>
+        <v>7.22238636016846</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G323" t="n">
-        <v>7.22238683700562</v>
+        <v>7.22238636016846</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G324" t="n">
-        <v>7.22238683700562</v>
+        <v>7.22238636016846</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>6.92834568023682</v>
+        <v>6.92834520339966</v>
       </c>
       <c r="H325" t="n">
         <v>1000</v>
@@ -9823,7 +9823,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G326" t="n">
-        <v>6.92834568023682</v>
+        <v>6.92834520339966</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G329" t="n">
-        <v>6.79970216751099</v>
+        <v>6.79970264434814</v>
       </c>
       <c r="H329" t="n">
         <v>1000</v>
@@ -10055,7 +10055,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G334" t="n">
-        <v>6.94672250747681</v>
+        <v>6.94672298431396</v>
       </c>
       <c r="H334" t="n">
         <v>500</v>
@@ -10084,7 +10084,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>6.94672250747681</v>
+        <v>6.94672298431396</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>6.94672250747681</v>
+        <v>6.94672298431396</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>6.79970216751099</v>
+        <v>6.79970264434814</v>
       </c>
       <c r="H337" t="n">
         <v>500</v>
@@ -10171,7 +10171,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>6.79970216751099</v>
+        <v>6.79970264434814</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10229,7 +10229,7 @@
         <v>6.5</v>
       </c>
       <c r="G340" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="H340" t="n">
         <v>32500</v>
@@ -10403,7 +10403,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G346" t="n">
-        <v>6.0462212562561</v>
+        <v>6.04622173309326</v>
       </c>
       <c r="H346" t="n">
         <v>1000</v>
@@ -10519,7 +10519,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G350" t="n">
-        <v>6.0462212562561</v>
+        <v>6.04622173309326</v>
       </c>
       <c r="H350" t="n">
         <v>1000</v>
@@ -10606,7 +10606,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G353" t="n">
-        <v>5.91757965087891</v>
+        <v>5.91757869720459</v>
       </c>
       <c r="H353" t="n">
         <v>3000</v>
@@ -10635,7 +10635,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G354" t="n">
-        <v>5.91757965087891</v>
+        <v>5.91757869720459</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -10809,7 +10809,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G360" t="n">
-        <v>6.68943786621094</v>
+        <v>6.68943738937378</v>
       </c>
       <c r="H360" t="n">
         <v>2000</v>
@@ -10867,7 +10867,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G362" t="n">
-        <v>6.68943786621094</v>
+        <v>6.68943738937378</v>
       </c>
       <c r="H362" t="n">
         <v>5500</v>
@@ -10896,7 +10896,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G363" t="n">
-        <v>6.68943786621094</v>
+        <v>6.68943738937378</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G365" t="n">
-        <v>6.59754943847656</v>
+        <v>6.5975489616394</v>
       </c>
       <c r="H365" t="n">
         <v>500</v>
@@ -11273,7 +11273,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G376" t="n">
-        <v>6.0462212562561</v>
+        <v>6.04622173309326</v>
       </c>
       <c r="H376" t="n">
         <v>3000</v>
@@ -11302,7 +11302,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>6.0462212562561</v>
+        <v>6.04622173309326</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>6.5</v>
       </c>
       <c r="G378" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="H378" t="n">
         <v>500</v>
@@ -11360,7 +11360,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>6.06459951400757</v>
+        <v>6.06459999084473</v>
       </c>
       <c r="H379" t="n">
         <v>1000</v>
@@ -11389,7 +11389,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>6.06459951400757</v>
+        <v>6.06459999084473</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>6.06459951400757</v>
+        <v>6.06459999084473</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G382" t="n">
-        <v>6.06459951400757</v>
+        <v>6.06459999084473</v>
       </c>
       <c r="H382" t="n">
         <v>500</v>
@@ -11476,7 +11476,7 @@
         <v>6.5</v>
       </c>
       <c r="G383" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="H383" t="n">
         <v>500</v>
@@ -11505,7 +11505,7 @@
         <v>6.5</v>
       </c>
       <c r="G384" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>6.5</v>
       </c>
       <c r="G385" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -11563,7 +11563,7 @@
         <v>6.5</v>
       </c>
       <c r="G386" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -11592,7 +11592,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G387" t="n">
-        <v>5.82569169998169</v>
+        <v>5.82569122314453</v>
       </c>
       <c r="H387" t="n">
         <v>500</v>
@@ -11621,7 +11621,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G388" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H388" t="n">
         <v>1000</v>
@@ -11650,7 +11650,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G389" t="n">
-        <v>5.93595695495605</v>
+        <v>5.9359564781189</v>
       </c>
       <c r="H389" t="n">
         <v>500</v>
@@ -11679,7 +11679,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>5.93595695495605</v>
+        <v>5.9359564781189</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G391" t="n">
-        <v>5.93595695495605</v>
+        <v>5.9359564781189</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -11737,7 +11737,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>5.93595695495605</v>
+        <v>5.9359564781189</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -11766,7 +11766,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G393" t="n">
-        <v>5.93595695495605</v>
+        <v>5.9359564781189</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -11795,7 +11795,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G394" t="n">
-        <v>5.93595695495605</v>
+        <v>5.9359564781189</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -11824,7 +11824,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G395" t="n">
-        <v>5.80731344223022</v>
+        <v>5.80731391906738</v>
       </c>
       <c r="H395" t="n">
         <v>1500</v>
@@ -11853,7 +11853,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G396" t="n">
-        <v>5.80731344223022</v>
+        <v>5.80731391906738</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G397" t="n">
-        <v>5.80731344223022</v>
+        <v>5.80731391906738</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -11911,7 +11911,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G398" t="n">
-        <v>5.91757965087891</v>
+        <v>5.91757869720459</v>
       </c>
       <c r="H398" t="n">
         <v>500</v>
@@ -11940,7 +11940,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G399" t="n">
-        <v>5.91757965087891</v>
+        <v>5.91757869720459</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -11969,7 +11969,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G400" t="n">
-        <v>6.10135412216187</v>
+        <v>6.10135507583618</v>
       </c>
       <c r="H400" t="n">
         <v>500</v>
@@ -12230,7 +12230,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G409" t="n">
-        <v>6.2851300239563</v>
+        <v>6.28513050079346</v>
       </c>
       <c r="H409" t="n">
         <v>1000</v>
@@ -12259,7 +12259,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G410" t="n">
-        <v>6.2851300239563</v>
+        <v>6.28513050079346</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -12288,7 +12288,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G411" t="n">
-        <v>6.2851300239563</v>
+        <v>6.28513050079346</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -12317,7 +12317,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G412" t="n">
-        <v>6.2851300239563</v>
+        <v>6.28513050079346</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>7</v>
       </c>
       <c r="G415" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H415" t="n">
         <v>1500</v>
@@ -12433,7 +12433,7 @@
         <v>7</v>
       </c>
       <c r="G416" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H416" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>7</v>
       </c>
       <c r="G417" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12491,7 +12491,7 @@
         <v>7</v>
       </c>
       <c r="G418" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>7</v>
       </c>
       <c r="G419" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>7</v>
       </c>
       <c r="G420" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>7</v>
       </c>
       <c r="G421" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H421" t="n">
         <v>500</v>
@@ -13071,7 +13071,7 @@
         <v>7</v>
       </c>
       <c r="G438" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215131759644</v>
       </c>
       <c r="H438" t="n">
         <v>3000</v>
@@ -13274,7 +13274,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G445" t="n">
-        <v>6.2299976348877</v>
+        <v>6.22999811172485</v>
       </c>
       <c r="H445" t="n">
         <v>500</v>
@@ -13303,7 +13303,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G446" t="n">
-        <v>6.2299976348877</v>
+        <v>6.22999811172485</v>
       </c>
       <c r="H446" t="n">
         <v>500</v>
@@ -13332,7 +13332,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G447" t="n">
-        <v>6.2299976348877</v>
+        <v>6.22999811172485</v>
       </c>
       <c r="H447" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G449" t="n">
-        <v>5.75218105316162</v>
+        <v>5.75218057632446</v>
       </c>
       <c r="H449" t="n">
         <v>3000</v>
@@ -13419,7 +13419,7 @@
         <v>6.5</v>
       </c>
       <c r="G450" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="H450" t="n">
         <v>500</v>
@@ -13448,7 +13448,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G451" t="n">
-        <v>6.00946664810181</v>
+        <v>6.00946712493896</v>
       </c>
       <c r="H451" t="n">
         <v>500</v>
@@ -13477,7 +13477,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G452" t="n">
-        <v>5.88082408905029</v>
+        <v>5.88082313537598</v>
       </c>
       <c r="H452" t="n">
         <v>1000</v>
@@ -13506,7 +13506,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G453" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893566131592</v>
       </c>
       <c r="H453" t="n">
         <v>500</v>
@@ -13535,7 +13535,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G454" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893566131592</v>
       </c>
       <c r="H454" t="n">
         <v>0</v>
@@ -13564,7 +13564,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G455" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893566131592</v>
       </c>
       <c r="H455" t="n">
         <v>0</v>
@@ -13593,7 +13593,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G456" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893566131592</v>
       </c>
       <c r="H456" t="n">
         <v>0</v>
@@ -13622,7 +13622,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G457" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893566131592</v>
       </c>
       <c r="H457" t="n">
         <v>0</v>
@@ -13651,7 +13651,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G458" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893566131592</v>
       </c>
       <c r="H458" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G459" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893566131592</v>
       </c>
       <c r="H459" t="n">
         <v>0</v>
@@ -13709,7 +13709,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G460" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893566131592</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G461" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893566131592</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13767,7 +13767,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G462" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893566131592</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G463" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893566131592</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -13825,7 +13825,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G464" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893566131592</v>
       </c>
       <c r="H464" t="n">
         <v>1000</v>
@@ -13854,7 +13854,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G465" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893566131592</v>
       </c>
       <c r="H465" t="n">
         <v>0</v>
@@ -13883,7 +13883,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G466" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893566131592</v>
       </c>
       <c r="H466" t="n">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G467" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893566131592</v>
       </c>
       <c r="H467" t="n">
         <v>0</v>
@@ -13999,7 +13999,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G470" t="n">
-        <v>5.58678293228149</v>
+        <v>5.58678245544434</v>
       </c>
       <c r="H470" t="n">
         <v>500</v>
@@ -14028,7 +14028,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>5.58678293228149</v>
+        <v>5.58678245544434</v>
       </c>
       <c r="H471" t="n">
         <v>0</v>
@@ -14057,7 +14057,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G472" t="n">
-        <v>5.58678293228149</v>
+        <v>5.58678245544434</v>
       </c>
       <c r="H472" t="n">
         <v>0</v>
@@ -14086,7 +14086,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G473" t="n">
-        <v>5.58678293228149</v>
+        <v>5.58678245544434</v>
       </c>
       <c r="H473" t="n">
         <v>0</v>
@@ -14144,7 +14144,7 @@
         <v>6</v>
       </c>
       <c r="G475" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H475" t="n">
         <v>500</v>
@@ -14173,7 +14173,7 @@
         <v>6</v>
       </c>
       <c r="G476" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H476" t="n">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>6</v>
       </c>
       <c r="G477" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H477" t="n">
         <v>0</v>
@@ -14231,7 +14231,7 @@
         <v>6</v>
       </c>
       <c r="G478" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H478" t="n">
         <v>0</v>
@@ -14289,7 +14289,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G480" t="n">
-        <v>5.45813989639282</v>
+        <v>5.45813941955566</v>
       </c>
       <c r="H480" t="n">
         <v>1500</v>
@@ -14318,7 +14318,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G481" t="n">
-        <v>5.56840467453003</v>
+        <v>5.56840515136719</v>
       </c>
       <c r="H481" t="n">
         <v>1500</v>
@@ -14434,7 +14434,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G485" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893566131592</v>
       </c>
       <c r="H485" t="n">
         <v>1500</v>
@@ -14463,7 +14463,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G486" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893566131592</v>
       </c>
       <c r="H486" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G487" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893566131592</v>
       </c>
       <c r="H487" t="n">
         <v>0</v>
@@ -14521,7 +14521,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G488" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893566131592</v>
       </c>
       <c r="H488" t="n">
         <v>1000</v>
@@ -14550,7 +14550,7 @@
         <v>6</v>
       </c>
       <c r="G489" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H489" t="n">
         <v>1500</v>
@@ -14579,7 +14579,7 @@
         <v>6</v>
       </c>
       <c r="G490" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H490" t="n">
         <v>3500</v>
@@ -14608,7 +14608,7 @@
         <v>6</v>
       </c>
       <c r="G491" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H491" t="n">
         <v>0</v>
@@ -14637,7 +14637,7 @@
         <v>6</v>
       </c>
       <c r="G492" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H492" t="n">
         <v>0</v>
@@ -14666,7 +14666,7 @@
         <v>6</v>
       </c>
       <c r="G493" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H493" t="n">
         <v>500</v>
@@ -14695,7 +14695,7 @@
         <v>6</v>
       </c>
       <c r="G494" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H494" t="n">
         <v>0</v>
@@ -14811,7 +14811,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G498" t="n">
-        <v>5.58678293228149</v>
+        <v>5.58678245544434</v>
       </c>
       <c r="H498" t="n">
         <v>500</v>
@@ -14840,7 +14840,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G499" t="n">
-        <v>5.58678293228149</v>
+        <v>5.58678245544434</v>
       </c>
       <c r="H499" t="n">
         <v>0</v>
@@ -14869,7 +14869,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G500" t="n">
-        <v>5.58678293228149</v>
+        <v>5.58678245544434</v>
       </c>
       <c r="H500" t="n">
         <v>1000</v>
@@ -15014,7 +15014,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>5.36625194549561</v>
+        <v>5.36625146865845</v>
       </c>
       <c r="H505" t="n">
         <v>1000</v>
@@ -15159,7 +15159,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G510" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893566131592</v>
       </c>
       <c r="H510" t="n">
         <v>1500</v>
@@ -15188,7 +15188,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G511" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893566131592</v>
       </c>
       <c r="H511" t="n">
         <v>0</v>
@@ -15217,7 +15217,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G512" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893566131592</v>
       </c>
       <c r="H512" t="n">
         <v>0</v>
@@ -15246,7 +15246,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G513" t="n">
-        <v>5.78893613815308</v>
+        <v>5.78893566131592</v>
       </c>
       <c r="H513" t="n">
         <v>0</v>
@@ -15478,7 +15478,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G521" t="n">
-        <v>5.45813989639282</v>
+        <v>5.45813941955566</v>
       </c>
       <c r="H521" t="n">
         <v>1000</v>
@@ -15594,7 +15594,7 @@
         <v>6</v>
       </c>
       <c r="G525" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H525" t="n">
         <v>500</v>
@@ -15623,7 +15623,7 @@
         <v>6</v>
       </c>
       <c r="G526" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H526" t="n">
         <v>0</v>
@@ -15652,7 +15652,7 @@
         <v>6</v>
       </c>
       <c r="G527" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H527" t="n">
         <v>26000</v>
@@ -15681,7 +15681,7 @@
         <v>6</v>
       </c>
       <c r="G528" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H528" t="n">
         <v>0</v>
@@ -15710,7 +15710,7 @@
         <v>6</v>
       </c>
       <c r="G529" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H529" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>6</v>
       </c>
       <c r="G530" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H530" t="n">
         <v>0</v>
@@ -15884,7 +15884,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H535" t="n">
         <v>500</v>
@@ -15913,7 +15913,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G536" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H536" t="n">
         <v>0</v>
@@ -15971,7 +15971,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G538" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H538" t="n">
         <v>1000</v>
@@ -16000,7 +16000,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G539" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H539" t="n">
         <v>0</v>
@@ -16029,7 +16029,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G540" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H540" t="n">
         <v>0</v>
@@ -16058,7 +16058,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G541" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -16116,7 +16116,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G543" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H543" t="n">
         <v>0</v>
@@ -16145,7 +16145,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G544" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H544" t="n">
         <v>0</v>
@@ -16174,7 +16174,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G545" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H546" t="n">
         <v>0</v>
@@ -16232,7 +16232,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G547" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G548" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H548" t="n">
         <v>1500</v>
@@ -16290,7 +16290,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G549" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H549" t="n">
         <v>0</v>
@@ -16319,7 +16319,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G550" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -16348,7 +16348,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G551" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H551" t="n">
         <v>0</v>
@@ -16377,7 +16377,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G552" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H552" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G553" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G563" t="n">
-        <v>5.45813989639282</v>
+        <v>5.45813941955566</v>
       </c>
       <c r="H563" t="n">
         <v>500</v>
@@ -16841,7 +16841,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G568" t="n">
-        <v>5.43976211547852</v>
+        <v>5.43976259231567</v>
       </c>
       <c r="H568" t="n">
         <v>500</v>
@@ -16870,7 +16870,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G569" t="n">
-        <v>5.2927417755127</v>
+        <v>5.29274129867554</v>
       </c>
       <c r="H569" t="n">
         <v>1000</v>
@@ -16899,7 +16899,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G570" t="n">
-        <v>5.2927417755127</v>
+        <v>5.29274129867554</v>
       </c>
       <c r="H570" t="n">
         <v>0</v>
@@ -16928,7 +16928,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G571" t="n">
-        <v>5.2927417755127</v>
+        <v>5.29274129867554</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G572" t="n">
-        <v>5.2927417755127</v>
+        <v>5.29274129867554</v>
       </c>
       <c r="H572" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G573" t="n">
-        <v>5.2927417755127</v>
+        <v>5.29274129867554</v>
       </c>
       <c r="H573" t="n">
         <v>0</v>
@@ -17044,7 +17044,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G575" t="n">
-        <v>5.45813989639282</v>
+        <v>5.45813941955566</v>
       </c>
       <c r="H575" t="n">
         <v>500</v>
@@ -17073,7 +17073,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G576" t="n">
-        <v>5.45813989639282</v>
+        <v>5.45813941955566</v>
       </c>
       <c r="H576" t="n">
         <v>0</v>
@@ -17102,7 +17102,7 @@
         <v>6</v>
       </c>
       <c r="G577" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H577" t="n">
         <v>13500</v>
@@ -17131,7 +17131,7 @@
         <v>6</v>
       </c>
       <c r="G578" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H578" t="n">
         <v>0</v>
@@ -17160,7 +17160,7 @@
         <v>6</v>
       </c>
       <c r="G579" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H579" t="n">
         <v>0</v>
@@ -17247,7 +17247,7 @@
         <v>6</v>
       </c>
       <c r="G582" t="n">
-        <v>5.51327228546143</v>
+        <v>5.51327276229858</v>
       </c>
       <c r="H582" t="n">
         <v>500</v>
@@ -17827,7 +17827,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G602" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H602" t="n">
         <v>500</v>
@@ -17914,7 +17914,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G605" t="n">
-        <v>5.48819732666016</v>
+        <v>5.488196849823</v>
       </c>
       <c r="H605" t="n">
         <v>3000</v>
@@ -17943,7 +17943,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>5.48819732666016</v>
+        <v>5.488196849823</v>
       </c>
       <c r="H606" t="n">
         <v>0</v>
@@ -17972,7 +17972,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G607" t="n">
-        <v>5.48819732666016</v>
+        <v>5.488196849823</v>
       </c>
       <c r="H607" t="n">
         <v>0</v>
@@ -18407,7 +18407,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G622" t="n">
-        <v>5.53470706939697</v>
+        <v>5.53470754623413</v>
       </c>
       <c r="H622" t="n">
         <v>3500</v>
@@ -18436,7 +18436,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G623" t="n">
-        <v>5.48819732666016</v>
+        <v>5.488196849823</v>
       </c>
       <c r="H623" t="n">
         <v>500</v>
@@ -18523,7 +18523,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G626" t="n">
-        <v>5.48819732666016</v>
+        <v>5.488196849823</v>
       </c>
       <c r="H626" t="n">
         <v>2500</v>
@@ -18552,7 +18552,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G627" t="n">
-        <v>5.48819732666016</v>
+        <v>5.488196849823</v>
       </c>
       <c r="H627" t="n">
         <v>0</v>
@@ -18581,7 +18581,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G628" t="n">
-        <v>5.48819732666016</v>
+        <v>5.488196849823</v>
       </c>
       <c r="H628" t="n">
         <v>5500</v>
@@ -18668,7 +18668,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G631" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H631" t="n">
         <v>1000</v>
@@ -18697,7 +18697,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G632" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H632" t="n">
         <v>500</v>
@@ -18726,7 +18726,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G633" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H633" t="n">
         <v>0</v>
@@ -18755,7 +18755,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G634" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H634" t="n">
         <v>0</v>
@@ -18784,7 +18784,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G635" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H635" t="n">
         <v>0</v>
@@ -18871,7 +18871,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G638" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H638" t="n">
         <v>5500</v>
@@ -19045,7 +19045,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G644" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H644" t="n">
         <v>2000</v>
@@ -19074,7 +19074,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G645" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H645" t="n">
         <v>0</v>
@@ -19103,7 +19103,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H646" t="n">
         <v>0</v>
@@ -19132,7 +19132,7 @@
         <v>5.25</v>
       </c>
       <c r="G647" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H647" t="n">
         <v>10000</v>
@@ -19161,7 +19161,7 @@
         <v>5.25</v>
       </c>
       <c r="G648" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H648" t="n">
         <v>12500</v>
@@ -19248,7 +19248,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G651" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H651" t="n">
         <v>9500</v>
@@ -19364,7 +19364,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H655" t="n">
         <v>1500</v>
@@ -19393,7 +19393,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G656" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H656" t="n">
         <v>0</v>
@@ -19451,7 +19451,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G658" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H658" t="n">
         <v>500</v>
@@ -19654,7 +19654,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G665" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H665" t="n">
         <v>500</v>
@@ -19712,7 +19712,7 @@
         <v>5.25</v>
       </c>
       <c r="G667" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H667" t="n">
         <v>7250</v>
@@ -19770,7 +19770,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G669" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H669" t="n">
         <v>500</v>
@@ -19799,7 +19799,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H670" t="n">
         <v>0</v>
@@ -19828,7 +19828,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H671" t="n">
         <v>0</v>
@@ -19886,7 +19886,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G673" t="n">
-        <v>4.97658491134644</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H673" t="n">
         <v>13250</v>
@@ -19944,7 +19944,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G675" t="n">
-        <v>5.06960535049438</v>
+        <v>5.06960582733154</v>
       </c>
       <c r="H675" t="n">
         <v>5250</v>
@@ -20002,7 +20002,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H677" t="n">
         <v>19750</v>
@@ -20031,7 +20031,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H678" t="n">
         <v>1750</v>
@@ -20060,7 +20060,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G679" t="n">
-        <v>4.97658491134644</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H679" t="n">
         <v>4750</v>
@@ -20089,7 +20089,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G680" t="n">
-        <v>4.97658491134644</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H680" t="n">
         <v>500</v>
@@ -20118,7 +20118,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>4.97658491134644</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H681" t="n">
         <v>0</v>
@@ -20147,7 +20147,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G682" t="n">
-        <v>4.97658491134644</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H682" t="n">
         <v>0</v>
@@ -20379,7 +20379,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G690" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H690" t="n">
         <v>3000</v>
@@ -20785,7 +20785,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G704" t="n">
-        <v>4.74403524398804</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H704" t="n">
         <v>41750</v>
@@ -20814,7 +20814,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G705" t="n">
-        <v>4.74403524398804</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H705" t="n">
         <v>7500</v>
@@ -20843,7 +20843,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G706" t="n">
-        <v>4.74403524398804</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H706" t="n">
         <v>2500</v>
@@ -20872,7 +20872,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G707" t="n">
-        <v>4.74403524398804</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H707" t="n">
         <v>7500</v>
@@ -20901,7 +20901,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G708" t="n">
-        <v>4.74403524398804</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H708" t="n">
         <v>2250</v>
@@ -20988,7 +20988,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G711" t="n">
-        <v>4.6975245475769</v>
+        <v>4.69752502441406</v>
       </c>
       <c r="H711" t="n">
         <v>2250</v>
@@ -21017,7 +21017,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G712" t="n">
-        <v>4.6975245475769</v>
+        <v>4.69752502441406</v>
       </c>
       <c r="H712" t="n">
         <v>0</v>
@@ -21046,7 +21046,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G713" t="n">
-        <v>4.6975245475769</v>
+        <v>4.69752502441406</v>
       </c>
       <c r="H713" t="n">
         <v>250</v>
@@ -21336,7 +21336,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G723" t="n">
-        <v>4.01847648620605</v>
+        <v>4.01847696304321</v>
       </c>
       <c r="H723" t="n">
         <v>20000</v>
@@ -21365,7 +21365,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G724" t="n">
-        <v>4.01847648620605</v>
+        <v>4.01847696304321</v>
       </c>
       <c r="H724" t="n">
         <v>6250</v>
@@ -21394,7 +21394,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G725" t="n">
-        <v>4.01847648620605</v>
+        <v>4.01847696304321</v>
       </c>
       <c r="H725" t="n">
         <v>32000</v>
@@ -21423,7 +21423,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G726" t="n">
-        <v>4.0556845664978</v>
+        <v>4.05568504333496</v>
       </c>
       <c r="H726" t="n">
         <v>6000</v>
@@ -21452,7 +21452,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G727" t="n">
-        <v>4.2417254447937</v>
+        <v>4.24172496795654</v>
       </c>
       <c r="H727" t="n">
         <v>1250</v>
@@ -22351,7 +22351,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G758" t="n">
-        <v>4.6975245475769</v>
+        <v>4.69752502441406</v>
       </c>
       <c r="H758" t="n">
         <v>250</v>
@@ -22409,7 +22409,7 @@
         <v>5.25</v>
       </c>
       <c r="G760" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H760" t="n">
         <v>3000</v>
@@ -22438,7 +22438,7 @@
         <v>5.25</v>
       </c>
       <c r="G761" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H761" t="n">
         <v>2000</v>
@@ -22467,7 +22467,7 @@
         <v>5.25</v>
       </c>
       <c r="G762" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H762" t="n">
         <v>500</v>
@@ -22496,7 +22496,7 @@
         <v>5.25</v>
       </c>
       <c r="G763" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H763" t="n">
         <v>250</v>
@@ -22525,7 +22525,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G764" t="n">
-        <v>4.74403524398804</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H764" t="n">
         <v>4000</v>
@@ -22554,7 +22554,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G765" t="n">
-        <v>4.74403524398804</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H765" t="n">
         <v>0</v>
@@ -22583,7 +22583,7 @@
         <v>5.25</v>
       </c>
       <c r="G766" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H766" t="n">
         <v>2750</v>
@@ -22612,7 +22612,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G767" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H767" t="n">
         <v>6000</v>
@@ -22641,7 +22641,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H768" t="n">
         <v>500</v>
@@ -22670,7 +22670,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G769" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H769" t="n">
         <v>0</v>
@@ -22728,7 +22728,7 @@
         <v>5.25</v>
       </c>
       <c r="G771" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H771" t="n">
         <v>7500</v>
@@ -22757,7 +22757,7 @@
         <v>5.25</v>
       </c>
       <c r="G772" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H772" t="n">
         <v>0</v>
@@ -22786,7 +22786,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G773" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H773" t="n">
         <v>3750</v>
@@ -22873,7 +22873,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G776" t="n">
-        <v>4.97658491134644</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H776" t="n">
         <v>2750</v>
@@ -22902,7 +22902,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G777" t="n">
-        <v>5.06960535049438</v>
+        <v>5.06960582733154</v>
       </c>
       <c r="H777" t="n">
         <v>2250</v>
@@ -22931,7 +22931,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G778" t="n">
-        <v>5.06960535049438</v>
+        <v>5.06960582733154</v>
       </c>
       <c r="H778" t="n">
         <v>0</v>
@@ -22989,7 +22989,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G780" t="n">
-        <v>4.97658491134644</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H780" t="n">
         <v>40750</v>
@@ -23018,7 +23018,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G781" t="n">
-        <v>5.06960535049438</v>
+        <v>5.06960582733154</v>
       </c>
       <c r="H781" t="n">
         <v>2750</v>
@@ -23076,7 +23076,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G783" t="n">
-        <v>5.67423725128174</v>
+        <v>5.6742377281189</v>
       </c>
       <c r="H783" t="n">
         <v>6750</v>
@@ -23221,7 +23221,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G788" t="n">
-        <v>5.86027860641479</v>
+        <v>5.86027812957764</v>
       </c>
       <c r="H788" t="n">
         <v>3250</v>
@@ -23250,7 +23250,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G789" t="n">
-        <v>5.86027860641479</v>
+        <v>5.86027812957764</v>
       </c>
       <c r="H789" t="n">
         <v>1500</v>
@@ -23308,7 +23308,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G791" t="n">
-        <v>5.86027860641479</v>
+        <v>5.86027812957764</v>
       </c>
       <c r="H791" t="n">
         <v>4750</v>
@@ -23337,7 +23337,7 @@
         <v>6.25</v>
       </c>
       <c r="G792" t="n">
-        <v>5.81376791000366</v>
+        <v>5.81376838684082</v>
       </c>
       <c r="H792" t="n">
         <v>2000</v>
@@ -23366,7 +23366,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G793" t="n">
-        <v>5.67423725128174</v>
+        <v>5.6742377281189</v>
       </c>
       <c r="H793" t="n">
         <v>1250</v>
@@ -23395,7 +23395,7 @@
         <v>6</v>
       </c>
       <c r="G794" t="n">
-        <v>5.58121728897095</v>
+        <v>5.58121776580811</v>
       </c>
       <c r="H794" t="n">
         <v>500</v>
@@ -23424,7 +23424,7 @@
         <v>6</v>
       </c>
       <c r="G795" t="n">
-        <v>5.58121728897095</v>
+        <v>5.58121776580811</v>
       </c>
       <c r="H795" t="n">
         <v>1250</v>
@@ -23540,7 +23540,7 @@
         <v>6</v>
       </c>
       <c r="G799" t="n">
-        <v>5.58121728897095</v>
+        <v>5.58121776580811</v>
       </c>
       <c r="H799" t="n">
         <v>1750</v>
@@ -23569,7 +23569,7 @@
         <v>6</v>
       </c>
       <c r="G800" t="n">
-        <v>5.58121728897095</v>
+        <v>5.58121776580811</v>
       </c>
       <c r="H800" t="n">
         <v>0</v>
@@ -23598,7 +23598,7 @@
         <v>6</v>
       </c>
       <c r="G801" t="n">
-        <v>5.58121728897095</v>
+        <v>5.58121776580811</v>
       </c>
       <c r="H801" t="n">
         <v>0</v>
@@ -23627,7 +23627,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G802" t="n">
-        <v>5.53470706939697</v>
+        <v>5.53470754623413</v>
       </c>
       <c r="H802" t="n">
         <v>750</v>
@@ -23685,7 +23685,7 @@
         <v>6</v>
       </c>
       <c r="G804" t="n">
-        <v>5.58121728897095</v>
+        <v>5.58121776580811</v>
       </c>
       <c r="H804" t="n">
         <v>1500</v>
@@ -23859,7 +23859,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G810" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H810" t="n">
         <v>1500</v>
@@ -23975,7 +23975,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G814" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H814" t="n">
         <v>3250</v>
@@ -24004,7 +24004,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G815" t="n">
-        <v>5.20913600921631</v>
+        <v>5.20913648605347</v>
       </c>
       <c r="H815" t="n">
         <v>0</v>
@@ -24120,7 +24120,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G819" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H819" t="n">
         <v>1000</v>
@@ -24149,7 +24149,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G820" t="n">
-        <v>5.06960535049438</v>
+        <v>5.06960582733154</v>
       </c>
       <c r="H820" t="n">
         <v>1500</v>
@@ -24178,7 +24178,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G821" t="n">
-        <v>5.06960535049438</v>
+        <v>5.06960582733154</v>
       </c>
       <c r="H821" t="n">
         <v>2000</v>
@@ -24207,7 +24207,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G822" t="n">
-        <v>5.06960535049438</v>
+        <v>5.06960582733154</v>
       </c>
       <c r="H822" t="n">
         <v>0</v>
@@ -24236,7 +24236,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G823" t="n">
-        <v>5.06960535049438</v>
+        <v>5.06960582733154</v>
       </c>
       <c r="H823" t="n">
         <v>0</v>
@@ -24265,7 +24265,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G824" t="n">
-        <v>5.06960535049438</v>
+        <v>5.06960582733154</v>
       </c>
       <c r="H824" t="n">
         <v>1250</v>
@@ -24294,7 +24294,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G825" t="n">
-        <v>4.97658491134644</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H825" t="n">
         <v>500</v>
@@ -24323,7 +24323,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G826" t="n">
-        <v>4.97658491134644</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H826" t="n">
         <v>1000</v>
@@ -24352,7 +24352,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G827" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H827" t="n">
         <v>250</v>
@@ -24381,7 +24381,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G828" t="n">
-        <v>5.06960535049438</v>
+        <v>5.06960582733154</v>
       </c>
       <c r="H828" t="n">
         <v>3000</v>
@@ -24410,7 +24410,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G829" t="n">
-        <v>5.06960535049438</v>
+        <v>5.06960582733154</v>
       </c>
       <c r="H829" t="n">
         <v>250</v>
@@ -24439,7 +24439,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G830" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H830" t="n">
         <v>9000</v>
@@ -24497,7 +24497,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G832" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H832" t="n">
         <v>750</v>
@@ -24526,7 +24526,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G833" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H833" t="n">
         <v>500</v>
@@ -24555,7 +24555,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G834" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -24584,7 +24584,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G835" t="n">
-        <v>4.74403524398804</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H835" t="n">
         <v>1000</v>
@@ -24613,7 +24613,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G836" t="n">
-        <v>4.74403524398804</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H836" t="n">
         <v>1000</v>
@@ -24642,7 +24642,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G837" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H837" t="n">
         <v>1500</v>
@@ -24990,7 +24990,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G849" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H849" t="n">
         <v>500</v>
@@ -25019,7 +25019,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G850" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H850" t="n">
         <v>1000</v>
@@ -25048,7 +25048,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G851" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H851" t="n">
         <v>1000</v>
@@ -25077,7 +25077,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G852" t="n">
-        <v>4.6975245475769</v>
+        <v>4.69752502441406</v>
       </c>
       <c r="H852" t="n">
         <v>1000</v>
@@ -43237,6 +43237,35 @@
         <v>11000</v>
       </c>
       <c r="I1478" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1479" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1479" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="D1479" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="E1479" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="F1479" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="G1479" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="H1479" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1479" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PLN.MI.xlsx
+++ b/data/PLN.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.41200017929077</v>
       </c>
       <c r="G2" t="n">
-        <v>4.05409288406372</v>
+        <v>4.05409336090088</v>
       </c>
       <c r="H2" t="n">
         <v>42000</v>
@@ -688,7 +688,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G11" t="n">
-        <v>4.0338773727417</v>
+        <v>4.03387689590454</v>
       </c>
       <c r="H11" t="n">
         <v>12000</v>
@@ -717,7 +717,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G12" t="n">
-        <v>3.9695565700531</v>
+        <v>3.96955585479736</v>
       </c>
       <c r="H12" t="n">
         <v>26000</v>
@@ -804,7 +804,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G15" t="n">
-        <v>3.89604520797729</v>
+        <v>3.89604544639587</v>
       </c>
       <c r="H15" t="n">
         <v>12500</v>
@@ -891,7 +891,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G18" t="n">
-        <v>3.72145915031433</v>
+        <v>3.72145891189575</v>
       </c>
       <c r="H18" t="n">
         <v>43500</v>
@@ -949,7 +949,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G20" t="n">
-        <v>3.87766814231873</v>
+        <v>3.87766790390015</v>
       </c>
       <c r="H20" t="n">
         <v>12000</v>
@@ -978,7 +978,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G21" t="n">
-        <v>3.87766814231873</v>
+        <v>3.87766790390015</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G22" t="n">
-        <v>3.87766814231873</v>
+        <v>3.87766790390015</v>
       </c>
       <c r="H22" t="n">
         <v>60000</v>
@@ -1152,7 +1152,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>4.1717095375061</v>
+        <v>4.17170906066895</v>
       </c>
       <c r="H27" t="n">
         <v>10500</v>
@@ -1181,7 +1181,7 @@
         <v>4.5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.13495445251465</v>
+        <v>4.13495397567749</v>
       </c>
       <c r="H28" t="n">
         <v>28500</v>
@@ -1500,7 +1500,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G39" t="n">
-        <v>4.09819889068604</v>
+        <v>4.09819841384888</v>
       </c>
       <c r="H39" t="n">
         <v>3500</v>
@@ -1529,7 +1529,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>4.09819889068604</v>
+        <v>4.09819841384888</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G41" t="n">
-        <v>4.1717095375061</v>
+        <v>4.17170906066895</v>
       </c>
       <c r="H41" t="n">
         <v>5500</v>
@@ -1587,7 +1587,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>4.1717095375061</v>
+        <v>4.17170906066895</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G45" t="n">
-        <v>4.0338773727417</v>
+        <v>4.03387689590454</v>
       </c>
       <c r="H45" t="n">
         <v>12500</v>
@@ -1732,7 +1732,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G47" t="n">
-        <v>3.99712228775024</v>
+        <v>3.99712252616882</v>
       </c>
       <c r="H47" t="n">
         <v>3000</v>
@@ -1848,7 +1848,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G51" t="n">
-        <v>3.89604520797729</v>
+        <v>3.89604544639587</v>
       </c>
       <c r="H51" t="n">
         <v>31000</v>
@@ -1906,7 +1906,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G53" t="n">
-        <v>3.89604520797729</v>
+        <v>3.89604544639587</v>
       </c>
       <c r="H53" t="n">
         <v>11000</v>
@@ -1935,7 +1935,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G54" t="n">
-        <v>3.85929012298584</v>
+        <v>3.85929036140442</v>
       </c>
       <c r="H54" t="n">
         <v>5000</v>
@@ -1964,7 +1964,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G55" t="n">
-        <v>3.85929012298584</v>
+        <v>3.85929036140442</v>
       </c>
       <c r="H55" t="n">
         <v>6000</v>
@@ -2109,7 +2109,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G60" t="n">
-        <v>4.0338773727417</v>
+        <v>4.03387689590454</v>
       </c>
       <c r="H60" t="n">
         <v>1000</v>
@@ -2138,7 +2138,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G61" t="n">
-        <v>3.99712228775024</v>
+        <v>3.99712252616882</v>
       </c>
       <c r="H61" t="n">
         <v>7000</v>
@@ -2167,7 +2167,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G62" t="n">
-        <v>3.93280100822449</v>
+        <v>3.93280124664307</v>
       </c>
       <c r="H62" t="n">
         <v>40500</v>
@@ -2341,7 +2341,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G68" t="n">
-        <v>4.26359701156616</v>
+        <v>4.263596534729</v>
       </c>
       <c r="H68" t="n">
         <v>12500</v>
@@ -2370,7 +2370,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G69" t="n">
-        <v>4.23603105545044</v>
+        <v>4.23603057861328</v>
       </c>
       <c r="H69" t="n">
         <v>7000</v>
@@ -2457,7 +2457,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G72" t="n">
-        <v>4.66790342330933</v>
+        <v>4.66790437698364</v>
       </c>
       <c r="H72" t="n">
         <v>16500</v>
@@ -2515,7 +2515,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G74" t="n">
-        <v>4.81492471694946</v>
+        <v>4.8149242401123</v>
       </c>
       <c r="H74" t="n">
         <v>1500</v>
@@ -2573,7 +2573,7 @@
         <v>5</v>
       </c>
       <c r="G76" t="n">
-        <v>4.59439325332642</v>
+        <v>4.59439373016357</v>
       </c>
       <c r="H76" t="n">
         <v>6000</v>
@@ -2631,7 +2631,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G78" t="n">
-        <v>4.70465850830078</v>
+        <v>4.70465898513794</v>
       </c>
       <c r="H78" t="n">
         <v>1500</v>
@@ -2660,7 +2660,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G79" t="n">
-        <v>4.81492471694946</v>
+        <v>4.8149242401123</v>
       </c>
       <c r="H79" t="n">
         <v>11500</v>
@@ -2747,7 +2747,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G82" t="n">
-        <v>4.77816963195801</v>
+        <v>4.77816915512085</v>
       </c>
       <c r="H82" t="n">
         <v>3500</v>
@@ -2776,7 +2776,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G83" t="n">
-        <v>4.92519044876099</v>
+        <v>4.92518997192383</v>
       </c>
       <c r="H83" t="n">
         <v>3500</v>
@@ -2834,7 +2834,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G85" t="n">
-        <v>4.96194505691528</v>
+        <v>4.96194553375244</v>
       </c>
       <c r="H85" t="n">
         <v>27000</v>
@@ -2892,7 +2892,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G87" t="n">
-        <v>5.31111907958984</v>
+        <v>5.311119556427</v>
       </c>
       <c r="H87" t="n">
         <v>23500</v>
@@ -2950,7 +2950,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G89" t="n">
-        <v>6.11973190307617</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H89" t="n">
         <v>78500</v>
@@ -3008,7 +3008,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G91" t="n">
-        <v>6.11973190307617</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H91" t="n">
         <v>34500</v>
@@ -3037,7 +3037,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G92" t="n">
-        <v>6.26675319671631</v>
+        <v>6.26675271987915</v>
       </c>
       <c r="H92" t="n">
         <v>23000</v>
@@ -3095,7 +3095,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G94" t="n">
-        <v>6.11973190307617</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H94" t="n">
         <v>29500</v>
@@ -3153,7 +3153,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>6.45052862167358</v>
+        <v>6.45052814483643</v>
       </c>
       <c r="H96" t="n">
         <v>59500</v>
@@ -3240,7 +3240,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G99" t="n">
-        <v>6.08297681808472</v>
+        <v>6.08297729492188</v>
       </c>
       <c r="H99" t="n">
         <v>19500</v>
@@ -3269,7 +3269,7 @@
         <v>6.5</v>
       </c>
       <c r="G100" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H100" t="n">
         <v>8000</v>
@@ -3298,7 +3298,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>5.9910888671875</v>
+        <v>5.99108982086182</v>
       </c>
       <c r="H101" t="n">
         <v>7000</v>
@@ -3327,7 +3327,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G102" t="n">
-        <v>6.10135507583618</v>
+        <v>6.10135459899902</v>
       </c>
       <c r="H102" t="n">
         <v>2000</v>
@@ -3356,7 +3356,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G103" t="n">
-        <v>6.10135507583618</v>
+        <v>6.10135459899902</v>
       </c>
       <c r="H103" t="n">
         <v>2000</v>
@@ -3414,7 +3414,7 @@
         <v>6.5</v>
       </c>
       <c r="G105" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H105" t="n">
         <v>22000</v>
@@ -3443,7 +3443,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G106" t="n">
-        <v>5.95433378219604</v>
+        <v>5.9543342590332</v>
       </c>
       <c r="H106" t="n">
         <v>11500</v>
@@ -3588,7 +3588,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G111" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H111" t="n">
         <v>3500</v>
@@ -3646,7 +3646,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>5.88082313537598</v>
+        <v>5.88082361221313</v>
       </c>
       <c r="H113" t="n">
         <v>500</v>
@@ -3675,7 +3675,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G114" t="n">
-        <v>5.88082313537598</v>
+        <v>5.88082361221313</v>
       </c>
       <c r="H114" t="n">
         <v>500</v>
@@ -3762,7 +3762,7 @@
         <v>6</v>
       </c>
       <c r="G117" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H117" t="n">
         <v>2500</v>
@@ -3791,7 +3791,7 @@
         <v>6</v>
       </c>
       <c r="G118" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H118" t="n">
         <v>12500</v>
@@ -3820,7 +3820,7 @@
         <v>6</v>
       </c>
       <c r="G119" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H119" t="n">
         <v>500</v>
@@ -3849,7 +3849,7 @@
         <v>6</v>
       </c>
       <c r="G120" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H120" t="n">
         <v>500</v>
@@ -3878,7 +3878,7 @@
         <v>6</v>
       </c>
       <c r="G121" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H121" t="n">
         <v>500</v>
@@ -3907,7 +3907,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G122" t="n">
-        <v>5.25598621368408</v>
+        <v>5.25598573684692</v>
       </c>
       <c r="H122" t="n">
         <v>10000</v>
@@ -3936,7 +3936,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G123" t="n">
-        <v>5.23760843276978</v>
+        <v>5.23760890960693</v>
       </c>
       <c r="H123" t="n">
         <v>13000</v>
@@ -3965,7 +3965,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G124" t="n">
-        <v>5.32949638366699</v>
+        <v>5.32949686050415</v>
       </c>
       <c r="H124" t="n">
         <v>500</v>
@@ -3994,7 +3994,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G125" t="n">
-        <v>5.71542501449585</v>
+        <v>5.71542549133301</v>
       </c>
       <c r="H125" t="n">
         <v>14000</v>
@@ -4052,7 +4052,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G127" t="n">
-        <v>5.25598621368408</v>
+        <v>5.25598573684692</v>
       </c>
       <c r="H127" t="n">
         <v>22000</v>
@@ -4139,7 +4139,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G130" t="n">
-        <v>5.49489498138428</v>
+        <v>5.49489450454712</v>
       </c>
       <c r="H130" t="n">
         <v>500</v>
@@ -4197,7 +4197,7 @@
         <v>6</v>
       </c>
       <c r="G132" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H132" t="n">
         <v>8500</v>
@@ -4226,7 +4226,7 @@
         <v>6</v>
       </c>
       <c r="G133" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H133" t="n">
         <v>1500</v>
@@ -4516,7 +4516,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G143" t="n">
-        <v>5.88082313537598</v>
+        <v>5.88082361221313</v>
       </c>
       <c r="H143" t="n">
         <v>5500</v>
@@ -4632,7 +4632,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>5.88082313537598</v>
+        <v>5.88082361221313</v>
       </c>
       <c r="H147" t="n">
         <v>5000</v>
@@ -4661,7 +4661,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G148" t="n">
-        <v>5.88082313537598</v>
+        <v>5.88082361221313</v>
       </c>
       <c r="H148" t="n">
         <v>500</v>
@@ -4690,7 +4690,7 @@
         <v>6.5</v>
       </c>
       <c r="G149" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H149" t="n">
         <v>2000</v>
@@ -4719,7 +4719,7 @@
         <v>6.5</v>
       </c>
       <c r="G150" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H150" t="n">
         <v>1500</v>
@@ -4748,7 +4748,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>6.06459999084473</v>
+        <v>6.06459903717041</v>
       </c>
       <c r="H151" t="n">
         <v>5500</v>
@@ -4806,7 +4806,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G153" t="n">
-        <v>6.06459999084473</v>
+        <v>6.06459903717041</v>
       </c>
       <c r="H153" t="n">
         <v>1000</v>
@@ -5183,7 +5183,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>6.56079387664795</v>
+        <v>6.56079435348511</v>
       </c>
       <c r="H166" t="n">
         <v>2500</v>
@@ -5328,7 +5328,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G171" t="n">
-        <v>6.45052862167358</v>
+        <v>6.45052814483643</v>
       </c>
       <c r="H171" t="n">
         <v>1500</v>
@@ -5386,7 +5386,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G173" t="n">
-        <v>6.46890592575073</v>
+        <v>6.46890687942505</v>
       </c>
       <c r="H173" t="n">
         <v>2000</v>
@@ -5502,7 +5502,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G177" t="n">
-        <v>7.27751970291138</v>
+        <v>7.27751922607422</v>
       </c>
       <c r="H177" t="n">
         <v>28000</v>
@@ -5560,7 +5560,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H179" t="n">
         <v>1500</v>
@@ -5589,7 +5589,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5618,7 +5618,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H181" t="n">
         <v>1500</v>
@@ -5647,7 +5647,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G182" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H182" t="n">
         <v>2500</v>
@@ -5676,7 +5676,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>7.5</v>
       </c>
       <c r="G185" t="n">
-        <v>6.89159059524536</v>
+        <v>6.8915901184082</v>
       </c>
       <c r="H185" t="n">
         <v>5000</v>
@@ -5763,7 +5763,7 @@
         <v>7.5</v>
       </c>
       <c r="G186" t="n">
-        <v>6.89159059524536</v>
+        <v>6.8915901184082</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G188" t="n">
-        <v>7.24076414108276</v>
+        <v>7.24076461791992</v>
       </c>
       <c r="H188" t="n">
         <v>1000</v>
@@ -5850,7 +5850,7 @@
         <v>8</v>
       </c>
       <c r="G189" t="n">
-        <v>7.35103034973145</v>
+        <v>7.35102987289429</v>
       </c>
       <c r="H189" t="n">
         <v>3500</v>
@@ -6024,7 +6024,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G195" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H195" t="n">
         <v>12000</v>
@@ -6285,7 +6285,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G204" t="n">
-        <v>7.79209041595459</v>
+        <v>7.79209089279175</v>
       </c>
       <c r="H204" t="n">
         <v>6500</v>
@@ -6372,7 +6372,7 @@
         <v>9</v>
       </c>
       <c r="G207" t="n">
-        <v>8.2699089050293</v>
+        <v>8.26990795135498</v>
       </c>
       <c r="H207" t="n">
         <v>3000</v>
@@ -6488,7 +6488,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G211" t="n">
-        <v>8.15964221954346</v>
+        <v>8.15964317321777</v>
       </c>
       <c r="H211" t="n">
         <v>8000</v>
@@ -6691,7 +6691,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G218" t="n">
-        <v>8.69259262084961</v>
+        <v>8.69259357452393</v>
       </c>
       <c r="H218" t="n">
         <v>3000</v>
@@ -6749,7 +6749,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>8.69259262084961</v>
+        <v>8.69259357452393</v>
       </c>
       <c r="H220" t="n">
         <v>3500</v>
@@ -6778,7 +6778,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>8.69259262084961</v>
+        <v>8.69259357452393</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G222" t="n">
-        <v>8.60070514678955</v>
+        <v>8.60070419311523</v>
       </c>
       <c r="H222" t="n">
         <v>2500</v>
@@ -6865,7 +6865,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G224" t="n">
-        <v>8.82123565673828</v>
+        <v>8.8212366104126</v>
       </c>
       <c r="H224" t="n">
         <v>2000</v>
@@ -6894,7 +6894,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.82123565673828</v>
+        <v>8.8212366104126</v>
       </c>
       <c r="H225" t="n">
         <v>3500</v>
@@ -6923,7 +6923,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G226" t="n">
-        <v>8.76610279083252</v>
+        <v>8.76610374450684</v>
       </c>
       <c r="H226" t="n">
         <v>500</v>
@@ -6981,7 +6981,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G228" t="n">
-        <v>8.63745975494385</v>
+        <v>8.63746070861816</v>
       </c>
       <c r="H228" t="n">
         <v>20000</v>
@@ -7010,7 +7010,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G229" t="n">
-        <v>8.63745975494385</v>
+        <v>8.63746070861816</v>
       </c>
       <c r="H229" t="n">
         <v>12500</v>
@@ -7039,7 +7039,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G230" t="n">
-        <v>8.63745975494385</v>
+        <v>8.63746070861816</v>
       </c>
       <c r="H230" t="n">
         <v>7000</v>
@@ -7068,7 +7068,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G231" t="n">
-        <v>8.60070514678955</v>
+        <v>8.60070419311523</v>
       </c>
       <c r="H231" t="n">
         <v>4000</v>
@@ -7126,7 +7126,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G233" t="n">
-        <v>8.63745975494385</v>
+        <v>8.63746070861816</v>
       </c>
       <c r="H233" t="n">
         <v>11000</v>
@@ -7300,7 +7300,7 @@
         <v>9</v>
       </c>
       <c r="G239" t="n">
-        <v>8.2699089050293</v>
+        <v>8.26990795135498</v>
       </c>
       <c r="H239" t="n">
         <v>3000</v>
@@ -7561,7 +7561,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G248" t="n">
-        <v>8.63745975494385</v>
+        <v>8.63746070861816</v>
       </c>
       <c r="H248" t="n">
         <v>7500</v>
@@ -7706,7 +7706,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G253" t="n">
-        <v>8.71096992492676</v>
+        <v>8.71096897125244</v>
       </c>
       <c r="H253" t="n">
         <v>10500</v>
@@ -7735,7 +7735,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G254" t="n">
-        <v>8.71096992492676</v>
+        <v>8.71096897125244</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G255" t="n">
-        <v>8.71096992492676</v>
+        <v>8.71096897125244</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G258" t="n">
-        <v>9.09689998626709</v>
+        <v>9.09689903259277</v>
       </c>
       <c r="H258" t="n">
         <v>1500</v>
@@ -7880,7 +7880,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G259" t="n">
-        <v>9.09689998626709</v>
+        <v>9.09689903259277</v>
       </c>
       <c r="H259" t="n">
         <v>4500</v>
@@ -7909,7 +7909,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G260" t="n">
-        <v>9.09689998626709</v>
+        <v>9.09689903259277</v>
       </c>
       <c r="H260" t="n">
         <v>500</v>
@@ -7996,7 +7996,7 @@
         <v>10</v>
       </c>
       <c r="G263" t="n">
-        <v>9.18878650665283</v>
+        <v>9.18878746032715</v>
       </c>
       <c r="H263" t="n">
         <v>500</v>
@@ -8025,7 +8025,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G264" t="n">
-        <v>8.69259262084961</v>
+        <v>8.69259357452393</v>
       </c>
       <c r="H264" t="n">
         <v>7000</v>
@@ -8054,7 +8054,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>8.69259262084961</v>
+        <v>8.69259357452393</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G267" t="n">
-        <v>8.69259262084961</v>
+        <v>8.69259357452393</v>
       </c>
       <c r="H267" t="n">
         <v>5500</v>
@@ -8141,7 +8141,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G268" t="n">
-        <v>8.50881767272949</v>
+        <v>8.50881862640381</v>
       </c>
       <c r="H268" t="n">
         <v>8500</v>
@@ -8199,7 +8199,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G270" t="n">
-        <v>8.67421531677246</v>
+        <v>8.67421436309814</v>
       </c>
       <c r="H270" t="n">
         <v>1000</v>
@@ -8257,7 +8257,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G272" t="n">
-        <v>7.47967338562012</v>
+        <v>7.47967290878296</v>
       </c>
       <c r="H272" t="n">
         <v>11000</v>
@@ -8286,7 +8286,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G273" t="n">
-        <v>7.29589748382568</v>
+        <v>7.29589700698853</v>
       </c>
       <c r="H273" t="n">
         <v>6500</v>
@@ -8315,7 +8315,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>7.53480529785156</v>
+        <v>7.5348048210144</v>
       </c>
       <c r="H274" t="n">
         <v>3000</v>
@@ -8344,7 +8344,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G275" t="n">
-        <v>7.1304988861084</v>
+        <v>7.13049936294556</v>
       </c>
       <c r="H275" t="n">
         <v>13500</v>
@@ -8431,7 +8431,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G278" t="n">
-        <v>7.66344833374023</v>
+        <v>7.66344785690308</v>
       </c>
       <c r="H278" t="n">
         <v>3000</v>
@@ -8518,7 +8518,7 @@
         <v>8</v>
       </c>
       <c r="G281" t="n">
-        <v>7.35103034973145</v>
+        <v>7.35102987289429</v>
       </c>
       <c r="H281" t="n">
         <v>3000</v>
@@ -8547,7 +8547,7 @@
         <v>8</v>
       </c>
       <c r="G282" t="n">
-        <v>7.35103034973145</v>
+        <v>7.35102987289429</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>8</v>
       </c>
       <c r="G283" t="n">
-        <v>7.35103034973145</v>
+        <v>7.35102987289429</v>
       </c>
       <c r="H283" t="n">
         <v>7500</v>
@@ -8692,7 +8692,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G287" t="n">
-        <v>7.27751970291138</v>
+        <v>7.27751922607422</v>
       </c>
       <c r="H287" t="n">
         <v>3500</v>
@@ -8750,7 +8750,7 @@
         <v>8</v>
       </c>
       <c r="G289" t="n">
-        <v>7.35103034973145</v>
+        <v>7.35102987289429</v>
       </c>
       <c r="H289" t="n">
         <v>1500</v>
@@ -8779,7 +8779,7 @@
         <v>8</v>
       </c>
       <c r="G290" t="n">
-        <v>7.35103034973145</v>
+        <v>7.35102987289429</v>
       </c>
       <c r="H290" t="n">
         <v>9000</v>
@@ -8808,7 +8808,7 @@
         <v>8</v>
       </c>
       <c r="G291" t="n">
-        <v>7.35103034973145</v>
+        <v>7.35102987289429</v>
       </c>
       <c r="H291" t="n">
         <v>1500</v>
@@ -8837,7 +8837,7 @@
         <v>8</v>
       </c>
       <c r="G292" t="n">
-        <v>7.35103034973145</v>
+        <v>7.35102987289429</v>
       </c>
       <c r="H292" t="n">
         <v>3000</v>
@@ -9127,7 +9127,7 @@
         <v>7.5</v>
       </c>
       <c r="G302" t="n">
-        <v>6.89159059524536</v>
+        <v>6.8915901184082</v>
       </c>
       <c r="H302" t="n">
         <v>2000</v>
@@ -9156,7 +9156,7 @@
         <v>7.5</v>
       </c>
       <c r="G303" t="n">
-        <v>6.89159059524536</v>
+        <v>6.8915901184082</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9185,7 +9185,7 @@
         <v>7.5</v>
       </c>
       <c r="G304" t="n">
-        <v>6.89159059524536</v>
+        <v>6.8915901184082</v>
       </c>
       <c r="H304" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>7.5</v>
       </c>
       <c r="G305" t="n">
-        <v>6.89159059524536</v>
+        <v>6.8915901184082</v>
       </c>
       <c r="H305" t="n">
         <v>15500</v>
@@ -9243,7 +9243,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G306" t="n">
-        <v>7.07536554336548</v>
+        <v>7.07536602020264</v>
       </c>
       <c r="H306" t="n">
         <v>1500</v>
@@ -9272,7 +9272,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G307" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H307" t="n">
         <v>500</v>
@@ -9301,7 +9301,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G308" t="n">
-        <v>6.72619295120239</v>
+        <v>6.72619247436523</v>
       </c>
       <c r="H308" t="n">
         <v>5000</v>
@@ -9359,7 +9359,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G310" t="n">
-        <v>7.07536554336548</v>
+        <v>7.07536602020264</v>
       </c>
       <c r="H310" t="n">
         <v>3000</v>
@@ -9388,7 +9388,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G311" t="n">
-        <v>7.55318307876587</v>
+        <v>7.55318355560303</v>
       </c>
       <c r="H311" t="n">
         <v>2000</v>
@@ -9417,7 +9417,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G312" t="n">
-        <v>7.53480529785156</v>
+        <v>7.5348048210144</v>
       </c>
       <c r="H312" t="n">
         <v>2000</v>
@@ -9446,7 +9446,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G313" t="n">
-        <v>7.38778495788574</v>
+        <v>7.38778448104858</v>
       </c>
       <c r="H313" t="n">
         <v>2000</v>
@@ -9475,7 +9475,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G314" t="n">
-        <v>7.44291830062866</v>
+        <v>7.4429178237915</v>
       </c>
       <c r="H314" t="n">
         <v>2000</v>
@@ -9504,7 +9504,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G315" t="n">
-        <v>7.44291830062866</v>
+        <v>7.4429178237915</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G316" t="n">
-        <v>7.44291830062866</v>
+        <v>7.4429178237915</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>7.44291830062866</v>
+        <v>7.4429178237915</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G318" t="n">
-        <v>7.44291830062866</v>
+        <v>7.4429178237915</v>
       </c>
       <c r="H318" t="n">
         <v>500</v>
@@ -9678,7 +9678,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G321" t="n">
-        <v>7.22238636016846</v>
+        <v>7.22238683700562</v>
       </c>
       <c r="H321" t="n">
         <v>500</v>
@@ -9707,7 +9707,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G322" t="n">
-        <v>7.22238636016846</v>
+        <v>7.22238683700562</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G323" t="n">
-        <v>7.22238636016846</v>
+        <v>7.22238683700562</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G324" t="n">
-        <v>7.22238636016846</v>
+        <v>7.22238683700562</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>6.92834520339966</v>
+        <v>6.92834568023682</v>
       </c>
       <c r="H325" t="n">
         <v>1000</v>
@@ -9823,7 +9823,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G326" t="n">
-        <v>6.92834520339966</v>
+        <v>6.92834568023682</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G330" t="n">
-        <v>7.02023363113403</v>
+        <v>7.02023267745972</v>
       </c>
       <c r="H330" t="n">
         <v>500</v>
@@ -9968,7 +9968,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G331" t="n">
-        <v>7.02023363113403</v>
+        <v>7.02023267745972</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G332" t="n">
-        <v>7.02023363113403</v>
+        <v>7.02023267745972</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G333" t="n">
-        <v>7.02023363113403</v>
+        <v>7.02023267745972</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10200,7 +10200,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G339" t="n">
-        <v>6.37701797485352</v>
+        <v>6.37701845169067</v>
       </c>
       <c r="H339" t="n">
         <v>4500</v>
@@ -10229,7 +10229,7 @@
         <v>6.5</v>
       </c>
       <c r="G340" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H340" t="n">
         <v>32500</v>
@@ -10258,7 +10258,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G341" t="n">
-        <v>6.15648746490479</v>
+        <v>6.15648698806763</v>
       </c>
       <c r="H341" t="n">
         <v>1000</v>
@@ -10287,7 +10287,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G342" t="n">
-        <v>6.15648746490479</v>
+        <v>6.15648698806763</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -10345,7 +10345,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G344" t="n">
-        <v>6.26675319671631</v>
+        <v>6.26675271987915</v>
       </c>
       <c r="H344" t="n">
         <v>1000</v>
@@ -10374,7 +10374,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G345" t="n">
-        <v>6.26675319671631</v>
+        <v>6.26675271987915</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10432,7 +10432,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G347" t="n">
-        <v>6.11973190307617</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H347" t="n">
         <v>1000</v>
@@ -10461,7 +10461,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G348" t="n">
-        <v>6.11973190307617</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -10548,7 +10548,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>5.9910888671875</v>
+        <v>5.99108982086182</v>
       </c>
       <c r="H351" t="n">
         <v>14500</v>
@@ -10577,7 +10577,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G352" t="n">
-        <v>5.9910888671875</v>
+        <v>5.99108982086182</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -10606,7 +10606,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G353" t="n">
-        <v>5.91757869720459</v>
+        <v>5.91757917404175</v>
       </c>
       <c r="H353" t="n">
         <v>3000</v>
@@ -10635,7 +10635,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G354" t="n">
-        <v>5.91757869720459</v>
+        <v>5.91757917404175</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G365" t="n">
-        <v>6.5975489616394</v>
+        <v>6.59754943847656</v>
       </c>
       <c r="H365" t="n">
         <v>500</v>
@@ -10983,7 +10983,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G366" t="n">
-        <v>6.15648746490479</v>
+        <v>6.15648698806763</v>
       </c>
       <c r="H366" t="n">
         <v>6500</v>
@@ -11244,7 +11244,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>6.15648746490479</v>
+        <v>6.15648698806763</v>
       </c>
       <c r="H375" t="n">
         <v>500</v>
@@ -11331,7 +11331,7 @@
         <v>6.5</v>
       </c>
       <c r="G378" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H378" t="n">
         <v>500</v>
@@ -11360,7 +11360,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>6.06459999084473</v>
+        <v>6.06459903717041</v>
       </c>
       <c r="H379" t="n">
         <v>1000</v>
@@ -11389,7 +11389,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>6.06459999084473</v>
+        <v>6.06459903717041</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>6.06459999084473</v>
+        <v>6.06459903717041</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G382" t="n">
-        <v>6.06459999084473</v>
+        <v>6.06459903717041</v>
       </c>
       <c r="H382" t="n">
         <v>500</v>
@@ -11476,7 +11476,7 @@
         <v>6.5</v>
       </c>
       <c r="G383" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H383" t="n">
         <v>500</v>
@@ -11505,7 +11505,7 @@
         <v>6.5</v>
       </c>
       <c r="G384" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>6.5</v>
       </c>
       <c r="G385" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -11563,7 +11563,7 @@
         <v>6.5</v>
       </c>
       <c r="G386" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -11621,7 +11621,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G388" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H388" t="n">
         <v>1000</v>
@@ -11911,7 +11911,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G398" t="n">
-        <v>5.91757869720459</v>
+        <v>5.91757917404175</v>
       </c>
       <c r="H398" t="n">
         <v>500</v>
@@ -11940,7 +11940,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G399" t="n">
-        <v>5.91757869720459</v>
+        <v>5.91757917404175</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -11969,7 +11969,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G400" t="n">
-        <v>6.10135507583618</v>
+        <v>6.10135459899902</v>
       </c>
       <c r="H400" t="n">
         <v>500</v>
@@ -11998,7 +11998,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G401" t="n">
-        <v>6.15648746490479</v>
+        <v>6.15648698806763</v>
       </c>
       <c r="H401" t="n">
         <v>2500</v>
@@ -12027,7 +12027,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G402" t="n">
-        <v>6.15648746490479</v>
+        <v>6.15648698806763</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G403" t="n">
-        <v>6.15648746490479</v>
+        <v>6.15648698806763</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -12085,7 +12085,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G404" t="n">
-        <v>6.11973190307617</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H404" t="n">
         <v>1000</v>
@@ -12114,7 +12114,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G405" t="n">
-        <v>6.11973190307617</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -12143,7 +12143,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G406" t="n">
-        <v>6.11973190307617</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G407" t="n">
-        <v>6.11973190307617</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -12201,7 +12201,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G408" t="n">
-        <v>6.11973190307617</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G413" t="n">
-        <v>6.45052862167358</v>
+        <v>6.45052814483643</v>
       </c>
       <c r="H413" t="n">
         <v>5500</v>
@@ -12375,7 +12375,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G414" t="n">
-        <v>6.45052862167358</v>
+        <v>6.45052814483643</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -12897,7 +12897,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G432" t="n">
-        <v>6.08297681808472</v>
+        <v>6.08297729492188</v>
       </c>
       <c r="H432" t="n">
         <v>500</v>
@@ -12926,7 +12926,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>6.08297681808472</v>
+        <v>6.08297729492188</v>
       </c>
       <c r="H433" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G434" t="n">
-        <v>6.08297681808472</v>
+        <v>6.08297729492188</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G435" t="n">
-        <v>6.08297681808472</v>
+        <v>6.08297729492188</v>
       </c>
       <c r="H435" t="n">
         <v>0</v>
@@ -13013,7 +13013,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G436" t="n">
-        <v>6.08297681808472</v>
+        <v>6.08297729492188</v>
       </c>
       <c r="H436" t="n">
         <v>0</v>
@@ -13042,7 +13042,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G437" t="n">
-        <v>6.08297681808472</v>
+        <v>6.08297729492188</v>
       </c>
       <c r="H437" t="n">
         <v>0</v>
@@ -13129,7 +13129,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>6.15648746490479</v>
+        <v>6.15648698806763</v>
       </c>
       <c r="H440" t="n">
         <v>1000</v>
@@ -13390,7 +13390,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G449" t="n">
-        <v>5.75218057632446</v>
+        <v>5.75218105316162</v>
       </c>
       <c r="H449" t="n">
         <v>3000</v>
@@ -13419,7 +13419,7 @@
         <v>6.5</v>
       </c>
       <c r="G450" t="n">
-        <v>5.97271203994751</v>
+        <v>5.97271156311035</v>
       </c>
       <c r="H450" t="n">
         <v>500</v>
@@ -13477,7 +13477,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G452" t="n">
-        <v>5.88082313537598</v>
+        <v>5.88082361221313</v>
       </c>
       <c r="H452" t="n">
         <v>1000</v>
@@ -13506,7 +13506,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G453" t="n">
-        <v>5.78893566131592</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H453" t="n">
         <v>500</v>
@@ -13535,7 +13535,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G454" t="n">
-        <v>5.78893566131592</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H454" t="n">
         <v>0</v>
@@ -13564,7 +13564,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G455" t="n">
-        <v>5.78893566131592</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H455" t="n">
         <v>0</v>
@@ -13593,7 +13593,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G456" t="n">
-        <v>5.78893566131592</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H456" t="n">
         <v>0</v>
@@ -13622,7 +13622,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G457" t="n">
-        <v>5.78893566131592</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H457" t="n">
         <v>0</v>
@@ -13651,7 +13651,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G458" t="n">
-        <v>5.78893566131592</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H458" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G459" t="n">
-        <v>5.78893566131592</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H459" t="n">
         <v>0</v>
@@ -13709,7 +13709,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G460" t="n">
-        <v>5.78893566131592</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G461" t="n">
-        <v>5.78893566131592</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13767,7 +13767,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G462" t="n">
-        <v>5.78893566131592</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G463" t="n">
-        <v>5.78893566131592</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H463" t="n">
         <v>0</v>
@@ -13825,7 +13825,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G464" t="n">
-        <v>5.78893566131592</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H464" t="n">
         <v>1000</v>
@@ -13854,7 +13854,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G465" t="n">
-        <v>5.78893566131592</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H465" t="n">
         <v>0</v>
@@ -13883,7 +13883,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G466" t="n">
-        <v>5.78893566131592</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H466" t="n">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G467" t="n">
-        <v>5.78893566131592</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H467" t="n">
         <v>0</v>
@@ -14144,7 +14144,7 @@
         <v>6</v>
       </c>
       <c r="G475" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H475" t="n">
         <v>500</v>
@@ -14173,7 +14173,7 @@
         <v>6</v>
       </c>
       <c r="G476" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H476" t="n">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>6</v>
       </c>
       <c r="G477" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H477" t="n">
         <v>0</v>
@@ -14231,7 +14231,7 @@
         <v>6</v>
       </c>
       <c r="G478" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H478" t="n">
         <v>0</v>
@@ -14260,7 +14260,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G479" t="n">
-        <v>5.3478741645813</v>
+        <v>5.34787464141846</v>
       </c>
       <c r="H479" t="n">
         <v>7000</v>
@@ -14434,7 +14434,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G485" t="n">
-        <v>5.78893566131592</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H485" t="n">
         <v>1500</v>
@@ -14463,7 +14463,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G486" t="n">
-        <v>5.78893566131592</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H486" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G487" t="n">
-        <v>5.78893566131592</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H487" t="n">
         <v>0</v>
@@ -14521,7 +14521,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G488" t="n">
-        <v>5.78893566131592</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H488" t="n">
         <v>1000</v>
@@ -14550,7 +14550,7 @@
         <v>6</v>
       </c>
       <c r="G489" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H489" t="n">
         <v>1500</v>
@@ -14579,7 +14579,7 @@
         <v>6</v>
       </c>
       <c r="G490" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H490" t="n">
         <v>3500</v>
@@ -14608,7 +14608,7 @@
         <v>6</v>
       </c>
       <c r="G491" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H491" t="n">
         <v>0</v>
@@ -14637,7 +14637,7 @@
         <v>6</v>
       </c>
       <c r="G492" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H492" t="n">
         <v>0</v>
@@ -14666,7 +14666,7 @@
         <v>6</v>
       </c>
       <c r="G493" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H493" t="n">
         <v>500</v>
@@ -14695,7 +14695,7 @@
         <v>6</v>
       </c>
       <c r="G494" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H494" t="n">
         <v>0</v>
@@ -15014,7 +15014,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>5.36625146865845</v>
+        <v>5.36625194549561</v>
       </c>
       <c r="H505" t="n">
         <v>1000</v>
@@ -15043,7 +15043,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G506" t="n">
-        <v>5.32949638366699</v>
+        <v>5.32949686050415</v>
       </c>
       <c r="H506" t="n">
         <v>1000</v>
@@ -15072,7 +15072,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>5.32949638366699</v>
+        <v>5.32949686050415</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G510" t="n">
-        <v>5.78893566131592</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H510" t="n">
         <v>1500</v>
@@ -15188,7 +15188,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G511" t="n">
-        <v>5.78893566131592</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H511" t="n">
         <v>0</v>
@@ -15217,7 +15217,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G512" t="n">
-        <v>5.78893566131592</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H512" t="n">
         <v>0</v>
@@ -15246,7 +15246,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G513" t="n">
-        <v>5.78893566131592</v>
+        <v>5.78893613815308</v>
       </c>
       <c r="H513" t="n">
         <v>0</v>
@@ -15594,7 +15594,7 @@
         <v>6</v>
       </c>
       <c r="G525" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H525" t="n">
         <v>500</v>
@@ -15623,7 +15623,7 @@
         <v>6</v>
       </c>
       <c r="G526" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H526" t="n">
         <v>0</v>
@@ -15652,7 +15652,7 @@
         <v>6</v>
       </c>
       <c r="G527" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H527" t="n">
         <v>26000</v>
@@ -15681,7 +15681,7 @@
         <v>6</v>
       </c>
       <c r="G528" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H528" t="n">
         <v>0</v>
@@ -15710,7 +15710,7 @@
         <v>6</v>
       </c>
       <c r="G529" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H529" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>6</v>
       </c>
       <c r="G530" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H530" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G548" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H548" t="n">
         <v>1500</v>
@@ -16290,7 +16290,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G549" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H549" t="n">
         <v>0</v>
@@ -16319,7 +16319,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G550" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -16348,7 +16348,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G551" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H551" t="n">
         <v>0</v>
@@ -16377,7 +16377,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G552" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H552" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G553" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -16725,7 +16725,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G564" t="n">
-        <v>5.27436351776123</v>
+        <v>5.27436399459839</v>
       </c>
       <c r="H564" t="n">
         <v>2500</v>
@@ -17015,7 +17015,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G574" t="n">
-        <v>5.27436351776123</v>
+        <v>5.27436399459839</v>
       </c>
       <c r="H574" t="n">
         <v>4500</v>
@@ -17102,7 +17102,7 @@
         <v>6</v>
       </c>
       <c r="G577" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H577" t="n">
         <v>13500</v>
@@ -17131,7 +17131,7 @@
         <v>6</v>
       </c>
       <c r="G578" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H578" t="n">
         <v>0</v>
@@ -17160,7 +17160,7 @@
         <v>6</v>
       </c>
       <c r="G579" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H579" t="n">
         <v>0</v>
@@ -17247,7 +17247,7 @@
         <v>6</v>
       </c>
       <c r="G582" t="n">
-        <v>5.51327276229858</v>
+        <v>5.51327228546143</v>
       </c>
       <c r="H582" t="n">
         <v>500</v>
@@ -18407,7 +18407,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G622" t="n">
-        <v>5.53470754623413</v>
+        <v>5.53470706939697</v>
       </c>
       <c r="H622" t="n">
         <v>3500</v>
@@ -19132,7 +19132,7 @@
         <v>5.25</v>
       </c>
       <c r="G647" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H647" t="n">
         <v>10000</v>
@@ -19161,7 +19161,7 @@
         <v>5.25</v>
       </c>
       <c r="G648" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H648" t="n">
         <v>12500</v>
@@ -19248,7 +19248,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G651" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H651" t="n">
         <v>9500</v>
@@ -19654,7 +19654,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G665" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H665" t="n">
         <v>500</v>
@@ -19712,7 +19712,7 @@
         <v>5.25</v>
       </c>
       <c r="G667" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H667" t="n">
         <v>7250</v>
@@ -19770,7 +19770,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G669" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H669" t="n">
         <v>500</v>
@@ -19799,7 +19799,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H670" t="n">
         <v>0</v>
@@ -19828,7 +19828,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H671" t="n">
         <v>0</v>
@@ -19886,7 +19886,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G673" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H673" t="n">
         <v>13250</v>
@@ -20002,7 +20002,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H677" t="n">
         <v>19750</v>
@@ -20031,7 +20031,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H678" t="n">
         <v>1750</v>
@@ -20060,7 +20060,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G679" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H679" t="n">
         <v>4750</v>
@@ -20089,7 +20089,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G680" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H680" t="n">
         <v>500</v>
@@ -20118,7 +20118,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H681" t="n">
         <v>0</v>
@@ -20147,7 +20147,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G682" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H682" t="n">
         <v>0</v>
@@ -20785,7 +20785,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G704" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403429031372</v>
       </c>
       <c r="H704" t="n">
         <v>41750</v>
@@ -20814,7 +20814,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G705" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403429031372</v>
       </c>
       <c r="H705" t="n">
         <v>7500</v>
@@ -20843,7 +20843,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G706" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403429031372</v>
       </c>
       <c r="H706" t="n">
         <v>2500</v>
@@ -20872,7 +20872,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G707" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403429031372</v>
       </c>
       <c r="H707" t="n">
         <v>7500</v>
@@ -20901,7 +20901,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G708" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403429031372</v>
       </c>
       <c r="H708" t="n">
         <v>2250</v>
@@ -21075,7 +21075,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G714" t="n">
-        <v>4.55799388885498</v>
+        <v>4.55799436569214</v>
       </c>
       <c r="H714" t="n">
         <v>4500</v>
@@ -21133,7 +21133,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G716" t="n">
-        <v>4.46497392654419</v>
+        <v>4.46497440338135</v>
       </c>
       <c r="H716" t="n">
         <v>22500</v>
@@ -21162,7 +21162,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G717" t="n">
-        <v>4.63241052627563</v>
+        <v>4.63241100311279</v>
       </c>
       <c r="H717" t="n">
         <v>1000</v>
@@ -21191,7 +21191,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G718" t="n">
-        <v>4.63241052627563</v>
+        <v>4.63241100311279</v>
       </c>
       <c r="H718" t="n">
         <v>0</v>
@@ -21220,7 +21220,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G719" t="n">
-        <v>4.63241052627563</v>
+        <v>4.63241100311279</v>
       </c>
       <c r="H719" t="n">
         <v>0</v>
@@ -21249,7 +21249,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G720" t="n">
-        <v>4.63241052627563</v>
+        <v>4.63241100311279</v>
       </c>
       <c r="H720" t="n">
         <v>0</v>
@@ -21278,7 +21278,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G721" t="n">
-        <v>4.37195348739624</v>
+        <v>4.3719539642334</v>
       </c>
       <c r="H721" t="n">
         <v>3000</v>
@@ -21336,7 +21336,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G723" t="n">
-        <v>4.01847696304321</v>
+        <v>4.01847648620605</v>
       </c>
       <c r="H723" t="n">
         <v>20000</v>
@@ -21365,7 +21365,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G724" t="n">
-        <v>4.01847696304321</v>
+        <v>4.01847648620605</v>
       </c>
       <c r="H724" t="n">
         <v>6250</v>
@@ -21394,7 +21394,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G725" t="n">
-        <v>4.01847696304321</v>
+        <v>4.01847648620605</v>
       </c>
       <c r="H725" t="n">
         <v>32000</v>
@@ -21423,7 +21423,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G726" t="n">
-        <v>4.05568504333496</v>
+        <v>4.0556845664978</v>
       </c>
       <c r="H726" t="n">
         <v>6000</v>
@@ -21655,7 +21655,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G734" t="n">
-        <v>4.37195348739624</v>
+        <v>4.3719539642334</v>
       </c>
       <c r="H734" t="n">
         <v>250</v>
@@ -21684,7 +21684,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G735" t="n">
-        <v>4.37195348739624</v>
+        <v>4.3719539642334</v>
       </c>
       <c r="H735" t="n">
         <v>0</v>
@@ -21713,7 +21713,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G736" t="n">
-        <v>4.37195348739624</v>
+        <v>4.3719539642334</v>
       </c>
       <c r="H736" t="n">
         <v>0</v>
@@ -21742,7 +21742,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G737" t="n">
-        <v>4.37195348739624</v>
+        <v>4.3719539642334</v>
       </c>
       <c r="H737" t="n">
         <v>0</v>
@@ -21771,7 +21771,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G738" t="n">
-        <v>4.37195348739624</v>
+        <v>4.3719539642334</v>
       </c>
       <c r="H738" t="n">
         <v>0</v>
@@ -21800,7 +21800,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G739" t="n">
-        <v>4.37195348739624</v>
+        <v>4.3719539642334</v>
       </c>
       <c r="H739" t="n">
         <v>0</v>
@@ -21829,7 +21829,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G740" t="n">
-        <v>4.44637012481689</v>
+        <v>4.44636964797974</v>
       </c>
       <c r="H740" t="n">
         <v>750</v>
@@ -22061,7 +22061,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G748" t="n">
-        <v>4.40916156768799</v>
+        <v>4.40916109085083</v>
       </c>
       <c r="H748" t="n">
         <v>500</v>
@@ -22090,7 +22090,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G749" t="n">
-        <v>4.40916156768799</v>
+        <v>4.40916109085083</v>
       </c>
       <c r="H749" t="n">
         <v>0</v>
@@ -22119,7 +22119,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G750" t="n">
-        <v>4.37195348739624</v>
+        <v>4.3719539642334</v>
       </c>
       <c r="H750" t="n">
         <v>750</v>
@@ -22148,7 +22148,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G751" t="n">
-        <v>4.37195348739624</v>
+        <v>4.3719539642334</v>
       </c>
       <c r="H751" t="n">
         <v>0</v>
@@ -22177,7 +22177,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G752" t="n">
-        <v>4.37195348739624</v>
+        <v>4.3719539642334</v>
       </c>
       <c r="H752" t="n">
         <v>0</v>
@@ -22206,7 +22206,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G753" t="n">
-        <v>4.42776584625244</v>
+        <v>4.4277663230896</v>
       </c>
       <c r="H753" t="n">
         <v>2250</v>
@@ -22235,7 +22235,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G754" t="n">
-        <v>4.35334968566895</v>
+        <v>4.35334920883179</v>
       </c>
       <c r="H754" t="n">
         <v>5500</v>
@@ -22264,7 +22264,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G755" t="n">
-        <v>4.42776584625244</v>
+        <v>4.4277663230896</v>
       </c>
       <c r="H755" t="n">
         <v>3250</v>
@@ -22293,7 +22293,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G756" t="n">
-        <v>4.42776584625244</v>
+        <v>4.4277663230896</v>
       </c>
       <c r="H756" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>5.25</v>
       </c>
       <c r="G760" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H760" t="n">
         <v>3000</v>
@@ -22438,7 +22438,7 @@
         <v>5.25</v>
       </c>
       <c r="G761" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H761" t="n">
         <v>2000</v>
@@ -22467,7 +22467,7 @@
         <v>5.25</v>
       </c>
       <c r="G762" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H762" t="n">
         <v>500</v>
@@ -22496,7 +22496,7 @@
         <v>5.25</v>
       </c>
       <c r="G763" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H763" t="n">
         <v>250</v>
@@ -22525,7 +22525,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G764" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403429031372</v>
       </c>
       <c r="H764" t="n">
         <v>4000</v>
@@ -22554,7 +22554,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G765" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403429031372</v>
       </c>
       <c r="H765" t="n">
         <v>0</v>
@@ -22583,7 +22583,7 @@
         <v>5.25</v>
       </c>
       <c r="G766" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H766" t="n">
         <v>2750</v>
@@ -22612,7 +22612,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G767" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H767" t="n">
         <v>6000</v>
@@ -22641,7 +22641,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H768" t="n">
         <v>500</v>
@@ -22670,7 +22670,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G769" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H769" t="n">
         <v>0</v>
@@ -22728,7 +22728,7 @@
         <v>5.25</v>
       </c>
       <c r="G771" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H771" t="n">
         <v>7500</v>
@@ -22757,7 +22757,7 @@
         <v>5.25</v>
       </c>
       <c r="G772" t="n">
-        <v>4.88356494903564</v>
+        <v>4.8835654258728</v>
       </c>
       <c r="H772" t="n">
         <v>0</v>
@@ -22786,7 +22786,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G773" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H773" t="n">
         <v>3750</v>
@@ -22873,7 +22873,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G776" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H776" t="n">
         <v>2750</v>
@@ -22989,7 +22989,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G780" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H780" t="n">
         <v>40750</v>
@@ -23076,7 +23076,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G783" t="n">
-        <v>5.6742377281189</v>
+        <v>5.67423820495605</v>
       </c>
       <c r="H783" t="n">
         <v>6750</v>
@@ -23105,7 +23105,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G784" t="n">
-        <v>5.76725769042969</v>
+        <v>5.76725816726685</v>
       </c>
       <c r="H784" t="n">
         <v>14500</v>
@@ -23163,7 +23163,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G786" t="n">
-        <v>5.95329809188843</v>
+        <v>5.95329856872559</v>
       </c>
       <c r="H786" t="n">
         <v>750</v>
@@ -23192,7 +23192,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G787" t="n">
-        <v>5.95329809188843</v>
+        <v>5.95329856872559</v>
       </c>
       <c r="H787" t="n">
         <v>0</v>
@@ -23221,7 +23221,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G788" t="n">
-        <v>5.86027812957764</v>
+        <v>5.86027860641479</v>
       </c>
       <c r="H788" t="n">
         <v>3250</v>
@@ -23250,7 +23250,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G789" t="n">
-        <v>5.86027812957764</v>
+        <v>5.86027860641479</v>
       </c>
       <c r="H789" t="n">
         <v>1500</v>
@@ -23279,7 +23279,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G790" t="n">
-        <v>5.76725769042969</v>
+        <v>5.76725816726685</v>
       </c>
       <c r="H790" t="n">
         <v>7750</v>
@@ -23308,7 +23308,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G791" t="n">
-        <v>5.86027812957764</v>
+        <v>5.86027860641479</v>
       </c>
       <c r="H791" t="n">
         <v>4750</v>
@@ -23366,7 +23366,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G793" t="n">
-        <v>5.6742377281189</v>
+        <v>5.67423820495605</v>
       </c>
       <c r="H793" t="n">
         <v>1250</v>
@@ -23395,7 +23395,7 @@
         <v>6</v>
       </c>
       <c r="G794" t="n">
-        <v>5.58121776580811</v>
+        <v>5.58121728897095</v>
       </c>
       <c r="H794" t="n">
         <v>500</v>
@@ -23424,7 +23424,7 @@
         <v>6</v>
       </c>
       <c r="G795" t="n">
-        <v>5.58121776580811</v>
+        <v>5.58121728897095</v>
       </c>
       <c r="H795" t="n">
         <v>1250</v>
@@ -23540,7 +23540,7 @@
         <v>6</v>
       </c>
       <c r="G799" t="n">
-        <v>5.58121776580811</v>
+        <v>5.58121728897095</v>
       </c>
       <c r="H799" t="n">
         <v>1750</v>
@@ -23569,7 +23569,7 @@
         <v>6</v>
       </c>
       <c r="G800" t="n">
-        <v>5.58121776580811</v>
+        <v>5.58121728897095</v>
       </c>
       <c r="H800" t="n">
         <v>0</v>
@@ -23598,7 +23598,7 @@
         <v>6</v>
       </c>
       <c r="G801" t="n">
-        <v>5.58121776580811</v>
+        <v>5.58121728897095</v>
       </c>
       <c r="H801" t="n">
         <v>0</v>
@@ -23627,7 +23627,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G802" t="n">
-        <v>5.53470754623413</v>
+        <v>5.53470706939697</v>
       </c>
       <c r="H802" t="n">
         <v>750</v>
@@ -23685,7 +23685,7 @@
         <v>6</v>
       </c>
       <c r="G804" t="n">
-        <v>5.58121776580811</v>
+        <v>5.58121728897095</v>
       </c>
       <c r="H804" t="n">
         <v>1500</v>
@@ -24120,7 +24120,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G819" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H819" t="n">
         <v>1000</v>
@@ -24294,7 +24294,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G825" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H825" t="n">
         <v>500</v>
@@ -24323,7 +24323,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G826" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H826" t="n">
         <v>1000</v>
@@ -24352,7 +24352,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G827" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H827" t="n">
         <v>250</v>
@@ -24439,7 +24439,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G830" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H830" t="n">
         <v>9000</v>
@@ -24497,7 +24497,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G832" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H832" t="n">
         <v>750</v>
@@ -24526,7 +24526,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G833" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H833" t="n">
         <v>500</v>
@@ -24555,7 +24555,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G834" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -24584,7 +24584,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G835" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403429031372</v>
       </c>
       <c r="H835" t="n">
         <v>1000</v>
@@ -24613,7 +24613,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G836" t="n">
-        <v>4.74403476715088</v>
+        <v>4.74403429031372</v>
       </c>
       <c r="H836" t="n">
         <v>1000</v>
@@ -24642,7 +24642,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G837" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H837" t="n">
         <v>1500</v>
@@ -24816,7 +24816,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G843" t="n">
-        <v>4.63241052627563</v>
+        <v>4.63241100311279</v>
       </c>
       <c r="H843" t="n">
         <v>2750</v>
@@ -24990,7 +24990,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G849" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H849" t="n">
         <v>500</v>
@@ -25019,7 +25019,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G850" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H850" t="n">
         <v>1000</v>
@@ -25048,7 +25048,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G851" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H851" t="n">
         <v>1000</v>
@@ -25106,7 +25106,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G853" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H853" t="n">
         <v>2500</v>
@@ -25193,7 +25193,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G856" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H856" t="n">
         <v>250</v>
@@ -25222,7 +25222,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G857" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H857" t="n">
         <v>0</v>
@@ -25251,7 +25251,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G858" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H858" t="n">
         <v>250</v>
@@ -25280,7 +25280,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G859" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H859" t="n">
         <v>1000</v>
@@ -25309,7 +25309,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G860" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H860" t="n">
         <v>1000</v>
@@ -25396,7 +25396,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H863" t="n">
         <v>1000</v>
@@ -25425,7 +25425,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G864" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H864" t="n">
         <v>250</v>
@@ -25454,7 +25454,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G865" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H865" t="n">
         <v>250</v>
@@ -25483,7 +25483,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G866" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -25512,7 +25512,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G867" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -25570,7 +25570,7 @@
         <v>5</v>
       </c>
       <c r="G869" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H869" t="n">
         <v>1000</v>
@@ -25599,7 +25599,7 @@
         <v>5</v>
       </c>
       <c r="G870" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H870" t="n">
         <v>0</v>
@@ -25628,7 +25628,7 @@
         <v>5</v>
       </c>
       <c r="G871" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H871" t="n">
         <v>0</v>
@@ -25657,7 +25657,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G872" t="n">
-        <v>4.79242420196533</v>
+        <v>4.79242467880249</v>
       </c>
       <c r="H872" t="n">
         <v>1000</v>
@@ -25686,7 +25686,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G873" t="n">
-        <v>4.79242420196533</v>
+        <v>4.79242467880249</v>
       </c>
       <c r="H873" t="n">
         <v>0</v>
@@ -25715,7 +25715,7 @@
         <v>5</v>
       </c>
       <c r="G874" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H874" t="n">
         <v>1500</v>
@@ -25802,7 +25802,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G877" t="n">
-        <v>4.70701456069946</v>
+        <v>4.70701503753662</v>
       </c>
       <c r="H877" t="n">
         <v>250</v>
@@ -25831,7 +25831,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>4.70701456069946</v>
+        <v>4.70701503753662</v>
       </c>
       <c r="H878" t="n">
         <v>0</v>
@@ -26005,7 +26005,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G884" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H884" t="n">
         <v>3000</v>
@@ -26034,7 +26034,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G885" t="n">
-        <v>4.79242420196533</v>
+        <v>4.79242467880249</v>
       </c>
       <c r="H885" t="n">
         <v>1750</v>
@@ -26150,7 +26150,7 @@
         <v>5</v>
       </c>
       <c r="G889" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H889" t="n">
         <v>8000</v>
@@ -26179,7 +26179,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G890" t="n">
-        <v>4.79242420196533</v>
+        <v>4.79242467880249</v>
       </c>
       <c r="H890" t="n">
         <v>500</v>
@@ -26208,7 +26208,7 @@
         <v>5</v>
       </c>
       <c r="G891" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H891" t="n">
         <v>750</v>
@@ -26237,7 +26237,7 @@
         <v>5</v>
       </c>
       <c r="G892" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H892" t="n">
         <v>1750</v>
@@ -26266,7 +26266,7 @@
         <v>5</v>
       </c>
       <c r="G893" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H893" t="n">
         <v>750</v>
@@ -26295,7 +26295,7 @@
         <v>5</v>
       </c>
       <c r="G894" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -26324,7 +26324,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G895" t="n">
-        <v>4.79242420196533</v>
+        <v>4.79242467880249</v>
       </c>
       <c r="H895" t="n">
         <v>2000</v>
@@ -26353,7 +26353,7 @@
         <v>5</v>
       </c>
       <c r="G896" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H896" t="n">
         <v>750</v>
@@ -26382,7 +26382,7 @@
         <v>5</v>
       </c>
       <c r="G897" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H897" t="n">
         <v>500</v>
@@ -26411,7 +26411,7 @@
         <v>5</v>
       </c>
       <c r="G898" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H898" t="n">
         <v>0</v>
@@ -26440,7 +26440,7 @@
         <v>5</v>
       </c>
       <c r="G899" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H899" t="n">
         <v>0</v>
@@ -26469,7 +26469,7 @@
         <v>5</v>
       </c>
       <c r="G900" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H900" t="n">
         <v>500</v>
@@ -26585,7 +26585,7 @@
         <v>5</v>
       </c>
       <c r="G904" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H904" t="n">
         <v>1000</v>
@@ -26614,7 +26614,7 @@
         <v>5</v>
       </c>
       <c r="G905" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H905" t="n">
         <v>3250</v>
@@ -26643,7 +26643,7 @@
         <v>5</v>
       </c>
       <c r="G906" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H906" t="n">
         <v>0</v>
@@ -26672,7 +26672,7 @@
         <v>5</v>
       </c>
       <c r="G907" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H907" t="n">
         <v>1250</v>
@@ -26701,7 +26701,7 @@
         <v>5</v>
       </c>
       <c r="G908" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H908" t="n">
         <v>0</v>
@@ -26730,7 +26730,7 @@
         <v>5</v>
       </c>
       <c r="G909" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H909" t="n">
         <v>500</v>
@@ -26759,7 +26759,7 @@
         <v>5</v>
       </c>
       <c r="G910" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H910" t="n">
         <v>0</v>
@@ -26788,7 +26788,7 @@
         <v>5</v>
       </c>
       <c r="G911" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -26817,7 +26817,7 @@
         <v>5</v>
       </c>
       <c r="G912" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -26846,7 +26846,7 @@
         <v>5</v>
       </c>
       <c r="G913" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H913" t="n">
         <v>0</v>
@@ -26875,7 +26875,7 @@
         <v>5</v>
       </c>
       <c r="G914" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H914" t="n">
         <v>500</v>
@@ -26904,7 +26904,7 @@
         <v>5</v>
       </c>
       <c r="G915" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H915" t="n">
         <v>1500</v>
@@ -26933,7 +26933,7 @@
         <v>5</v>
       </c>
       <c r="G916" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H916" t="n">
         <v>1000</v>
@@ -26962,7 +26962,7 @@
         <v>5</v>
       </c>
       <c r="G917" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -26991,7 +26991,7 @@
         <v>5</v>
       </c>
       <c r="G918" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H918" t="n">
         <v>500</v>
@@ -27020,7 +27020,7 @@
         <v>5</v>
       </c>
       <c r="G919" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H919" t="n">
         <v>0</v>
@@ -27049,7 +27049,7 @@
         <v>5</v>
       </c>
       <c r="G920" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H920" t="n">
         <v>0</v>
@@ -27078,7 +27078,7 @@
         <v>5</v>
       </c>
       <c r="G921" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>
@@ -27165,7 +27165,7 @@
         <v>5</v>
       </c>
       <c r="G924" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H924" t="n">
         <v>4000</v>
@@ -27194,7 +27194,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G925" t="n">
-        <v>4.61211538314819</v>
+        <v>4.61211490631104</v>
       </c>
       <c r="H925" t="n">
         <v>5750</v>
@@ -27223,7 +27223,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G926" t="n">
-        <v>4.61211538314819</v>
+        <v>4.61211490631104</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -27252,7 +27252,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G927" t="n">
-        <v>4.61211538314819</v>
+        <v>4.61211490631104</v>
       </c>
       <c r="H927" t="n">
         <v>0</v>
@@ -27281,7 +27281,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G928" t="n">
-        <v>4.61211538314819</v>
+        <v>4.61211490631104</v>
       </c>
       <c r="H928" t="n">
         <v>0</v>
@@ -27310,7 +27310,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G929" t="n">
-        <v>4.61211538314819</v>
+        <v>4.61211490631104</v>
       </c>
       <c r="H929" t="n">
         <v>0</v>
@@ -27339,7 +27339,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G930" t="n">
-        <v>4.61211538314819</v>
+        <v>4.61211490631104</v>
       </c>
       <c r="H930" t="n">
         <v>0</v>
@@ -27368,7 +27368,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G931" t="n">
-        <v>4.61211538314819</v>
+        <v>4.61211490631104</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -27426,7 +27426,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G933" t="n">
-        <v>4.79242420196533</v>
+        <v>4.79242467880249</v>
       </c>
       <c r="H933" t="n">
         <v>750</v>
@@ -27455,7 +27455,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G934" t="n">
-        <v>4.79242420196533</v>
+        <v>4.79242467880249</v>
       </c>
       <c r="H934" t="n">
         <v>0</v>
@@ -27484,7 +27484,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G935" t="n">
-        <v>4.79242420196533</v>
+        <v>4.79242467880249</v>
       </c>
       <c r="H935" t="n">
         <v>250</v>
@@ -27629,7 +27629,7 @@
         <v>5</v>
       </c>
       <c r="G940" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H940" t="n">
         <v>500</v>
@@ -27658,7 +27658,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G941" t="n">
-        <v>4.63109540939331</v>
+        <v>4.63109493255615</v>
       </c>
       <c r="H941" t="n">
         <v>500</v>
@@ -27687,7 +27687,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G942" t="n">
-        <v>4.65007495880127</v>
+        <v>4.65007543563843</v>
       </c>
       <c r="H942" t="n">
         <v>1500</v>
@@ -27716,7 +27716,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G943" t="n">
-        <v>4.65007495880127</v>
+        <v>4.65007543563843</v>
       </c>
       <c r="H943" t="n">
         <v>0</v>
@@ -27745,7 +27745,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G944" t="n">
-        <v>4.65007495880127</v>
+        <v>4.65007543563843</v>
       </c>
       <c r="H944" t="n">
         <v>0</v>
@@ -27774,7 +27774,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G945" t="n">
-        <v>4.65007495880127</v>
+        <v>4.65007543563843</v>
       </c>
       <c r="H945" t="n">
         <v>0</v>
@@ -27803,7 +27803,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G946" t="n">
-        <v>4.65007495880127</v>
+        <v>4.65007543563843</v>
       </c>
       <c r="H946" t="n">
         <v>0</v>
@@ -27832,7 +27832,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G947" t="n">
-        <v>4.65007495880127</v>
+        <v>4.65007543563843</v>
       </c>
       <c r="H947" t="n">
         <v>0</v>
@@ -27861,7 +27861,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G948" t="n">
-        <v>4.65007495880127</v>
+        <v>4.65007543563843</v>
       </c>
       <c r="H948" t="n">
         <v>0</v>
@@ -27890,7 +27890,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G949" t="n">
-        <v>4.65007495880127</v>
+        <v>4.65007543563843</v>
       </c>
       <c r="H949" t="n">
         <v>0</v>
@@ -27919,7 +27919,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G950" t="n">
-        <v>4.63109540939331</v>
+        <v>4.63109493255615</v>
       </c>
       <c r="H950" t="n">
         <v>2250</v>
@@ -27948,7 +27948,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G951" t="n">
-        <v>4.63109540939331</v>
+        <v>4.63109493255615</v>
       </c>
       <c r="H951" t="n">
         <v>0</v>
@@ -27977,7 +27977,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G952" t="n">
-        <v>4.63109540939331</v>
+        <v>4.63109493255615</v>
       </c>
       <c r="H952" t="n">
         <v>250</v>
@@ -28006,7 +28006,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G953" t="n">
-        <v>4.63109540939331</v>
+        <v>4.63109493255615</v>
       </c>
       <c r="H953" t="n">
         <v>0</v>
@@ -28180,7 +28180,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G959" t="n">
-        <v>4.49823570251465</v>
+        <v>4.49823522567749</v>
       </c>
       <c r="H959" t="n">
         <v>1250</v>
@@ -28238,7 +28238,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G961" t="n">
-        <v>4.49823570251465</v>
+        <v>4.49823522567749</v>
       </c>
       <c r="H961" t="n">
         <v>1000</v>
@@ -28267,7 +28267,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G962" t="n">
-        <v>4.36537599563599</v>
+        <v>4.36537647247314</v>
       </c>
       <c r="H962" t="n">
         <v>1250</v>
@@ -28296,7 +28296,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G963" t="n">
-        <v>4.36537599563599</v>
+        <v>4.36537647247314</v>
       </c>
       <c r="H963" t="n">
         <v>2250</v>
@@ -28325,7 +28325,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G964" t="n">
-        <v>4.32741689682007</v>
+        <v>4.32741641998291</v>
       </c>
       <c r="H964" t="n">
         <v>1500</v>
@@ -28528,7 +28528,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G971" t="n">
-        <v>4.36537599563599</v>
+        <v>4.36537647247314</v>
       </c>
       <c r="H971" t="n">
         <v>7500</v>
@@ -28644,7 +28644,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G975" t="n">
-        <v>4.13761758804321</v>
+        <v>4.13761806488037</v>
       </c>
       <c r="H975" t="n">
         <v>2000</v>
@@ -28905,7 +28905,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G984" t="n">
-        <v>4.36537599563599</v>
+        <v>4.36537647247314</v>
       </c>
       <c r="H984" t="n">
         <v>1250</v>
@@ -28934,7 +28934,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G985" t="n">
-        <v>4.36537599563599</v>
+        <v>4.36537647247314</v>
       </c>
       <c r="H985" t="n">
         <v>1750</v>
@@ -28963,7 +28963,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G986" t="n">
-        <v>4.36537599563599</v>
+        <v>4.36537647247314</v>
       </c>
       <c r="H986" t="n">
         <v>5750</v>
@@ -28992,7 +28992,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G987" t="n">
-        <v>4.34639692306519</v>
+        <v>4.34639644622803</v>
       </c>
       <c r="H987" t="n">
         <v>750</v>
@@ -29050,7 +29050,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G989" t="n">
-        <v>4.32741689682007</v>
+        <v>4.32741641998291</v>
       </c>
       <c r="H989" t="n">
         <v>4250</v>
@@ -29079,7 +29079,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G990" t="n">
-        <v>4.36537599563599</v>
+        <v>4.36537647247314</v>
       </c>
       <c r="H990" t="n">
         <v>750</v>
@@ -29137,7 +29137,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G992" t="n">
-        <v>4.36537599563599</v>
+        <v>4.36537647247314</v>
       </c>
       <c r="H992" t="n">
         <v>4000</v>
@@ -29514,7 +29514,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.55517578125</v>
+        <v>4.55517530441284</v>
       </c>
       <c r="H1005" t="n">
         <v>500</v>
@@ -29572,7 +29572,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.57415580749512</v>
+        <v>4.57415533065796</v>
       </c>
       <c r="H1007" t="n">
         <v>18500</v>
@@ -29688,7 +29688,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.63109540939331</v>
+        <v>4.63109493255615</v>
       </c>
       <c r="H1011" t="n">
         <v>500</v>
@@ -30036,7 +30036,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.32741689682007</v>
+        <v>4.32741641998291</v>
       </c>
       <c r="H1023" t="n">
         <v>500</v>
@@ -30065,7 +30065,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.32741689682007</v>
+        <v>4.32741641998291</v>
       </c>
       <c r="H1024" t="n">
         <v>750</v>
@@ -30094,7 +30094,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.32741689682007</v>
+        <v>4.32741641998291</v>
       </c>
       <c r="H1025" t="n">
         <v>0</v>
@@ -30123,7 +30123,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.32741689682007</v>
+        <v>4.32741641998291</v>
       </c>
       <c r="H1026" t="n">
         <v>0</v>
@@ -30152,7 +30152,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.32741689682007</v>
+        <v>4.32741641998291</v>
       </c>
       <c r="H1027" t="n">
         <v>0</v>
@@ -30210,7 +30210,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.13761758804321</v>
+        <v>4.13761806488037</v>
       </c>
       <c r="H1029" t="n">
         <v>2000</v>
@@ -30239,7 +30239,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1030" t="n">
-        <v>4.1186375617981</v>
+        <v>4.11863803863525</v>
       </c>
       <c r="H1030" t="n">
         <v>1250</v>
@@ -30384,7 +30384,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.85291934013367</v>
+        <v>3.85291910171509</v>
       </c>
       <c r="H1035" t="n">
         <v>7500</v>
@@ -30587,7 +30587,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.08067798614502</v>
+        <v>4.08067846298218</v>
       </c>
       <c r="H1042" t="n">
         <v>750</v>
@@ -30790,7 +30790,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.08067798614502</v>
+        <v>4.08067846298218</v>
       </c>
       <c r="H1049" t="n">
         <v>250</v>
@@ -30819,7 +30819,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.08067798614502</v>
+        <v>4.08067846298218</v>
       </c>
       <c r="H1050" t="n">
         <v>0</v>
@@ -30848,7 +30848,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.08067798614502</v>
+        <v>4.08067846298218</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -30906,7 +30906,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1053" t="n">
-        <v>4.08067798614502</v>
+        <v>4.08067846298218</v>
       </c>
       <c r="H1053" t="n">
         <v>4500</v>
@@ -30993,7 +30993,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.94781851768494</v>
+        <v>3.94781875610352</v>
       </c>
       <c r="H1056" t="n">
         <v>1750</v>
@@ -31022,7 +31022,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.94781851768494</v>
+        <v>3.94781875610352</v>
       </c>
       <c r="H1057" t="n">
         <v>0</v>
@@ -31138,7 +31138,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.89087891578674</v>
+        <v>3.89087915420532</v>
       </c>
       <c r="H1061" t="n">
         <v>5750</v>
@@ -31225,7 +31225,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.60618042945862</v>
+        <v>3.6061806678772</v>
       </c>
       <c r="H1064" t="n">
         <v>3750</v>
@@ -31747,7 +31747,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.5872004032135</v>
+        <v>3.58720064163208</v>
       </c>
       <c r="H1082" t="n">
         <v>2750</v>
@@ -31921,7 +31921,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.60618042945862</v>
+        <v>3.6061806678772</v>
       </c>
       <c r="H1088" t="n">
         <v>500</v>
@@ -32037,7 +32037,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.81495952606201</v>
+        <v>3.81495928764343</v>
       </c>
       <c r="H1092" t="n">
         <v>19500</v>
@@ -32153,7 +32153,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1096" t="n">
-        <v>4.1186375617981</v>
+        <v>4.11863803863525</v>
       </c>
       <c r="H1096" t="n">
         <v>3750</v>
@@ -43266,6 +43266,64 @@
         <v>0</v>
       </c>
       <c r="I1479" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1480" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1480" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="D1480" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="E1480" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="F1480" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="G1480" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="H1480" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1480" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1481" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1481" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="D1481" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="E1481" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F1481" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="G1481" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="H1481" t="n">
+        <v>5750</v>
+      </c>
+      <c r="I1481" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PLN.MI.xlsx
+++ b/data/PLN.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.41200017929077</v>
       </c>
       <c r="G2" t="n">
-        <v>4.05409336090088</v>
+        <v>4.05409288406372</v>
       </c>
       <c r="H2" t="n">
         <v>42000</v>
@@ -456,7 +456,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1165771484375</v>
+        <v>4.11657667160034</v>
       </c>
       <c r="H3" t="n">
         <v>8500</v>
@@ -514,7 +514,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G5" t="n">
-        <v>4.22684192657471</v>
+        <v>4.22684240341187</v>
       </c>
       <c r="H5" t="n">
         <v>12000</v>
@@ -543,7 +543,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G6" t="n">
-        <v>4.21765375137329</v>
+        <v>4.21765327453613</v>
       </c>
       <c r="H6" t="n">
         <v>37000</v>
@@ -572,7 +572,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G7" t="n">
-        <v>4.19927549362183</v>
+        <v>4.19927644729614</v>
       </c>
       <c r="H7" t="n">
         <v>11500</v>
@@ -601,7 +601,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G8" t="n">
-        <v>4.15333223342896</v>
+        <v>4.1533317565918</v>
       </c>
       <c r="H8" t="n">
         <v>6500</v>
@@ -688,7 +688,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G11" t="n">
-        <v>4.03387689590454</v>
+        <v>4.03387784957886</v>
       </c>
       <c r="H11" t="n">
         <v>12000</v>
@@ -717,7 +717,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G12" t="n">
-        <v>3.96955585479736</v>
+        <v>3.96955633163452</v>
       </c>
       <c r="H12" t="n">
         <v>26000</v>
@@ -746,7 +746,7 @@
         <v>4.25</v>
       </c>
       <c r="G13" t="n">
-        <v>3.90523433685303</v>
+        <v>3.90523457527161</v>
       </c>
       <c r="H13" t="n">
         <v>19500</v>
@@ -804,7 +804,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G15" t="n">
-        <v>3.89604544639587</v>
+        <v>3.89604592323303</v>
       </c>
       <c r="H15" t="n">
         <v>12500</v>
@@ -949,7 +949,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G20" t="n">
-        <v>3.87766790390015</v>
+        <v>3.87766814231873</v>
       </c>
       <c r="H20" t="n">
         <v>12000</v>
@@ -978,7 +978,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G21" t="n">
-        <v>3.87766790390015</v>
+        <v>3.87766814231873</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G22" t="n">
-        <v>3.87766790390015</v>
+        <v>3.87766814231873</v>
       </c>
       <c r="H22" t="n">
         <v>60000</v>
@@ -1036,7 +1036,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G23" t="n">
-        <v>3.85010194778442</v>
+        <v>3.850102186203</v>
       </c>
       <c r="H23" t="n">
         <v>32000</v>
@@ -1065,7 +1065,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G24" t="n">
-        <v>3.88685727119446</v>
+        <v>3.8868567943573</v>
       </c>
       <c r="H24" t="n">
         <v>500</v>
@@ -1123,7 +1123,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G26" t="n">
-        <v>4.18089866638184</v>
+        <v>4.18089818954468</v>
       </c>
       <c r="H26" t="n">
         <v>15000</v>
@@ -1181,7 +1181,7 @@
         <v>4.5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.13495397567749</v>
+        <v>4.13495445251465</v>
       </c>
       <c r="H28" t="n">
         <v>28500</v>
@@ -1210,7 +1210,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G29" t="n">
-        <v>4.20846462249756</v>
+        <v>4.2084641456604</v>
       </c>
       <c r="H29" t="n">
         <v>24500</v>
@@ -1239,7 +1239,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G30" t="n">
-        <v>4.18089866638184</v>
+        <v>4.18089818954468</v>
       </c>
       <c r="H30" t="n">
         <v>3500</v>
@@ -1268,7 +1268,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G31" t="n">
-        <v>4.15333223342896</v>
+        <v>4.1533317565918</v>
       </c>
       <c r="H31" t="n">
         <v>9000</v>
@@ -1326,7 +1326,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>4.15333223342896</v>
+        <v>4.1533317565918</v>
       </c>
       <c r="H33" t="n">
         <v>2000</v>
@@ -1384,7 +1384,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>4.1165771484375</v>
+        <v>4.11657667160034</v>
       </c>
       <c r="H35" t="n">
         <v>27500</v>
@@ -1413,7 +1413,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G36" t="n">
-        <v>4.06144380569458</v>
+        <v>4.06144428253174</v>
       </c>
       <c r="H36" t="n">
         <v>18500</v>
@@ -1442,7 +1442,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G37" t="n">
-        <v>4.05225515365601</v>
+        <v>4.05225467681885</v>
       </c>
       <c r="H37" t="n">
         <v>2000</v>
@@ -1471,7 +1471,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G38" t="n">
-        <v>4.05225515365601</v>
+        <v>4.05225467681885</v>
       </c>
       <c r="H38" t="n">
         <v>11500</v>
@@ -1500,7 +1500,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G39" t="n">
-        <v>4.09819841384888</v>
+        <v>4.09819936752319</v>
       </c>
       <c r="H39" t="n">
         <v>3500</v>
@@ -1529,7 +1529,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>4.09819841384888</v>
+        <v>4.09819936752319</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>4.08901071548462</v>
+        <v>4.08901023864746</v>
       </c>
       <c r="H43" t="n">
         <v>2000</v>
@@ -1645,7 +1645,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>4.08901071548462</v>
+        <v>4.08901023864746</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G45" t="n">
-        <v>4.03387689590454</v>
+        <v>4.03387784957886</v>
       </c>
       <c r="H45" t="n">
         <v>12500</v>
@@ -1732,7 +1732,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G47" t="n">
-        <v>3.99712252616882</v>
+        <v>3.99712228775024</v>
       </c>
       <c r="H47" t="n">
         <v>3000</v>
@@ -1848,7 +1848,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G51" t="n">
-        <v>3.89604544639587</v>
+        <v>3.89604592323303</v>
       </c>
       <c r="H51" t="n">
         <v>31000</v>
@@ -1906,7 +1906,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G53" t="n">
-        <v>3.89604544639587</v>
+        <v>3.89604592323303</v>
       </c>
       <c r="H53" t="n">
         <v>11000</v>
@@ -1993,7 +1993,7 @@
         <v>4.25</v>
       </c>
       <c r="G56" t="n">
-        <v>3.90523433685303</v>
+        <v>3.90523457527161</v>
       </c>
       <c r="H56" t="n">
         <v>7500</v>
@@ -2022,7 +2022,7 @@
         <v>4.25</v>
       </c>
       <c r="G57" t="n">
-        <v>3.90523433685303</v>
+        <v>3.90523457527161</v>
       </c>
       <c r="H57" t="n">
         <v>3000</v>
@@ -2109,7 +2109,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G60" t="n">
-        <v>4.03387689590454</v>
+        <v>4.03387784957886</v>
       </c>
       <c r="H60" t="n">
         <v>1000</v>
@@ -2138,7 +2138,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G61" t="n">
-        <v>3.99712252616882</v>
+        <v>3.99712228775024</v>
       </c>
       <c r="H61" t="n">
         <v>7000</v>
@@ -2225,7 +2225,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G64" t="n">
-        <v>4.05225515365601</v>
+        <v>4.05225467681885</v>
       </c>
       <c r="H64" t="n">
         <v>26000</v>
@@ -2283,7 +2283,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G66" t="n">
-        <v>4.16252040863037</v>
+        <v>4.16252088546753</v>
       </c>
       <c r="H66" t="n">
         <v>21000</v>
@@ -2341,7 +2341,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G68" t="n">
-        <v>4.263596534729</v>
+        <v>4.26359701156616</v>
       </c>
       <c r="H68" t="n">
         <v>12500</v>
@@ -2428,7 +2428,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G71" t="n">
-        <v>4.48412847518921</v>
+        <v>4.48412799835205</v>
       </c>
       <c r="H71" t="n">
         <v>24000</v>
@@ -2457,7 +2457,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G72" t="n">
-        <v>4.66790437698364</v>
+        <v>4.66790390014648</v>
       </c>
       <c r="H72" t="n">
         <v>16500</v>
@@ -2486,7 +2486,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G73" t="n">
-        <v>4.72303628921509</v>
+        <v>4.72303676605225</v>
       </c>
       <c r="H73" t="n">
         <v>3000</v>
@@ -2515,7 +2515,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G74" t="n">
-        <v>4.8149242401123</v>
+        <v>4.81492471694946</v>
       </c>
       <c r="H74" t="n">
         <v>1500</v>
@@ -2544,7 +2544,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>4.61277103424072</v>
+        <v>4.61277151107788</v>
       </c>
       <c r="H75" t="n">
         <v>9500</v>
@@ -2602,7 +2602,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G77" t="n">
-        <v>4.52088308334351</v>
+        <v>4.52088356018066</v>
       </c>
       <c r="H77" t="n">
         <v>500</v>
@@ -2660,7 +2660,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G79" t="n">
-        <v>4.8149242401123</v>
+        <v>4.81492471694946</v>
       </c>
       <c r="H79" t="n">
         <v>11500</v>
@@ -2747,7 +2747,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G82" t="n">
-        <v>4.77816915512085</v>
+        <v>4.77816963195801</v>
       </c>
       <c r="H82" t="n">
         <v>3500</v>
@@ -2834,7 +2834,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G85" t="n">
-        <v>4.96194553375244</v>
+        <v>4.96194505691528</v>
       </c>
       <c r="H85" t="n">
         <v>27000</v>
@@ -2892,7 +2892,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G87" t="n">
-        <v>5.311119556427</v>
+        <v>5.31111860275269</v>
       </c>
       <c r="H87" t="n">
         <v>23500</v>
@@ -2950,7 +2950,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G89" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H89" t="n">
         <v>78500</v>
@@ -3008,7 +3008,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G91" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H91" t="n">
         <v>34500</v>
@@ -3037,7 +3037,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G92" t="n">
-        <v>6.26675271987915</v>
+        <v>6.26675319671631</v>
       </c>
       <c r="H92" t="n">
         <v>23000</v>
@@ -3095,7 +3095,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G94" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H94" t="n">
         <v>29500</v>
@@ -3124,7 +3124,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G95" t="n">
-        <v>6.32188558578491</v>
+        <v>6.32188606262207</v>
       </c>
       <c r="H95" t="n">
         <v>57500</v>
@@ -3240,7 +3240,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G99" t="n">
-        <v>6.08297729492188</v>
+        <v>6.08297681808472</v>
       </c>
       <c r="H99" t="n">
         <v>19500</v>
@@ -3298,7 +3298,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>5.99108982086182</v>
+        <v>5.9910888671875</v>
       </c>
       <c r="H101" t="n">
         <v>7000</v>
@@ -3385,7 +3385,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G104" t="n">
-        <v>6.02784442901611</v>
+        <v>6.02784395217896</v>
       </c>
       <c r="H104" t="n">
         <v>15000</v>
@@ -3501,7 +3501,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>6.04622173309326</v>
+        <v>6.04622220993042</v>
       </c>
       <c r="H108" t="n">
         <v>12500</v>
@@ -3588,7 +3588,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G111" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H111" t="n">
         <v>3500</v>
@@ -3646,7 +3646,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>5.88082361221313</v>
+        <v>5.88082408905029</v>
       </c>
       <c r="H113" t="n">
         <v>500</v>
@@ -3675,7 +3675,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G114" t="n">
-        <v>5.88082361221313</v>
+        <v>5.88082408905029</v>
       </c>
       <c r="H114" t="n">
         <v>500</v>
@@ -3936,7 +3936,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G123" t="n">
-        <v>5.23760890960693</v>
+        <v>5.23760843276978</v>
       </c>
       <c r="H123" t="n">
         <v>13000</v>
@@ -3965,7 +3965,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G124" t="n">
-        <v>5.32949686050415</v>
+        <v>5.32949733734131</v>
       </c>
       <c r="H124" t="n">
         <v>500</v>
@@ -4081,7 +4081,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G128" t="n">
-        <v>5.56840515136719</v>
+        <v>5.56840467453003</v>
       </c>
       <c r="H128" t="n">
         <v>10500</v>
@@ -4110,7 +4110,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G129" t="n">
-        <v>5.43976259231567</v>
+        <v>5.43976211547852</v>
       </c>
       <c r="H129" t="n">
         <v>500</v>
@@ -4139,7 +4139,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G130" t="n">
-        <v>5.49489450454712</v>
+        <v>5.49489498138428</v>
       </c>
       <c r="H130" t="n">
         <v>500</v>
@@ -4168,7 +4168,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G131" t="n">
-        <v>5.43976259231567</v>
+        <v>5.43976211547852</v>
       </c>
       <c r="H131" t="n">
         <v>3500</v>
@@ -4313,7 +4313,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>5.55002737045288</v>
+        <v>5.55002784729004</v>
       </c>
       <c r="H136" t="n">
         <v>7000</v>
@@ -4342,7 +4342,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>5.55002737045288</v>
+        <v>5.55002784729004</v>
       </c>
       <c r="H137" t="n">
         <v>1000</v>
@@ -4371,7 +4371,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G138" t="n">
-        <v>5.55002737045288</v>
+        <v>5.55002784729004</v>
       </c>
       <c r="H138" t="n">
         <v>3000</v>
@@ -4400,7 +4400,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G139" t="n">
-        <v>5.55002737045288</v>
+        <v>5.55002784729004</v>
       </c>
       <c r="H139" t="n">
         <v>10500</v>
@@ -4429,7 +4429,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H140" t="n">
         <v>2000</v>
@@ -4458,7 +4458,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G141" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G142" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G143" t="n">
-        <v>5.88082361221313</v>
+        <v>5.88082408905029</v>
       </c>
       <c r="H143" t="n">
         <v>5500</v>
@@ -4545,7 +4545,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G144" t="n">
-        <v>5.66029262542725</v>
+        <v>5.6602931022644</v>
       </c>
       <c r="H144" t="n">
         <v>2500</v>
@@ -4632,7 +4632,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>5.88082361221313</v>
+        <v>5.88082408905029</v>
       </c>
       <c r="H147" t="n">
         <v>5000</v>
@@ -4661,7 +4661,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G148" t="n">
-        <v>5.88082361221313</v>
+        <v>5.88082408905029</v>
       </c>
       <c r="H148" t="n">
         <v>500</v>
@@ -4777,7 +4777,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G152" t="n">
-        <v>6.02784442901611</v>
+        <v>6.02784395217896</v>
       </c>
       <c r="H152" t="n">
         <v>6000</v>
@@ -5183,7 +5183,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>6.56079435348511</v>
+        <v>6.56079387664795</v>
       </c>
       <c r="H166" t="n">
         <v>2500</v>
@@ -5386,7 +5386,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G173" t="n">
-        <v>6.46890687942505</v>
+        <v>6.46890640258789</v>
       </c>
       <c r="H173" t="n">
         <v>2000</v>
@@ -5415,7 +5415,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G174" t="n">
-        <v>6.39539623260498</v>
+        <v>6.39539575576782</v>
       </c>
       <c r="H174" t="n">
         <v>4500</v>
@@ -5502,7 +5502,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G177" t="n">
-        <v>7.27751922607422</v>
+        <v>7.27751970291138</v>
       </c>
       <c r="H177" t="n">
         <v>28000</v>
@@ -5531,7 +5531,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G178" t="n">
-        <v>7.20400905609131</v>
+        <v>7.20400953292847</v>
       </c>
       <c r="H178" t="n">
         <v>25000</v>
@@ -5560,7 +5560,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H179" t="n">
         <v>1500</v>
@@ -5589,7 +5589,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5618,7 +5618,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H181" t="n">
         <v>1500</v>
@@ -5647,7 +5647,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G182" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H182" t="n">
         <v>2500</v>
@@ -5676,7 +5676,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G187" t="n">
-        <v>7.05698823928833</v>
+        <v>7.05698871612549</v>
       </c>
       <c r="H187" t="n">
         <v>5500</v>
@@ -5850,7 +5850,7 @@
         <v>8</v>
       </c>
       <c r="G189" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H189" t="n">
         <v>3500</v>
@@ -5908,7 +5908,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G191" t="n">
-        <v>7.14887666702271</v>
+        <v>7.14887714385986</v>
       </c>
       <c r="H191" t="n">
         <v>1000</v>
@@ -5937,7 +5937,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G192" t="n">
-        <v>7.36940765380859</v>
+        <v>7.36940813064575</v>
       </c>
       <c r="H192" t="n">
         <v>4000</v>
@@ -6024,7 +6024,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G195" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H195" t="n">
         <v>12000</v>
@@ -6227,7 +6227,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G202" t="n">
-        <v>7.70020389556885</v>
+        <v>7.70020437240601</v>
       </c>
       <c r="H202" t="n">
         <v>6500</v>
@@ -6256,7 +6256,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G203" t="n">
-        <v>7.70020389556885</v>
+        <v>7.70020437240601</v>
       </c>
       <c r="H203" t="n">
         <v>3000</v>
@@ -6285,7 +6285,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G204" t="n">
-        <v>7.79209089279175</v>
+        <v>7.79209184646606</v>
       </c>
       <c r="H204" t="n">
         <v>6500</v>
@@ -6314,7 +6314,7 @@
         <v>8.5</v>
       </c>
       <c r="G205" t="n">
-        <v>7.81046867370605</v>
+        <v>7.81046915054321</v>
       </c>
       <c r="H205" t="n">
         <v>6500</v>
@@ -6343,7 +6343,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G206" t="n">
-        <v>8.12288761138916</v>
+        <v>8.12288856506348</v>
       </c>
       <c r="H206" t="n">
         <v>16500</v>
@@ -6372,7 +6372,7 @@
         <v>9</v>
       </c>
       <c r="G207" t="n">
-        <v>8.26990795135498</v>
+        <v>8.2699089050293</v>
       </c>
       <c r="H207" t="n">
         <v>3000</v>
@@ -6459,7 +6459,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G210" t="n">
-        <v>8.01262283325195</v>
+        <v>8.01262378692627</v>
       </c>
       <c r="H210" t="n">
         <v>3500</v>
@@ -6488,7 +6488,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G211" t="n">
-        <v>8.15964317321777</v>
+        <v>8.15964221954346</v>
       </c>
       <c r="H211" t="n">
         <v>8000</v>
@@ -6517,7 +6517,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G212" t="n">
-        <v>8.12288761138916</v>
+        <v>8.12288856506348</v>
       </c>
       <c r="H212" t="n">
         <v>500</v>
@@ -6604,7 +6604,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G215" t="n">
-        <v>8.41692924499512</v>
+        <v>8.4169282913208</v>
       </c>
       <c r="H215" t="n">
         <v>1000</v>
@@ -6633,7 +6633,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G216" t="n">
-        <v>8.54557228088379</v>
+        <v>8.54557132720947</v>
       </c>
       <c r="H216" t="n">
         <v>2500</v>
@@ -6691,7 +6691,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G218" t="n">
-        <v>8.69259357452393</v>
+        <v>8.69259262084961</v>
       </c>
       <c r="H218" t="n">
         <v>3000</v>
@@ -6749,7 +6749,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>8.69259357452393</v>
+        <v>8.69259262084961</v>
       </c>
       <c r="H220" t="n">
         <v>3500</v>
@@ -6778,7 +6778,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>8.69259357452393</v>
+        <v>8.69259262084961</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G224" t="n">
-        <v>8.8212366104126</v>
+        <v>8.82123565673828</v>
       </c>
       <c r="H224" t="n">
         <v>2000</v>
@@ -6894,7 +6894,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.8212366104126</v>
+        <v>8.82123565673828</v>
       </c>
       <c r="H225" t="n">
         <v>3500</v>
@@ -6923,7 +6923,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G226" t="n">
-        <v>8.76610374450684</v>
+        <v>8.76610279083252</v>
       </c>
       <c r="H226" t="n">
         <v>500</v>
@@ -6952,7 +6952,7 @@
         <v>9.5</v>
       </c>
       <c r="G227" t="n">
-        <v>8.72934722900391</v>
+        <v>8.72934818267822</v>
       </c>
       <c r="H227" t="n">
         <v>4500</v>
@@ -6981,7 +6981,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G228" t="n">
-        <v>8.63746070861816</v>
+        <v>8.63745975494385</v>
       </c>
       <c r="H228" t="n">
         <v>20000</v>
@@ -7010,7 +7010,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G229" t="n">
-        <v>8.63746070861816</v>
+        <v>8.63745975494385</v>
       </c>
       <c r="H229" t="n">
         <v>12500</v>
@@ -7039,7 +7039,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G230" t="n">
-        <v>8.63746070861816</v>
+        <v>8.63745975494385</v>
       </c>
       <c r="H230" t="n">
         <v>7000</v>
@@ -7126,7 +7126,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G233" t="n">
-        <v>8.63746070861816</v>
+        <v>8.63745975494385</v>
       </c>
       <c r="H233" t="n">
         <v>11000</v>
@@ -7155,7 +7155,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G234" t="n">
-        <v>8.54557228088379</v>
+        <v>8.54557132720947</v>
       </c>
       <c r="H234" t="n">
         <v>4500</v>
@@ -7184,7 +7184,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>8.54557228088379</v>
+        <v>8.54557132720947</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G236" t="n">
-        <v>8.14126491546631</v>
+        <v>8.14126586914062</v>
       </c>
       <c r="H236" t="n">
         <v>6500</v>
@@ -7242,7 +7242,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>8.233154296875</v>
+        <v>8.23315334320068</v>
       </c>
       <c r="H237" t="n">
         <v>8500</v>
@@ -7300,7 +7300,7 @@
         <v>9</v>
       </c>
       <c r="G239" t="n">
-        <v>8.26990795135498</v>
+        <v>8.2699089050293</v>
       </c>
       <c r="H239" t="n">
         <v>3000</v>
@@ -7474,7 +7474,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G245" t="n">
-        <v>8.36179733276367</v>
+        <v>8.36179637908936</v>
       </c>
       <c r="H245" t="n">
         <v>500</v>
@@ -7503,7 +7503,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G246" t="n">
-        <v>8.36179733276367</v>
+        <v>8.36179637908936</v>
       </c>
       <c r="H246" t="n">
         <v>1500</v>
@@ -7532,7 +7532,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>8.54557228088379</v>
+        <v>8.54557132720947</v>
       </c>
       <c r="H247" t="n">
         <v>7500</v>
@@ -7561,7 +7561,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G248" t="n">
-        <v>8.63746070861816</v>
+        <v>8.63745975494385</v>
       </c>
       <c r="H248" t="n">
         <v>7500</v>
@@ -7590,7 +7590,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G249" t="n">
-        <v>8.45368385314941</v>
+        <v>8.45368480682373</v>
       </c>
       <c r="H249" t="n">
         <v>1000</v>
@@ -7619,7 +7619,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G250" t="n">
-        <v>8.49043941497803</v>
+        <v>8.49043846130371</v>
       </c>
       <c r="H250" t="n">
         <v>500</v>
@@ -7648,7 +7648,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G251" t="n">
-        <v>8.54557228088379</v>
+        <v>8.54557132720947</v>
       </c>
       <c r="H251" t="n">
         <v>6000</v>
@@ -7677,7 +7677,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G252" t="n">
-        <v>8.54557228088379</v>
+        <v>8.54557132720947</v>
       </c>
       <c r="H252" t="n">
         <v>500</v>
@@ -7706,7 +7706,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G253" t="n">
-        <v>8.71096897125244</v>
+        <v>8.71096992492676</v>
       </c>
       <c r="H253" t="n">
         <v>10500</v>
@@ -7735,7 +7735,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G254" t="n">
-        <v>8.71096897125244</v>
+        <v>8.71096992492676</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G255" t="n">
-        <v>8.71096897125244</v>
+        <v>8.71096992492676</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
         <v>9.5</v>
       </c>
       <c r="G256" t="n">
-        <v>8.72934722900391</v>
+        <v>8.72934818267822</v>
       </c>
       <c r="H256" t="n">
         <v>500</v>
@@ -7822,7 +7822,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G257" t="n">
-        <v>8.87636852264404</v>
+        <v>8.87636756896973</v>
       </c>
       <c r="H257" t="n">
         <v>4000</v>
@@ -7938,7 +7938,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G261" t="n">
-        <v>8.98663330078125</v>
+        <v>8.98663425445557</v>
       </c>
       <c r="H261" t="n">
         <v>1000</v>
@@ -7967,7 +7967,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G262" t="n">
-        <v>8.98663330078125</v>
+        <v>8.98663425445557</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G264" t="n">
-        <v>8.69259357452393</v>
+        <v>8.69259262084961</v>
       </c>
       <c r="H264" t="n">
         <v>7000</v>
@@ -8054,7 +8054,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>8.69259357452393</v>
+        <v>8.69259262084961</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>9.5</v>
       </c>
       <c r="G266" t="n">
-        <v>8.72934722900391</v>
+        <v>8.72934818267822</v>
       </c>
       <c r="H266" t="n">
         <v>3000</v>
@@ -8112,7 +8112,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G267" t="n">
-        <v>8.69259357452393</v>
+        <v>8.69259262084961</v>
       </c>
       <c r="H267" t="n">
         <v>5500</v>
@@ -8141,7 +8141,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G268" t="n">
-        <v>8.50881862640381</v>
+        <v>8.50881767272949</v>
       </c>
       <c r="H268" t="n">
         <v>8500</v>
@@ -8228,7 +8228,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G271" t="n">
-        <v>8.39855098724365</v>
+        <v>8.39855289459229</v>
       </c>
       <c r="H271" t="n">
         <v>5000</v>
@@ -8257,7 +8257,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G272" t="n">
-        <v>7.47967290878296</v>
+        <v>7.47967338562012</v>
       </c>
       <c r="H272" t="n">
         <v>11000</v>
@@ -8315,7 +8315,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>7.5348048210144</v>
+        <v>7.53480577468872</v>
       </c>
       <c r="H274" t="n">
         <v>3000</v>
@@ -8344,7 +8344,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G275" t="n">
-        <v>7.13049936294556</v>
+        <v>7.1304988861084</v>
       </c>
       <c r="H275" t="n">
         <v>13500</v>
@@ -8431,7 +8431,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G278" t="n">
-        <v>7.66344785690308</v>
+        <v>7.66344881057739</v>
       </c>
       <c r="H278" t="n">
         <v>3000</v>
@@ -8518,7 +8518,7 @@
         <v>8</v>
       </c>
       <c r="G281" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H281" t="n">
         <v>3000</v>
@@ -8547,7 +8547,7 @@
         <v>8</v>
       </c>
       <c r="G282" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>8</v>
       </c>
       <c r="G283" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H283" t="n">
         <v>7500</v>
@@ -8692,7 +8692,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G287" t="n">
-        <v>7.27751922607422</v>
+        <v>7.27751970291138</v>
       </c>
       <c r="H287" t="n">
         <v>3500</v>
@@ -8750,7 +8750,7 @@
         <v>8</v>
       </c>
       <c r="G289" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H289" t="n">
         <v>1500</v>
@@ -8779,7 +8779,7 @@
         <v>8</v>
       </c>
       <c r="G290" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H290" t="n">
         <v>9000</v>
@@ -8808,7 +8808,7 @@
         <v>8</v>
       </c>
       <c r="G291" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H291" t="n">
         <v>1500</v>
@@ -8837,7 +8837,7 @@
         <v>8</v>
       </c>
       <c r="G292" t="n">
-        <v>7.35102987289429</v>
+        <v>7.35102939605713</v>
       </c>
       <c r="H292" t="n">
         <v>3000</v>
@@ -8982,7 +8982,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>6.79970264434814</v>
+        <v>6.79970216751099</v>
       </c>
       <c r="H297" t="n">
         <v>3500</v>
@@ -9011,7 +9011,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>6.98347806930542</v>
+        <v>6.98347854614258</v>
       </c>
       <c r="H298" t="n">
         <v>7000</v>
@@ -9040,7 +9040,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>6.98347806930542</v>
+        <v>6.98347854614258</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>6.98347806930542</v>
+        <v>6.98347854614258</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G301" t="n">
-        <v>6.98347806930542</v>
+        <v>6.98347854614258</v>
       </c>
       <c r="H301" t="n">
         <v>18500</v>
@@ -9272,7 +9272,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G307" t="n">
-        <v>7.16725444793701</v>
+        <v>7.16725397109985</v>
       </c>
       <c r="H307" t="n">
         <v>500</v>
@@ -9301,7 +9301,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G308" t="n">
-        <v>6.72619247436523</v>
+        <v>6.72619199752808</v>
       </c>
       <c r="H308" t="n">
         <v>5000</v>
@@ -9330,7 +9330,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G309" t="n">
-        <v>7.05698823928833</v>
+        <v>7.05698871612549</v>
       </c>
       <c r="H309" t="n">
         <v>1000</v>
@@ -9417,7 +9417,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G312" t="n">
-        <v>7.5348048210144</v>
+        <v>7.53480577468872</v>
       </c>
       <c r="H312" t="n">
         <v>2000</v>
@@ -9678,7 +9678,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G321" t="n">
-        <v>7.22238683700562</v>
+        <v>7.22238636016846</v>
       </c>
       <c r="H321" t="n">
         <v>500</v>
@@ -9707,7 +9707,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G322" t="n">
-        <v>7.22238683700562</v>
+        <v>7.22238636016846</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G323" t="n">
-        <v>7.22238683700562</v>
+        <v>7.22238636016846</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G324" t="n">
-        <v>7.22238683700562</v>
+        <v>7.22238636016846</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G328" t="n">
-        <v>6.98347806930542</v>
+        <v>6.98347854614258</v>
       </c>
       <c r="H328" t="n">
         <v>1000</v>
@@ -9910,7 +9910,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G329" t="n">
-        <v>6.79970264434814</v>
+        <v>6.79970216751099</v>
       </c>
       <c r="H329" t="n">
         <v>1000</v>
@@ -9939,7 +9939,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G330" t="n">
-        <v>7.02023267745972</v>
+        <v>7.02023363113403</v>
       </c>
       <c r="H330" t="n">
         <v>500</v>
@@ -9968,7 +9968,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G331" t="n">
-        <v>7.02023267745972</v>
+        <v>7.02023363113403</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G332" t="n">
-        <v>7.02023267745972</v>
+        <v>7.02023363113403</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G333" t="n">
-        <v>7.02023267745972</v>
+        <v>7.02023363113403</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>6.79970264434814</v>
+        <v>6.79970216751099</v>
       </c>
       <c r="H337" t="n">
         <v>500</v>
@@ -10171,7 +10171,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>6.79970264434814</v>
+        <v>6.79970216751099</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G341" t="n">
-        <v>6.15648698806763</v>
+        <v>6.15648746490479</v>
       </c>
       <c r="H341" t="n">
         <v>1000</v>
@@ -10287,7 +10287,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G342" t="n">
-        <v>6.15648698806763</v>
+        <v>6.15648746490479</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -10316,7 +10316,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G343" t="n">
-        <v>6.02784442901611</v>
+        <v>6.02784395217896</v>
       </c>
       <c r="H343" t="n">
         <v>9500</v>
@@ -10345,7 +10345,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G344" t="n">
-        <v>6.26675271987915</v>
+        <v>6.26675319671631</v>
       </c>
       <c r="H344" t="n">
         <v>1000</v>
@@ -10374,7 +10374,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G345" t="n">
-        <v>6.26675271987915</v>
+        <v>6.26675319671631</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G346" t="n">
-        <v>6.04622173309326</v>
+        <v>6.04622220993042</v>
       </c>
       <c r="H346" t="n">
         <v>1000</v>
@@ -10432,7 +10432,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G347" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H347" t="n">
         <v>1000</v>
@@ -10461,7 +10461,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G348" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -10490,7 +10490,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G349" t="n">
-        <v>6.21162033081055</v>
+        <v>6.21162080764771</v>
       </c>
       <c r="H349" t="n">
         <v>1500</v>
@@ -10519,7 +10519,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G350" t="n">
-        <v>6.04622173309326</v>
+        <v>6.04622220993042</v>
       </c>
       <c r="H350" t="n">
         <v>1000</v>
@@ -10548,7 +10548,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>5.99108982086182</v>
+        <v>5.9910888671875</v>
       </c>
       <c r="H351" t="n">
         <v>14500</v>
@@ -10577,7 +10577,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G352" t="n">
-        <v>5.99108982086182</v>
+        <v>5.9910888671875</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G366" t="n">
-        <v>6.15648698806763</v>
+        <v>6.15648746490479</v>
       </c>
       <c r="H366" t="n">
         <v>6500</v>
@@ -11128,7 +11128,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G371" t="n">
-        <v>6.21162033081055</v>
+        <v>6.21162080764771</v>
       </c>
       <c r="H371" t="n">
         <v>4000</v>
@@ -11157,7 +11157,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G372" t="n">
-        <v>6.21162033081055</v>
+        <v>6.21162080764771</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G373" t="n">
-        <v>6.21162033081055</v>
+        <v>6.21162080764771</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G374" t="n">
-        <v>6.21162033081055</v>
+        <v>6.21162080764771</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G375" t="n">
-        <v>6.15648698806763</v>
+        <v>6.15648746490479</v>
       </c>
       <c r="H375" t="n">
         <v>500</v>
@@ -11273,7 +11273,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G376" t="n">
-        <v>6.04622173309326</v>
+        <v>6.04622220993042</v>
       </c>
       <c r="H376" t="n">
         <v>3000</v>
@@ -11302,7 +11302,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>6.04622173309326</v>
+        <v>6.04622220993042</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11621,7 +11621,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G388" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H388" t="n">
         <v>1000</v>
@@ -11824,7 +11824,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G395" t="n">
-        <v>5.80731391906738</v>
+        <v>5.80731344223022</v>
       </c>
       <c r="H395" t="n">
         <v>1500</v>
@@ -11853,7 +11853,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G396" t="n">
-        <v>5.80731391906738</v>
+        <v>5.80731344223022</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G397" t="n">
-        <v>5.80731391906738</v>
+        <v>5.80731344223022</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G401" t="n">
-        <v>6.15648698806763</v>
+        <v>6.15648746490479</v>
       </c>
       <c r="H401" t="n">
         <v>2500</v>
@@ -12027,7 +12027,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G402" t="n">
-        <v>6.15648698806763</v>
+        <v>6.15648746490479</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G403" t="n">
-        <v>6.15648698806763</v>
+        <v>6.15648746490479</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -12085,7 +12085,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G404" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H404" t="n">
         <v>1000</v>
@@ -12114,7 +12114,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G405" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -12143,7 +12143,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G406" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G407" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -12201,7 +12201,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G408" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973142623901</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G431" t="n">
-        <v>6.21162033081055</v>
+        <v>6.21162080764771</v>
       </c>
       <c r="H431" t="n">
         <v>1000</v>
@@ -12897,7 +12897,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G432" t="n">
-        <v>6.08297729492188</v>
+        <v>6.08297681808472</v>
       </c>
       <c r="H432" t="n">
         <v>500</v>
@@ -12926,7 +12926,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>6.08297729492188</v>
+        <v>6.08297681808472</v>
       </c>
       <c r="H433" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G434" t="n">
-        <v>6.08297729492188</v>
+        <v>6.08297681808472</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G435" t="n">
-        <v>6.08297729492188</v>
+        <v>6.08297681808472</v>
       </c>
       <c r="H435" t="n">
         <v>0</v>
@@ -13013,7 +13013,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G436" t="n">
-        <v>6.08297729492188</v>
+        <v>6.08297681808472</v>
       </c>
       <c r="H436" t="n">
         <v>0</v>
@@ -13042,7 +13042,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G437" t="n">
-        <v>6.08297729492188</v>
+        <v>6.08297681808472</v>
       </c>
       <c r="H437" t="n">
         <v>0</v>
@@ -13129,7 +13129,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>6.15648698806763</v>
+        <v>6.15648746490479</v>
       </c>
       <c r="H440" t="n">
         <v>1000</v>
@@ -13158,7 +13158,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G441" t="n">
-        <v>6.32188558578491</v>
+        <v>6.32188606262207</v>
       </c>
       <c r="H441" t="n">
         <v>500</v>
@@ -13187,7 +13187,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G442" t="n">
-        <v>6.32188558578491</v>
+        <v>6.32188606262207</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G443" t="n">
-        <v>6.32188558578491</v>
+        <v>6.32188606262207</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G444" t="n">
-        <v>6.32188558578491</v>
+        <v>6.32188606262207</v>
       </c>
       <c r="H444" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G448" t="n">
-        <v>6.02784442901611</v>
+        <v>6.02784395217896</v>
       </c>
       <c r="H448" t="n">
         <v>1000</v>
@@ -13448,7 +13448,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G451" t="n">
-        <v>6.00946712493896</v>
+        <v>6.00946664810181</v>
       </c>
       <c r="H451" t="n">
         <v>500</v>
@@ -13477,7 +13477,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G452" t="n">
-        <v>5.88082361221313</v>
+        <v>5.88082408905029</v>
       </c>
       <c r="H452" t="n">
         <v>1000</v>
@@ -14115,7 +14115,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G474" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H474" t="n">
         <v>500</v>
@@ -14260,7 +14260,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G479" t="n">
-        <v>5.34787464141846</v>
+        <v>5.3478741645813</v>
       </c>
       <c r="H479" t="n">
         <v>7000</v>
@@ -14289,7 +14289,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G480" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H480" t="n">
         <v>1500</v>
@@ -14318,7 +14318,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G481" t="n">
-        <v>5.56840515136719</v>
+        <v>5.56840467453003</v>
       </c>
       <c r="H481" t="n">
         <v>1500</v>
@@ -14724,7 +14724,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G495" t="n">
-        <v>5.73380327224731</v>
+        <v>5.73380279541016</v>
       </c>
       <c r="H495" t="n">
         <v>2000</v>
@@ -14753,7 +14753,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G496" t="n">
-        <v>5.73380327224731</v>
+        <v>5.73380279541016</v>
       </c>
       <c r="H496" t="n">
         <v>0</v>
@@ -14782,7 +14782,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G497" t="n">
-        <v>5.73380327224731</v>
+        <v>5.73380279541016</v>
       </c>
       <c r="H497" t="n">
         <v>0</v>
@@ -14898,7 +14898,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G501" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H501" t="n">
         <v>500</v>
@@ -14927,7 +14927,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G502" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H502" t="n">
         <v>0</v>
@@ -14956,7 +14956,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G503" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H503" t="n">
         <v>0</v>
@@ -14985,7 +14985,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15014,7 +15014,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>5.36625194549561</v>
+        <v>5.36625242233276</v>
       </c>
       <c r="H505" t="n">
         <v>1000</v>
@@ -15043,7 +15043,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G506" t="n">
-        <v>5.32949686050415</v>
+        <v>5.32949733734131</v>
       </c>
       <c r="H506" t="n">
         <v>1000</v>
@@ -15072,7 +15072,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>5.32949686050415</v>
+        <v>5.32949733734131</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -15101,7 +15101,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>5.55002737045288</v>
+        <v>5.55002784729004</v>
       </c>
       <c r="H508" t="n">
         <v>500</v>
@@ -15275,7 +15275,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G514" t="n">
-        <v>5.55002737045288</v>
+        <v>5.55002784729004</v>
       </c>
       <c r="H514" t="n">
         <v>1000</v>
@@ -15478,7 +15478,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G521" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H521" t="n">
         <v>1000</v>
@@ -15942,7 +15942,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G537" t="n">
-        <v>5.66029262542725</v>
+        <v>5.6602931022644</v>
       </c>
       <c r="H537" t="n">
         <v>5000</v>
@@ -16261,7 +16261,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G548" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H548" t="n">
         <v>1500</v>
@@ -16290,7 +16290,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G549" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H549" t="n">
         <v>0</v>
@@ -16319,7 +16319,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G550" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -16348,7 +16348,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G551" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H551" t="n">
         <v>0</v>
@@ -16377,7 +16377,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G552" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H552" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G553" t="n">
-        <v>5.77055835723877</v>
+        <v>5.77055883407593</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G563" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H563" t="n">
         <v>500</v>
@@ -16725,7 +16725,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G564" t="n">
-        <v>5.27436399459839</v>
+        <v>5.27436351776123</v>
       </c>
       <c r="H564" t="n">
         <v>2500</v>
@@ -16841,7 +16841,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G568" t="n">
-        <v>5.43976259231567</v>
+        <v>5.43976211547852</v>
       </c>
       <c r="H568" t="n">
         <v>500</v>
@@ -17015,7 +17015,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G574" t="n">
-        <v>5.27436399459839</v>
+        <v>5.27436351776123</v>
       </c>
       <c r="H574" t="n">
         <v>4500</v>
@@ -17044,7 +17044,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G575" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H575" t="n">
         <v>500</v>
@@ -17073,7 +17073,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G576" t="n">
-        <v>5.45813941955566</v>
+        <v>5.45813989639282</v>
       </c>
       <c r="H576" t="n">
         <v>0</v>
@@ -17276,7 +17276,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G583" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H583" t="n">
         <v>1500</v>
@@ -17305,7 +17305,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G584" t="n">
-        <v>5.42138433456421</v>
+        <v>5.42138481140137</v>
       </c>
       <c r="H584" t="n">
         <v>0</v>
@@ -17421,7 +17421,7 @@
         <v>5.75</v>
       </c>
       <c r="G588" t="n">
-        <v>5.28355264663696</v>
+        <v>5.2835521697998</v>
       </c>
       <c r="H588" t="n">
         <v>2000</v>
@@ -17450,7 +17450,7 @@
         <v>5.75</v>
       </c>
       <c r="G589" t="n">
-        <v>5.28355264663696</v>
+        <v>5.2835521697998</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -17479,7 +17479,7 @@
         <v>5.75</v>
       </c>
       <c r="G590" t="n">
-        <v>5.28355264663696</v>
+        <v>5.2835521697998</v>
       </c>
       <c r="H590" t="n">
         <v>0</v>
@@ -17682,7 +17682,7 @@
         <v>5.75</v>
       </c>
       <c r="G597" t="n">
-        <v>5.28355264663696</v>
+        <v>5.2835521697998</v>
       </c>
       <c r="H597" t="n">
         <v>1000</v>
@@ -17711,7 +17711,7 @@
         <v>5.75</v>
       </c>
       <c r="G598" t="n">
-        <v>5.28355264663696</v>
+        <v>5.2835521697998</v>
       </c>
       <c r="H598" t="n">
         <v>0</v>
@@ -17740,7 +17740,7 @@
         <v>5.75</v>
       </c>
       <c r="G599" t="n">
-        <v>5.28355264663696</v>
+        <v>5.2835521697998</v>
       </c>
       <c r="H599" t="n">
         <v>0</v>
@@ -17827,7 +17827,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G602" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H602" t="n">
         <v>500</v>
@@ -17856,7 +17856,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G603" t="n">
-        <v>5.25564622879028</v>
+        <v>5.25564670562744</v>
       </c>
       <c r="H603" t="n">
         <v>500</v>
@@ -17885,7 +17885,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G604" t="n">
-        <v>5.25564622879028</v>
+        <v>5.25564670562744</v>
       </c>
       <c r="H604" t="n">
         <v>0</v>
@@ -17914,7 +17914,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G605" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H605" t="n">
         <v>3000</v>
@@ -17943,7 +17943,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G606" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H606" t="n">
         <v>0</v>
@@ -17972,7 +17972,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G607" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H607" t="n">
         <v>0</v>
@@ -18001,7 +18001,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G608" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H608" t="n">
         <v>2000</v>
@@ -18030,7 +18030,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G609" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H609" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G616" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H616" t="n">
         <v>500</v>
@@ -18262,7 +18262,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G617" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H617" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G618" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -18320,7 +18320,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G619" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -18349,7 +18349,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G620" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H620" t="n">
         <v>0</v>
@@ -18378,7 +18378,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G621" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H621" t="n">
         <v>1000</v>
@@ -18407,7 +18407,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G622" t="n">
-        <v>5.53470706939697</v>
+        <v>5.53470754623413</v>
       </c>
       <c r="H622" t="n">
         <v>3500</v>
@@ -18436,7 +18436,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G623" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H623" t="n">
         <v>500</v>
@@ -18523,7 +18523,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G626" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H626" t="n">
         <v>2500</v>
@@ -18552,7 +18552,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G627" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H627" t="n">
         <v>0</v>
@@ -18581,7 +18581,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G628" t="n">
-        <v>5.488196849823</v>
+        <v>5.48819732666016</v>
       </c>
       <c r="H628" t="n">
         <v>5500</v>
@@ -18610,7 +18610,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G629" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H629" t="n">
         <v>2000</v>
@@ -18639,7 +18639,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G630" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H630" t="n">
         <v>500</v>
@@ -18668,7 +18668,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G631" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H631" t="n">
         <v>1000</v>
@@ -18697,7 +18697,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G632" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H632" t="n">
         <v>500</v>
@@ -18726,7 +18726,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G633" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H633" t="n">
         <v>0</v>
@@ -18755,7 +18755,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G634" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H634" t="n">
         <v>0</v>
@@ -18784,7 +18784,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G635" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H635" t="n">
         <v>0</v>
@@ -18871,7 +18871,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G638" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H638" t="n">
         <v>5500</v>
@@ -18900,7 +18900,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G639" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H639" t="n">
         <v>3250</v>
@@ -18929,7 +18929,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G640" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H640" t="n">
         <v>0</v>
@@ -18958,7 +18958,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G641" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H641" t="n">
         <v>0</v>
@@ -18987,7 +18987,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G642" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H642" t="n">
         <v>0</v>
@@ -19016,7 +19016,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G643" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H643" t="n">
         <v>0</v>
@@ -19045,7 +19045,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G644" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H644" t="n">
         <v>2000</v>
@@ -19074,7 +19074,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G645" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H645" t="n">
         <v>0</v>
@@ -19103,7 +19103,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H646" t="n">
         <v>0</v>
@@ -19132,7 +19132,7 @@
         <v>5.25</v>
       </c>
       <c r="G647" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H647" t="n">
         <v>10000</v>
@@ -19161,7 +19161,7 @@
         <v>5.25</v>
       </c>
       <c r="G648" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H648" t="n">
         <v>12500</v>
@@ -19190,7 +19190,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G649" t="n">
-        <v>4.5021824836731</v>
+        <v>4.50218200683594</v>
       </c>
       <c r="H649" t="n">
         <v>67000</v>
@@ -19219,7 +19219,7 @@
         <v>5</v>
       </c>
       <c r="G650" t="n">
-        <v>4.65101432800293</v>
+        <v>4.65101480484009</v>
       </c>
       <c r="H650" t="n">
         <v>8500</v>
@@ -19248,7 +19248,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G651" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H651" t="n">
         <v>9500</v>
@@ -19364,7 +19364,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H655" t="n">
         <v>1500</v>
@@ -19393,7 +19393,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G656" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H656" t="n">
         <v>0</v>
@@ -19451,7 +19451,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G658" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H658" t="n">
         <v>500</v>
@@ -19480,7 +19480,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G659" t="n">
-        <v>5.25564622879028</v>
+        <v>5.25564670562744</v>
       </c>
       <c r="H659" t="n">
         <v>2250</v>
@@ -19509,7 +19509,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G660" t="n">
-        <v>5.25564622879028</v>
+        <v>5.25564670562744</v>
       </c>
       <c r="H660" t="n">
         <v>1500</v>
@@ -19538,7 +19538,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G661" t="n">
-        <v>5.25564622879028</v>
+        <v>5.25564670562744</v>
       </c>
       <c r="H661" t="n">
         <v>0</v>
@@ -19567,7 +19567,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G662" t="n">
-        <v>5.25564622879028</v>
+        <v>5.25564670562744</v>
       </c>
       <c r="H662" t="n">
         <v>0</v>
@@ -19654,7 +19654,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G665" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H665" t="n">
         <v>500</v>
@@ -19712,7 +19712,7 @@
         <v>5.25</v>
       </c>
       <c r="G667" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H667" t="n">
         <v>7250</v>
@@ -19770,7 +19770,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G669" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H669" t="n">
         <v>500</v>
@@ -19799,7 +19799,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H670" t="n">
         <v>0</v>
@@ -19828,7 +19828,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H671" t="n">
         <v>0</v>
@@ -20002,7 +20002,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H677" t="n">
         <v>19750</v>
@@ -20031,7 +20031,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H678" t="n">
         <v>1750</v>
@@ -20350,7 +20350,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G689" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H689" t="n">
         <v>1250</v>
@@ -20379,7 +20379,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G690" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H690" t="n">
         <v>3000</v>
@@ -20437,7 +20437,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G692" t="n">
-        <v>5.25564622879028</v>
+        <v>5.25564670562744</v>
       </c>
       <c r="H692" t="n">
         <v>500</v>
@@ -20785,7 +20785,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G704" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H704" t="n">
         <v>41750</v>
@@ -20814,7 +20814,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G705" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H705" t="n">
         <v>7500</v>
@@ -20843,7 +20843,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G706" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H706" t="n">
         <v>2500</v>
@@ -20872,7 +20872,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G707" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H707" t="n">
         <v>7500</v>
@@ -20901,7 +20901,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G708" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H708" t="n">
         <v>2250</v>
@@ -20930,7 +20930,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G709" t="n">
-        <v>4.52078628540039</v>
+        <v>4.52078580856323</v>
       </c>
       <c r="H709" t="n">
         <v>36250</v>
@@ -21075,7 +21075,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G714" t="n">
-        <v>4.55799436569214</v>
+        <v>4.5579948425293</v>
       </c>
       <c r="H714" t="n">
         <v>4500</v>
@@ -21133,7 +21133,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G716" t="n">
-        <v>4.46497440338135</v>
+        <v>4.46497392654419</v>
       </c>
       <c r="H716" t="n">
         <v>22500</v>
@@ -21162,7 +21162,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G717" t="n">
-        <v>4.63241100311279</v>
+        <v>4.63241052627563</v>
       </c>
       <c r="H717" t="n">
         <v>1000</v>
@@ -21191,7 +21191,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G718" t="n">
-        <v>4.63241100311279</v>
+        <v>4.63241052627563</v>
       </c>
       <c r="H718" t="n">
         <v>0</v>
@@ -21220,7 +21220,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G719" t="n">
-        <v>4.63241100311279</v>
+        <v>4.63241052627563</v>
       </c>
       <c r="H719" t="n">
         <v>0</v>
@@ -21249,7 +21249,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G720" t="n">
-        <v>4.63241100311279</v>
+        <v>4.63241052627563</v>
       </c>
       <c r="H720" t="n">
         <v>0</v>
@@ -21278,7 +21278,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G721" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H721" t="n">
         <v>3000</v>
@@ -21423,7 +21423,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G726" t="n">
-        <v>4.0556845664978</v>
+        <v>4.05568504333496</v>
       </c>
       <c r="H726" t="n">
         <v>6000</v>
@@ -21510,7 +21510,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>4.27893304824829</v>
+        <v>4.27893352508545</v>
       </c>
       <c r="H729" t="n">
         <v>1250</v>
@@ -21539,7 +21539,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G730" t="n">
-        <v>4.27893304824829</v>
+        <v>4.27893352508545</v>
       </c>
       <c r="H730" t="n">
         <v>0</v>
@@ -21655,7 +21655,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G734" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H734" t="n">
         <v>250</v>
@@ -21684,7 +21684,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G735" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H735" t="n">
         <v>0</v>
@@ -21713,7 +21713,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G736" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H736" t="n">
         <v>0</v>
@@ -21742,7 +21742,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G737" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H737" t="n">
         <v>0</v>
@@ -21771,7 +21771,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G738" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H738" t="n">
         <v>0</v>
@@ -21800,7 +21800,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G739" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H739" t="n">
         <v>0</v>
@@ -21829,7 +21829,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G740" t="n">
-        <v>4.44636964797974</v>
+        <v>4.44637012481689</v>
       </c>
       <c r="H740" t="n">
         <v>750</v>
@@ -22119,7 +22119,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G750" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H750" t="n">
         <v>750</v>
@@ -22148,7 +22148,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G751" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H751" t="n">
         <v>0</v>
@@ -22177,7 +22177,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G752" t="n">
-        <v>4.3719539642334</v>
+        <v>4.37195348739624</v>
       </c>
       <c r="H752" t="n">
         <v>0</v>
@@ -22206,7 +22206,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G753" t="n">
-        <v>4.4277663230896</v>
+        <v>4.42776584625244</v>
       </c>
       <c r="H753" t="n">
         <v>2250</v>
@@ -22264,7 +22264,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G755" t="n">
-        <v>4.4277663230896</v>
+        <v>4.42776584625244</v>
       </c>
       <c r="H755" t="n">
         <v>3250</v>
@@ -22293,7 +22293,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G756" t="n">
-        <v>4.4277663230896</v>
+        <v>4.42776584625244</v>
       </c>
       <c r="H756" t="n">
         <v>0</v>
@@ -22322,7 +22322,7 @@
         <v>5</v>
       </c>
       <c r="G757" t="n">
-        <v>4.65101432800293</v>
+        <v>4.65101480484009</v>
       </c>
       <c r="H757" t="n">
         <v>2750</v>
@@ -22409,7 +22409,7 @@
         <v>5.25</v>
       </c>
       <c r="G760" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H760" t="n">
         <v>3000</v>
@@ -22438,7 +22438,7 @@
         <v>5.25</v>
       </c>
       <c r="G761" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H761" t="n">
         <v>2000</v>
@@ -22467,7 +22467,7 @@
         <v>5.25</v>
       </c>
       <c r="G762" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H762" t="n">
         <v>500</v>
@@ -22496,7 +22496,7 @@
         <v>5.25</v>
       </c>
       <c r="G763" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H763" t="n">
         <v>250</v>
@@ -22525,7 +22525,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G764" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H764" t="n">
         <v>4000</v>
@@ -22554,7 +22554,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G765" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H765" t="n">
         <v>0</v>
@@ -22583,7 +22583,7 @@
         <v>5.25</v>
       </c>
       <c r="G766" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H766" t="n">
         <v>2750</v>
@@ -22612,7 +22612,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G767" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H767" t="n">
         <v>6000</v>
@@ -22641,7 +22641,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H768" t="n">
         <v>500</v>
@@ -22670,7 +22670,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G769" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H769" t="n">
         <v>0</v>
@@ -22728,7 +22728,7 @@
         <v>5.25</v>
       </c>
       <c r="G771" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H771" t="n">
         <v>7500</v>
@@ -22757,7 +22757,7 @@
         <v>5.25</v>
       </c>
       <c r="G772" t="n">
-        <v>4.8835654258728</v>
+        <v>4.88356494903564</v>
       </c>
       <c r="H772" t="n">
         <v>0</v>
@@ -22786,7 +22786,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G773" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H773" t="n">
         <v>3750</v>
@@ -23047,7 +23047,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G782" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H782" t="n">
         <v>1750</v>
@@ -23076,7 +23076,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G783" t="n">
-        <v>5.67423820495605</v>
+        <v>5.6742377281189</v>
       </c>
       <c r="H783" t="n">
         <v>6750</v>
@@ -23105,7 +23105,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G784" t="n">
-        <v>5.76725816726685</v>
+        <v>5.76725769042969</v>
       </c>
       <c r="H784" t="n">
         <v>14500</v>
@@ -23134,7 +23134,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G785" t="n">
-        <v>5.99980878829956</v>
+        <v>5.9998083114624</v>
       </c>
       <c r="H785" t="n">
         <v>6250</v>
@@ -23221,7 +23221,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G788" t="n">
-        <v>5.86027860641479</v>
+        <v>5.86027812957764</v>
       </c>
       <c r="H788" t="n">
         <v>3250</v>
@@ -23250,7 +23250,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G789" t="n">
-        <v>5.86027860641479</v>
+        <v>5.86027812957764</v>
       </c>
       <c r="H789" t="n">
         <v>1500</v>
@@ -23279,7 +23279,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G790" t="n">
-        <v>5.76725816726685</v>
+        <v>5.76725769042969</v>
       </c>
       <c r="H790" t="n">
         <v>7750</v>
@@ -23308,7 +23308,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G791" t="n">
-        <v>5.86027860641479</v>
+        <v>5.86027812957764</v>
       </c>
       <c r="H791" t="n">
         <v>4750</v>
@@ -23366,7 +23366,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G793" t="n">
-        <v>5.67423820495605</v>
+        <v>5.6742377281189</v>
       </c>
       <c r="H793" t="n">
         <v>1250</v>
@@ -23511,7 +23511,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G798" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H798" t="n">
         <v>1000</v>
@@ -23627,7 +23627,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G802" t="n">
-        <v>5.53470706939697</v>
+        <v>5.53470754623413</v>
       </c>
       <c r="H802" t="n">
         <v>750</v>
@@ -23656,7 +23656,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G803" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H803" t="n">
         <v>750</v>
@@ -23714,7 +23714,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G805" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H805" t="n">
         <v>2750</v>
@@ -23743,7 +23743,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G806" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H806" t="n">
         <v>1750</v>
@@ -23772,7 +23772,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G807" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H807" t="n">
         <v>0</v>
@@ -23801,7 +23801,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G808" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H808" t="n">
         <v>0</v>
@@ -23830,7 +23830,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G809" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H809" t="n">
         <v>0</v>
@@ -23859,7 +23859,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G810" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H810" t="n">
         <v>1500</v>
@@ -23917,7 +23917,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G812" t="n">
-        <v>5.25564622879028</v>
+        <v>5.25564670562744</v>
       </c>
       <c r="H812" t="n">
         <v>750</v>
@@ -23946,7 +23946,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G813" t="n">
-        <v>5.25564622879028</v>
+        <v>5.25564670562744</v>
       </c>
       <c r="H813" t="n">
         <v>0</v>
@@ -23975,7 +23975,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G814" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H814" t="n">
         <v>3250</v>
@@ -24004,7 +24004,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G815" t="n">
-        <v>5.20913648605347</v>
+        <v>5.20913600921631</v>
       </c>
       <c r="H815" t="n">
         <v>0</v>
@@ -24120,7 +24120,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G819" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H819" t="n">
         <v>1000</v>
@@ -24352,7 +24352,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G827" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H827" t="n">
         <v>250</v>
@@ -24439,7 +24439,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G830" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H830" t="n">
         <v>9000</v>
@@ -24497,7 +24497,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G832" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H832" t="n">
         <v>750</v>
@@ -24526,7 +24526,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G833" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H833" t="n">
         <v>500</v>
@@ -24555,7 +24555,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G834" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -24584,7 +24584,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G835" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H835" t="n">
         <v>1000</v>
@@ -24613,7 +24613,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G836" t="n">
-        <v>4.74403429031372</v>
+        <v>4.74403476715088</v>
       </c>
       <c r="H836" t="n">
         <v>1000</v>
@@ -24642,7 +24642,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G837" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H837" t="n">
         <v>1500</v>
@@ -24816,7 +24816,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G843" t="n">
-        <v>4.63241100311279</v>
+        <v>4.63241052627563</v>
       </c>
       <c r="H843" t="n">
         <v>2750</v>
@@ -24845,7 +24845,7 @@
         <v>5</v>
       </c>
       <c r="G844" t="n">
-        <v>4.65101432800293</v>
+        <v>4.65101480484009</v>
       </c>
       <c r="H844" t="n">
         <v>250</v>
@@ -24874,7 +24874,7 @@
         <v>5</v>
       </c>
       <c r="G845" t="n">
-        <v>4.65101432800293</v>
+        <v>4.65101480484009</v>
       </c>
       <c r="H845" t="n">
         <v>0</v>
@@ -24903,7 +24903,7 @@
         <v>5</v>
       </c>
       <c r="G846" t="n">
-        <v>4.65101432800293</v>
+        <v>4.65101480484009</v>
       </c>
       <c r="H846" t="n">
         <v>500</v>
@@ -24932,7 +24932,7 @@
         <v>5</v>
       </c>
       <c r="G847" t="n">
-        <v>4.65101432800293</v>
+        <v>4.65101480484009</v>
       </c>
       <c r="H847" t="n">
         <v>0</v>
@@ -24990,7 +24990,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G849" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H849" t="n">
         <v>500</v>
@@ -25019,7 +25019,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G850" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H850" t="n">
         <v>1000</v>
@@ -25048,7 +25048,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G851" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H851" t="n">
         <v>1000</v>
@@ -43324,6 +43324,35 @@
         <v>5750</v>
       </c>
       <c r="I1481" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1482" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1482" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="D1482" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="E1482" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="F1482" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="G1482" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="H1482" t="n">
+        <v>250</v>
+      </c>
+      <c r="I1482" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PLN.MI.xlsx
+++ b/data/PLN.MI.xlsx
@@ -456,7 +456,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G3" t="n">
-        <v>4.11657667160034</v>
+        <v>4.11657619476318</v>
       </c>
       <c r="H3" t="n">
         <v>8500</v>
@@ -485,7 +485,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G4" t="n">
-        <v>4.10738754272461</v>
+        <v>4.10738801956177</v>
       </c>
       <c r="H4" t="n">
         <v>6000</v>
@@ -543,7 +543,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G6" t="n">
-        <v>4.21765327453613</v>
+        <v>4.21765375137329</v>
       </c>
       <c r="H6" t="n">
         <v>37000</v>
@@ -688,7 +688,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G11" t="n">
-        <v>4.03387784957886</v>
+        <v>4.0338773727417</v>
       </c>
       <c r="H11" t="n">
         <v>12000</v>
@@ -746,7 +746,7 @@
         <v>4.25</v>
       </c>
       <c r="G13" t="n">
-        <v>3.90523457527161</v>
+        <v>3.90523433685303</v>
       </c>
       <c r="H13" t="n">
         <v>19500</v>
@@ -775,7 +775,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G14" t="n">
-        <v>3.95117878913879</v>
+        <v>3.95117831230164</v>
       </c>
       <c r="H14" t="n">
         <v>19000</v>
@@ -804,7 +804,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G15" t="n">
-        <v>3.89604592323303</v>
+        <v>3.89604568481445</v>
       </c>
       <c r="H15" t="n">
         <v>12500</v>
@@ -862,7 +862,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G17" t="n">
-        <v>3.81334686279297</v>
+        <v>3.81334638595581</v>
       </c>
       <c r="H17" t="n">
         <v>19000</v>
@@ -891,7 +891,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G18" t="n">
-        <v>3.72145891189575</v>
+        <v>3.72145867347717</v>
       </c>
       <c r="H18" t="n">
         <v>43500</v>
@@ -920,7 +920,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G19" t="n">
-        <v>3.95117878913879</v>
+        <v>3.95117831230164</v>
       </c>
       <c r="H19" t="n">
         <v>44000</v>
@@ -949,7 +949,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G20" t="n">
-        <v>3.87766814231873</v>
+        <v>3.87766790390015</v>
       </c>
       <c r="H20" t="n">
         <v>12000</v>
@@ -978,7 +978,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G21" t="n">
-        <v>3.87766814231873</v>
+        <v>3.87766790390015</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G22" t="n">
-        <v>3.87766814231873</v>
+        <v>3.87766790390015</v>
       </c>
       <c r="H22" t="n">
         <v>60000</v>
@@ -1036,7 +1036,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G23" t="n">
-        <v>3.850102186203</v>
+        <v>3.85010194778442</v>
       </c>
       <c r="H23" t="n">
         <v>32000</v>
@@ -1065,7 +1065,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G24" t="n">
-        <v>3.8868567943573</v>
+        <v>3.88685703277588</v>
       </c>
       <c r="H24" t="n">
         <v>500</v>
@@ -1297,7 +1297,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G32" t="n">
-        <v>4.10738754272461</v>
+        <v>4.10738801956177</v>
       </c>
       <c r="H32" t="n">
         <v>5500</v>
@@ -1355,7 +1355,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G34" t="n">
-        <v>4.10738754272461</v>
+        <v>4.10738801956177</v>
       </c>
       <c r="H34" t="n">
         <v>500</v>
@@ -1384,7 +1384,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>4.11657667160034</v>
+        <v>4.11657619476318</v>
       </c>
       <c r="H35" t="n">
         <v>27500</v>
@@ -1413,7 +1413,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G36" t="n">
-        <v>4.06144428253174</v>
+        <v>4.06144380569458</v>
       </c>
       <c r="H36" t="n">
         <v>18500</v>
@@ -1616,7 +1616,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>4.08901023864746</v>
+        <v>4.0890097618103</v>
       </c>
       <c r="H43" t="n">
         <v>2000</v>
@@ -1645,7 +1645,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G44" t="n">
-        <v>4.08901023864746</v>
+        <v>4.0890097618103</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G45" t="n">
-        <v>4.03387784957886</v>
+        <v>4.0338773727417</v>
       </c>
       <c r="H45" t="n">
         <v>12500</v>
@@ -1703,7 +1703,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G46" t="n">
-        <v>3.95117878913879</v>
+        <v>3.95117831230164</v>
       </c>
       <c r="H46" t="n">
         <v>4000</v>
@@ -1761,7 +1761,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G48" t="n">
-        <v>3.95117878913879</v>
+        <v>3.95117831230164</v>
       </c>
       <c r="H48" t="n">
         <v>2000</v>
@@ -1790,7 +1790,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G49" t="n">
-        <v>3.95117878913879</v>
+        <v>3.95117831230164</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G51" t="n">
-        <v>3.89604592323303</v>
+        <v>3.89604568481445</v>
       </c>
       <c r="H51" t="n">
         <v>31000</v>
@@ -1877,7 +1877,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>3.92361235618591</v>
+        <v>3.92361187934875</v>
       </c>
       <c r="H52" t="n">
         <v>9500</v>
@@ -1906,7 +1906,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G53" t="n">
-        <v>3.89604592323303</v>
+        <v>3.89604568481445</v>
       </c>
       <c r="H53" t="n">
         <v>11000</v>
@@ -1935,7 +1935,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G54" t="n">
-        <v>3.85929036140442</v>
+        <v>3.859290599823</v>
       </c>
       <c r="H54" t="n">
         <v>5000</v>
@@ -1964,7 +1964,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G55" t="n">
-        <v>3.85929036140442</v>
+        <v>3.859290599823</v>
       </c>
       <c r="H55" t="n">
         <v>6000</v>
@@ -1993,7 +1993,7 @@
         <v>4.25</v>
       </c>
       <c r="G56" t="n">
-        <v>3.90523457527161</v>
+        <v>3.90523433685303</v>
       </c>
       <c r="H56" t="n">
         <v>7500</v>
@@ -2022,7 +2022,7 @@
         <v>4.25</v>
       </c>
       <c r="G57" t="n">
-        <v>3.90523457527161</v>
+        <v>3.90523433685303</v>
       </c>
       <c r="H57" t="n">
         <v>3000</v>
@@ -2051,7 +2051,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>3.95117878913879</v>
+        <v>3.95117831230164</v>
       </c>
       <c r="H58" t="n">
         <v>3500</v>
@@ -2080,7 +2080,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>3.95117878913879</v>
+        <v>3.95117831230164</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G60" t="n">
-        <v>4.03387784957886</v>
+        <v>4.0338773727417</v>
       </c>
       <c r="H60" t="n">
         <v>1000</v>
@@ -2167,7 +2167,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G62" t="n">
-        <v>3.93280124664307</v>
+        <v>3.93280076980591</v>
       </c>
       <c r="H62" t="n">
         <v>40500</v>
@@ -2254,7 +2254,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G65" t="n">
-        <v>4.10738754272461</v>
+        <v>4.10738801956177</v>
       </c>
       <c r="H65" t="n">
         <v>12000</v>
@@ -2341,7 +2341,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G68" t="n">
-        <v>4.26359701156616</v>
+        <v>4.263596534729</v>
       </c>
       <c r="H68" t="n">
         <v>12500</v>
@@ -2399,7 +2399,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G70" t="n">
-        <v>4.42899560928345</v>
+        <v>4.42899513244629</v>
       </c>
       <c r="H70" t="n">
         <v>64500</v>
@@ -2457,7 +2457,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G72" t="n">
-        <v>4.66790390014648</v>
+        <v>4.66790342330933</v>
       </c>
       <c r="H72" t="n">
         <v>16500</v>
@@ -2544,7 +2544,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>4.61277151107788</v>
+        <v>4.61277103424072</v>
       </c>
       <c r="H75" t="n">
         <v>9500</v>
@@ -2573,7 +2573,7 @@
         <v>5</v>
       </c>
       <c r="G76" t="n">
-        <v>4.59439373016357</v>
+        <v>4.59439420700073</v>
       </c>
       <c r="H76" t="n">
         <v>6000</v>
@@ -2602,7 +2602,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G77" t="n">
-        <v>4.52088356018066</v>
+        <v>4.52088308334351</v>
       </c>
       <c r="H77" t="n">
         <v>500</v>
@@ -2747,7 +2747,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G82" t="n">
-        <v>4.77816963195801</v>
+        <v>4.77816915512085</v>
       </c>
       <c r="H82" t="n">
         <v>3500</v>
@@ -2776,7 +2776,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G83" t="n">
-        <v>4.92518997192383</v>
+        <v>4.92519044876099</v>
       </c>
       <c r="H83" t="n">
         <v>3500</v>
@@ -2805,7 +2805,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>5.18247556686401</v>
+        <v>5.18247604370117</v>
       </c>
       <c r="H84" t="n">
         <v>27000</v>
@@ -2834,7 +2834,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G85" t="n">
-        <v>4.96194505691528</v>
+        <v>4.96194553375244</v>
       </c>
       <c r="H85" t="n">
         <v>27000</v>
@@ -2863,7 +2863,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G86" t="n">
-        <v>5.18247556686401</v>
+        <v>5.18247604370117</v>
       </c>
       <c r="H86" t="n">
         <v>18000</v>
@@ -2892,7 +2892,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G87" t="n">
-        <v>5.31111860275269</v>
+        <v>5.31111907958984</v>
       </c>
       <c r="H87" t="n">
         <v>23500</v>
@@ -2950,7 +2950,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G89" t="n">
-        <v>6.11973142623901</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H89" t="n">
         <v>78500</v>
@@ -3008,7 +3008,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G91" t="n">
-        <v>6.11973142623901</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H91" t="n">
         <v>34500</v>
@@ -3037,7 +3037,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G92" t="n">
-        <v>6.26675319671631</v>
+        <v>6.26675271987915</v>
       </c>
       <c r="H92" t="n">
         <v>23000</v>
@@ -3066,7 +3066,7 @@
         <v>7</v>
       </c>
       <c r="G93" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H93" t="n">
         <v>93500</v>
@@ -3095,7 +3095,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G94" t="n">
-        <v>6.11973142623901</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H94" t="n">
         <v>29500</v>
@@ -3124,7 +3124,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G95" t="n">
-        <v>6.32188606262207</v>
+        <v>6.32188558578491</v>
       </c>
       <c r="H95" t="n">
         <v>57500</v>
@@ -3153,7 +3153,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>6.45052814483643</v>
+        <v>6.45052862167358</v>
       </c>
       <c r="H96" t="n">
         <v>59500</v>
@@ -3269,7 +3269,7 @@
         <v>6.5</v>
       </c>
       <c r="G100" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="H100" t="n">
         <v>8000</v>
@@ -3327,7 +3327,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G102" t="n">
-        <v>6.10135459899902</v>
+        <v>6.10135412216187</v>
       </c>
       <c r="H102" t="n">
         <v>2000</v>
@@ -3356,7 +3356,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G103" t="n">
-        <v>6.10135459899902</v>
+        <v>6.10135412216187</v>
       </c>
       <c r="H103" t="n">
         <v>2000</v>
@@ -3385,7 +3385,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G104" t="n">
-        <v>6.02784395217896</v>
+        <v>6.02784442901611</v>
       </c>
       <c r="H104" t="n">
         <v>15000</v>
@@ -3414,7 +3414,7 @@
         <v>6.5</v>
       </c>
       <c r="G105" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="H105" t="n">
         <v>22000</v>
@@ -3443,7 +3443,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G106" t="n">
-        <v>5.9543342590332</v>
+        <v>5.95433378219604</v>
       </c>
       <c r="H106" t="n">
         <v>11500</v>
@@ -3501,7 +3501,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>6.04622220993042</v>
+        <v>6.04622173309326</v>
       </c>
       <c r="H108" t="n">
         <v>12500</v>
@@ -3588,7 +3588,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G111" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H111" t="n">
         <v>3500</v>
@@ -3617,7 +3617,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G112" t="n">
-        <v>5.82569122314453</v>
+        <v>5.82569169998169</v>
       </c>
       <c r="H112" t="n">
         <v>3500</v>
@@ -3704,7 +3704,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G115" t="n">
-        <v>5.6419153213501</v>
+        <v>5.64191579818726</v>
       </c>
       <c r="H115" t="n">
         <v>21000</v>
@@ -3733,7 +3733,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G116" t="n">
-        <v>5.53165006637573</v>
+        <v>5.53164958953857</v>
       </c>
       <c r="H116" t="n">
         <v>6000</v>
@@ -3907,7 +3907,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G122" t="n">
-        <v>5.25598573684692</v>
+        <v>5.25598621368408</v>
       </c>
       <c r="H122" t="n">
         <v>10000</v>
@@ -3965,7 +3965,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G124" t="n">
-        <v>5.32949733734131</v>
+        <v>5.32949686050415</v>
       </c>
       <c r="H124" t="n">
         <v>500</v>
@@ -3994,7 +3994,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G125" t="n">
-        <v>5.71542549133301</v>
+        <v>5.71542501449585</v>
       </c>
       <c r="H125" t="n">
         <v>14000</v>
@@ -4052,7 +4052,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G127" t="n">
-        <v>5.25598573684692</v>
+        <v>5.25598621368408</v>
       </c>
       <c r="H127" t="n">
         <v>22000</v>
@@ -4255,7 +4255,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G134" t="n">
-        <v>5.53165006637573</v>
+        <v>5.53164958953857</v>
       </c>
       <c r="H134" t="n">
         <v>1500</v>
@@ -4284,7 +4284,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>5.53165006637573</v>
+        <v>5.53164958953857</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G144" t="n">
-        <v>5.6602931022644</v>
+        <v>5.66029262542725</v>
       </c>
       <c r="H144" t="n">
         <v>2500</v>
@@ -4690,7 +4690,7 @@
         <v>6.5</v>
       </c>
       <c r="G149" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="H149" t="n">
         <v>2000</v>
@@ -4719,7 +4719,7 @@
         <v>6.5</v>
       </c>
       <c r="G150" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="H150" t="n">
         <v>1500</v>
@@ -4748,7 +4748,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>6.06459903717041</v>
+        <v>6.06459999084473</v>
       </c>
       <c r="H151" t="n">
         <v>5500</v>
@@ -4777,7 +4777,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G152" t="n">
-        <v>6.02784395217896</v>
+        <v>6.02784442901611</v>
       </c>
       <c r="H152" t="n">
         <v>6000</v>
@@ -4806,7 +4806,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G153" t="n">
-        <v>6.06459903717041</v>
+        <v>6.06459999084473</v>
       </c>
       <c r="H153" t="n">
         <v>1000</v>
@@ -4980,7 +4980,7 @@
         <v>7</v>
       </c>
       <c r="G159" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H159" t="n">
         <v>4000</v>
@@ -5154,7 +5154,7 @@
         <v>7</v>
       </c>
       <c r="G165" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H165" t="n">
         <v>2500</v>
@@ -5212,7 +5212,7 @@
         <v>7</v>
       </c>
       <c r="G167" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H167" t="n">
         <v>2000</v>
@@ -5241,7 +5241,7 @@
         <v>7</v>
       </c>
       <c r="G168" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>7</v>
       </c>
       <c r="G169" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H169" t="n">
         <v>1000</v>
@@ -5299,7 +5299,7 @@
         <v>7</v>
       </c>
       <c r="G170" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H170" t="n">
         <v>1000</v>
@@ -5328,7 +5328,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G171" t="n">
-        <v>6.45052814483643</v>
+        <v>6.45052862167358</v>
       </c>
       <c r="H171" t="n">
         <v>1500</v>
@@ -5357,7 +5357,7 @@
         <v>7</v>
       </c>
       <c r="G172" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H172" t="n">
         <v>1500</v>
@@ -5386,7 +5386,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G173" t="n">
-        <v>6.46890640258789</v>
+        <v>6.46890592575073</v>
       </c>
       <c r="H173" t="n">
         <v>2000</v>
@@ -5415,7 +5415,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G174" t="n">
-        <v>6.39539575576782</v>
+        <v>6.39539623260498</v>
       </c>
       <c r="H174" t="n">
         <v>4500</v>
@@ -5444,7 +5444,7 @@
         <v>7</v>
       </c>
       <c r="G175" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H175" t="n">
         <v>2000</v>
@@ -5531,7 +5531,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G178" t="n">
-        <v>7.20400953292847</v>
+        <v>7.20400905609131</v>
       </c>
       <c r="H178" t="n">
         <v>25000</v>
@@ -5560,7 +5560,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H179" t="n">
         <v>1500</v>
@@ -5589,7 +5589,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G180" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5618,7 +5618,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G181" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H181" t="n">
         <v>1500</v>
@@ -5647,7 +5647,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G182" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H182" t="n">
         <v>2500</v>
@@ -5676,7 +5676,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G184" t="n">
-        <v>6.94672298431396</v>
+        <v>6.94672250747681</v>
       </c>
       <c r="H184" t="n">
         <v>6000</v>
@@ -5792,7 +5792,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G187" t="n">
-        <v>7.05698871612549</v>
+        <v>7.05698823928833</v>
       </c>
       <c r="H187" t="n">
         <v>5500</v>
@@ -5908,7 +5908,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G191" t="n">
-        <v>7.14887714385986</v>
+        <v>7.14887666702271</v>
       </c>
       <c r="H191" t="n">
         <v>1000</v>
@@ -5937,7 +5937,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G192" t="n">
-        <v>7.36940813064575</v>
+        <v>7.36940765380859</v>
       </c>
       <c r="H192" t="n">
         <v>4000</v>
@@ -6024,7 +6024,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G195" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H195" t="n">
         <v>12000</v>
@@ -6169,7 +6169,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>7.31427478790283</v>
+        <v>7.31427431106567</v>
       </c>
       <c r="H200" t="n">
         <v>7500</v>
@@ -6198,7 +6198,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G201" t="n">
-        <v>7.31427478790283</v>
+        <v>7.31427431106567</v>
       </c>
       <c r="H201" t="n">
         <v>6000</v>
@@ -6227,7 +6227,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G202" t="n">
-        <v>7.70020437240601</v>
+        <v>7.70020389556885</v>
       </c>
       <c r="H202" t="n">
         <v>6500</v>
@@ -6256,7 +6256,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G203" t="n">
-        <v>7.70020437240601</v>
+        <v>7.70020389556885</v>
       </c>
       <c r="H203" t="n">
         <v>3000</v>
@@ -6285,7 +6285,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G204" t="n">
-        <v>7.79209184646606</v>
+        <v>7.79209136962891</v>
       </c>
       <c r="H204" t="n">
         <v>6500</v>
@@ -6314,7 +6314,7 @@
         <v>8.5</v>
       </c>
       <c r="G205" t="n">
-        <v>7.81046915054321</v>
+        <v>7.81046867370605</v>
       </c>
       <c r="H205" t="n">
         <v>6500</v>
@@ -6343,7 +6343,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G206" t="n">
-        <v>8.12288856506348</v>
+        <v>8.12288761138916</v>
       </c>
       <c r="H206" t="n">
         <v>16500</v>
@@ -6459,7 +6459,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G210" t="n">
-        <v>8.01262378692627</v>
+        <v>8.01262283325195</v>
       </c>
       <c r="H210" t="n">
         <v>3500</v>
@@ -6488,7 +6488,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G211" t="n">
-        <v>8.15964221954346</v>
+        <v>8.15964317321777</v>
       </c>
       <c r="H211" t="n">
         <v>8000</v>
@@ -6517,7 +6517,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G212" t="n">
-        <v>8.12288856506348</v>
+        <v>8.12288761138916</v>
       </c>
       <c r="H212" t="n">
         <v>500</v>
@@ -6546,7 +6546,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G213" t="n">
-        <v>8.28828620910645</v>
+        <v>8.28828525543213</v>
       </c>
       <c r="H213" t="n">
         <v>4000</v>
@@ -6633,7 +6633,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G216" t="n">
-        <v>8.54557132720947</v>
+        <v>8.54557228088379</v>
       </c>
       <c r="H216" t="n">
         <v>2500</v>
@@ -6865,7 +6865,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G224" t="n">
-        <v>8.82123565673828</v>
+        <v>8.8212366104126</v>
       </c>
       <c r="H224" t="n">
         <v>2000</v>
@@ -6894,7 +6894,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.82123565673828</v>
+        <v>8.8212366104126</v>
       </c>
       <c r="H225" t="n">
         <v>3500</v>
@@ -6923,7 +6923,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G226" t="n">
-        <v>8.76610279083252</v>
+        <v>8.76610374450684</v>
       </c>
       <c r="H226" t="n">
         <v>500</v>
@@ -7155,7 +7155,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G234" t="n">
-        <v>8.54557132720947</v>
+        <v>8.54557228088379</v>
       </c>
       <c r="H234" t="n">
         <v>4500</v>
@@ -7184,7 +7184,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>8.54557132720947</v>
+        <v>8.54557228088379</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>8.23315334320068</v>
+        <v>8.23315238952637</v>
       </c>
       <c r="H237" t="n">
         <v>8500</v>
@@ -7387,7 +7387,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G242" t="n">
-        <v>8.28828620910645</v>
+        <v>8.28828525543213</v>
       </c>
       <c r="H242" t="n">
         <v>500</v>
@@ -7532,7 +7532,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>8.54557132720947</v>
+        <v>8.54557228088379</v>
       </c>
       <c r="H247" t="n">
         <v>7500</v>
@@ -7619,7 +7619,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G250" t="n">
-        <v>8.49043846130371</v>
+        <v>8.49043941497803</v>
       </c>
       <c r="H250" t="n">
         <v>500</v>
@@ -7648,7 +7648,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G251" t="n">
-        <v>8.54557132720947</v>
+        <v>8.54557228088379</v>
       </c>
       <c r="H251" t="n">
         <v>6000</v>
@@ -7677,7 +7677,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G252" t="n">
-        <v>8.54557132720947</v>
+        <v>8.54557228088379</v>
       </c>
       <c r="H252" t="n">
         <v>500</v>
@@ -7822,7 +7822,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G257" t="n">
-        <v>8.87636756896973</v>
+        <v>8.87636852264404</v>
       </c>
       <c r="H257" t="n">
         <v>4000</v>
@@ -7851,7 +7851,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G258" t="n">
-        <v>9.09689903259277</v>
+        <v>9.09689807891846</v>
       </c>
       <c r="H258" t="n">
         <v>1500</v>
@@ -7880,7 +7880,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G259" t="n">
-        <v>9.09689903259277</v>
+        <v>9.09689807891846</v>
       </c>
       <c r="H259" t="n">
         <v>4500</v>
@@ -7909,7 +7909,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G260" t="n">
-        <v>9.09689903259277</v>
+        <v>9.09689807891846</v>
       </c>
       <c r="H260" t="n">
         <v>500</v>
@@ -7938,7 +7938,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G261" t="n">
-        <v>8.98663425445557</v>
+        <v>8.98663330078125</v>
       </c>
       <c r="H261" t="n">
         <v>1000</v>
@@ -7967,7 +7967,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G262" t="n">
-        <v>8.98663425445557</v>
+        <v>8.98663330078125</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>10</v>
       </c>
       <c r="G263" t="n">
-        <v>9.18878746032715</v>
+        <v>9.18878841400146</v>
       </c>
       <c r="H263" t="n">
         <v>500</v>
@@ -8199,7 +8199,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G270" t="n">
-        <v>8.67421436309814</v>
+        <v>8.67421531677246</v>
       </c>
       <c r="H270" t="n">
         <v>1000</v>
@@ -8315,7 +8315,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>7.53480577468872</v>
+        <v>7.53480529785156</v>
       </c>
       <c r="H274" t="n">
         <v>3000</v>
@@ -8431,7 +8431,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G278" t="n">
-        <v>7.66344881057739</v>
+        <v>7.66344833374023</v>
       </c>
       <c r="H278" t="n">
         <v>3000</v>
@@ -8866,7 +8866,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G293" t="n">
-        <v>7.11212110519409</v>
+        <v>7.11212158203125</v>
       </c>
       <c r="H293" t="n">
         <v>7500</v>
@@ -8895,7 +8895,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G294" t="n">
-        <v>7.11212110519409</v>
+        <v>7.11212158203125</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -8982,7 +8982,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>6.79970216751099</v>
+        <v>6.79970264434814</v>
       </c>
       <c r="H297" t="n">
         <v>3500</v>
@@ -9011,7 +9011,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>6.98347854614258</v>
+        <v>6.98347806930542</v>
       </c>
       <c r="H298" t="n">
         <v>7000</v>
@@ -9040,7 +9040,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>6.98347854614258</v>
+        <v>6.98347806930542</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>6.98347854614258</v>
+        <v>6.98347806930542</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G301" t="n">
-        <v>6.98347854614258</v>
+        <v>6.98347806930542</v>
       </c>
       <c r="H301" t="n">
         <v>18500</v>
@@ -9272,7 +9272,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G307" t="n">
-        <v>7.16725397109985</v>
+        <v>7.16725444793701</v>
       </c>
       <c r="H307" t="n">
         <v>500</v>
@@ -9330,7 +9330,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G309" t="n">
-        <v>7.05698871612549</v>
+        <v>7.05698823928833</v>
       </c>
       <c r="H309" t="n">
         <v>1000</v>
@@ -9388,7 +9388,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G311" t="n">
-        <v>7.55318355560303</v>
+        <v>7.55318403244019</v>
       </c>
       <c r="H311" t="n">
         <v>2000</v>
@@ -9417,7 +9417,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G312" t="n">
-        <v>7.53480577468872</v>
+        <v>7.53480529785156</v>
       </c>
       <c r="H312" t="n">
         <v>2000</v>
@@ -9446,7 +9446,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G313" t="n">
-        <v>7.38778448104858</v>
+        <v>7.38778495788574</v>
       </c>
       <c r="H313" t="n">
         <v>2000</v>
@@ -9475,7 +9475,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G314" t="n">
-        <v>7.4429178237915</v>
+        <v>7.44291734695435</v>
       </c>
       <c r="H314" t="n">
         <v>2000</v>
@@ -9504,7 +9504,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G315" t="n">
-        <v>7.4429178237915</v>
+        <v>7.44291734695435</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G316" t="n">
-        <v>7.4429178237915</v>
+        <v>7.44291734695435</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>7.4429178237915</v>
+        <v>7.44291734695435</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G318" t="n">
-        <v>7.4429178237915</v>
+        <v>7.44291734695435</v>
       </c>
       <c r="H318" t="n">
         <v>500</v>
@@ -9678,7 +9678,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G321" t="n">
-        <v>7.22238636016846</v>
+        <v>7.22238683700562</v>
       </c>
       <c r="H321" t="n">
         <v>500</v>
@@ -9707,7 +9707,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G322" t="n">
-        <v>7.22238636016846</v>
+        <v>7.22238683700562</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G323" t="n">
-        <v>7.22238636016846</v>
+        <v>7.22238683700562</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G324" t="n">
-        <v>7.22238636016846</v>
+        <v>7.22238683700562</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G328" t="n">
-        <v>6.98347854614258</v>
+        <v>6.98347806930542</v>
       </c>
       <c r="H328" t="n">
         <v>1000</v>
@@ -9910,7 +9910,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G329" t="n">
-        <v>6.79970216751099</v>
+        <v>6.79970264434814</v>
       </c>
       <c r="H329" t="n">
         <v>1000</v>
@@ -10055,7 +10055,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G334" t="n">
-        <v>6.94672298431396</v>
+        <v>6.94672250747681</v>
       </c>
       <c r="H334" t="n">
         <v>500</v>
@@ -10084,7 +10084,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>6.94672298431396</v>
+        <v>6.94672250747681</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G336" t="n">
-        <v>6.94672298431396</v>
+        <v>6.94672250747681</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>6.79970216751099</v>
+        <v>6.79970264434814</v>
       </c>
       <c r="H337" t="n">
         <v>500</v>
@@ -10171,7 +10171,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>6.79970216751099</v>
+        <v>6.79970264434814</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10229,7 +10229,7 @@
         <v>6.5</v>
       </c>
       <c r="G340" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="H340" t="n">
         <v>32500</v>
@@ -10316,7 +10316,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G343" t="n">
-        <v>6.02784395217896</v>
+        <v>6.02784442901611</v>
       </c>
       <c r="H343" t="n">
         <v>9500</v>
@@ -10345,7 +10345,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G344" t="n">
-        <v>6.26675319671631</v>
+        <v>6.26675271987915</v>
       </c>
       <c r="H344" t="n">
         <v>1000</v>
@@ -10374,7 +10374,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G345" t="n">
-        <v>6.26675319671631</v>
+        <v>6.26675271987915</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G346" t="n">
-        <v>6.04622220993042</v>
+        <v>6.04622173309326</v>
       </c>
       <c r="H346" t="n">
         <v>1000</v>
@@ -10432,7 +10432,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G347" t="n">
-        <v>6.11973142623901</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H347" t="n">
         <v>1000</v>
@@ -10461,7 +10461,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G348" t="n">
-        <v>6.11973142623901</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -10490,7 +10490,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G349" t="n">
-        <v>6.21162080764771</v>
+        <v>6.21162033081055</v>
       </c>
       <c r="H349" t="n">
         <v>1500</v>
@@ -10519,7 +10519,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G350" t="n">
-        <v>6.04622220993042</v>
+        <v>6.04622173309326</v>
       </c>
       <c r="H350" t="n">
         <v>1000</v>
@@ -10606,7 +10606,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G353" t="n">
-        <v>5.91757917404175</v>
+        <v>5.91757965087891</v>
       </c>
       <c r="H353" t="n">
         <v>3000</v>
@@ -10635,7 +10635,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G354" t="n">
-        <v>5.91757917404175</v>
+        <v>5.91757965087891</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G371" t="n">
-        <v>6.21162080764771</v>
+        <v>6.21162033081055</v>
       </c>
       <c r="H371" t="n">
         <v>4000</v>
@@ -11157,7 +11157,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G372" t="n">
-        <v>6.21162080764771</v>
+        <v>6.21162033081055</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G373" t="n">
-        <v>6.21162080764771</v>
+        <v>6.21162033081055</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G374" t="n">
-        <v>6.21162080764771</v>
+        <v>6.21162033081055</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G376" t="n">
-        <v>6.04622220993042</v>
+        <v>6.04622173309326</v>
       </c>
       <c r="H376" t="n">
         <v>3000</v>
@@ -11302,7 +11302,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>6.04622220993042</v>
+        <v>6.04622173309326</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>6.5</v>
       </c>
       <c r="G378" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="H378" t="n">
         <v>500</v>
@@ -11360,7 +11360,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>6.06459903717041</v>
+        <v>6.06459999084473</v>
       </c>
       <c r="H379" t="n">
         <v>1000</v>
@@ -11389,7 +11389,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>6.06459903717041</v>
+        <v>6.06459999084473</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>6.06459903717041</v>
+        <v>6.06459999084473</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G382" t="n">
-        <v>6.06459903717041</v>
+        <v>6.06459999084473</v>
       </c>
       <c r="H382" t="n">
         <v>500</v>
@@ -11476,7 +11476,7 @@
         <v>6.5</v>
       </c>
       <c r="G383" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="H383" t="n">
         <v>500</v>
@@ -11505,7 +11505,7 @@
         <v>6.5</v>
       </c>
       <c r="G384" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>6.5</v>
       </c>
       <c r="G385" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -11563,7 +11563,7 @@
         <v>6.5</v>
       </c>
       <c r="G386" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -11592,7 +11592,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G387" t="n">
-        <v>5.82569122314453</v>
+        <v>5.82569169998169</v>
       </c>
       <c r="H387" t="n">
         <v>500</v>
@@ -11621,7 +11621,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G388" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H388" t="n">
         <v>1000</v>
@@ -11911,7 +11911,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G398" t="n">
-        <v>5.91757917404175</v>
+        <v>5.91757965087891</v>
       </c>
       <c r="H398" t="n">
         <v>500</v>
@@ -11940,7 +11940,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G399" t="n">
-        <v>5.91757917404175</v>
+        <v>5.91757965087891</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -11969,7 +11969,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G400" t="n">
-        <v>6.10135459899902</v>
+        <v>6.10135412216187</v>
       </c>
       <c r="H400" t="n">
         <v>500</v>
@@ -12085,7 +12085,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G404" t="n">
-        <v>6.11973142623901</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H404" t="n">
         <v>1000</v>
@@ -12114,7 +12114,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G405" t="n">
-        <v>6.11973142623901</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -12143,7 +12143,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G406" t="n">
-        <v>6.11973142623901</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G407" t="n">
-        <v>6.11973142623901</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -12201,7 +12201,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G408" t="n">
-        <v>6.11973142623901</v>
+        <v>6.11973237991333</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G413" t="n">
-        <v>6.45052814483643</v>
+        <v>6.45052862167358</v>
       </c>
       <c r="H413" t="n">
         <v>5500</v>
@@ -12375,7 +12375,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G414" t="n">
-        <v>6.45052814483643</v>
+        <v>6.45052862167358</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>7</v>
       </c>
       <c r="G415" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H415" t="n">
         <v>1500</v>
@@ -12433,7 +12433,7 @@
         <v>7</v>
       </c>
       <c r="G416" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H416" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>7</v>
       </c>
       <c r="G417" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12491,7 +12491,7 @@
         <v>7</v>
       </c>
       <c r="G418" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>7</v>
       </c>
       <c r="G419" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>7</v>
       </c>
       <c r="G420" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>7</v>
       </c>
       <c r="G421" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H421" t="n">
         <v>500</v>
@@ -12868,7 +12868,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G431" t="n">
-        <v>6.21162080764771</v>
+        <v>6.21162033081055</v>
       </c>
       <c r="H431" t="n">
         <v>1000</v>
@@ -13071,7 +13071,7 @@
         <v>7</v>
       </c>
       <c r="G438" t="n">
-        <v>6.43215131759644</v>
+        <v>6.43215084075928</v>
       </c>
       <c r="H438" t="n">
         <v>3000</v>
@@ -13158,7 +13158,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G441" t="n">
-        <v>6.32188606262207</v>
+        <v>6.32188558578491</v>
       </c>
       <c r="H441" t="n">
         <v>500</v>
@@ -13187,7 +13187,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G442" t="n">
-        <v>6.32188606262207</v>
+        <v>6.32188558578491</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G443" t="n">
-        <v>6.32188606262207</v>
+        <v>6.32188558578491</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G444" t="n">
-        <v>6.32188606262207</v>
+        <v>6.32188558578491</v>
       </c>
       <c r="H444" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G448" t="n">
-        <v>6.02784395217896</v>
+        <v>6.02784442901611</v>
       </c>
       <c r="H448" t="n">
         <v>1000</v>
@@ -13419,7 +13419,7 @@
         <v>6.5</v>
       </c>
       <c r="G450" t="n">
-        <v>5.97271156311035</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="H450" t="n">
         <v>500</v>
@@ -13448,7 +13448,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G451" t="n">
-        <v>6.00946664810181</v>
+        <v>6.00946712493896</v>
       </c>
       <c r="H451" t="n">
         <v>500</v>
@@ -14115,7 +14115,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G474" t="n">
-        <v>5.42138481140137</v>
+        <v>5.42138433456421</v>
       </c>
       <c r="H474" t="n">
         <v>500</v>
@@ -14724,7 +14724,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G495" t="n">
-        <v>5.73380279541016</v>
+        <v>5.73380327224731</v>
       </c>
       <c r="H495" t="n">
         <v>2000</v>
@@ -14753,7 +14753,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G496" t="n">
-        <v>5.73380279541016</v>
+        <v>5.73380327224731</v>
       </c>
       <c r="H496" t="n">
         <v>0</v>
@@ -14782,7 +14782,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G497" t="n">
-        <v>5.73380279541016</v>
+        <v>5.73380327224731</v>
       </c>
       <c r="H497" t="n">
         <v>0</v>
@@ -14898,7 +14898,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G501" t="n">
-        <v>5.42138481140137</v>
+        <v>5.42138433456421</v>
       </c>
       <c r="H501" t="n">
         <v>500</v>
@@ -14927,7 +14927,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G502" t="n">
-        <v>5.42138481140137</v>
+        <v>5.42138433456421</v>
       </c>
       <c r="H502" t="n">
         <v>0</v>
@@ -14956,7 +14956,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G503" t="n">
-        <v>5.42138481140137</v>
+        <v>5.42138433456421</v>
       </c>
       <c r="H503" t="n">
         <v>0</v>
@@ -14985,7 +14985,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>5.42138481140137</v>
+        <v>5.42138433456421</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15014,7 +15014,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>5.36625242233276</v>
+        <v>5.36625194549561</v>
       </c>
       <c r="H505" t="n">
         <v>1000</v>
@@ -15043,7 +15043,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G506" t="n">
-        <v>5.32949733734131</v>
+        <v>5.32949686050415</v>
       </c>
       <c r="H506" t="n">
         <v>1000</v>
@@ -15072,7 +15072,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>5.32949733734131</v>
+        <v>5.32949686050415</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G509" t="n">
-        <v>5.6419153213501</v>
+        <v>5.64191579818726</v>
       </c>
       <c r="H509" t="n">
         <v>1000</v>
@@ -15304,7 +15304,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G515" t="n">
-        <v>5.62353754043579</v>
+        <v>5.62353706359863</v>
       </c>
       <c r="H515" t="n">
         <v>1500</v>
@@ -15333,7 +15333,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G516" t="n">
-        <v>5.62353754043579</v>
+        <v>5.62353706359863</v>
       </c>
       <c r="H516" t="n">
         <v>0</v>
@@ -15362,7 +15362,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G517" t="n">
-        <v>5.62353754043579</v>
+        <v>5.62353706359863</v>
       </c>
       <c r="H517" t="n">
         <v>0</v>
@@ -15391,7 +15391,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G518" t="n">
-        <v>5.62353754043579</v>
+        <v>5.62353706359863</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15420,7 +15420,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G519" t="n">
-        <v>5.62353754043579</v>
+        <v>5.62353706359863</v>
       </c>
       <c r="H519" t="n">
         <v>0</v>
@@ -15449,7 +15449,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G520" t="n">
-        <v>5.62353754043579</v>
+        <v>5.62353706359863</v>
       </c>
       <c r="H520" t="n">
         <v>0</v>
@@ -15768,7 +15768,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G531" t="n">
-        <v>5.53165006637573</v>
+        <v>5.53164958953857</v>
       </c>
       <c r="H531" t="n">
         <v>500</v>
@@ -15797,7 +15797,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G532" t="n">
-        <v>5.62353754043579</v>
+        <v>5.62353706359863</v>
       </c>
       <c r="H532" t="n">
         <v>500</v>
@@ -15826,7 +15826,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G533" t="n">
-        <v>5.62353754043579</v>
+        <v>5.62353706359863</v>
       </c>
       <c r="H533" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G534" t="n">
-        <v>5.62353754043579</v>
+        <v>5.62353706359863</v>
       </c>
       <c r="H534" t="n">
         <v>0</v>
@@ -15884,7 +15884,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H535" t="n">
         <v>500</v>
@@ -15913,7 +15913,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G536" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H536" t="n">
         <v>0</v>
@@ -15942,7 +15942,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G537" t="n">
-        <v>5.6602931022644</v>
+        <v>5.66029262542725</v>
       </c>
       <c r="H537" t="n">
         <v>5000</v>
@@ -15971,7 +15971,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G538" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H538" t="n">
         <v>1000</v>
@@ -16000,7 +16000,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G539" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H539" t="n">
         <v>0</v>
@@ -16029,7 +16029,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G540" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H540" t="n">
         <v>0</v>
@@ -16058,7 +16058,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G541" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -16116,7 +16116,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G543" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H543" t="n">
         <v>0</v>
@@ -16145,7 +16145,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G544" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H544" t="n">
         <v>0</v>
@@ -16174,7 +16174,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G545" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H546" t="n">
         <v>0</v>
@@ -16232,7 +16232,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G547" t="n">
-        <v>5.6970477104187</v>
+        <v>5.69704818725586</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G548" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H548" t="n">
         <v>1500</v>
@@ -16290,7 +16290,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G549" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H549" t="n">
         <v>0</v>
@@ -16319,7 +16319,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G550" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -16348,7 +16348,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G551" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H551" t="n">
         <v>0</v>
@@ -16377,7 +16377,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G552" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H552" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G553" t="n">
-        <v>5.77055883407593</v>
+        <v>5.77055835723877</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -16725,7 +16725,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G564" t="n">
-        <v>5.27436351776123</v>
+        <v>5.27436399459839</v>
       </c>
       <c r="H564" t="n">
         <v>2500</v>
@@ -16870,7 +16870,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G569" t="n">
-        <v>5.29274129867554</v>
+        <v>5.2927417755127</v>
       </c>
       <c r="H569" t="n">
         <v>1000</v>
@@ -16899,7 +16899,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G570" t="n">
-        <v>5.29274129867554</v>
+        <v>5.2927417755127</v>
       </c>
       <c r="H570" t="n">
         <v>0</v>
@@ -16928,7 +16928,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G571" t="n">
-        <v>5.29274129867554</v>
+        <v>5.2927417755127</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G572" t="n">
-        <v>5.29274129867554</v>
+        <v>5.2927417755127</v>
       </c>
       <c r="H572" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G573" t="n">
-        <v>5.29274129867554</v>
+        <v>5.2927417755127</v>
       </c>
       <c r="H573" t="n">
         <v>0</v>
@@ -17015,7 +17015,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G574" t="n">
-        <v>5.27436351776123</v>
+        <v>5.27436399459839</v>
       </c>
       <c r="H574" t="n">
         <v>4500</v>
@@ -17276,7 +17276,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G583" t="n">
-        <v>5.42138481140137</v>
+        <v>5.42138433456421</v>
       </c>
       <c r="H583" t="n">
         <v>1500</v>
@@ -17305,7 +17305,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G584" t="n">
-        <v>5.42138481140137</v>
+        <v>5.42138433456421</v>
       </c>
       <c r="H584" t="n">
         <v>0</v>
@@ -17421,7 +17421,7 @@
         <v>5.75</v>
       </c>
       <c r="G588" t="n">
-        <v>5.2835521697998</v>
+        <v>5.28355264663696</v>
       </c>
       <c r="H588" t="n">
         <v>2000</v>
@@ -17450,7 +17450,7 @@
         <v>5.75</v>
       </c>
       <c r="G589" t="n">
-        <v>5.2835521697998</v>
+        <v>5.28355264663696</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -17479,7 +17479,7 @@
         <v>5.75</v>
       </c>
       <c r="G590" t="n">
-        <v>5.2835521697998</v>
+        <v>5.28355264663696</v>
       </c>
       <c r="H590" t="n">
         <v>0</v>
@@ -17682,7 +17682,7 @@
         <v>5.75</v>
       </c>
       <c r="G597" t="n">
-        <v>5.2835521697998</v>
+        <v>5.28355264663696</v>
       </c>
       <c r="H597" t="n">
         <v>1000</v>
@@ -17711,7 +17711,7 @@
         <v>5.75</v>
       </c>
       <c r="G598" t="n">
-        <v>5.2835521697998</v>
+        <v>5.28355264663696</v>
       </c>
       <c r="H598" t="n">
         <v>0</v>
@@ -17740,7 +17740,7 @@
         <v>5.75</v>
       </c>
       <c r="G599" t="n">
-        <v>5.2835521697998</v>
+        <v>5.28355264663696</v>
       </c>
       <c r="H599" t="n">
         <v>0</v>
@@ -18001,7 +18001,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G608" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H608" t="n">
         <v>2000</v>
@@ -18030,7 +18030,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G609" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H609" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G616" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H616" t="n">
         <v>500</v>
@@ -18262,7 +18262,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G617" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H617" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G618" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -18320,7 +18320,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G619" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -18349,7 +18349,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G620" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H620" t="n">
         <v>0</v>
@@ -18378,7 +18378,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G621" t="n">
-        <v>5.39517736434937</v>
+        <v>5.39517688751221</v>
       </c>
       <c r="H621" t="n">
         <v>1000</v>
@@ -18407,7 +18407,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G622" t="n">
-        <v>5.53470754623413</v>
+        <v>5.53470706939697</v>
       </c>
       <c r="H622" t="n">
         <v>3500</v>
@@ -18610,7 +18610,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G629" t="n">
-        <v>5.39517736434937</v>
+        <v>5.39517688751221</v>
       </c>
       <c r="H629" t="n">
         <v>2000</v>
@@ -18639,7 +18639,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G630" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H630" t="n">
         <v>500</v>
@@ -18813,7 +18813,7 @@
         <v>5.5</v>
       </c>
       <c r="G636" t="n">
-        <v>5.11611604690552</v>
+        <v>5.11611557006836</v>
       </c>
       <c r="H636" t="n">
         <v>1500</v>
@@ -18842,7 +18842,7 @@
         <v>5.5</v>
       </c>
       <c r="G637" t="n">
-        <v>5.11611604690552</v>
+        <v>5.11611557006836</v>
       </c>
       <c r="H637" t="n">
         <v>0</v>
@@ -18900,7 +18900,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G639" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H639" t="n">
         <v>3250</v>
@@ -18929,7 +18929,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G640" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H640" t="n">
         <v>0</v>
@@ -18958,7 +18958,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G641" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H641" t="n">
         <v>0</v>
@@ -18987,7 +18987,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G642" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H642" t="n">
         <v>0</v>
@@ -19016,7 +19016,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G643" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H643" t="n">
         <v>0</v>
@@ -19219,7 +19219,7 @@
         <v>5</v>
       </c>
       <c r="G650" t="n">
-        <v>4.65101480484009</v>
+        <v>4.65101432800293</v>
       </c>
       <c r="H650" t="n">
         <v>8500</v>
@@ -19248,7 +19248,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G651" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H651" t="n">
         <v>9500</v>
@@ -19277,7 +19277,7 @@
         <v>5.5</v>
       </c>
       <c r="G652" t="n">
-        <v>5.11611604690552</v>
+        <v>5.11611557006836</v>
       </c>
       <c r="H652" t="n">
         <v>5500</v>
@@ -19306,7 +19306,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G653" t="n">
-        <v>5.16262626647949</v>
+        <v>5.16262674331665</v>
       </c>
       <c r="H653" t="n">
         <v>6000</v>
@@ -19335,7 +19335,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G654" t="n">
-        <v>5.16262626647949</v>
+        <v>5.16262674331665</v>
       </c>
       <c r="H654" t="n">
         <v>0</v>
@@ -19422,7 +19422,7 @@
         <v>5.5</v>
       </c>
       <c r="G657" t="n">
-        <v>5.11611604690552</v>
+        <v>5.11611557006836</v>
       </c>
       <c r="H657" t="n">
         <v>500</v>
@@ -19596,7 +19596,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G663" t="n">
-        <v>5.16262626647949</v>
+        <v>5.16262674331665</v>
       </c>
       <c r="H663" t="n">
         <v>2500</v>
@@ -19625,7 +19625,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G664" t="n">
-        <v>5.16262626647949</v>
+        <v>5.16262674331665</v>
       </c>
       <c r="H664" t="n">
         <v>0</v>
@@ -19654,7 +19654,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G665" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H665" t="n">
         <v>500</v>
@@ -19770,7 +19770,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G669" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H669" t="n">
         <v>500</v>
@@ -19799,7 +19799,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H670" t="n">
         <v>0</v>
@@ -19828,7 +19828,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H671" t="n">
         <v>0</v>
@@ -19886,7 +19886,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G673" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H673" t="n">
         <v>13250</v>
@@ -19915,7 +19915,7 @@
         <v>5.5</v>
       </c>
       <c r="G674" t="n">
-        <v>5.11611604690552</v>
+        <v>5.11611557006836</v>
       </c>
       <c r="H674" t="n">
         <v>6750</v>
@@ -19973,7 +19973,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G676" t="n">
-        <v>5.16262626647949</v>
+        <v>5.16262674331665</v>
       </c>
       <c r="H676" t="n">
         <v>1000</v>
@@ -20002,7 +20002,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H677" t="n">
         <v>19750</v>
@@ -20031,7 +20031,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H678" t="n">
         <v>1750</v>
@@ -20060,7 +20060,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G679" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H679" t="n">
         <v>4750</v>
@@ -20089,7 +20089,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G680" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H680" t="n">
         <v>500</v>
@@ -20118,7 +20118,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H681" t="n">
         <v>0</v>
@@ -20147,7 +20147,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G682" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H682" t="n">
         <v>0</v>
@@ -20350,7 +20350,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G689" t="n">
-        <v>5.39517736434937</v>
+        <v>5.39517688751221</v>
       </c>
       <c r="H689" t="n">
         <v>1250</v>
@@ -20408,7 +20408,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G691" t="n">
-        <v>5.16262626647949</v>
+        <v>5.16262674331665</v>
       </c>
       <c r="H691" t="n">
         <v>1250</v>
@@ -20466,7 +20466,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G693" t="n">
-        <v>5.16262626647949</v>
+        <v>5.16262674331665</v>
       </c>
       <c r="H693" t="n">
         <v>750</v>
@@ -20495,7 +20495,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G694" t="n">
-        <v>5.16262626647949</v>
+        <v>5.16262674331665</v>
       </c>
       <c r="H694" t="n">
         <v>0</v>
@@ -20524,7 +20524,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G695" t="n">
-        <v>5.16262626647949</v>
+        <v>5.16262674331665</v>
       </c>
       <c r="H695" t="n">
         <v>0</v>
@@ -20553,7 +20553,7 @@
         <v>5.5</v>
       </c>
       <c r="G696" t="n">
-        <v>5.11611604690552</v>
+        <v>5.11611557006836</v>
       </c>
       <c r="H696" t="n">
         <v>1000</v>
@@ -20582,7 +20582,7 @@
         <v>5.5</v>
       </c>
       <c r="G697" t="n">
-        <v>5.11611604690552</v>
+        <v>5.11611557006836</v>
       </c>
       <c r="H697" t="n">
         <v>3000</v>
@@ -20611,7 +20611,7 @@
         <v>5.5</v>
       </c>
       <c r="G698" t="n">
-        <v>5.11611604690552</v>
+        <v>5.11611557006836</v>
       </c>
       <c r="H698" t="n">
         <v>0</v>
@@ -20640,7 +20640,7 @@
         <v>5.5</v>
       </c>
       <c r="G699" t="n">
-        <v>5.11611604690552</v>
+        <v>5.11611557006836</v>
       </c>
       <c r="H699" t="n">
         <v>0</v>
@@ -20669,7 +20669,7 @@
         <v>5.5</v>
       </c>
       <c r="G700" t="n">
-        <v>5.11611604690552</v>
+        <v>5.11611557006836</v>
       </c>
       <c r="H700" t="n">
         <v>250</v>
@@ -20698,7 +20698,7 @@
         <v>5.5</v>
       </c>
       <c r="G701" t="n">
-        <v>5.11611604690552</v>
+        <v>5.11611557006836</v>
       </c>
       <c r="H701" t="n">
         <v>8500</v>
@@ -20727,7 +20727,7 @@
         <v>5.5</v>
       </c>
       <c r="G702" t="n">
-        <v>5.11611604690552</v>
+        <v>5.11611557006836</v>
       </c>
       <c r="H702" t="n">
         <v>0</v>
@@ -20756,7 +20756,7 @@
         <v>5.5</v>
       </c>
       <c r="G703" t="n">
-        <v>5.11611604690552</v>
+        <v>5.11611557006836</v>
       </c>
       <c r="H703" t="n">
         <v>20000</v>
@@ -20930,7 +20930,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G709" t="n">
-        <v>4.52078580856323</v>
+        <v>4.52078628540039</v>
       </c>
       <c r="H709" t="n">
         <v>36250</v>
@@ -20988,7 +20988,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G711" t="n">
-        <v>4.69752502441406</v>
+        <v>4.6975245475769</v>
       </c>
       <c r="H711" t="n">
         <v>2250</v>
@@ -21017,7 +21017,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G712" t="n">
-        <v>4.69752502441406</v>
+        <v>4.6975245475769</v>
       </c>
       <c r="H712" t="n">
         <v>0</v>
@@ -21046,7 +21046,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G713" t="n">
-        <v>4.69752502441406</v>
+        <v>4.6975245475769</v>
       </c>
       <c r="H713" t="n">
         <v>250</v>
@@ -21075,7 +21075,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G714" t="n">
-        <v>4.5579948425293</v>
+        <v>4.55799436569214</v>
       </c>
       <c r="H714" t="n">
         <v>4500</v>
@@ -21104,7 +21104,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G715" t="n">
-        <v>4.59520244598389</v>
+        <v>4.59520196914673</v>
       </c>
       <c r="H715" t="n">
         <v>250</v>
@@ -21133,7 +21133,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G716" t="n">
-        <v>4.46497392654419</v>
+        <v>4.46497440338135</v>
       </c>
       <c r="H716" t="n">
         <v>22500</v>
@@ -21423,7 +21423,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G726" t="n">
-        <v>4.05568504333496</v>
+        <v>4.0556845664978</v>
       </c>
       <c r="H726" t="n">
         <v>6000</v>
@@ -21452,7 +21452,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G727" t="n">
-        <v>4.24172496795654</v>
+        <v>4.2417254447937</v>
       </c>
       <c r="H727" t="n">
         <v>1250</v>
@@ -21510,7 +21510,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>4.27893352508545</v>
+        <v>4.27893304824829</v>
       </c>
       <c r="H729" t="n">
         <v>1250</v>
@@ -21539,7 +21539,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G730" t="n">
-        <v>4.27893352508545</v>
+        <v>4.27893304824829</v>
       </c>
       <c r="H730" t="n">
         <v>0</v>
@@ -21858,7 +21858,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G741" t="n">
-        <v>4.48357820510864</v>
+        <v>4.4835786819458</v>
       </c>
       <c r="H741" t="n">
         <v>2250</v>
@@ -21887,7 +21887,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G742" t="n">
-        <v>4.59520244598389</v>
+        <v>4.59520196914673</v>
       </c>
       <c r="H742" t="n">
         <v>2250</v>
@@ -21916,7 +21916,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G743" t="n">
-        <v>4.59520244598389</v>
+        <v>4.59520196914673</v>
       </c>
       <c r="H743" t="n">
         <v>0</v>
@@ -21945,7 +21945,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G744" t="n">
-        <v>4.59520244598389</v>
+        <v>4.59520196914673</v>
       </c>
       <c r="H744" t="n">
         <v>1000</v>
@@ -21974,7 +21974,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G745" t="n">
-        <v>4.59520244598389</v>
+        <v>4.59520196914673</v>
       </c>
       <c r="H745" t="n">
         <v>0</v>
@@ -22003,7 +22003,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G746" t="n">
-        <v>4.48357820510864</v>
+        <v>4.4835786819458</v>
       </c>
       <c r="H746" t="n">
         <v>4500</v>
@@ -22032,7 +22032,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G747" t="n">
-        <v>4.48357820510864</v>
+        <v>4.4835786819458</v>
       </c>
       <c r="H747" t="n">
         <v>0</v>
@@ -22061,7 +22061,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G748" t="n">
-        <v>4.40916109085083</v>
+        <v>4.40916156768799</v>
       </c>
       <c r="H748" t="n">
         <v>500</v>
@@ -22090,7 +22090,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G749" t="n">
-        <v>4.40916109085083</v>
+        <v>4.40916156768799</v>
       </c>
       <c r="H749" t="n">
         <v>0</v>
@@ -22322,7 +22322,7 @@
         <v>5</v>
       </c>
       <c r="G757" t="n">
-        <v>4.65101480484009</v>
+        <v>4.65101432800293</v>
       </c>
       <c r="H757" t="n">
         <v>2750</v>
@@ -22351,7 +22351,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G758" t="n">
-        <v>4.69752502441406</v>
+        <v>4.6975245475769</v>
       </c>
       <c r="H758" t="n">
         <v>250</v>
@@ -22612,7 +22612,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G767" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H767" t="n">
         <v>6000</v>
@@ -22641,7 +22641,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H768" t="n">
         <v>500</v>
@@ -22670,7 +22670,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G769" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H769" t="n">
         <v>0</v>
@@ -22786,7 +22786,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G773" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H773" t="n">
         <v>3750</v>
@@ -22873,7 +22873,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G776" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H776" t="n">
         <v>2750</v>
@@ -22960,7 +22960,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G779" t="n">
-        <v>5.16262626647949</v>
+        <v>5.16262674331665</v>
       </c>
       <c r="H779" t="n">
         <v>2250</v>
@@ -22989,7 +22989,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G780" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H780" t="n">
         <v>40750</v>
@@ -23047,7 +23047,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G782" t="n">
-        <v>5.39517736434937</v>
+        <v>5.39517688751221</v>
       </c>
       <c r="H782" t="n">
         <v>1750</v>
@@ -23076,7 +23076,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G783" t="n">
-        <v>5.6742377281189</v>
+        <v>5.67423725128174</v>
       </c>
       <c r="H783" t="n">
         <v>6750</v>
@@ -23134,7 +23134,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G785" t="n">
-        <v>5.9998083114624</v>
+        <v>5.99980878829956</v>
       </c>
       <c r="H785" t="n">
         <v>6250</v>
@@ -23163,7 +23163,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G786" t="n">
-        <v>5.95329856872559</v>
+        <v>5.95329809188843</v>
       </c>
       <c r="H786" t="n">
         <v>750</v>
@@ -23192,7 +23192,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G787" t="n">
-        <v>5.95329856872559</v>
+        <v>5.95329809188843</v>
       </c>
       <c r="H787" t="n">
         <v>0</v>
@@ -23221,7 +23221,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G788" t="n">
-        <v>5.86027812957764</v>
+        <v>5.86027860641479</v>
       </c>
       <c r="H788" t="n">
         <v>3250</v>
@@ -23250,7 +23250,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G789" t="n">
-        <v>5.86027812957764</v>
+        <v>5.86027860641479</v>
       </c>
       <c r="H789" t="n">
         <v>1500</v>
@@ -23308,7 +23308,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G791" t="n">
-        <v>5.86027812957764</v>
+        <v>5.86027860641479</v>
       </c>
       <c r="H791" t="n">
         <v>4750</v>
@@ -23337,7 +23337,7 @@
         <v>6.25</v>
       </c>
       <c r="G792" t="n">
-        <v>5.81376838684082</v>
+        <v>5.81376791000366</v>
       </c>
       <c r="H792" t="n">
         <v>2000</v>
@@ -23366,7 +23366,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G793" t="n">
-        <v>5.6742377281189</v>
+        <v>5.67423725128174</v>
       </c>
       <c r="H793" t="n">
         <v>1250</v>
@@ -23511,7 +23511,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G798" t="n">
-        <v>5.39517736434937</v>
+        <v>5.39517688751221</v>
       </c>
       <c r="H798" t="n">
         <v>1000</v>
@@ -23627,7 +23627,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G802" t="n">
-        <v>5.53470754623413</v>
+        <v>5.53470706939697</v>
       </c>
       <c r="H802" t="n">
         <v>750</v>
@@ -23656,7 +23656,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G803" t="n">
-        <v>5.39517736434937</v>
+        <v>5.39517688751221</v>
       </c>
       <c r="H803" t="n">
         <v>750</v>
@@ -23714,7 +23714,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G805" t="n">
-        <v>5.39517736434937</v>
+        <v>5.39517688751221</v>
       </c>
       <c r="H805" t="n">
         <v>2750</v>
@@ -23743,7 +23743,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G806" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H806" t="n">
         <v>1750</v>
@@ -23772,7 +23772,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G807" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H807" t="n">
         <v>0</v>
@@ -23801,7 +23801,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G808" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H808" t="n">
         <v>0</v>
@@ -23830,7 +23830,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G809" t="n">
-        <v>5.3021559715271</v>
+        <v>5.30215644836426</v>
       </c>
       <c r="H809" t="n">
         <v>0</v>
@@ -23888,7 +23888,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G811" t="n">
-        <v>5.16262626647949</v>
+        <v>5.16262674331665</v>
       </c>
       <c r="H811" t="n">
         <v>2500</v>
@@ -24033,7 +24033,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G816" t="n">
-        <v>5.16262626647949</v>
+        <v>5.16262674331665</v>
       </c>
       <c r="H816" t="n">
         <v>2750</v>
@@ -24062,7 +24062,7 @@
         <v>5.5</v>
       </c>
       <c r="G817" t="n">
-        <v>5.11611604690552</v>
+        <v>5.11611557006836</v>
       </c>
       <c r="H817" t="n">
         <v>4000</v>
@@ -24091,7 +24091,7 @@
         <v>5.5</v>
       </c>
       <c r="G818" t="n">
-        <v>5.11611604690552</v>
+        <v>5.11611557006836</v>
       </c>
       <c r="H818" t="n">
         <v>2000</v>
@@ -24120,7 +24120,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G819" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H819" t="n">
         <v>1000</v>
@@ -24294,7 +24294,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G825" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H825" t="n">
         <v>500</v>
@@ -24323,7 +24323,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G826" t="n">
-        <v>4.97658586502075</v>
+        <v>4.97658538818359</v>
       </c>
       <c r="H826" t="n">
         <v>1000</v>
@@ -24352,7 +24352,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G827" t="n">
-        <v>5.02309560775757</v>
+        <v>5.02309608459473</v>
       </c>
       <c r="H827" t="n">
         <v>250</v>
@@ -24439,7 +24439,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G830" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H830" t="n">
         <v>9000</v>
@@ -24497,7 +24497,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G832" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H832" t="n">
         <v>750</v>
@@ -24526,7 +24526,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G833" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H833" t="n">
         <v>500</v>
@@ -24555,7 +24555,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G834" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -24642,7 +24642,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G837" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H837" t="n">
         <v>1500</v>
@@ -24845,7 +24845,7 @@
         <v>5</v>
       </c>
       <c r="G844" t="n">
-        <v>4.65101480484009</v>
+        <v>4.65101432800293</v>
       </c>
       <c r="H844" t="n">
         <v>250</v>
@@ -24874,7 +24874,7 @@
         <v>5</v>
       </c>
       <c r="G845" t="n">
-        <v>4.65101480484009</v>
+        <v>4.65101432800293</v>
       </c>
       <c r="H845" t="n">
         <v>0</v>
@@ -24903,7 +24903,7 @@
         <v>5</v>
       </c>
       <c r="G846" t="n">
-        <v>4.65101480484009</v>
+        <v>4.65101432800293</v>
       </c>
       <c r="H846" t="n">
         <v>500</v>
@@ -24932,7 +24932,7 @@
         <v>5</v>
       </c>
       <c r="G847" t="n">
-        <v>4.65101480484009</v>
+        <v>4.65101432800293</v>
       </c>
       <c r="H847" t="n">
         <v>0</v>
@@ -24990,7 +24990,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G849" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H849" t="n">
         <v>500</v>
@@ -25019,7 +25019,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G850" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H850" t="n">
         <v>1000</v>
@@ -25048,7 +25048,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G851" t="n">
-        <v>4.83705520629883</v>
+        <v>4.83705472946167</v>
       </c>
       <c r="H851" t="n">
         <v>1000</v>
@@ -25077,7 +25077,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G852" t="n">
-        <v>4.69752502441406</v>
+        <v>4.6975245475769</v>
       </c>
       <c r="H852" t="n">
         <v>1000</v>
@@ -25106,7 +25106,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G853" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H853" t="n">
         <v>2500</v>
@@ -25193,7 +25193,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G856" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H856" t="n">
         <v>250</v>
@@ -25222,7 +25222,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G857" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H857" t="n">
         <v>0</v>
@@ -25251,7 +25251,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G858" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H858" t="n">
         <v>250</v>
@@ -25280,7 +25280,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G859" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H859" t="n">
         <v>1000</v>
@@ -25309,7 +25309,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G860" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H860" t="n">
         <v>1000</v>
@@ -25396,7 +25396,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H863" t="n">
         <v>1000</v>
@@ -25425,7 +25425,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G864" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H864" t="n">
         <v>250</v>
@@ -25454,7 +25454,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G865" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H865" t="n">
         <v>250</v>
@@ -25483,7 +25483,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G866" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -25512,7 +25512,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G867" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -25570,7 +25570,7 @@
         <v>5</v>
       </c>
       <c r="G869" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H869" t="n">
         <v>1000</v>
@@ -25599,7 +25599,7 @@
         <v>5</v>
       </c>
       <c r="G870" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H870" t="n">
         <v>0</v>
@@ -25628,7 +25628,7 @@
         <v>5</v>
       </c>
       <c r="G871" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H871" t="n">
         <v>0</v>
@@ -25657,7 +25657,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G872" t="n">
-        <v>4.79242467880249</v>
+        <v>4.79242420196533</v>
       </c>
       <c r="H872" t="n">
         <v>1000</v>
@@ -25686,7 +25686,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G873" t="n">
-        <v>4.79242467880249</v>
+        <v>4.79242420196533</v>
       </c>
       <c r="H873" t="n">
         <v>0</v>
@@ -25715,7 +25715,7 @@
         <v>5</v>
       </c>
       <c r="G874" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H874" t="n">
         <v>1500</v>
@@ -25802,7 +25802,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G877" t="n">
-        <v>4.70701503753662</v>
+        <v>4.70701456069946</v>
       </c>
       <c r="H877" t="n">
         <v>250</v>
@@ -25831,7 +25831,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>4.70701503753662</v>
+        <v>4.70701456069946</v>
       </c>
       <c r="H878" t="n">
         <v>0</v>
@@ -26005,7 +26005,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G884" t="n">
-        <v>4.93477344512939</v>
+        <v>4.93477296829224</v>
       </c>
       <c r="H884" t="n">
         <v>3000</v>
@@ -26034,7 +26034,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G885" t="n">
-        <v>4.79242467880249</v>
+        <v>4.79242420196533</v>
       </c>
       <c r="H885" t="n">
         <v>1750</v>
@@ -26150,7 +26150,7 @@
         <v>5</v>
       </c>
       <c r="G889" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H889" t="n">
         <v>8000</v>
@@ -26179,7 +26179,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G890" t="n">
-        <v>4.79242467880249</v>
+        <v>4.79242420196533</v>
       </c>
       <c r="H890" t="n">
         <v>500</v>
@@ -26208,7 +26208,7 @@
         <v>5</v>
       </c>
       <c r="G891" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H891" t="n">
         <v>750</v>
@@ -26237,7 +26237,7 @@
         <v>5</v>
       </c>
       <c r="G892" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H892" t="n">
         <v>1750</v>
@@ -26266,7 +26266,7 @@
         <v>5</v>
       </c>
       <c r="G893" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H893" t="n">
         <v>750</v>
@@ -26295,7 +26295,7 @@
         <v>5</v>
       </c>
       <c r="G894" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -26324,7 +26324,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G895" t="n">
-        <v>4.79242467880249</v>
+        <v>4.79242420196533</v>
       </c>
       <c r="H895" t="n">
         <v>2000</v>
@@ -26353,7 +26353,7 @@
         <v>5</v>
       </c>
       <c r="G896" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H896" t="n">
         <v>750</v>
@@ -26382,7 +26382,7 @@
         <v>5</v>
       </c>
       <c r="G897" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H897" t="n">
         <v>500</v>
@@ -26411,7 +26411,7 @@
         <v>5</v>
       </c>
       <c r="G898" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H898" t="n">
         <v>0</v>
@@ -26440,7 +26440,7 @@
         <v>5</v>
       </c>
       <c r="G899" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H899" t="n">
         <v>0</v>
@@ -26469,7 +26469,7 @@
         <v>5</v>
       </c>
       <c r="G900" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H900" t="n">
         <v>500</v>
@@ -26585,7 +26585,7 @@
         <v>5</v>
       </c>
       <c r="G904" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H904" t="n">
         <v>1000</v>
@@ -26614,7 +26614,7 @@
         <v>5</v>
       </c>
       <c r="G905" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H905" t="n">
         <v>3250</v>
@@ -26643,7 +26643,7 @@
         <v>5</v>
       </c>
       <c r="G906" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H906" t="n">
         <v>0</v>
@@ -26672,7 +26672,7 @@
         <v>5</v>
       </c>
       <c r="G907" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H907" t="n">
         <v>1250</v>
@@ -26701,7 +26701,7 @@
         <v>5</v>
       </c>
       <c r="G908" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H908" t="n">
         <v>0</v>
@@ -26730,7 +26730,7 @@
         <v>5</v>
       </c>
       <c r="G909" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H909" t="n">
         <v>500</v>
@@ -26759,7 +26759,7 @@
         <v>5</v>
       </c>
       <c r="G910" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H910" t="n">
         <v>0</v>
@@ -26788,7 +26788,7 @@
         <v>5</v>
       </c>
       <c r="G911" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -26817,7 +26817,7 @@
         <v>5</v>
       </c>
       <c r="G912" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -26846,7 +26846,7 @@
         <v>5</v>
       </c>
       <c r="G913" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H913" t="n">
         <v>0</v>
@@ -26875,7 +26875,7 @@
         <v>5</v>
       </c>
       <c r="G914" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H914" t="n">
         <v>500</v>
@@ -26904,7 +26904,7 @@
         <v>5</v>
       </c>
       <c r="G915" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H915" t="n">
         <v>1500</v>
@@ -26933,7 +26933,7 @@
         <v>5</v>
       </c>
       <c r="G916" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H916" t="n">
         <v>1000</v>
@@ -26962,7 +26962,7 @@
         <v>5</v>
       </c>
       <c r="G917" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -26991,7 +26991,7 @@
         <v>5</v>
       </c>
       <c r="G918" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H918" t="n">
         <v>500</v>
@@ -27020,7 +27020,7 @@
         <v>5</v>
       </c>
       <c r="G919" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H919" t="n">
         <v>0</v>
@@ -27049,7 +27049,7 @@
         <v>5</v>
       </c>
       <c r="G920" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H920" t="n">
         <v>0</v>
@@ -27078,7 +27078,7 @@
         <v>5</v>
       </c>
       <c r="G921" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>
@@ -27165,7 +27165,7 @@
         <v>5</v>
       </c>
       <c r="G924" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H924" t="n">
         <v>4000</v>
@@ -27194,7 +27194,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G925" t="n">
-        <v>4.61211490631104</v>
+        <v>4.61211538314819</v>
       </c>
       <c r="H925" t="n">
         <v>5750</v>
@@ -27223,7 +27223,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G926" t="n">
-        <v>4.61211490631104</v>
+        <v>4.61211538314819</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -27252,7 +27252,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G927" t="n">
-        <v>4.61211490631104</v>
+        <v>4.61211538314819</v>
       </c>
       <c r="H927" t="n">
         <v>0</v>
@@ -27281,7 +27281,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G928" t="n">
-        <v>4.61211490631104</v>
+        <v>4.61211538314819</v>
       </c>
       <c r="H928" t="n">
         <v>0</v>
@@ -27310,7 +27310,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G929" t="n">
-        <v>4.61211490631104</v>
+        <v>4.61211538314819</v>
       </c>
       <c r="H929" t="n">
         <v>0</v>
@@ -27339,7 +27339,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G930" t="n">
-        <v>4.61211490631104</v>
+        <v>4.61211538314819</v>
       </c>
       <c r="H930" t="n">
         <v>0</v>
@@ -27368,7 +27368,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G931" t="n">
-        <v>4.61211490631104</v>
+        <v>4.61211538314819</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -27426,7 +27426,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G933" t="n">
-        <v>4.79242467880249</v>
+        <v>4.79242420196533</v>
       </c>
       <c r="H933" t="n">
         <v>750</v>
@@ -27455,7 +27455,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G934" t="n">
-        <v>4.79242467880249</v>
+        <v>4.79242420196533</v>
       </c>
       <c r="H934" t="n">
         <v>0</v>
@@ -27484,7 +27484,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G935" t="n">
-        <v>4.79242467880249</v>
+        <v>4.79242420196533</v>
       </c>
       <c r="H935" t="n">
         <v>250</v>
@@ -27629,7 +27629,7 @@
         <v>5</v>
       </c>
       <c r="G940" t="n">
-        <v>4.7449746131897</v>
+        <v>4.74497413635254</v>
       </c>
       <c r="H940" t="n">
         <v>500</v>
@@ -27658,7 +27658,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G941" t="n">
-        <v>4.63109493255615</v>
+        <v>4.63109540939331</v>
       </c>
       <c r="H941" t="n">
         <v>500</v>
@@ -27687,7 +27687,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G942" t="n">
-        <v>4.65007543563843</v>
+        <v>4.65007495880127</v>
       </c>
       <c r="H942" t="n">
         <v>1500</v>
@@ -27716,7 +27716,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G943" t="n">
-        <v>4.65007543563843</v>
+        <v>4.65007495880127</v>
       </c>
       <c r="H943" t="n">
         <v>0</v>
@@ -27745,7 +27745,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G944" t="n">
-        <v>4.65007543563843</v>
+        <v>4.65007495880127</v>
       </c>
       <c r="H944" t="n">
         <v>0</v>
@@ -27774,7 +27774,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G945" t="n">
-        <v>4.65007543563843</v>
+        <v>4.65007495880127</v>
       </c>
       <c r="H945" t="n">
         <v>0</v>
@@ -27803,7 +27803,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G946" t="n">
-        <v>4.65007543563843</v>
+        <v>4.65007495880127</v>
       </c>
       <c r="H946" t="n">
         <v>0</v>
@@ -27832,7 +27832,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G947" t="n">
-        <v>4.65007543563843</v>
+        <v>4.65007495880127</v>
       </c>
       <c r="H947" t="n">
         <v>0</v>
@@ -27861,7 +27861,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G948" t="n">
-        <v>4.65007543563843</v>
+        <v>4.65007495880127</v>
       </c>
       <c r="H948" t="n">
         <v>0</v>
@@ -27890,7 +27890,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G949" t="n">
-        <v>4.65007543563843</v>
+        <v>4.65007495880127</v>
       </c>
       <c r="H949" t="n">
         <v>0</v>
@@ -27919,7 +27919,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G950" t="n">
-        <v>4.63109493255615</v>
+        <v>4.63109540939331</v>
       </c>
       <c r="H950" t="n">
         <v>2250</v>
@@ -27948,7 +27948,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G951" t="n">
-        <v>4.63109493255615</v>
+        <v>4.63109540939331</v>
       </c>
       <c r="H951" t="n">
         <v>0</v>
@@ -27977,7 +27977,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G952" t="n">
-        <v>4.63109493255615</v>
+        <v>4.63109540939331</v>
       </c>
       <c r="H952" t="n">
         <v>250</v>
@@ -28006,7 +28006,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G953" t="n">
-        <v>4.63109493255615</v>
+        <v>4.63109540939331</v>
       </c>
       <c r="H953" t="n">
         <v>0</v>
@@ -28180,7 +28180,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G959" t="n">
-        <v>4.49823522567749</v>
+        <v>4.49823570251465</v>
       </c>
       <c r="H959" t="n">
         <v>1250</v>
@@ -28238,7 +28238,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G961" t="n">
-        <v>4.49823522567749</v>
+        <v>4.49823570251465</v>
       </c>
       <c r="H961" t="n">
         <v>1000</v>
@@ -28267,7 +28267,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G962" t="n">
-        <v>4.36537647247314</v>
+        <v>4.36537599563599</v>
       </c>
       <c r="H962" t="n">
         <v>1250</v>
@@ -28296,7 +28296,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G963" t="n">
-        <v>4.36537647247314</v>
+        <v>4.36537599563599</v>
       </c>
       <c r="H963" t="n">
         <v>2250</v>
@@ -28325,7 +28325,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G964" t="n">
-        <v>4.32741641998291</v>
+        <v>4.32741689682007</v>
       </c>
       <c r="H964" t="n">
         <v>1500</v>
@@ -28528,7 +28528,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G971" t="n">
-        <v>4.36537647247314</v>
+        <v>4.36537599563599</v>
       </c>
       <c r="H971" t="n">
         <v>7500</v>
@@ -28644,7 +28644,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G975" t="n">
-        <v>4.13761806488037</v>
+        <v>4.13761758804321</v>
       </c>
       <c r="H975" t="n">
         <v>2000</v>
@@ -28905,7 +28905,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G984" t="n">
-        <v>4.36537647247314</v>
+        <v>4.36537599563599</v>
       </c>
       <c r="H984" t="n">
         <v>1250</v>
@@ -28934,7 +28934,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G985" t="n">
-        <v>4.36537647247314</v>
+        <v>4.36537599563599</v>
       </c>
       <c r="H985" t="n">
         <v>1750</v>
@@ -28963,7 +28963,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G986" t="n">
-        <v>4.36537647247314</v>
+        <v>4.36537599563599</v>
       </c>
       <c r="H986" t="n">
         <v>5750</v>
@@ -28992,7 +28992,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G987" t="n">
-        <v>4.34639644622803</v>
+        <v>4.34639692306519</v>
       </c>
       <c r="H987" t="n">
         <v>750</v>
@@ -29050,7 +29050,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G989" t="n">
-        <v>4.32741641998291</v>
+        <v>4.32741689682007</v>
       </c>
       <c r="H989" t="n">
         <v>4250</v>
@@ -29079,7 +29079,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G990" t="n">
-        <v>4.36537647247314</v>
+        <v>4.36537599563599</v>
       </c>
       <c r="H990" t="n">
         <v>750</v>
@@ -29137,7 +29137,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G992" t="n">
-        <v>4.36537647247314</v>
+        <v>4.36537599563599</v>
       </c>
       <c r="H992" t="n">
         <v>4000</v>
@@ -29514,7 +29514,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.55517530441284</v>
+        <v>4.55517578125</v>
       </c>
       <c r="H1005" t="n">
         <v>500</v>
@@ -29572,7 +29572,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.57415533065796</v>
+        <v>4.57415580749512</v>
       </c>
       <c r="H1007" t="n">
         <v>18500</v>
@@ -29688,7 +29688,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.63109493255615</v>
+        <v>4.63109540939331</v>
       </c>
       <c r="H1011" t="n">
         <v>500</v>
@@ -30036,7 +30036,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.32741641998291</v>
+        <v>4.32741689682007</v>
       </c>
       <c r="H1023" t="n">
         <v>500</v>
@@ -30065,7 +30065,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.32741641998291</v>
+        <v>4.32741689682007</v>
       </c>
       <c r="H1024" t="n">
         <v>750</v>
@@ -30094,7 +30094,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.32741641998291</v>
+        <v>4.32741689682007</v>
       </c>
       <c r="H1025" t="n">
         <v>0</v>
@@ -30123,7 +30123,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.32741641998291</v>
+        <v>4.32741689682007</v>
       </c>
       <c r="H1026" t="n">
         <v>0</v>
@@ -30152,7 +30152,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.32741641998291</v>
+        <v>4.32741689682007</v>
       </c>
       <c r="H1027" t="n">
         <v>0</v>
@@ -30210,7 +30210,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.13761806488037</v>
+        <v>4.13761758804321</v>
       </c>
       <c r="H1029" t="n">
         <v>2000</v>
@@ -30239,7 +30239,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1030" t="n">
-        <v>4.11863803863525</v>
+        <v>4.1186375617981</v>
       </c>
       <c r="H1030" t="n">
         <v>1250</v>
@@ -30384,7 +30384,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.85291910171509</v>
+        <v>3.85291934013367</v>
       </c>
       <c r="H1035" t="n">
         <v>7500</v>
@@ -30587,7 +30587,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.08067846298218</v>
+        <v>4.08067798614502</v>
       </c>
       <c r="H1042" t="n">
         <v>750</v>
@@ -30790,7 +30790,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.08067846298218</v>
+        <v>4.08067798614502</v>
       </c>
       <c r="H1049" t="n">
         <v>250</v>
@@ -30819,7 +30819,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.08067846298218</v>
+        <v>4.08067798614502</v>
       </c>
       <c r="H1050" t="n">
         <v>0</v>
@@ -30848,7 +30848,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.08067846298218</v>
+        <v>4.08067798614502</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -30906,7 +30906,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1053" t="n">
-        <v>4.08067846298218</v>
+        <v>4.08067798614502</v>
       </c>
       <c r="H1053" t="n">
         <v>4500</v>
@@ -30993,7 +30993,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.94781875610352</v>
+        <v>3.94781851768494</v>
       </c>
       <c r="H1056" t="n">
         <v>1750</v>
@@ -31022,7 +31022,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.94781875610352</v>
+        <v>3.94781851768494</v>
       </c>
       <c r="H1057" t="n">
         <v>0</v>
@@ -31138,7 +31138,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.89087915420532</v>
+        <v>3.89087891578674</v>
       </c>
       <c r="H1061" t="n">
         <v>5750</v>
@@ -31225,7 +31225,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.6061806678772</v>
+        <v>3.60618042945862</v>
       </c>
       <c r="H1064" t="n">
         <v>3750</v>
@@ -31747,7 +31747,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.58720064163208</v>
+        <v>3.5872004032135</v>
       </c>
       <c r="H1082" t="n">
         <v>2750</v>
@@ -31921,7 +31921,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.6061806678772</v>
+        <v>3.60618042945862</v>
       </c>
       <c r="H1088" t="n">
         <v>500</v>
@@ -32037,7 +32037,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.81495928764343</v>
+        <v>3.81495952606201</v>
       </c>
       <c r="H1092" t="n">
         <v>19500</v>
@@ -32153,7 +32153,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1096" t="n">
-        <v>4.11863803863525</v>
+        <v>4.1186375617981</v>
       </c>
       <c r="H1096" t="n">
         <v>3750</v>

--- a/data/PLN.MI.xlsx
+++ b/data/PLN.MI.xlsx
@@ -543,7 +543,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G6" t="n">
-        <v>4.21765375137329</v>
+        <v>4.21765327453613</v>
       </c>
       <c r="H6" t="n">
         <v>37000</v>
@@ -630,7 +630,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G9" t="n">
-        <v>4.12576532363892</v>
+        <v>4.12576484680176</v>
       </c>
       <c r="H9" t="n">
         <v>11500</v>
@@ -659,7 +659,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G10" t="n">
-        <v>4.04306650161743</v>
+        <v>4.04306697845459</v>
       </c>
       <c r="H10" t="n">
         <v>53000</v>
@@ -775,7 +775,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G14" t="n">
-        <v>3.95117831230164</v>
+        <v>3.95117878913879</v>
       </c>
       <c r="H14" t="n">
         <v>19000</v>
@@ -833,7 +833,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G16" t="n">
-        <v>3.84091281890869</v>
+        <v>3.84091305732727</v>
       </c>
       <c r="H16" t="n">
         <v>21500</v>
@@ -920,7 +920,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G19" t="n">
-        <v>3.95117831230164</v>
+        <v>3.95117878913879</v>
       </c>
       <c r="H19" t="n">
         <v>44000</v>
@@ -1036,7 +1036,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G23" t="n">
-        <v>3.85010194778442</v>
+        <v>3.85010170936584</v>
       </c>
       <c r="H23" t="n">
         <v>32000</v>
@@ -1065,7 +1065,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G24" t="n">
-        <v>3.88685703277588</v>
+        <v>3.8868567943573</v>
       </c>
       <c r="H24" t="n">
         <v>500</v>
@@ -1094,7 +1094,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>3.98793387413025</v>
+        <v>3.98793435096741</v>
       </c>
       <c r="H25" t="n">
         <v>7500</v>
@@ -1413,7 +1413,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G36" t="n">
-        <v>4.06144380569458</v>
+        <v>4.06144428253174</v>
       </c>
       <c r="H36" t="n">
         <v>18500</v>
@@ -1500,7 +1500,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G39" t="n">
-        <v>4.09819936752319</v>
+        <v>4.09819889068604</v>
       </c>
       <c r="H39" t="n">
         <v>3500</v>
@@ -1529,7 +1529,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>4.09819936752319</v>
+        <v>4.09819889068604</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G46" t="n">
-        <v>3.95117831230164</v>
+        <v>3.95117878913879</v>
       </c>
       <c r="H46" t="n">
         <v>4000</v>
@@ -1761,7 +1761,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G48" t="n">
-        <v>3.95117831230164</v>
+        <v>3.95117878913879</v>
       </c>
       <c r="H48" t="n">
         <v>2000</v>
@@ -1790,7 +1790,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G49" t="n">
-        <v>3.95117831230164</v>
+        <v>3.95117878913879</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>4.04306650161743</v>
+        <v>4.04306697845459</v>
       </c>
       <c r="H50" t="n">
         <v>3000</v>
@@ -1877,7 +1877,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G52" t="n">
-        <v>3.92361187934875</v>
+        <v>3.92361235618591</v>
       </c>
       <c r="H52" t="n">
         <v>9500</v>
@@ -1935,7 +1935,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G54" t="n">
-        <v>3.859290599823</v>
+        <v>3.85929036140442</v>
       </c>
       <c r="H54" t="n">
         <v>5000</v>
@@ -1964,7 +1964,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G55" t="n">
-        <v>3.859290599823</v>
+        <v>3.85929036140442</v>
       </c>
       <c r="H55" t="n">
         <v>6000</v>
@@ -2051,7 +2051,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G58" t="n">
-        <v>3.95117831230164</v>
+        <v>3.95117878913879</v>
       </c>
       <c r="H58" t="n">
         <v>3500</v>
@@ -2080,7 +2080,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G59" t="n">
-        <v>3.95117831230164</v>
+        <v>3.95117878913879</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G63" t="n">
-        <v>4.01550006866455</v>
+        <v>4.01550054550171</v>
       </c>
       <c r="H63" t="n">
         <v>40500</v>
@@ -2399,7 +2399,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G70" t="n">
-        <v>4.42899513244629</v>
+        <v>4.42899560928345</v>
       </c>
       <c r="H70" t="n">
         <v>64500</v>
@@ -2573,7 +2573,7 @@
         <v>5</v>
       </c>
       <c r="G76" t="n">
-        <v>4.59439420700073</v>
+        <v>4.59439373016357</v>
       </c>
       <c r="H76" t="n">
         <v>6000</v>
@@ -2718,7 +2718,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G81" t="n">
-        <v>4.87005758285522</v>
+        <v>4.87005710601807</v>
       </c>
       <c r="H81" t="n">
         <v>8000</v>
@@ -2776,7 +2776,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G83" t="n">
-        <v>4.92519044876099</v>
+        <v>4.92518997192383</v>
       </c>
       <c r="H83" t="n">
         <v>3500</v>
@@ -2834,7 +2834,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G85" t="n">
-        <v>4.96194553375244</v>
+        <v>4.96194505691528</v>
       </c>
       <c r="H85" t="n">
         <v>27000</v>
@@ -2950,7 +2950,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G89" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H89" t="n">
         <v>78500</v>
@@ -3008,7 +3008,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G91" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H91" t="n">
         <v>34500</v>
@@ -3066,7 +3066,7 @@
         <v>7</v>
       </c>
       <c r="G93" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215036392212</v>
       </c>
       <c r="H93" t="n">
         <v>93500</v>
@@ -3095,7 +3095,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G94" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H94" t="n">
         <v>29500</v>
@@ -3124,7 +3124,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G95" t="n">
-        <v>6.32188558578491</v>
+        <v>6.32188606262207</v>
       </c>
       <c r="H95" t="n">
         <v>57500</v>
@@ -3153,7 +3153,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>6.45052862167358</v>
+        <v>6.45052814483643</v>
       </c>
       <c r="H96" t="n">
         <v>59500</v>
@@ -3182,7 +3182,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G97" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H97" t="n">
         <v>40000</v>
@@ -3298,7 +3298,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G101" t="n">
-        <v>5.9910888671875</v>
+        <v>5.99108934402466</v>
       </c>
       <c r="H101" t="n">
         <v>7000</v>
@@ -3385,7 +3385,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G104" t="n">
-        <v>6.02784442901611</v>
+        <v>6.02784395217896</v>
       </c>
       <c r="H104" t="n">
         <v>15000</v>
@@ -3443,7 +3443,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G106" t="n">
-        <v>5.95433378219604</v>
+        <v>5.9543342590332</v>
       </c>
       <c r="H106" t="n">
         <v>11500</v>
@@ -3704,7 +3704,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G115" t="n">
-        <v>5.64191579818726</v>
+        <v>5.6419153213501</v>
       </c>
       <c r="H115" t="n">
         <v>21000</v>
@@ -3907,7 +3907,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G122" t="n">
-        <v>5.25598621368408</v>
+        <v>5.25598573684692</v>
       </c>
       <c r="H122" t="n">
         <v>10000</v>
@@ -3936,7 +3936,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G123" t="n">
-        <v>5.23760843276978</v>
+        <v>5.23760890960693</v>
       </c>
       <c r="H123" t="n">
         <v>13000</v>
@@ -4052,7 +4052,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G127" t="n">
-        <v>5.25598621368408</v>
+        <v>5.25598573684692</v>
       </c>
       <c r="H127" t="n">
         <v>22000</v>
@@ -4081,7 +4081,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G128" t="n">
-        <v>5.56840467453003</v>
+        <v>5.56840515136719</v>
       </c>
       <c r="H128" t="n">
         <v>10500</v>
@@ -4110,7 +4110,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G129" t="n">
-        <v>5.43976211547852</v>
+        <v>5.43976163864136</v>
       </c>
       <c r="H129" t="n">
         <v>500</v>
@@ -4168,7 +4168,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G131" t="n">
-        <v>5.43976211547852</v>
+        <v>5.43976163864136</v>
       </c>
       <c r="H131" t="n">
         <v>3500</v>
@@ -4748,7 +4748,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>6.06459999084473</v>
+        <v>6.06459951400757</v>
       </c>
       <c r="H151" t="n">
         <v>5500</v>
@@ -4777,7 +4777,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G152" t="n">
-        <v>6.02784442901611</v>
+        <v>6.02784395217896</v>
       </c>
       <c r="H152" t="n">
         <v>6000</v>
@@ -4806,7 +4806,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G153" t="n">
-        <v>6.06459999084473</v>
+        <v>6.06459951400757</v>
       </c>
       <c r="H153" t="n">
         <v>1000</v>
@@ -4835,7 +4835,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G154" t="n">
-        <v>6.248375415802</v>
+        <v>6.24837589263916</v>
       </c>
       <c r="H154" t="n">
         <v>55500</v>
@@ -4922,7 +4922,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G157" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H157" t="n">
         <v>1000</v>
@@ -4951,7 +4951,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G158" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H158" t="n">
         <v>4500</v>
@@ -4980,7 +4980,7 @@
         <v>7</v>
       </c>
       <c r="G159" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215036392212</v>
       </c>
       <c r="H159" t="n">
         <v>4000</v>
@@ -5009,7 +5009,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G160" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H160" t="n">
         <v>2000</v>
@@ -5038,7 +5038,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G161" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H161" t="n">
         <v>1000</v>
@@ -5067,7 +5067,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G162" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G163" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H163" t="n">
         <v>4500</v>
@@ -5125,7 +5125,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G164" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H164" t="n">
         <v>17000</v>
@@ -5154,7 +5154,7 @@
         <v>7</v>
       </c>
       <c r="G165" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215036392212</v>
       </c>
       <c r="H165" t="n">
         <v>2500</v>
@@ -5212,7 +5212,7 @@
         <v>7</v>
       </c>
       <c r="G167" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215036392212</v>
       </c>
       <c r="H167" t="n">
         <v>2000</v>
@@ -5241,7 +5241,7 @@
         <v>7</v>
       </c>
       <c r="G168" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215036392212</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>7</v>
       </c>
       <c r="G169" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215036392212</v>
       </c>
       <c r="H169" t="n">
         <v>1000</v>
@@ -5299,7 +5299,7 @@
         <v>7</v>
       </c>
       <c r="G170" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215036392212</v>
       </c>
       <c r="H170" t="n">
         <v>1000</v>
@@ -5328,7 +5328,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G171" t="n">
-        <v>6.45052862167358</v>
+        <v>6.45052814483643</v>
       </c>
       <c r="H171" t="n">
         <v>1500</v>
@@ -5357,7 +5357,7 @@
         <v>7</v>
       </c>
       <c r="G172" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215036392212</v>
       </c>
       <c r="H172" t="n">
         <v>1500</v>
@@ -5444,7 +5444,7 @@
         <v>7</v>
       </c>
       <c r="G175" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215036392212</v>
       </c>
       <c r="H175" t="n">
         <v>2000</v>
@@ -5502,7 +5502,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G177" t="n">
-        <v>7.27751970291138</v>
+        <v>7.27751922607422</v>
       </c>
       <c r="H177" t="n">
         <v>28000</v>
@@ -5792,7 +5792,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G187" t="n">
-        <v>7.05698823928833</v>
+        <v>7.05698871612549</v>
       </c>
       <c r="H187" t="n">
         <v>5500</v>
@@ -5850,7 +5850,7 @@
         <v>8</v>
       </c>
       <c r="G189" t="n">
-        <v>7.35102939605713</v>
+        <v>7.35102987289429</v>
       </c>
       <c r="H189" t="n">
         <v>3500</v>
@@ -5908,7 +5908,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G191" t="n">
-        <v>7.14887666702271</v>
+        <v>7.14887714385986</v>
       </c>
       <c r="H191" t="n">
         <v>1000</v>
@@ -6227,7 +6227,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G202" t="n">
-        <v>7.70020389556885</v>
+        <v>7.70020341873169</v>
       </c>
       <c r="H202" t="n">
         <v>6500</v>
@@ -6256,7 +6256,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G203" t="n">
-        <v>7.70020389556885</v>
+        <v>7.70020341873169</v>
       </c>
       <c r="H203" t="n">
         <v>3000</v>
@@ -6343,7 +6343,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G206" t="n">
-        <v>8.12288761138916</v>
+        <v>8.12288856506348</v>
       </c>
       <c r="H206" t="n">
         <v>16500</v>
@@ -6401,7 +6401,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G208" t="n">
-        <v>8.08613300323486</v>
+        <v>8.08613395690918</v>
       </c>
       <c r="H208" t="n">
         <v>3000</v>
@@ -6430,7 +6430,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G209" t="n">
-        <v>8.0310001373291</v>
+        <v>8.03100109100342</v>
       </c>
       <c r="H209" t="n">
         <v>3000</v>
@@ -6488,7 +6488,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G211" t="n">
-        <v>8.15964317321777</v>
+        <v>8.15964221954346</v>
       </c>
       <c r="H211" t="n">
         <v>8000</v>
@@ -6517,7 +6517,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G212" t="n">
-        <v>8.12288761138916</v>
+        <v>8.12288856506348</v>
       </c>
       <c r="H212" t="n">
         <v>500</v>
@@ -6575,7 +6575,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G214" t="n">
-        <v>8.25153064727783</v>
+        <v>8.25152969360352</v>
       </c>
       <c r="H214" t="n">
         <v>1000</v>
@@ -6691,7 +6691,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G218" t="n">
-        <v>8.69259262084961</v>
+        <v>8.69259357452393</v>
       </c>
       <c r="H218" t="n">
         <v>3000</v>
@@ -6749,7 +6749,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>8.69259262084961</v>
+        <v>8.69259357452393</v>
       </c>
       <c r="H220" t="n">
         <v>3500</v>
@@ -6778,7 +6778,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>8.69259262084961</v>
+        <v>8.69259357452393</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G228" t="n">
-        <v>8.63745975494385</v>
+        <v>8.63746070861816</v>
       </c>
       <c r="H228" t="n">
         <v>20000</v>
@@ -7010,7 +7010,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G229" t="n">
-        <v>8.63745975494385</v>
+        <v>8.63746070861816</v>
       </c>
       <c r="H229" t="n">
         <v>12500</v>
@@ -7039,7 +7039,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G230" t="n">
-        <v>8.63745975494385</v>
+        <v>8.63746070861816</v>
       </c>
       <c r="H230" t="n">
         <v>7000</v>
@@ -7126,7 +7126,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G233" t="n">
-        <v>8.63745975494385</v>
+        <v>8.63746070861816</v>
       </c>
       <c r="H233" t="n">
         <v>11000</v>
@@ -7271,7 +7271,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G238" t="n">
-        <v>8.25153064727783</v>
+        <v>8.25152969360352</v>
       </c>
       <c r="H238" t="n">
         <v>1000</v>
@@ -7329,7 +7329,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G240" t="n">
-        <v>8.25153064727783</v>
+        <v>8.25152969360352</v>
       </c>
       <c r="H240" t="n">
         <v>2500</v>
@@ -7358,7 +7358,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G241" t="n">
-        <v>8.25153064727783</v>
+        <v>8.25152969360352</v>
       </c>
       <c r="H241" t="n">
         <v>500</v>
@@ -7561,7 +7561,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G248" t="n">
-        <v>8.63745975494385</v>
+        <v>8.63746070861816</v>
       </c>
       <c r="H248" t="n">
         <v>7500</v>
@@ -7619,7 +7619,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G250" t="n">
-        <v>8.49043941497803</v>
+        <v>8.49043846130371</v>
       </c>
       <c r="H250" t="n">
         <v>500</v>
@@ -7822,7 +7822,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G257" t="n">
-        <v>8.87636852264404</v>
+        <v>8.87636947631836</v>
       </c>
       <c r="H257" t="n">
         <v>4000</v>
@@ -7996,7 +7996,7 @@
         <v>10</v>
       </c>
       <c r="G263" t="n">
-        <v>9.18878841400146</v>
+        <v>9.18878746032715</v>
       </c>
       <c r="H263" t="n">
         <v>500</v>
@@ -8025,7 +8025,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G264" t="n">
-        <v>8.69259262084961</v>
+        <v>8.69259357452393</v>
       </c>
       <c r="H264" t="n">
         <v>7000</v>
@@ -8054,7 +8054,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>8.69259262084961</v>
+        <v>8.69259357452393</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G267" t="n">
-        <v>8.69259262084961</v>
+        <v>8.69259357452393</v>
       </c>
       <c r="H267" t="n">
         <v>5500</v>
@@ -8170,7 +8170,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G269" t="n">
-        <v>8.74772548675537</v>
+        <v>8.74772644042969</v>
       </c>
       <c r="H269" t="n">
         <v>4000</v>
@@ -8199,7 +8199,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G270" t="n">
-        <v>8.67421531677246</v>
+        <v>8.67421436309814</v>
       </c>
       <c r="H270" t="n">
         <v>1000</v>
@@ -8431,7 +8431,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G278" t="n">
-        <v>7.66344833374023</v>
+        <v>7.66344881057739</v>
       </c>
       <c r="H278" t="n">
         <v>3000</v>
@@ -8460,7 +8460,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G279" t="n">
-        <v>7.64507102966309</v>
+        <v>7.64507055282593</v>
       </c>
       <c r="H279" t="n">
         <v>1000</v>
@@ -8489,7 +8489,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G280" t="n">
-        <v>7.4245400428772</v>
+        <v>7.42454051971436</v>
       </c>
       <c r="H280" t="n">
         <v>3500</v>
@@ -8518,7 +8518,7 @@
         <v>8</v>
       </c>
       <c r="G281" t="n">
-        <v>7.35102939605713</v>
+        <v>7.35102987289429</v>
       </c>
       <c r="H281" t="n">
         <v>3000</v>
@@ -8547,7 +8547,7 @@
         <v>8</v>
       </c>
       <c r="G282" t="n">
-        <v>7.35102939605713</v>
+        <v>7.35102987289429</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>8</v>
       </c>
       <c r="G283" t="n">
-        <v>7.35102939605713</v>
+        <v>7.35102987289429</v>
       </c>
       <c r="H283" t="n">
         <v>7500</v>
@@ -8692,7 +8692,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G287" t="n">
-        <v>7.27751970291138</v>
+        <v>7.27751922607422</v>
       </c>
       <c r="H287" t="n">
         <v>3500</v>
@@ -8750,7 +8750,7 @@
         <v>8</v>
       </c>
       <c r="G289" t="n">
-        <v>7.35102939605713</v>
+        <v>7.35102987289429</v>
       </c>
       <c r="H289" t="n">
         <v>1500</v>
@@ -8779,7 +8779,7 @@
         <v>8</v>
       </c>
       <c r="G290" t="n">
-        <v>7.35102939605713</v>
+        <v>7.35102987289429</v>
       </c>
       <c r="H290" t="n">
         <v>9000</v>
@@ -8808,7 +8808,7 @@
         <v>8</v>
       </c>
       <c r="G291" t="n">
-        <v>7.35102939605713</v>
+        <v>7.35102987289429</v>
       </c>
       <c r="H291" t="n">
         <v>1500</v>
@@ -8837,7 +8837,7 @@
         <v>8</v>
       </c>
       <c r="G292" t="n">
-        <v>7.35102939605713</v>
+        <v>7.35102987289429</v>
       </c>
       <c r="H292" t="n">
         <v>3000</v>
@@ -8866,7 +8866,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G293" t="n">
-        <v>7.11212158203125</v>
+        <v>7.11212110519409</v>
       </c>
       <c r="H293" t="n">
         <v>7500</v>
@@ -8895,7 +8895,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G294" t="n">
-        <v>7.11212158203125</v>
+        <v>7.11212110519409</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -8982,7 +8982,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>6.79970264434814</v>
+        <v>6.79970216751099</v>
       </c>
       <c r="H297" t="n">
         <v>3500</v>
@@ -9301,7 +9301,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G308" t="n">
-        <v>6.72619199752808</v>
+        <v>6.72619247436523</v>
       </c>
       <c r="H308" t="n">
         <v>5000</v>
@@ -9330,7 +9330,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G309" t="n">
-        <v>7.05698823928833</v>
+        <v>7.05698871612549</v>
       </c>
       <c r="H309" t="n">
         <v>1000</v>
@@ -9678,7 +9678,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G321" t="n">
-        <v>7.22238683700562</v>
+        <v>7.22238636016846</v>
       </c>
       <c r="H321" t="n">
         <v>500</v>
@@ -9707,7 +9707,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G322" t="n">
-        <v>7.22238683700562</v>
+        <v>7.22238636016846</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G323" t="n">
-        <v>7.22238683700562</v>
+        <v>7.22238636016846</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G324" t="n">
-        <v>7.22238683700562</v>
+        <v>7.22238636016846</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G327" t="n">
-        <v>7.00185585021973</v>
+        <v>7.00185632705688</v>
       </c>
       <c r="H327" t="n">
         <v>1000</v>
@@ -9910,7 +9910,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G329" t="n">
-        <v>6.79970264434814</v>
+        <v>6.79970216751099</v>
       </c>
       <c r="H329" t="n">
         <v>1000</v>
@@ -9939,7 +9939,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G330" t="n">
-        <v>7.02023363113403</v>
+        <v>7.02023315429688</v>
       </c>
       <c r="H330" t="n">
         <v>500</v>
@@ -9968,7 +9968,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G331" t="n">
-        <v>7.02023363113403</v>
+        <v>7.02023315429688</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G332" t="n">
-        <v>7.02023363113403</v>
+        <v>7.02023315429688</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G333" t="n">
-        <v>7.02023363113403</v>
+        <v>7.02023315429688</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G337" t="n">
-        <v>6.79970264434814</v>
+        <v>6.79970216751099</v>
       </c>
       <c r="H337" t="n">
         <v>500</v>
@@ -10171,7 +10171,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>6.79970264434814</v>
+        <v>6.79970216751099</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10316,7 +10316,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G343" t="n">
-        <v>6.02784442901611</v>
+        <v>6.02784395217896</v>
       </c>
       <c r="H343" t="n">
         <v>9500</v>
@@ -10432,7 +10432,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G347" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H347" t="n">
         <v>1000</v>
@@ -10461,7 +10461,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G348" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -10548,7 +10548,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G351" t="n">
-        <v>5.9910888671875</v>
+        <v>5.99108934402466</v>
       </c>
       <c r="H351" t="n">
         <v>14500</v>
@@ -10577,7 +10577,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G352" t="n">
-        <v>5.9910888671875</v>
+        <v>5.99108934402466</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G355" t="n">
-        <v>6.248375415802</v>
+        <v>6.24837589263916</v>
       </c>
       <c r="H355" t="n">
         <v>4000</v>
@@ -10693,7 +10693,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>6.248375415802</v>
+        <v>6.24837589263916</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -10722,7 +10722,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G357" t="n">
-        <v>6.248375415802</v>
+        <v>6.24837589263916</v>
       </c>
       <c r="H357" t="n">
         <v>500</v>
@@ -10751,7 +10751,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G358" t="n">
-        <v>6.248375415802</v>
+        <v>6.24837589263916</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -10780,7 +10780,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G359" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H359" t="n">
         <v>500</v>
@@ -10954,7 +10954,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G365" t="n">
-        <v>6.59754943847656</v>
+        <v>6.5975489616394</v>
       </c>
       <c r="H365" t="n">
         <v>500</v>
@@ -11012,7 +11012,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G367" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H367" t="n">
         <v>2000</v>
@@ -11041,7 +11041,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G368" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G369" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G370" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11360,7 +11360,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>6.06459999084473</v>
+        <v>6.06459951400757</v>
       </c>
       <c r="H379" t="n">
         <v>1000</v>
@@ -11389,7 +11389,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>6.06459999084473</v>
+        <v>6.06459951400757</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>6.06459999084473</v>
+        <v>6.06459951400757</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G382" t="n">
-        <v>6.06459999084473</v>
+        <v>6.06459951400757</v>
       </c>
       <c r="H382" t="n">
         <v>500</v>
@@ -12085,7 +12085,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G404" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H404" t="n">
         <v>1000</v>
@@ -12114,7 +12114,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G405" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -12143,7 +12143,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G406" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G407" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -12201,7 +12201,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G408" t="n">
-        <v>6.11973237991333</v>
+        <v>6.11973190307617</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G413" t="n">
-        <v>6.45052862167358</v>
+        <v>6.45052814483643</v>
       </c>
       <c r="H413" t="n">
         <v>5500</v>
@@ -12375,7 +12375,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G414" t="n">
-        <v>6.45052862167358</v>
+        <v>6.45052814483643</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>7</v>
       </c>
       <c r="G415" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215036392212</v>
       </c>
       <c r="H415" t="n">
         <v>1500</v>
@@ -12433,7 +12433,7 @@
         <v>7</v>
       </c>
       <c r="G416" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215036392212</v>
       </c>
       <c r="H416" t="n">
         <v>0</v>
@@ -12462,7 +12462,7 @@
         <v>7</v>
       </c>
       <c r="G417" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215036392212</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12491,7 +12491,7 @@
         <v>7</v>
       </c>
       <c r="G418" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215036392212</v>
       </c>
       <c r="H418" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>7</v>
       </c>
       <c r="G419" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215036392212</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>7</v>
       </c>
       <c r="G420" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215036392212</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>7</v>
       </c>
       <c r="G421" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215036392212</v>
       </c>
       <c r="H421" t="n">
         <v>500</v>
@@ -13071,7 +13071,7 @@
         <v>7</v>
       </c>
       <c r="G438" t="n">
-        <v>6.43215084075928</v>
+        <v>6.43215036392212</v>
       </c>
       <c r="H438" t="n">
         <v>3000</v>
@@ -13100,7 +13100,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G439" t="n">
-        <v>6.34026336669922</v>
+        <v>6.34026384353638</v>
       </c>
       <c r="H439" t="n">
         <v>3000</v>
@@ -13158,7 +13158,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G441" t="n">
-        <v>6.32188558578491</v>
+        <v>6.32188606262207</v>
       </c>
       <c r="H441" t="n">
         <v>500</v>
@@ -13187,7 +13187,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G442" t="n">
-        <v>6.32188558578491</v>
+        <v>6.32188606262207</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G443" t="n">
-        <v>6.32188558578491</v>
+        <v>6.32188606262207</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G444" t="n">
-        <v>6.32188558578491</v>
+        <v>6.32188606262207</v>
       </c>
       <c r="H444" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G448" t="n">
-        <v>6.02784442901611</v>
+        <v>6.02784395217896</v>
       </c>
       <c r="H448" t="n">
         <v>1000</v>
@@ -14260,7 +14260,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G479" t="n">
-        <v>5.3478741645813</v>
+        <v>5.34787368774414</v>
       </c>
       <c r="H479" t="n">
         <v>7000</v>
@@ -14318,7 +14318,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G481" t="n">
-        <v>5.56840467453003</v>
+        <v>5.56840515136719</v>
       </c>
       <c r="H481" t="n">
         <v>1500</v>
@@ -15130,7 +15130,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G509" t="n">
-        <v>5.64191579818726</v>
+        <v>5.6419153213501</v>
       </c>
       <c r="H509" t="n">
         <v>1000</v>
@@ -15304,7 +15304,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G515" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H515" t="n">
         <v>1500</v>
@@ -15333,7 +15333,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G516" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H516" t="n">
         <v>0</v>
@@ -15362,7 +15362,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G517" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H517" t="n">
         <v>0</v>
@@ -15391,7 +15391,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G518" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15420,7 +15420,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G519" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H519" t="n">
         <v>0</v>
@@ -15449,7 +15449,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G520" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H520" t="n">
         <v>0</v>
@@ -15797,7 +15797,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G532" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H532" t="n">
         <v>500</v>
@@ -15826,7 +15826,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G533" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H533" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G534" t="n">
-        <v>5.62353706359863</v>
+        <v>5.62353754043579</v>
       </c>
       <c r="H534" t="n">
         <v>0</v>
@@ -15884,7 +15884,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H535" t="n">
         <v>500</v>
@@ -15913,7 +15913,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G536" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H536" t="n">
         <v>0</v>
@@ -15971,7 +15971,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G538" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H538" t="n">
         <v>1000</v>
@@ -16000,7 +16000,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G539" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H539" t="n">
         <v>0</v>
@@ -16029,7 +16029,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G540" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H540" t="n">
         <v>0</v>
@@ -16058,7 +16058,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G541" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G542" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -16116,7 +16116,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G543" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H543" t="n">
         <v>0</v>
@@ -16145,7 +16145,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G544" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H544" t="n">
         <v>0</v>
@@ -16174,7 +16174,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G545" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H546" t="n">
         <v>0</v>
@@ -16232,7 +16232,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G547" t="n">
-        <v>5.69704818725586</v>
+        <v>5.6970477104187</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -16725,7 +16725,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G564" t="n">
-        <v>5.27436399459839</v>
+        <v>5.27436351776123</v>
       </c>
       <c r="H564" t="n">
         <v>2500</v>
@@ -16754,7 +16754,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G565" t="n">
-        <v>5.21923065185547</v>
+        <v>5.21923112869263</v>
       </c>
       <c r="H565" t="n">
         <v>1500</v>
@@ -16783,7 +16783,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G566" t="n">
-        <v>5.21923065185547</v>
+        <v>5.21923112869263</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -16812,7 +16812,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G567" t="n">
-        <v>5.21923065185547</v>
+        <v>5.21923112869263</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G568" t="n">
-        <v>5.43976211547852</v>
+        <v>5.43976163864136</v>
       </c>
       <c r="H568" t="n">
         <v>500</v>
@@ -16870,7 +16870,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G569" t="n">
-        <v>5.2927417755127</v>
+        <v>5.29274129867554</v>
       </c>
       <c r="H569" t="n">
         <v>1000</v>
@@ -16899,7 +16899,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G570" t="n">
-        <v>5.2927417755127</v>
+        <v>5.29274129867554</v>
       </c>
       <c r="H570" t="n">
         <v>0</v>
@@ -16928,7 +16928,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G571" t="n">
-        <v>5.2927417755127</v>
+        <v>5.29274129867554</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G572" t="n">
-        <v>5.2927417755127</v>
+        <v>5.29274129867554</v>
       </c>
       <c r="H572" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G573" t="n">
-        <v>5.2927417755127</v>
+        <v>5.29274129867554</v>
       </c>
       <c r="H573" t="n">
         <v>0</v>
@@ -17015,7 +17015,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G574" t="n">
-        <v>5.27436399459839</v>
+        <v>5.27436351776123</v>
       </c>
       <c r="H574" t="n">
         <v>4500</v>
@@ -17363,7 +17363,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G586" t="n">
-        <v>5.4673285484314</v>
+        <v>5.46732807159424</v>
       </c>
       <c r="H586" t="n">
         <v>500</v>
@@ -17392,7 +17392,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G587" t="n">
-        <v>5.4673285484314</v>
+        <v>5.46732807159424</v>
       </c>
       <c r="H587" t="n">
         <v>0</v>
@@ -17508,7 +17508,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G591" t="n">
-        <v>5.4673285484314</v>
+        <v>5.46732807159424</v>
       </c>
       <c r="H591" t="n">
         <v>500</v>
@@ -17537,7 +17537,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G592" t="n">
-        <v>5.4673285484314</v>
+        <v>5.46732807159424</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -17566,7 +17566,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G593" t="n">
-        <v>5.4673285484314</v>
+        <v>5.46732807159424</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G594" t="n">
-        <v>5.4673285484314</v>
+        <v>5.46732807159424</v>
       </c>
       <c r="H594" t="n">
         <v>1000</v>
@@ -17624,7 +17624,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G595" t="n">
-        <v>5.4673285484314</v>
+        <v>5.46732807159424</v>
       </c>
       <c r="H595" t="n">
         <v>0</v>
@@ -17653,7 +17653,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G596" t="n">
-        <v>5.4673285484314</v>
+        <v>5.46732807159424</v>
       </c>
       <c r="H596" t="n">
         <v>0</v>
@@ -18001,7 +18001,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G608" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H608" t="n">
         <v>2000</v>
@@ -18030,7 +18030,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G609" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H609" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G616" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H616" t="n">
         <v>500</v>
@@ -18262,7 +18262,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G617" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H617" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G618" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -18320,7 +18320,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G619" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -18349,7 +18349,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G620" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H620" t="n">
         <v>0</v>
@@ -18378,7 +18378,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G621" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H621" t="n">
         <v>1000</v>
@@ -18407,7 +18407,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G622" t="n">
-        <v>5.53470706939697</v>
+        <v>5.53470754623413</v>
       </c>
       <c r="H622" t="n">
         <v>3500</v>
@@ -18610,7 +18610,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G629" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H629" t="n">
         <v>2000</v>
@@ -18639,7 +18639,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G630" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H630" t="n">
         <v>500</v>
@@ -18813,7 +18813,7 @@
         <v>5.5</v>
       </c>
       <c r="G636" t="n">
-        <v>5.11611557006836</v>
+        <v>5.11611604690552</v>
       </c>
       <c r="H636" t="n">
         <v>1500</v>
@@ -18842,7 +18842,7 @@
         <v>5.5</v>
       </c>
       <c r="G637" t="n">
-        <v>5.11611557006836</v>
+        <v>5.11611604690552</v>
       </c>
       <c r="H637" t="n">
         <v>0</v>
@@ -18900,7 +18900,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G639" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H639" t="n">
         <v>3250</v>
@@ -18929,7 +18929,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G640" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H640" t="n">
         <v>0</v>
@@ -18958,7 +18958,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G641" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H641" t="n">
         <v>0</v>
@@ -18987,7 +18987,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G642" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H642" t="n">
         <v>0</v>
@@ -19016,7 +19016,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G643" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H643" t="n">
         <v>0</v>
@@ -19219,7 +19219,7 @@
         <v>5</v>
       </c>
       <c r="G650" t="n">
-        <v>4.65101432800293</v>
+        <v>4.65101480484009</v>
       </c>
       <c r="H650" t="n">
         <v>8500</v>
@@ -19248,7 +19248,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G651" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H651" t="n">
         <v>9500</v>
@@ -19277,7 +19277,7 @@
         <v>5.5</v>
       </c>
       <c r="G652" t="n">
-        <v>5.11611557006836</v>
+        <v>5.11611604690552</v>
       </c>
       <c r="H652" t="n">
         <v>5500</v>
@@ -19306,7 +19306,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G653" t="n">
-        <v>5.16262674331665</v>
+        <v>5.16262626647949</v>
       </c>
       <c r="H653" t="n">
         <v>6000</v>
@@ -19335,7 +19335,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G654" t="n">
-        <v>5.16262674331665</v>
+        <v>5.16262626647949</v>
       </c>
       <c r="H654" t="n">
         <v>0</v>
@@ -19422,7 +19422,7 @@
         <v>5.5</v>
       </c>
       <c r="G657" t="n">
-        <v>5.11611557006836</v>
+        <v>5.11611604690552</v>
       </c>
       <c r="H657" t="n">
         <v>500</v>
@@ -19596,7 +19596,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G663" t="n">
-        <v>5.16262674331665</v>
+        <v>5.16262626647949</v>
       </c>
       <c r="H663" t="n">
         <v>2500</v>
@@ -19625,7 +19625,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G664" t="n">
-        <v>5.16262674331665</v>
+        <v>5.16262626647949</v>
       </c>
       <c r="H664" t="n">
         <v>0</v>
@@ -19654,7 +19654,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G665" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H665" t="n">
         <v>500</v>
@@ -19770,7 +19770,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G669" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H669" t="n">
         <v>500</v>
@@ -19799,7 +19799,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H670" t="n">
         <v>0</v>
@@ -19828,7 +19828,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H671" t="n">
         <v>0</v>
@@ -19886,7 +19886,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G673" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H673" t="n">
         <v>13250</v>
@@ -19915,7 +19915,7 @@
         <v>5.5</v>
       </c>
       <c r="G674" t="n">
-        <v>5.11611557006836</v>
+        <v>5.11611604690552</v>
       </c>
       <c r="H674" t="n">
         <v>6750</v>
@@ -19973,7 +19973,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G676" t="n">
-        <v>5.16262674331665</v>
+        <v>5.16262626647949</v>
       </c>
       <c r="H676" t="n">
         <v>1000</v>
@@ -20002,7 +20002,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G677" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H677" t="n">
         <v>19750</v>
@@ -20031,7 +20031,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H678" t="n">
         <v>1750</v>
@@ -20060,7 +20060,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G679" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H679" t="n">
         <v>4750</v>
@@ -20089,7 +20089,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G680" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H680" t="n">
         <v>500</v>
@@ -20118,7 +20118,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H681" t="n">
         <v>0</v>
@@ -20147,7 +20147,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G682" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H682" t="n">
         <v>0</v>
@@ -20350,7 +20350,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G689" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H689" t="n">
         <v>1250</v>
@@ -20408,7 +20408,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G691" t="n">
-        <v>5.16262674331665</v>
+        <v>5.16262626647949</v>
       </c>
       <c r="H691" t="n">
         <v>1250</v>
@@ -20466,7 +20466,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G693" t="n">
-        <v>5.16262674331665</v>
+        <v>5.16262626647949</v>
       </c>
       <c r="H693" t="n">
         <v>750</v>
@@ -20495,7 +20495,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G694" t="n">
-        <v>5.16262674331665</v>
+        <v>5.16262626647949</v>
       </c>
       <c r="H694" t="n">
         <v>0</v>
@@ -20524,7 +20524,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G695" t="n">
-        <v>5.16262674331665</v>
+        <v>5.16262626647949</v>
       </c>
       <c r="H695" t="n">
         <v>0</v>
@@ -20553,7 +20553,7 @@
         <v>5.5</v>
       </c>
       <c r="G696" t="n">
-        <v>5.11611557006836</v>
+        <v>5.11611604690552</v>
       </c>
       <c r="H696" t="n">
         <v>1000</v>
@@ -20582,7 +20582,7 @@
         <v>5.5</v>
       </c>
       <c r="G697" t="n">
-        <v>5.11611557006836</v>
+        <v>5.11611604690552</v>
       </c>
       <c r="H697" t="n">
         <v>3000</v>
@@ -20611,7 +20611,7 @@
         <v>5.5</v>
       </c>
       <c r="G698" t="n">
-        <v>5.11611557006836</v>
+        <v>5.11611604690552</v>
       </c>
       <c r="H698" t="n">
         <v>0</v>
@@ -20640,7 +20640,7 @@
         <v>5.5</v>
       </c>
       <c r="G699" t="n">
-        <v>5.11611557006836</v>
+        <v>5.11611604690552</v>
       </c>
       <c r="H699" t="n">
         <v>0</v>
@@ -20669,7 +20669,7 @@
         <v>5.5</v>
       </c>
       <c r="G700" t="n">
-        <v>5.11611557006836</v>
+        <v>5.11611604690552</v>
       </c>
       <c r="H700" t="n">
         <v>250</v>
@@ -20698,7 +20698,7 @@
         <v>5.5</v>
       </c>
       <c r="G701" t="n">
-        <v>5.11611557006836</v>
+        <v>5.11611604690552</v>
       </c>
       <c r="H701" t="n">
         <v>8500</v>
@@ -20727,7 +20727,7 @@
         <v>5.5</v>
       </c>
       <c r="G702" t="n">
-        <v>5.11611557006836</v>
+        <v>5.11611604690552</v>
       </c>
       <c r="H702" t="n">
         <v>0</v>
@@ -20756,7 +20756,7 @@
         <v>5.5</v>
       </c>
       <c r="G703" t="n">
-        <v>5.11611557006836</v>
+        <v>5.11611604690552</v>
       </c>
       <c r="H703" t="n">
         <v>20000</v>
@@ -20930,7 +20930,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G709" t="n">
-        <v>4.52078628540039</v>
+        <v>4.52078580856323</v>
       </c>
       <c r="H709" t="n">
         <v>36250</v>
@@ -20988,7 +20988,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G711" t="n">
-        <v>4.6975245475769</v>
+        <v>4.69752502441406</v>
       </c>
       <c r="H711" t="n">
         <v>2250</v>
@@ -21017,7 +21017,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G712" t="n">
-        <v>4.6975245475769</v>
+        <v>4.69752502441406</v>
       </c>
       <c r="H712" t="n">
         <v>0</v>
@@ -21046,7 +21046,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G713" t="n">
-        <v>4.6975245475769</v>
+        <v>4.69752502441406</v>
       </c>
       <c r="H713" t="n">
         <v>250</v>
@@ -21075,7 +21075,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G714" t="n">
-        <v>4.55799436569214</v>
+        <v>4.5579948425293</v>
       </c>
       <c r="H714" t="n">
         <v>4500</v>
@@ -21104,7 +21104,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G715" t="n">
-        <v>4.59520196914673</v>
+        <v>4.59520244598389</v>
       </c>
       <c r="H715" t="n">
         <v>250</v>
@@ -21133,7 +21133,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G716" t="n">
-        <v>4.46497440338135</v>
+        <v>4.46497392654419</v>
       </c>
       <c r="H716" t="n">
         <v>22500</v>
@@ -21423,7 +21423,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G726" t="n">
-        <v>4.0556845664978</v>
+        <v>4.05568504333496</v>
       </c>
       <c r="H726" t="n">
         <v>6000</v>
@@ -21452,7 +21452,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G727" t="n">
-        <v>4.2417254447937</v>
+        <v>4.24172496795654</v>
       </c>
       <c r="H727" t="n">
         <v>1250</v>
@@ -21510,7 +21510,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>4.27893304824829</v>
+        <v>4.27893352508545</v>
       </c>
       <c r="H729" t="n">
         <v>1250</v>
@@ -21539,7 +21539,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G730" t="n">
-        <v>4.27893304824829</v>
+        <v>4.27893352508545</v>
       </c>
       <c r="H730" t="n">
         <v>0</v>
@@ -21858,7 +21858,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G741" t="n">
-        <v>4.4835786819458</v>
+        <v>4.48357820510864</v>
       </c>
       <c r="H741" t="n">
         <v>2250</v>
@@ -21887,7 +21887,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G742" t="n">
-        <v>4.59520196914673</v>
+        <v>4.59520244598389</v>
       </c>
       <c r="H742" t="n">
         <v>2250</v>
@@ -21916,7 +21916,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G743" t="n">
-        <v>4.59520196914673</v>
+        <v>4.59520244598389</v>
       </c>
       <c r="H743" t="n">
         <v>0</v>
@@ -21945,7 +21945,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G744" t="n">
-        <v>4.59520196914673</v>
+        <v>4.59520244598389</v>
       </c>
       <c r="H744" t="n">
         <v>1000</v>
@@ -21974,7 +21974,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G745" t="n">
-        <v>4.59520196914673</v>
+        <v>4.59520244598389</v>
       </c>
       <c r="H745" t="n">
         <v>0</v>
@@ -22003,7 +22003,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G746" t="n">
-        <v>4.4835786819458</v>
+        <v>4.48357820510864</v>
       </c>
       <c r="H746" t="n">
         <v>4500</v>
@@ -22032,7 +22032,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G747" t="n">
-        <v>4.4835786819458</v>
+        <v>4.48357820510864</v>
       </c>
       <c r="H747" t="n">
         <v>0</v>
@@ -22061,7 +22061,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G748" t="n">
-        <v>4.40916156768799</v>
+        <v>4.40916109085083</v>
       </c>
       <c r="H748" t="n">
         <v>500</v>
@@ -22090,7 +22090,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G749" t="n">
-        <v>4.40916156768799</v>
+        <v>4.40916109085083</v>
       </c>
       <c r="H749" t="n">
         <v>0</v>
@@ -22322,7 +22322,7 @@
         <v>5</v>
       </c>
       <c r="G757" t="n">
-        <v>4.65101432800293</v>
+        <v>4.65101480484009</v>
       </c>
       <c r="H757" t="n">
         <v>2750</v>
@@ -22351,7 +22351,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G758" t="n">
-        <v>4.6975245475769</v>
+        <v>4.69752502441406</v>
       </c>
       <c r="H758" t="n">
         <v>250</v>
@@ -22612,7 +22612,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G767" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H767" t="n">
         <v>6000</v>
@@ -22641,7 +22641,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H768" t="n">
         <v>500</v>
@@ -22670,7 +22670,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G769" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H769" t="n">
         <v>0</v>
@@ -22786,7 +22786,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G773" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H773" t="n">
         <v>3750</v>
@@ -22873,7 +22873,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G776" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H776" t="n">
         <v>2750</v>
@@ -22960,7 +22960,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G779" t="n">
-        <v>5.16262674331665</v>
+        <v>5.16262626647949</v>
       </c>
       <c r="H779" t="n">
         <v>2250</v>
@@ -22989,7 +22989,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G780" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H780" t="n">
         <v>40750</v>
@@ -23047,7 +23047,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G782" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H782" t="n">
         <v>1750</v>
@@ -23076,7 +23076,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G783" t="n">
-        <v>5.67423725128174</v>
+        <v>5.6742377281189</v>
       </c>
       <c r="H783" t="n">
         <v>6750</v>
@@ -23134,7 +23134,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G785" t="n">
-        <v>5.99980878829956</v>
+        <v>5.9998083114624</v>
       </c>
       <c r="H785" t="n">
         <v>6250</v>
@@ -23163,7 +23163,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G786" t="n">
-        <v>5.95329809188843</v>
+        <v>5.95329856872559</v>
       </c>
       <c r="H786" t="n">
         <v>750</v>
@@ -23192,7 +23192,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G787" t="n">
-        <v>5.95329809188843</v>
+        <v>5.95329856872559</v>
       </c>
       <c r="H787" t="n">
         <v>0</v>
@@ -23221,7 +23221,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G788" t="n">
-        <v>5.86027860641479</v>
+        <v>5.86027812957764</v>
       </c>
       <c r="H788" t="n">
         <v>3250</v>
@@ -23250,7 +23250,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G789" t="n">
-        <v>5.86027860641479</v>
+        <v>5.86027812957764</v>
       </c>
       <c r="H789" t="n">
         <v>1500</v>
@@ -23308,7 +23308,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G791" t="n">
-        <v>5.86027860641479</v>
+        <v>5.86027812957764</v>
       </c>
       <c r="H791" t="n">
         <v>4750</v>
@@ -23337,7 +23337,7 @@
         <v>6.25</v>
       </c>
       <c r="G792" t="n">
-        <v>5.81376791000366</v>
+        <v>5.81376838684082</v>
       </c>
       <c r="H792" t="n">
         <v>2000</v>
@@ -23366,7 +23366,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G793" t="n">
-        <v>5.67423725128174</v>
+        <v>5.6742377281189</v>
       </c>
       <c r="H793" t="n">
         <v>1250</v>
@@ -23511,7 +23511,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G798" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H798" t="n">
         <v>1000</v>
@@ -23627,7 +23627,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G802" t="n">
-        <v>5.53470706939697</v>
+        <v>5.53470754623413</v>
       </c>
       <c r="H802" t="n">
         <v>750</v>
@@ -23656,7 +23656,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G803" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H803" t="n">
         <v>750</v>
@@ -23714,7 +23714,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G805" t="n">
-        <v>5.39517688751221</v>
+        <v>5.39517736434937</v>
       </c>
       <c r="H805" t="n">
         <v>2750</v>
@@ -23743,7 +23743,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G806" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H806" t="n">
         <v>1750</v>
@@ -23772,7 +23772,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G807" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H807" t="n">
         <v>0</v>
@@ -23801,7 +23801,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G808" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H808" t="n">
         <v>0</v>
@@ -23830,7 +23830,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G809" t="n">
-        <v>5.30215644836426</v>
+        <v>5.3021559715271</v>
       </c>
       <c r="H809" t="n">
         <v>0</v>
@@ -23888,7 +23888,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G811" t="n">
-        <v>5.16262674331665</v>
+        <v>5.16262626647949</v>
       </c>
       <c r="H811" t="n">
         <v>2500</v>
@@ -24033,7 +24033,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G816" t="n">
-        <v>5.16262674331665</v>
+        <v>5.16262626647949</v>
       </c>
       <c r="H816" t="n">
         <v>2750</v>
@@ -24062,7 +24062,7 @@
         <v>5.5</v>
       </c>
       <c r="G817" t="n">
-        <v>5.11611557006836</v>
+        <v>5.11611604690552</v>
       </c>
       <c r="H817" t="n">
         <v>4000</v>
@@ -24091,7 +24091,7 @@
         <v>5.5</v>
       </c>
       <c r="G818" t="n">
-        <v>5.11611557006836</v>
+        <v>5.11611604690552</v>
       </c>
       <c r="H818" t="n">
         <v>2000</v>
@@ -24120,7 +24120,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G819" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H819" t="n">
         <v>1000</v>
@@ -24294,7 +24294,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G825" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H825" t="n">
         <v>500</v>
@@ -24323,7 +24323,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G826" t="n">
-        <v>4.97658538818359</v>
+        <v>4.97658586502075</v>
       </c>
       <c r="H826" t="n">
         <v>1000</v>
@@ -24352,7 +24352,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G827" t="n">
-        <v>5.02309608459473</v>
+        <v>5.02309560775757</v>
       </c>
       <c r="H827" t="n">
         <v>250</v>
@@ -24439,7 +24439,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G830" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H830" t="n">
         <v>9000</v>
@@ -24497,7 +24497,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G832" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H832" t="n">
         <v>750</v>
@@ -24526,7 +24526,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G833" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H833" t="n">
         <v>500</v>
@@ -24555,7 +24555,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G834" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -24642,7 +24642,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G837" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H837" t="n">
         <v>1500</v>
@@ -24845,7 +24845,7 @@
         <v>5</v>
       </c>
       <c r="G844" t="n">
-        <v>4.65101432800293</v>
+        <v>4.65101480484009</v>
       </c>
       <c r="H844" t="n">
         <v>250</v>
@@ -24874,7 +24874,7 @@
         <v>5</v>
       </c>
       <c r="G845" t="n">
-        <v>4.65101432800293</v>
+        <v>4.65101480484009</v>
       </c>
       <c r="H845" t="n">
         <v>0</v>
@@ -24903,7 +24903,7 @@
         <v>5</v>
       </c>
       <c r="G846" t="n">
-        <v>4.65101432800293</v>
+        <v>4.65101480484009</v>
       </c>
       <c r="H846" t="n">
         <v>500</v>
@@ -24932,7 +24932,7 @@
         <v>5</v>
       </c>
       <c r="G847" t="n">
-        <v>4.65101432800293</v>
+        <v>4.65101480484009</v>
       </c>
       <c r="H847" t="n">
         <v>0</v>
@@ -24990,7 +24990,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G849" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H849" t="n">
         <v>500</v>
@@ -25019,7 +25019,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G850" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H850" t="n">
         <v>1000</v>
@@ -25048,7 +25048,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G851" t="n">
-        <v>4.83705472946167</v>
+        <v>4.83705520629883</v>
       </c>
       <c r="H851" t="n">
         <v>1000</v>
@@ -25077,7 +25077,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G852" t="n">
-        <v>4.6975245475769</v>
+        <v>4.69752502441406</v>
       </c>
       <c r="H852" t="n">
         <v>1000</v>
@@ -25106,7 +25106,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G853" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H853" t="n">
         <v>2500</v>
@@ -25193,7 +25193,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G856" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H856" t="n">
         <v>250</v>
@@ -25222,7 +25222,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G857" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H857" t="n">
         <v>0</v>
@@ -25251,7 +25251,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G858" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H858" t="n">
         <v>250</v>
@@ -25280,7 +25280,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G859" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H859" t="n">
         <v>1000</v>
@@ -25309,7 +25309,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G860" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H860" t="n">
         <v>1000</v>
@@ -25396,7 +25396,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H863" t="n">
         <v>1000</v>
@@ -25425,7 +25425,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G864" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H864" t="n">
         <v>250</v>
@@ -25454,7 +25454,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G865" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H865" t="n">
         <v>250</v>
@@ -25483,7 +25483,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G866" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -25512,7 +25512,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G867" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -25570,7 +25570,7 @@
         <v>5</v>
       </c>
       <c r="G869" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H869" t="n">
         <v>1000</v>
@@ -25599,7 +25599,7 @@
         <v>5</v>
       </c>
       <c r="G870" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H870" t="n">
         <v>0</v>
@@ -25628,7 +25628,7 @@
         <v>5</v>
       </c>
       <c r="G871" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H871" t="n">
         <v>0</v>
@@ -25657,7 +25657,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G872" t="n">
-        <v>4.79242420196533</v>
+        <v>4.79242467880249</v>
       </c>
       <c r="H872" t="n">
         <v>1000</v>
@@ -25686,7 +25686,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G873" t="n">
-        <v>4.79242420196533</v>
+        <v>4.79242467880249</v>
       </c>
       <c r="H873" t="n">
         <v>0</v>
@@ -25715,7 +25715,7 @@
         <v>5</v>
       </c>
       <c r="G874" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H874" t="n">
         <v>1500</v>
@@ -25802,7 +25802,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G877" t="n">
-        <v>4.70701456069946</v>
+        <v>4.70701503753662</v>
       </c>
       <c r="H877" t="n">
         <v>250</v>
@@ -25831,7 +25831,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G878" t="n">
-        <v>4.70701456069946</v>
+        <v>4.70701503753662</v>
       </c>
       <c r="H878" t="n">
         <v>0</v>
@@ -26005,7 +26005,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G884" t="n">
-        <v>4.93477296829224</v>
+        <v>4.93477344512939</v>
       </c>
       <c r="H884" t="n">
         <v>3000</v>
@@ -26034,7 +26034,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G885" t="n">
-        <v>4.79242420196533</v>
+        <v>4.79242467880249</v>
       </c>
       <c r="H885" t="n">
         <v>1750</v>
@@ -26150,7 +26150,7 @@
         <v>5</v>
       </c>
       <c r="G889" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H889" t="n">
         <v>8000</v>
@@ -26179,7 +26179,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G890" t="n">
-        <v>4.79242420196533</v>
+        <v>4.79242467880249</v>
       </c>
       <c r="H890" t="n">
         <v>500</v>
@@ -26208,7 +26208,7 @@
         <v>5</v>
       </c>
       <c r="G891" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H891" t="n">
         <v>750</v>
@@ -26237,7 +26237,7 @@
         <v>5</v>
       </c>
       <c r="G892" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H892" t="n">
         <v>1750</v>
@@ -26266,7 +26266,7 @@
         <v>5</v>
       </c>
       <c r="G893" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H893" t="n">
         <v>750</v>
@@ -26295,7 +26295,7 @@
         <v>5</v>
       </c>
       <c r="G894" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -26324,7 +26324,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G895" t="n">
-        <v>4.79242420196533</v>
+        <v>4.79242467880249</v>
       </c>
       <c r="H895" t="n">
         <v>2000</v>
@@ -26353,7 +26353,7 @@
         <v>5</v>
       </c>
       <c r="G896" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H896" t="n">
         <v>750</v>
@@ -26382,7 +26382,7 @@
         <v>5</v>
       </c>
       <c r="G897" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H897" t="n">
         <v>500</v>
@@ -26411,7 +26411,7 @@
         <v>5</v>
       </c>
       <c r="G898" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H898" t="n">
         <v>0</v>
@@ -26440,7 +26440,7 @@
         <v>5</v>
       </c>
       <c r="G899" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H899" t="n">
         <v>0</v>
@@ -26469,7 +26469,7 @@
         <v>5</v>
       </c>
       <c r="G900" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H900" t="n">
         <v>500</v>
@@ -26585,7 +26585,7 @@
         <v>5</v>
       </c>
       <c r="G904" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H904" t="n">
         <v>1000</v>
@@ -26614,7 +26614,7 @@
         <v>5</v>
       </c>
       <c r="G905" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H905" t="n">
         <v>3250</v>
@@ -26643,7 +26643,7 @@
         <v>5</v>
       </c>
       <c r="G906" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H906" t="n">
         <v>0</v>
@@ -26672,7 +26672,7 @@
         <v>5</v>
       </c>
       <c r="G907" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H907" t="n">
         <v>1250</v>
@@ -26701,7 +26701,7 @@
         <v>5</v>
       </c>
       <c r="G908" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H908" t="n">
         <v>0</v>
@@ -26730,7 +26730,7 @@
         <v>5</v>
       </c>
       <c r="G909" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H909" t="n">
         <v>500</v>
@@ -26759,7 +26759,7 @@
         <v>5</v>
       </c>
       <c r="G910" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H910" t="n">
         <v>0</v>
@@ -26788,7 +26788,7 @@
         <v>5</v>
       </c>
       <c r="G911" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -26817,7 +26817,7 @@
         <v>5</v>
       </c>
       <c r="G912" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -26846,7 +26846,7 @@
         <v>5</v>
       </c>
       <c r="G913" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H913" t="n">
         <v>0</v>
@@ -26875,7 +26875,7 @@
         <v>5</v>
       </c>
       <c r="G914" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H914" t="n">
         <v>500</v>
@@ -26904,7 +26904,7 @@
         <v>5</v>
       </c>
       <c r="G915" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H915" t="n">
         <v>1500</v>
@@ -26933,7 +26933,7 @@
         <v>5</v>
       </c>
       <c r="G916" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H916" t="n">
         <v>1000</v>
@@ -26962,7 +26962,7 @@
         <v>5</v>
       </c>
       <c r="G917" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -26991,7 +26991,7 @@
         <v>5</v>
       </c>
       <c r="G918" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H918" t="n">
         <v>500</v>
@@ -27020,7 +27020,7 @@
         <v>5</v>
       </c>
       <c r="G919" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H919" t="n">
         <v>0</v>
@@ -27049,7 +27049,7 @@
         <v>5</v>
       </c>
       <c r="G920" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H920" t="n">
         <v>0</v>
@@ -27078,7 +27078,7 @@
         <v>5</v>
       </c>
       <c r="G921" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>
@@ -27165,7 +27165,7 @@
         <v>5</v>
       </c>
       <c r="G924" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H924" t="n">
         <v>4000</v>
@@ -27194,7 +27194,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G925" t="n">
-        <v>4.61211538314819</v>
+        <v>4.61211490631104</v>
       </c>
       <c r="H925" t="n">
         <v>5750</v>
@@ -27223,7 +27223,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G926" t="n">
-        <v>4.61211538314819</v>
+        <v>4.61211490631104</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -27252,7 +27252,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G927" t="n">
-        <v>4.61211538314819</v>
+        <v>4.61211490631104</v>
       </c>
       <c r="H927" t="n">
         <v>0</v>
@@ -27281,7 +27281,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G928" t="n">
-        <v>4.61211538314819</v>
+        <v>4.61211490631104</v>
       </c>
       <c r="H928" t="n">
         <v>0</v>
@@ -27310,7 +27310,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G929" t="n">
-        <v>4.61211538314819</v>
+        <v>4.61211490631104</v>
       </c>
       <c r="H929" t="n">
         <v>0</v>
@@ -27339,7 +27339,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G930" t="n">
-        <v>4.61211538314819</v>
+        <v>4.61211490631104</v>
       </c>
       <c r="H930" t="n">
         <v>0</v>
@@ -27368,7 +27368,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G931" t="n">
-        <v>4.61211538314819</v>
+        <v>4.61211490631104</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -27426,7 +27426,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G933" t="n">
-        <v>4.79242420196533</v>
+        <v>4.79242467880249</v>
       </c>
       <c r="H933" t="n">
         <v>750</v>
@@ -27455,7 +27455,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G934" t="n">
-        <v>4.79242420196533</v>
+        <v>4.79242467880249</v>
       </c>
       <c r="H934" t="n">
         <v>0</v>
@@ -27484,7 +27484,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G935" t="n">
-        <v>4.79242420196533</v>
+        <v>4.79242467880249</v>
       </c>
       <c r="H935" t="n">
         <v>250</v>
@@ -27629,7 +27629,7 @@
         <v>5</v>
       </c>
       <c r="G940" t="n">
-        <v>4.74497413635254</v>
+        <v>4.7449746131897</v>
       </c>
       <c r="H940" t="n">
         <v>500</v>
@@ -27658,7 +27658,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G941" t="n">
-        <v>4.63109540939331</v>
+        <v>4.63109493255615</v>
       </c>
       <c r="H941" t="n">
         <v>500</v>
@@ -27687,7 +27687,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G942" t="n">
-        <v>4.65007495880127</v>
+        <v>4.65007543563843</v>
       </c>
       <c r="H942" t="n">
         <v>1500</v>
@@ -27716,7 +27716,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G943" t="n">
-        <v>4.65007495880127</v>
+        <v>4.65007543563843</v>
       </c>
       <c r="H943" t="n">
         <v>0</v>
@@ -27745,7 +27745,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G944" t="n">
-        <v>4.65007495880127</v>
+        <v>4.65007543563843</v>
       </c>
       <c r="H944" t="n">
         <v>0</v>
@@ -27774,7 +27774,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G945" t="n">
-        <v>4.65007495880127</v>
+        <v>4.65007543563843</v>
       </c>
       <c r="H945" t="n">
         <v>0</v>
@@ -27803,7 +27803,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G946" t="n">
-        <v>4.65007495880127</v>
+        <v>4.65007543563843</v>
       </c>
       <c r="H946" t="n">
         <v>0</v>
@@ -27832,7 +27832,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G947" t="n">
-        <v>4.65007495880127</v>
+        <v>4.65007543563843</v>
       </c>
       <c r="H947" t="n">
         <v>0</v>
@@ -27861,7 +27861,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G948" t="n">
-        <v>4.65007495880127</v>
+        <v>4.65007543563843</v>
       </c>
       <c r="H948" t="n">
         <v>0</v>
@@ -27890,7 +27890,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G949" t="n">
-        <v>4.65007495880127</v>
+        <v>4.65007543563843</v>
       </c>
       <c r="H949" t="n">
         <v>0</v>
@@ -27919,7 +27919,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G950" t="n">
-        <v>4.63109540939331</v>
+        <v>4.63109493255615</v>
       </c>
       <c r="H950" t="n">
         <v>2250</v>
@@ -27948,7 +27948,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G951" t="n">
-        <v>4.63109540939331</v>
+        <v>4.63109493255615</v>
       </c>
       <c r="H951" t="n">
         <v>0</v>
@@ -27977,7 +27977,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G952" t="n">
-        <v>4.63109540939331</v>
+        <v>4.63109493255615</v>
       </c>
       <c r="H952" t="n">
         <v>250</v>
@@ -28006,7 +28006,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G953" t="n">
-        <v>4.63109540939331</v>
+        <v>4.63109493255615</v>
       </c>
       <c r="H953" t="n">
         <v>0</v>
@@ -28180,7 +28180,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G959" t="n">
-        <v>4.49823570251465</v>
+        <v>4.49823522567749</v>
       </c>
       <c r="H959" t="n">
         <v>1250</v>
@@ -28238,7 +28238,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G961" t="n">
-        <v>4.49823570251465</v>
+        <v>4.49823522567749</v>
       </c>
       <c r="H961" t="n">
         <v>1000</v>
@@ -28267,7 +28267,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G962" t="n">
-        <v>4.36537599563599</v>
+        <v>4.36537647247314</v>
       </c>
       <c r="H962" t="n">
         <v>1250</v>
@@ -28296,7 +28296,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G963" t="n">
-        <v>4.36537599563599</v>
+        <v>4.36537647247314</v>
       </c>
       <c r="H963" t="n">
         <v>2250</v>
@@ -28325,7 +28325,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G964" t="n">
-        <v>4.32741689682007</v>
+        <v>4.32741641998291</v>
       </c>
       <c r="H964" t="n">
         <v>1500</v>
@@ -28528,7 +28528,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G971" t="n">
-        <v>4.36537599563599</v>
+        <v>4.36537647247314</v>
       </c>
       <c r="H971" t="n">
         <v>7500</v>
@@ -28644,7 +28644,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G975" t="n">
-        <v>4.13761758804321</v>
+        <v>4.13761806488037</v>
       </c>
       <c r="H975" t="n">
         <v>2000</v>
@@ -28905,7 +28905,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G984" t="n">
-        <v>4.36537599563599</v>
+        <v>4.36537647247314</v>
       </c>
       <c r="H984" t="n">
         <v>1250</v>
@@ -28934,7 +28934,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G985" t="n">
-        <v>4.36537599563599</v>
+        <v>4.36537647247314</v>
       </c>
       <c r="H985" t="n">
         <v>1750</v>
@@ -28963,7 +28963,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G986" t="n">
-        <v>4.36537599563599</v>
+        <v>4.36537647247314</v>
       </c>
       <c r="H986" t="n">
         <v>5750</v>
@@ -28992,7 +28992,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G987" t="n">
-        <v>4.34639692306519</v>
+        <v>4.34639644622803</v>
       </c>
       <c r="H987" t="n">
         <v>750</v>
@@ -29050,7 +29050,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G989" t="n">
-        <v>4.32741689682007</v>
+        <v>4.32741641998291</v>
       </c>
       <c r="H989" t="n">
         <v>4250</v>
@@ -29079,7 +29079,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G990" t="n">
-        <v>4.36537599563599</v>
+        <v>4.36537647247314</v>
       </c>
       <c r="H990" t="n">
         <v>750</v>
@@ -29137,7 +29137,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G992" t="n">
-        <v>4.36537599563599</v>
+        <v>4.36537647247314</v>
       </c>
       <c r="H992" t="n">
         <v>4000</v>
@@ -29514,7 +29514,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1005" t="n">
-        <v>4.55517578125</v>
+        <v>4.55517530441284</v>
       </c>
       <c r="H1005" t="n">
         <v>500</v>
@@ -29572,7 +29572,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.57415580749512</v>
+        <v>4.57415533065796</v>
       </c>
       <c r="H1007" t="n">
         <v>18500</v>
@@ -29688,7 +29688,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.63109540939331</v>
+        <v>4.63109493255615</v>
       </c>
       <c r="H1011" t="n">
         <v>500</v>
@@ -30036,7 +30036,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1023" t="n">
-        <v>4.32741689682007</v>
+        <v>4.32741641998291</v>
       </c>
       <c r="H1023" t="n">
         <v>500</v>
@@ -30065,7 +30065,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1024" t="n">
-        <v>4.32741689682007</v>
+        <v>4.32741641998291</v>
       </c>
       <c r="H1024" t="n">
         <v>750</v>
@@ -30094,7 +30094,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1025" t="n">
-        <v>4.32741689682007</v>
+        <v>4.32741641998291</v>
       </c>
       <c r="H1025" t="n">
         <v>0</v>
@@ -30123,7 +30123,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1026" t="n">
-        <v>4.32741689682007</v>
+        <v>4.32741641998291</v>
       </c>
       <c r="H1026" t="n">
         <v>0</v>
@@ -30152,7 +30152,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1027" t="n">
-        <v>4.32741689682007</v>
+        <v>4.32741641998291</v>
       </c>
       <c r="H1027" t="n">
         <v>0</v>
@@ -30210,7 +30210,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1029" t="n">
-        <v>4.13761758804321</v>
+        <v>4.13761806488037</v>
       </c>
       <c r="H1029" t="n">
         <v>2000</v>
@@ -30239,7 +30239,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1030" t="n">
-        <v>4.1186375617981</v>
+        <v>4.11863803863525</v>
       </c>
       <c r="H1030" t="n">
         <v>1250</v>
@@ -30384,7 +30384,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.85291934013367</v>
+        <v>3.85291910171509</v>
       </c>
       <c r="H1035" t="n">
         <v>7500</v>
@@ -30587,7 +30587,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1042" t="n">
-        <v>4.08067798614502</v>
+        <v>4.08067846298218</v>
       </c>
       <c r="H1042" t="n">
         <v>750</v>
@@ -30790,7 +30790,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.08067798614502</v>
+        <v>4.08067846298218</v>
       </c>
       <c r="H1049" t="n">
         <v>250</v>
@@ -30819,7 +30819,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.08067798614502</v>
+        <v>4.08067846298218</v>
       </c>
       <c r="H1050" t="n">
         <v>0</v>
@@ -30848,7 +30848,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1051" t="n">
-        <v>4.08067798614502</v>
+        <v>4.08067846298218</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -30906,7 +30906,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1053" t="n">
-        <v>4.08067798614502</v>
+        <v>4.08067846298218</v>
       </c>
       <c r="H1053" t="n">
         <v>4500</v>
@@ -30993,7 +30993,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.94781851768494</v>
+        <v>3.94781875610352</v>
       </c>
       <c r="H1056" t="n">
         <v>1750</v>
@@ -31022,7 +31022,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.94781851768494</v>
+        <v>3.94781875610352</v>
       </c>
       <c r="H1057" t="n">
         <v>0</v>
@@ -31138,7 +31138,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.89087891578674</v>
+        <v>3.89087915420532</v>
       </c>
       <c r="H1061" t="n">
         <v>5750</v>
@@ -31225,7 +31225,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.60618042945862</v>
+        <v>3.6061806678772</v>
       </c>
       <c r="H1064" t="n">
         <v>3750</v>
@@ -31747,7 +31747,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.5872004032135</v>
+        <v>3.58720064163208</v>
       </c>
       <c r="H1082" t="n">
         <v>2750</v>
@@ -31921,7 +31921,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.60618042945862</v>
+        <v>3.6061806678772</v>
       </c>
       <c r="H1088" t="n">
         <v>500</v>
@@ -32037,7 +32037,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.81495952606201</v>
+        <v>3.81495928764343</v>
       </c>
       <c r="H1092" t="n">
         <v>19500</v>
@@ -32153,7 +32153,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1096" t="n">
-        <v>4.1186375617981</v>
+        <v>4.11863803863525</v>
       </c>
       <c r="H1096" t="n">
         <v>3750</v>
@@ -43353,6 +43353,64 @@
         <v>250</v>
       </c>
       <c r="I1482" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1483" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1483" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="D1483" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="E1483" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="F1483" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="G1483" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="H1483" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1483" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1484" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1484" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="D1484" t="n">
+        <v>3.85999989509583</v>
+      </c>
+      <c r="E1484" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="F1484" t="n">
+        <v>3.85999989509583</v>
+      </c>
+      <c r="G1484" t="n">
+        <v>3.85999989509583</v>
+      </c>
+      <c r="H1484" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I1484" t="s">
         <v>9</v>
       </c>
     </row>
